--- a/Översikt MÖRBYLÅNGA.xlsx
+++ b/Översikt MÖRBYLÅNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44964</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>44655</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>45177</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45096</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45685</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>45475</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>45062</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>46195</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>46189</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>45254</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>45062</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>44508</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>44467</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 60875-2025</t>
+          <t>A 38039-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2349,14 +2349,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45999</v>
+        <v>44811</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2369,31 +2369,31 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.1</v>
+        <v>7.4</v>
       </c>
       <c r="J15" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
         <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R15" t="n">
         <v>2</v>
@@ -2402,12 +2402,127 @@
         <v>11</v>
       </c>
       <c r="T15" t="n">
+        <v>13</v>
+      </c>
+      <c r="U15" t="n">
         <v>12</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Grov gulmossa
+Backtimjan
+Dvärgjordstjärna
+Solvända
+Ängsstarr
+Murgröna
+Alvarmalört
+Grönvit nattviol
+Krutbrännare
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 38039-2022 artfynd.xlsx", "A 38039-2022")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 38039-2022 karta.png", "A 38039-2022")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 38039-2022 georefererad karta.tif", "A 38039-2022")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 38039-2022 FSC-klagomål.docx", "A 38039-2022")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 38039-2022 FSC-klagomål mail.docx", "A 38039-2022")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 38039-2022 tillsynsbegäran.docx", "A 38039-2022")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 38039-2022 tillsynsbegäran mail.docx", "A 38039-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 60875-2025</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45999</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>8</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>5</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>7</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2</v>
+      </c>
+      <c r="S16" t="n">
+        <v>11</v>
+      </c>
+      <c r="T16" t="n">
+        <v>12</v>
+      </c>
+      <c r="U16" t="n">
         <v>3</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Järnek
 Mosippa
@@ -2422,111 +2537,111 @@
 Skogsduva</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 60875-2025 artfynd.xlsx", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 60875-2025 karta.png", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 60875-2025 georefererad karta.tif", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 60875-2025 FSC-klagomål.docx", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 60875-2025 FSC-klagomål mail.docx", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 60875-2025 tillsynsbegäran.docx", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 60875-2025 tillsynsbegäran mail.docx", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 60875-2025 prioriterade fågelarter.docx", "A 60875-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 38039-2022</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 27636-2023</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D16" s="1" t="n">
-        <v>44811</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="D17" s="1" t="n">
+        <v>45097</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I16" t="n">
+      <c r="I17" t="n">
         <v>7.4</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J17" t="n">
         <v>4</v>
       </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
         <v>4</v>
       </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>6</v>
       </c>
-      <c r="R16" t="n">
+      <c r="R17" t="n">
         <v>2</v>
       </c>
-      <c r="S16" t="n">
+      <c r="S17" t="n">
         <v>11</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T17" t="n">
         <v>13</v>
       </c>
-      <c r="U16" t="n">
-        <v>12</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="U17" t="n">
+        <v>11</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Ask
 Grov gulmossa
@@ -2541,121 +2656,6 @@
 Gullviva</t>
         </is>
       </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 38039-2022 artfynd.xlsx", "A 38039-2022")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 38039-2022 karta.png", "A 38039-2022")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 38039-2022 georefererad karta.tif", "A 38039-2022")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 38039-2022 FSC-klagomål.docx", "A 38039-2022")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 38039-2022 FSC-klagomål mail.docx", "A 38039-2022")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 38039-2022 tillsynsbegäran.docx", "A 38039-2022")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 38039-2022 tillsynsbegäran mail.docx", "A 38039-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 27636-2023</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45097</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="J17" t="n">
-        <v>4</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>4</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>6</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2</v>
-      </c>
-      <c r="S17" t="n">
-        <v>11</v>
-      </c>
-      <c r="T17" t="n">
-        <v>13</v>
-      </c>
-      <c r="U17" t="n">
-        <v>11</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Grov gulmossa
-Backtimjan
-Dvärgjordstjärna
-Solvända
-Ängsstarr
-Murgröna
-Alvarmalört
-Grönvit nattviol
-Krutbrännare
-Gullviva</t>
-        </is>
-      </c>
       <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 27636-2023 artfynd.xlsx", "A 27636-2023")</f>
         <v/>
@@ -2705,7 +2705,7 @@
         <v>44728</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>45551</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>44616</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>45000</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>45530</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>45223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>45075</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>45169</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 43714-2025</t>
+          <t>A 43704-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3620,7 +3620,7 @@
         <v>45912</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3633,19 +3633,19 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>7.9</v>
+        <v>2.7</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -3657,21 +3657,131 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>6</v>
       </c>
       <c r="T26" t="n">
+        <v>6</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp
+Långbensgroda
+Större vattensalamander
+Åkergroda
+Mindre vattensalamander
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43704-2025 artfynd.xlsx", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="X26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43704-2025 karta.png", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="Y26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43704-2025 georefererad karta.tif", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="AA26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43704-2025 FSC-klagomål.docx", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="AB26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43704-2025 FSC-klagomål mail.docx", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="AC26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43704-2025 tillsynsbegäran.docx", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="AD26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43704-2025 tillsynsbegäran mail.docx", "A 43704-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 43714-2025</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>45912</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2</v>
+      </c>
+      <c r="S27" t="n">
+        <v>6</v>
+      </c>
+      <c r="T27" t="n">
         <v>8</v>
       </c>
-      <c r="U26" t="n">
+      <c r="U27" t="n">
         <v>2</v>
       </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>Mindre bastardsvärmare
 Sexfläckig bastardsvärmare
@@ -3681,146 +3791,36 @@
 Trädporella</t>
         </is>
       </c>
-      <c r="W26">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43714-2025 artfynd.xlsx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="X26">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43714-2025 karta.png", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="Y26">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43714-2025 georefererad karta.tif", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AA26">
+      <c r="AA27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43714-2025 FSC-klagomål.docx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AB26">
+      <c r="AB27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43714-2025 FSC-klagomål mail.docx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AC26">
+      <c r="AC27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43714-2025 tillsynsbegäran.docx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AD26">
+      <c r="AD27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43714-2025 tillsynsbegäran mail.docx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AE26">
+      <c r="AE27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 43714-2025 prioriterade fågelarter.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 43704-2025</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>45912</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J27" t="n">
-        <v>5</v>
-      </c>
-      <c r="K27" t="n">
-        <v>1</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>6</v>
-      </c>
-      <c r="T27" t="n">
-        <v>6</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Blomkålssvamp
-Långbensgroda
-Större vattensalamander
-Åkergroda
-Mindre vattensalamander
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43704-2025 artfynd.xlsx", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43704-2025 karta.png", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43704-2025 georefererad karta.tif", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43704-2025 FSC-klagomål.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43704-2025 FSC-klagomål mail.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43704-2025 tillsynsbegäran.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43704-2025 tillsynsbegäran mail.docx", "A 43704-2025")</f>
         <v/>
       </c>
     </row>
@@ -3844,7 +3844,7 @@
         <v>46190</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>46003</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>46038</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         <v>45616</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 19459-2023</t>
+          <t>A 26440-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4285,10 +4285,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45049</v>
+        <v>46183</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4301,16 +4301,16 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4325,7 +4325,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -4334,12 +4334,232 @@
         <v>4</v>
       </c>
       <c r="T32" t="n">
+        <v>5</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>Backstarr
+Murgröna
+Nästrot
+Vätteros</t>
+        </is>
+      </c>
+      <c r="W32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 26440-2026 artfynd.xlsx", "A 26440-2026")</f>
+        <v/>
+      </c>
+      <c r="X32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 26440-2026 karta.png", "A 26440-2026")</f>
+        <v/>
+      </c>
+      <c r="Y32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 26440-2026 georefererad karta.tif", "A 26440-2026")</f>
+        <v/>
+      </c>
+      <c r="AA32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 26440-2026 FSC-klagomål.docx", "A 26440-2026")</f>
+        <v/>
+      </c>
+      <c r="AB32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 26440-2026 FSC-klagomål mail.docx", "A 26440-2026")</f>
+        <v/>
+      </c>
+      <c r="AC32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 26440-2026 tillsynsbegäran.docx", "A 26440-2026")</f>
+        <v/>
+      </c>
+      <c r="AD32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 26440-2026 tillsynsbegäran mail.docx", "A 26440-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>A 34431-2026</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" t="n">
+        <v>3</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>3</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
         <v>4</v>
       </c>
-      <c r="U32" t="n">
+      <c r="T33" t="n">
+        <v>5</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Mindre hackspett
+Sandtimotej
+Murgröna</t>
+        </is>
+      </c>
+      <c r="W33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 34431-2026 artfynd.xlsx", "A 34431-2026")</f>
+        <v/>
+      </c>
+      <c r="X33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 34431-2026 karta.png", "A 34431-2026")</f>
+        <v/>
+      </c>
+      <c r="Y33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 34431-2026 georefererad karta.tif", "A 34431-2026")</f>
+        <v/>
+      </c>
+      <c r="AA33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 34431-2026 FSC-klagomål.docx", "A 34431-2026")</f>
+        <v/>
+      </c>
+      <c r="AB33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 34431-2026 FSC-klagomål mail.docx", "A 34431-2026")</f>
+        <v/>
+      </c>
+      <c r="AC33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 34431-2026 tillsynsbegäran.docx", "A 34431-2026")</f>
+        <v/>
+      </c>
+      <c r="AD33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 34431-2026 tillsynsbegäran mail.docx", "A 34431-2026")</f>
+        <v/>
+      </c>
+      <c r="AE33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 34431-2026 prioriterade fågelarter.docx", "A 34431-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>A 19459-2023</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="n">
+        <v>45049</v>
+      </c>
+      <c r="E34" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
         <v>4</v>
       </c>
-      <c r="V32" s="2" t="inlineStr">
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>4</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>4</v>
+      </c>
+      <c r="T34" t="n">
+        <v>4</v>
+      </c>
+      <c r="U34" t="n">
+        <v>4</v>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>Kavelhirs
 Kösa
@@ -4347,252 +4567,32 @@
 Riddarsporre</t>
         </is>
       </c>
-      <c r="W32">
+      <c r="W34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 19459-2023 artfynd.xlsx", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="X32">
+      <c r="X34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 19459-2023 karta.png", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="Y32">
+      <c r="Y34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 19459-2023 georefererad karta.tif", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="AA32">
+      <c r="AA34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 19459-2023 FSC-klagomål.docx", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="AB32">
+      <c r="AB34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 19459-2023 FSC-klagomål mail.docx", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="AC32">
+      <c r="AC34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 19459-2023 tillsynsbegäran.docx", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="AD32">
+      <c r="AD34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 19459-2023 tillsynsbegäran mail.docx", "A 19459-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>A 26440-2026</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D33" s="1" t="n">
-        <v>46183</v>
-      </c>
-      <c r="E33" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J33" t="n">
-        <v>1</v>
-      </c>
-      <c r="K33" t="n">
-        <v>3</v>
-      </c>
-      <c r="L33" t="n">
-        <v>1</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>4</v>
-      </c>
-      <c r="T33" t="n">
-        <v>5</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
-        <is>
-          <t>Backstarr
-Murgröna
-Nästrot
-Vätteros</t>
-        </is>
-      </c>
-      <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 26440-2026 artfynd.xlsx", "A 26440-2026")</f>
-        <v/>
-      </c>
-      <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 26440-2026 karta.png", "A 26440-2026")</f>
-        <v/>
-      </c>
-      <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 26440-2026 georefererad karta.tif", "A 26440-2026")</f>
-        <v/>
-      </c>
-      <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 26440-2026 FSC-klagomål.docx", "A 26440-2026")</f>
-        <v/>
-      </c>
-      <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 26440-2026 FSC-klagomål mail.docx", "A 26440-2026")</f>
-        <v/>
-      </c>
-      <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 26440-2026 tillsynsbegäran.docx", "A 26440-2026")</f>
-        <v/>
-      </c>
-      <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 26440-2026 tillsynsbegäran mail.docx", "A 26440-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>A 34431-2026</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="n">
-        <v>46254</v>
-      </c>
-      <c r="E34" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="J34" t="n">
-        <v>2</v>
-      </c>
-      <c r="K34" t="n">
-        <v>1</v>
-      </c>
-      <c r="L34" t="n">
-        <v>3</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>3</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>4</v>
-      </c>
-      <c r="T34" t="n">
-        <v>5</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1</v>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Mindre hackspett
-Sandtimotej
-Murgröna</t>
-        </is>
-      </c>
-      <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 34431-2026 artfynd.xlsx", "A 34431-2026")</f>
-        <v/>
-      </c>
-      <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 34431-2026 karta.png", "A 34431-2026")</f>
-        <v/>
-      </c>
-      <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 34431-2026 georefererad karta.tif", "A 34431-2026")</f>
-        <v/>
-      </c>
-      <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 34431-2026 FSC-klagomål.docx", "A 34431-2026")</f>
-        <v/>
-      </c>
-      <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 34431-2026 FSC-klagomål mail.docx", "A 34431-2026")</f>
-        <v/>
-      </c>
-      <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 34431-2026 tillsynsbegäran.docx", "A 34431-2026")</f>
-        <v/>
-      </c>
-      <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 34431-2026 tillsynsbegäran mail.docx", "A 34431-2026")</f>
-        <v/>
-      </c>
-      <c r="AE34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 34431-2026 prioriterade fågelarter.docx", "A 34431-2026")</f>
         <v/>
       </c>
     </row>
@@ -4616,7 +4616,7 @@
         <v>44460</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>45912</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 15600-2025</t>
+          <t>A 29360-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4827,10 +4827,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45747</v>
+        <v>46203</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4843,19 +4843,19 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -4867,10 +4867,10 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S37" t="n">
         <v>3</v>
@@ -4882,145 +4882,145 @@
         <v>1</v>
       </c>
       <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>Mindre blåvinge
+Silversmygare
+Ekoxe</t>
+        </is>
+      </c>
+      <c r="W37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 29360-2026 artfynd.xlsx", "A 29360-2026")</f>
+        <v/>
+      </c>
+      <c r="X37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 29360-2026 karta.png", "A 29360-2026")</f>
+        <v/>
+      </c>
+      <c r="Y37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 29360-2026 georefererad karta.tif", "A 29360-2026")</f>
+        <v/>
+      </c>
+      <c r="AA37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 29360-2026 FSC-klagomål.docx", "A 29360-2026")</f>
+        <v/>
+      </c>
+      <c r="AB37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 29360-2026 FSC-klagomål mail.docx", "A 29360-2026")</f>
+        <v/>
+      </c>
+      <c r="AC37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 29360-2026 tillsynsbegäran.docx", "A 29360-2026")</f>
+        <v/>
+      </c>
+      <c r="AD37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 29360-2026 tillsynsbegäran mail.docx", "A 29360-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>A 15600-2025</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D38" s="1" t="n">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
         <is>
           <t>Kragjordstjärna
 Murgröna
 Scharlakansvårskål agg.</t>
         </is>
       </c>
-      <c r="W37">
+      <c r="W38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 15600-2025 artfynd.xlsx", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="X37">
+      <c r="X38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 15600-2025 karta.png", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="Y37">
+      <c r="Y38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 15600-2025 georefererad karta.tif", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="AA37">
+      <c r="AA38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 15600-2025 FSC-klagomål.docx", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="AB37">
+      <c r="AB38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 15600-2025 FSC-klagomål mail.docx", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="AC37">
+      <c r="AC38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 15600-2025 tillsynsbegäran.docx", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="AD37">
+      <c r="AD38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 15600-2025 tillsynsbegäran mail.docx", "A 15600-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>A 29360-2026</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D38" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="E38" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I38" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J38" t="n">
-        <v>1</v>
-      </c>
-      <c r="K38" t="n">
-        <v>1</v>
-      </c>
-      <c r="L38" t="n">
-        <v>1</v>
-      </c>
-      <c r="M38" t="n">
-        <v>1</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>2</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1</v>
-      </c>
-      <c r="S38" t="n">
-        <v>3</v>
-      </c>
-      <c r="T38" t="n">
-        <v>3</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1</v>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t>Mindre blåvinge
-Silversmygare
-Ekoxe</t>
-        </is>
-      </c>
-      <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 29360-2026 artfynd.xlsx", "A 29360-2026")</f>
-        <v/>
-      </c>
-      <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 29360-2026 karta.png", "A 29360-2026")</f>
-        <v/>
-      </c>
-      <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 29360-2026 georefererad karta.tif", "A 29360-2026")</f>
-        <v/>
-      </c>
-      <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 29360-2026 FSC-klagomål.docx", "A 29360-2026")</f>
-        <v/>
-      </c>
-      <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 29360-2026 FSC-klagomål mail.docx", "A 29360-2026")</f>
-        <v/>
-      </c>
-      <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 29360-2026 tillsynsbegäran.docx", "A 29360-2026")</f>
-        <v/>
-      </c>
-      <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 29360-2026 tillsynsbegäran mail.docx", "A 29360-2026")</f>
         <v/>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
         <v>44470</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 72167-2021</t>
+          <t>A 62231-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5143,14 +5143,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44544</v>
+        <v>45267</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J40" t="n">
         <v>1</v>
@@ -5204,46 +5204,42 @@
       <c r="V40" s="2" t="inlineStr">
         <is>
           <t>Murgröna
-Röd glada</t>
+Blåsippa</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 72167-2021 artfynd.xlsx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62231-2023 artfynd.xlsx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 72167-2021 karta.png", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62231-2023 karta.png", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 72167-2021 georefererad karta.tif", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62231-2023 georefererad karta.tif", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 72167-2021 FSC-klagomål.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62231-2023 FSC-klagomål.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 72167-2021 FSC-klagomål mail.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62231-2023 FSC-klagomål mail.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 72167-2021 tillsynsbegäran.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62231-2023 tillsynsbegäran.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 72167-2021 tillsynsbegäran mail.docx", "A 72167-2021")</f>
-        <v/>
-      </c>
-      <c r="AE40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 72167-2021 prioriterade fågelarter.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62231-2023 tillsynsbegäran mail.docx", "A 62231-2023")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 62231-2023</t>
+          <t>A 72167-2021</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5253,14 +5249,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45267</v>
+        <v>44544</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5273,7 +5269,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J41" t="n">
         <v>1</v>
@@ -5314,35 +5310,39 @@
       <c r="V41" s="2" t="inlineStr">
         <is>
           <t>Murgröna
-Blåsippa</t>
+Röd glada</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62231-2023 artfynd.xlsx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 72167-2021 artfynd.xlsx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62231-2023 karta.png", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 72167-2021 karta.png", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62231-2023 georefererad karta.tif", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 72167-2021 georefererad karta.tif", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62231-2023 FSC-klagomål.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 72167-2021 FSC-klagomål.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62231-2023 FSC-klagomål mail.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 72167-2021 FSC-klagomål mail.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62231-2023 tillsynsbegäran.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 72167-2021 tillsynsbegäran.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62231-2023 tillsynsbegäran mail.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 72167-2021 tillsynsbegäran mail.docx", "A 72167-2021")</f>
+        <v/>
+      </c>
+      <c r="AE41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 72167-2021 prioriterade fågelarter.docx", "A 72167-2021")</f>
         <v/>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
         <v>46246</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 13040-2024</t>
+          <t>A 62183-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5465,14 +5465,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45385</v>
+        <v>46006</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5494,13 +5494,13 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5512,7 +5512,7 @@
         <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5521,46 +5521,46 @@
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13040-2024 artfynd.xlsx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62183-2025 artfynd.xlsx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13040-2024 karta.png", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62183-2025 karta.png", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13040-2024 georefererad karta.tif", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62183-2025 georefererad karta.tif", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13040-2024 FSC-klagomål.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62183-2025 FSC-klagomål.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13040-2024 FSC-klagomål mail.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62183-2025 FSC-klagomål mail.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13040-2024 tillsynsbegäran.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62183-2025 tillsynsbegäran.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13040-2024 tillsynsbegäran mail.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62183-2025 tillsynsbegäran mail.docx", "A 62183-2025")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 13384-2023</t>
+          <t>A 24698-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5574,10 +5574,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45005</v>
+        <v>45084</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5590,16 +5590,16 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>5.5</v>
       </c>
       <c r="J44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -5614,7 +5614,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -5630,42 +5630,42 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13384-2023 artfynd.xlsx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24698-2023 artfynd.xlsx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13384-2023 karta.png", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24698-2023 karta.png", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13384-2023 georefererad karta.tif", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24698-2023 georefererad karta.tif", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13384-2023 FSC-klagomål.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24698-2023 FSC-klagomål.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13384-2023 FSC-klagomål mail.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24698-2023 FSC-klagomål mail.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13384-2023 tillsynsbegäran.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24698-2023 tillsynsbegäran.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13384-2023 tillsynsbegäran mail.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24698-2023 tillsynsbegäran mail.docx", "A 24698-2023")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 62183-2025</t>
+          <t>A 13040-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5675,14 +5675,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46006</v>
+        <v>45385</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5704,13 +5704,13 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5722,7 +5722,7 @@
         <v>1</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5731,39 +5731,39 @@
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62183-2025 artfynd.xlsx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13040-2024 artfynd.xlsx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62183-2025 karta.png", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13040-2024 karta.png", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62183-2025 georefererad karta.tif", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13040-2024 georefererad karta.tif", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62183-2025 FSC-klagomål.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13040-2024 FSC-klagomål.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62183-2025 FSC-klagomål mail.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13040-2024 FSC-klagomål mail.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62183-2025 tillsynsbegäran.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13040-2024 tillsynsbegäran.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62183-2025 tillsynsbegäran mail.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13040-2024 tillsynsbegäran mail.docx", "A 13040-2024")</f>
         <v/>
       </c>
     </row>
@@ -5787,7 +5787,7 @@
         <v>46210</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         <v>46273</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 24698-2023</t>
+          <t>A 13384-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5994,10 +5994,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45084</v>
+        <v>45005</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6010,16 +6010,16 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>5.5</v>
+        <v>0.9</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -6034,7 +6034,7 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
@@ -6050,35 +6050,35 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24698-2023 artfynd.xlsx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13384-2023 artfynd.xlsx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="X48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24698-2023 karta.png", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13384-2023 karta.png", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="Y48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24698-2023 georefererad karta.tif", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13384-2023 georefererad karta.tif", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AA48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24698-2023 FSC-klagomål.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13384-2023 FSC-klagomål.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AB48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24698-2023 FSC-klagomål mail.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13384-2023 FSC-klagomål mail.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AC48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24698-2023 tillsynsbegäran.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13384-2023 tillsynsbegäran.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AD48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24698-2023 tillsynsbegäran mail.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13384-2023 tillsynsbegäran mail.docx", "A 13384-2023")</f>
         <v/>
       </c>
     </row>
@@ -6102,7 +6102,7 @@
         <v>44740</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>45980</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>46171</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>

--- a/Översikt MÖRBYLÅNGA.xlsx
+++ b/Översikt MÖRBYLÅNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44964</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>44655</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>45177</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45096</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45685</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>45475</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>45062</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>46195</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>46189</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>45254</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>45062</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>44508</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>44467</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>44811</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 60875-2025</t>
+          <t>A 27636-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2464,14 +2464,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45999</v>
+        <v>45097</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2484,31 +2484,31 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.1</v>
+        <v>7.4</v>
       </c>
       <c r="J16" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
         <v>1</v>
       </c>
       <c r="O16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R16" t="n">
         <v>2</v>
@@ -2517,12 +2517,127 @@
         <v>11</v>
       </c>
       <c r="T16" t="n">
+        <v>13</v>
+      </c>
+      <c r="U16" t="n">
+        <v>11</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Grov gulmossa
+Backtimjan
+Dvärgjordstjärna
+Solvända
+Ängsstarr
+Murgröna
+Alvarmalört
+Grönvit nattviol
+Krutbrännare
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 27636-2023 artfynd.xlsx", "A 27636-2023")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 27636-2023 karta.png", "A 27636-2023")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 27636-2023 georefererad karta.tif", "A 27636-2023")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 27636-2023 FSC-klagomål.docx", "A 27636-2023")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 27636-2023 FSC-klagomål mail.docx", "A 27636-2023")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 27636-2023 tillsynsbegäran.docx", "A 27636-2023")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 27636-2023 tillsynsbegäran mail.docx", "A 27636-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 60875-2025</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45999</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>8</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>5</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>7</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2</v>
+      </c>
+      <c r="S17" t="n">
+        <v>11</v>
+      </c>
+      <c r="T17" t="n">
         <v>12</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U17" t="n">
         <v>3</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Järnek
 Mosippa
@@ -2537,151 +2652,36 @@
 Skogsduva</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 60875-2025 artfynd.xlsx", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 60875-2025 karta.png", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 60875-2025 georefererad karta.tif", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 60875-2025 FSC-klagomål.docx", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 60875-2025 FSC-klagomål mail.docx", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 60875-2025 tillsynsbegäran.docx", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 60875-2025 tillsynsbegäran mail.docx", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 60875-2025 prioriterade fågelarter.docx", "A 60875-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 27636-2023</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45097</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="J17" t="n">
-        <v>4</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>4</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>6</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2</v>
-      </c>
-      <c r="S17" t="n">
-        <v>11</v>
-      </c>
-      <c r="T17" t="n">
-        <v>13</v>
-      </c>
-      <c r="U17" t="n">
-        <v>11</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Grov gulmossa
-Backtimjan
-Dvärgjordstjärna
-Solvända
-Ängsstarr
-Murgröna
-Alvarmalört
-Grönvit nattviol
-Krutbrännare
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 27636-2023 artfynd.xlsx", "A 27636-2023")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 27636-2023 karta.png", "A 27636-2023")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 27636-2023 georefererad karta.tif", "A 27636-2023")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 27636-2023 FSC-klagomål.docx", "A 27636-2023")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 27636-2023 FSC-klagomål mail.docx", "A 27636-2023")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 27636-2023 tillsynsbegäran.docx", "A 27636-2023")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 27636-2023 tillsynsbegäran mail.docx", "A 27636-2023")</f>
         <v/>
       </c>
     </row>
@@ -2705,7 +2705,7 @@
         <v>44728</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>45551</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>44616</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>45000</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>45530</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>45223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>45075</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>45169</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 43704-2025</t>
+          <t>A 43714-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3620,7 +3620,7 @@
         <v>45912</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3633,19 +3633,19 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.7</v>
+        <v>7.9</v>
       </c>
       <c r="J26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -3657,21 +3657,135 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S26" t="n">
         <v>6</v>
       </c>
       <c r="T26" t="n">
+        <v>8</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Mindre bastardsvärmare
+Sexfläckig bastardsvärmare
+Grönsångare
+Murgröna
+Tibast
+Trädporella</t>
+        </is>
+      </c>
+      <c r="W26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43714-2025 artfynd.xlsx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="X26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43714-2025 karta.png", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="Y26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43714-2025 georefererad karta.tif", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AA26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43714-2025 FSC-klagomål.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AB26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43714-2025 FSC-klagomål mail.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AC26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43714-2025 tillsynsbegäran.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AD26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43714-2025 tillsynsbegäran mail.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 43714-2025 prioriterade fågelarter.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 43704-2025</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>45912</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J27" t="n">
+        <v>5</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
         <v>6</v>
       </c>
-      <c r="U26" t="n">
-        <v>1</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="T27" t="n">
+        <v>6</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>Blomkålssvamp
 Långbensgroda
@@ -3681,146 +3795,32 @@
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W26">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43704-2025 artfynd.xlsx", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="X26">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43704-2025 karta.png", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="Y26">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43704-2025 georefererad karta.tif", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="AA26">
+      <c r="AA27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43704-2025 FSC-klagomål.docx", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="AB26">
+      <c r="AB27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43704-2025 FSC-klagomål mail.docx", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="AC26">
+      <c r="AC27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43704-2025 tillsynsbegäran.docx", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="AD26">
+      <c r="AD27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43704-2025 tillsynsbegäran mail.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 43714-2025</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>45912</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="J27" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>3</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1</v>
-      </c>
-      <c r="M27" t="n">
-        <v>2</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>3</v>
-      </c>
-      <c r="R27" t="n">
-        <v>2</v>
-      </c>
-      <c r="S27" t="n">
-        <v>6</v>
-      </c>
-      <c r="T27" t="n">
-        <v>8</v>
-      </c>
-      <c r="U27" t="n">
-        <v>2</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Mindre bastardsvärmare
-Sexfläckig bastardsvärmare
-Grönsångare
-Murgröna
-Tibast
-Trädporella</t>
-        </is>
-      </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43714-2025 artfynd.xlsx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43714-2025 karta.png", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43714-2025 georefererad karta.tif", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43714-2025 FSC-klagomål.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43714-2025 FSC-klagomål mail.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43714-2025 tillsynsbegäran.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43714-2025 tillsynsbegäran mail.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 43714-2025 prioriterade fågelarter.docx", "A 43714-2025")</f>
         <v/>
       </c>
     </row>
@@ -3844,7 +3844,7 @@
         <v>46190</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>46003</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>46038</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 54167-2024</t>
+          <t>A 19459-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4173,14 +4173,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45616</v>
+        <v>45049</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4193,22 +4193,22 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4217,21 +4217,129 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
       </c>
       <c r="T31" t="n">
+        <v>4</v>
+      </c>
+      <c r="U31" t="n">
+        <v>4</v>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>Kavelhirs
+Kösa
+Luddvicker
+Riddarsporre</t>
+        </is>
+      </c>
+      <c r="W31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 19459-2023 artfynd.xlsx", "A 19459-2023")</f>
+        <v/>
+      </c>
+      <c r="X31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 19459-2023 karta.png", "A 19459-2023")</f>
+        <v/>
+      </c>
+      <c r="Y31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 19459-2023 georefererad karta.tif", "A 19459-2023")</f>
+        <v/>
+      </c>
+      <c r="AA31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 19459-2023 FSC-klagomål.docx", "A 19459-2023")</f>
+        <v/>
+      </c>
+      <c r="AB31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 19459-2023 FSC-klagomål mail.docx", "A 19459-2023")</f>
+        <v/>
+      </c>
+      <c r="AC31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 19459-2023 tillsynsbegäran.docx", "A 19459-2023")</f>
+        <v/>
+      </c>
+      <c r="AD31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 19459-2023 tillsynsbegäran mail.docx", "A 19459-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>A 54167-2024</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="n">
+        <v>45616</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1</v>
+      </c>
+      <c r="S32" t="n">
+        <v>4</v>
+      </c>
+      <c r="T32" t="n">
         <v>8</v>
       </c>
-      <c r="U31" t="n">
+      <c r="U32" t="n">
         <v>8</v>
       </c>
-      <c r="V31" s="2" t="inlineStr">
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>Ask
 Murgröna
@@ -4239,107 +4347,107 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W31">
+      <c r="W32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 54167-2024 artfynd.xlsx", "A 54167-2024")</f>
         <v/>
       </c>
-      <c r="X31">
+      <c r="X32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 54167-2024 karta.png", "A 54167-2024")</f>
         <v/>
       </c>
-      <c r="Y31">
+      <c r="Y32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 54167-2024 georefererad karta.tif", "A 54167-2024")</f>
         <v/>
       </c>
-      <c r="AA31">
+      <c r="AA32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 54167-2024 FSC-klagomål.docx", "A 54167-2024")</f>
         <v/>
       </c>
-      <c r="AB31">
+      <c r="AB32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 54167-2024 FSC-klagomål mail.docx", "A 54167-2024")</f>
         <v/>
       </c>
-      <c r="AC31">
+      <c r="AC32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 54167-2024 tillsynsbegäran.docx", "A 54167-2024")</f>
         <v/>
       </c>
-      <c r="AD31">
+      <c r="AD32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 54167-2024 tillsynsbegäran mail.docx", "A 54167-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>A 26440-2026</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D32" s="1" t="n">
+      <c r="D33" s="1" t="n">
         <v>46183</v>
       </c>
-      <c r="E32" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F32" t="inlineStr">
+      <c r="E33" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I32" t="n">
+      <c r="I33" t="n">
         <v>1.1</v>
       </c>
-      <c r="J32" t="n">
-        <v>1</v>
-      </c>
-      <c r="K32" t="n">
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="n">
         <v>3</v>
       </c>
-      <c r="L32" t="n">
-        <v>1</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>1</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
+      <c r="L33" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
         <v>4</v>
       </c>
-      <c r="T32" t="n">
+      <c r="T33" t="n">
         <v>5</v>
       </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
         <is>
           <t>Backstarr
 Murgröna
@@ -4347,107 +4455,107 @@
 Vätteros</t>
         </is>
       </c>
-      <c r="W32">
+      <c r="W33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 26440-2026 artfynd.xlsx", "A 26440-2026")</f>
         <v/>
       </c>
-      <c r="X32">
+      <c r="X33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 26440-2026 karta.png", "A 26440-2026")</f>
         <v/>
       </c>
-      <c r="Y32">
+      <c r="Y33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 26440-2026 georefererad karta.tif", "A 26440-2026")</f>
         <v/>
       </c>
-      <c r="AA32">
+      <c r="AA33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 26440-2026 FSC-klagomål.docx", "A 26440-2026")</f>
         <v/>
       </c>
-      <c r="AB32">
+      <c r="AB33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 26440-2026 FSC-klagomål mail.docx", "A 26440-2026")</f>
         <v/>
       </c>
-      <c r="AC32">
+      <c r="AC33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 26440-2026 tillsynsbegäran.docx", "A 26440-2026")</f>
         <v/>
       </c>
-      <c r="AD32">
+      <c r="AD33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 26440-2026 tillsynsbegäran mail.docx", "A 26440-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>A 34431-2026</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D33" s="1" t="n">
+      <c r="D34" s="1" t="n">
         <v>46254</v>
       </c>
-      <c r="E33" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F33" t="inlineStr">
+      <c r="E34" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I33" t="n">
+      <c r="I34" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="J33" t="n">
+      <c r="J34" t="n">
         <v>2</v>
       </c>
-      <c r="K33" t="n">
-        <v>1</v>
-      </c>
-      <c r="L33" t="n">
+      <c r="K34" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" t="n">
         <v>3</v>
       </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
         <v>3</v>
       </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
         <v>4</v>
       </c>
-      <c r="T33" t="n">
+      <c r="T34" t="n">
         <v>5</v>
       </c>
-      <c r="U33" t="n">
-        <v>1</v>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
+      <c r="U34" t="n">
+        <v>1</v>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>Entita
 Mindre hackspett
@@ -4455,144 +4563,36 @@
 Murgröna</t>
         </is>
       </c>
-      <c r="W33">
+      <c r="W34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 34431-2026 artfynd.xlsx", "A 34431-2026")</f>
         <v/>
       </c>
-      <c r="X33">
+      <c r="X34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 34431-2026 karta.png", "A 34431-2026")</f>
         <v/>
       </c>
-      <c r="Y33">
+      <c r="Y34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 34431-2026 georefererad karta.tif", "A 34431-2026")</f>
         <v/>
       </c>
-      <c r="AA33">
+      <c r="AA34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 34431-2026 FSC-klagomål.docx", "A 34431-2026")</f>
         <v/>
       </c>
-      <c r="AB33">
+      <c r="AB34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 34431-2026 FSC-klagomål mail.docx", "A 34431-2026")</f>
         <v/>
       </c>
-      <c r="AC33">
+      <c r="AC34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 34431-2026 tillsynsbegäran.docx", "A 34431-2026")</f>
         <v/>
       </c>
-      <c r="AD33">
+      <c r="AD34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 34431-2026 tillsynsbegäran mail.docx", "A 34431-2026")</f>
         <v/>
       </c>
-      <c r="AE33">
+      <c r="AE34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 34431-2026 prioriterade fågelarter.docx", "A 34431-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>A 19459-2023</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="n">
-        <v>45049</v>
-      </c>
-      <c r="E34" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>4</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>4</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>4</v>
-      </c>
-      <c r="T34" t="n">
-        <v>4</v>
-      </c>
-      <c r="U34" t="n">
-        <v>4</v>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>Kavelhirs
-Kösa
-Luddvicker
-Riddarsporre</t>
-        </is>
-      </c>
-      <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 19459-2023 artfynd.xlsx", "A 19459-2023")</f>
-        <v/>
-      </c>
-      <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 19459-2023 karta.png", "A 19459-2023")</f>
-        <v/>
-      </c>
-      <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 19459-2023 georefererad karta.tif", "A 19459-2023")</f>
-        <v/>
-      </c>
-      <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 19459-2023 FSC-klagomål.docx", "A 19459-2023")</f>
-        <v/>
-      </c>
-      <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 19459-2023 FSC-klagomål mail.docx", "A 19459-2023")</f>
-        <v/>
-      </c>
-      <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 19459-2023 tillsynsbegäran.docx", "A 19459-2023")</f>
-        <v/>
-      </c>
-      <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 19459-2023 tillsynsbegäran mail.docx", "A 19459-2023")</f>
         <v/>
       </c>
     </row>
@@ -4616,7 +4616,7 @@
         <v>44460</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>45912</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 29360-2026</t>
+          <t>A 15600-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4827,10 +4827,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46203</v>
+        <v>45747</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4843,19 +4843,19 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -4867,10 +4867,10 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>3</v>
@@ -4882,145 +4882,145 @@
         <v>1</v>
       </c>
       <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>Kragjordstjärna
+Murgröna
+Scharlakansvårskål agg.</t>
+        </is>
+      </c>
+      <c r="W37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 15600-2025 artfynd.xlsx", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="X37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 15600-2025 karta.png", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="Y37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 15600-2025 georefererad karta.tif", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="AA37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 15600-2025 FSC-klagomål.docx", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="AB37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 15600-2025 FSC-klagomål mail.docx", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="AC37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 15600-2025 tillsynsbegäran.docx", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="AD37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 15600-2025 tillsynsbegäran mail.docx", "A 15600-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>A 29360-2026</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D38" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
         <is>
           <t>Mindre blåvinge
 Silversmygare
 Ekoxe</t>
         </is>
       </c>
-      <c r="W37">
+      <c r="W38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 29360-2026 artfynd.xlsx", "A 29360-2026")</f>
         <v/>
       </c>
-      <c r="X37">
+      <c r="X38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 29360-2026 karta.png", "A 29360-2026")</f>
         <v/>
       </c>
-      <c r="Y37">
+      <c r="Y38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 29360-2026 georefererad karta.tif", "A 29360-2026")</f>
         <v/>
       </c>
-      <c r="AA37">
+      <c r="AA38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 29360-2026 FSC-klagomål.docx", "A 29360-2026")</f>
         <v/>
       </c>
-      <c r="AB37">
+      <c r="AB38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 29360-2026 FSC-klagomål mail.docx", "A 29360-2026")</f>
         <v/>
       </c>
-      <c r="AC37">
+      <c r="AC38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 29360-2026 tillsynsbegäran.docx", "A 29360-2026")</f>
         <v/>
       </c>
-      <c r="AD37">
+      <c r="AD38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 29360-2026 tillsynsbegäran mail.docx", "A 29360-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>A 15600-2025</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D38" s="1" t="n">
-        <v>45747</v>
-      </c>
-      <c r="E38" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I38" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="n">
-        <v>3</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>3</v>
-      </c>
-      <c r="T38" t="n">
-        <v>3</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1</v>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t>Kragjordstjärna
-Murgröna
-Scharlakansvårskål agg.</t>
-        </is>
-      </c>
-      <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 15600-2025 artfynd.xlsx", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 15600-2025 karta.png", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 15600-2025 georefererad karta.tif", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 15600-2025 FSC-klagomål.docx", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 15600-2025 FSC-klagomål mail.docx", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 15600-2025 tillsynsbegäran.docx", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 15600-2025 tillsynsbegäran mail.docx", "A 15600-2025")</f>
         <v/>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
         <v>44470</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         <v>45267</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
         <v>44544</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         <v>46246</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 62183-2025</t>
+          <t>A 13040-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5465,14 +5465,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46006</v>
+        <v>45385</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5494,13 +5494,13 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5512,7 +5512,7 @@
         <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5521,46 +5521,46 @@
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62183-2025 artfynd.xlsx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13040-2024 artfynd.xlsx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62183-2025 karta.png", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13040-2024 karta.png", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62183-2025 georefererad karta.tif", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13040-2024 georefererad karta.tif", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62183-2025 FSC-klagomål.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13040-2024 FSC-klagomål.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62183-2025 FSC-klagomål mail.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13040-2024 FSC-klagomål mail.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62183-2025 tillsynsbegäran.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13040-2024 tillsynsbegäran.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62183-2025 tillsynsbegäran mail.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13040-2024 tillsynsbegäran mail.docx", "A 13040-2024")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 24698-2023</t>
+          <t>A 13384-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5574,10 +5574,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45084</v>
+        <v>45005</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5590,16 +5590,16 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>5.5</v>
+        <v>0.9</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -5614,7 +5614,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -5630,42 +5630,42 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24698-2023 artfynd.xlsx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13384-2023 artfynd.xlsx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24698-2023 karta.png", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13384-2023 karta.png", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24698-2023 georefererad karta.tif", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13384-2023 georefererad karta.tif", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24698-2023 FSC-klagomål.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13384-2023 FSC-klagomål.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24698-2023 FSC-klagomål mail.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13384-2023 FSC-klagomål mail.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24698-2023 tillsynsbegäran.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13384-2023 tillsynsbegäran.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24698-2023 tillsynsbegäran mail.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13384-2023 tillsynsbegäran mail.docx", "A 13384-2023")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 13040-2024</t>
+          <t>A 62183-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5675,14 +5675,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45385</v>
+        <v>46006</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5704,13 +5704,13 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5722,7 +5722,7 @@
         <v>1</v>
       </c>
       <c r="R45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5731,39 +5731,39 @@
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13040-2024 artfynd.xlsx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62183-2025 artfynd.xlsx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13040-2024 karta.png", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62183-2025 karta.png", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13040-2024 georefererad karta.tif", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62183-2025 georefererad karta.tif", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13040-2024 FSC-klagomål.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62183-2025 FSC-klagomål.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13040-2024 FSC-klagomål mail.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62183-2025 FSC-klagomål mail.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13040-2024 tillsynsbegäran.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62183-2025 tillsynsbegäran.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13040-2024 tillsynsbegäran mail.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62183-2025 tillsynsbegäran mail.docx", "A 62183-2025")</f>
         <v/>
       </c>
     </row>
@@ -5787,7 +5787,7 @@
         <v>46210</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         <v>46273</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 13384-2023</t>
+          <t>A 24698-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5994,10 +5994,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45005</v>
+        <v>45084</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6010,16 +6010,16 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.9</v>
+        <v>5.5</v>
       </c>
       <c r="J48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -6034,7 +6034,7 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
@@ -6050,35 +6050,35 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="W48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13384-2023 artfynd.xlsx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24698-2023 artfynd.xlsx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="X48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13384-2023 karta.png", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24698-2023 karta.png", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="Y48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13384-2023 georefererad karta.tif", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24698-2023 georefererad karta.tif", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AA48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13384-2023 FSC-klagomål.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24698-2023 FSC-klagomål.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AB48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13384-2023 FSC-klagomål mail.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24698-2023 FSC-klagomål mail.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AC48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13384-2023 tillsynsbegäran.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24698-2023 tillsynsbegäran.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AD48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13384-2023 tillsynsbegäran mail.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24698-2023 tillsynsbegäran mail.docx", "A 24698-2023")</f>
         <v/>
       </c>
     </row>
@@ -6102,7 +6102,7 @@
         <v>44740</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>45980</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>46171</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>

--- a/Översikt MÖRBYLÅNGA.xlsx
+++ b/Översikt MÖRBYLÅNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44964</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>44655</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>45177</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45096</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45685</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>45475</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>45062</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>46195</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>46189</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>45254</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>45062</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>44508</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>44467</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 38039-2022</t>
+          <t>A 60875-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2349,14 +2349,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44811</v>
+        <v>45999</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2369,31 +2369,31 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>7.4</v>
+        <v>2.1</v>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R15" t="n">
         <v>2</v>
@@ -2402,12 +2402,246 @@
         <v>11</v>
       </c>
       <c r="T15" t="n">
+        <v>12</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Järnek
+Mosippa
+Grönsångare
+Gulsparv
+Göktyta
+Mindre hackspett
+Svinrot
+Murgröna
+Spillkråka
+Kråka
+Skogsduva</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 60875-2025 artfynd.xlsx", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 60875-2025 karta.png", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 60875-2025 georefererad karta.tif", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 60875-2025 FSC-klagomål.docx", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 60875-2025 FSC-klagomål mail.docx", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 60875-2025 tillsynsbegäran.docx", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 60875-2025 tillsynsbegäran mail.docx", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 60875-2025 prioriterade fågelarter.docx", "A 60875-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 24778-2022</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>44728</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>7</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>8</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>11</v>
+      </c>
+      <c r="T16" t="n">
+        <v>20</v>
+      </c>
+      <c r="U16" t="n">
+        <v>20</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Tofsäxing
+Backtimjan
+Flentimotej
+Grådådra
+Poppeltofsskivling
+Slåtterfibbla
+Sminkrot
+Solvända
+Kalktallört
+Murgröna
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24778-2022 artfynd.xlsx", "A 24778-2022")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24778-2022 karta.png", "A 24778-2022")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24778-2022 georefererad karta.tif", "A 24778-2022")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24778-2022 FSC-klagomål.docx", "A 24778-2022")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24778-2022 FSC-klagomål mail.docx", "A 24778-2022")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24778-2022 tillsynsbegäran.docx", "A 24778-2022")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24778-2022 tillsynsbegäran mail.docx", "A 24778-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 38039-2022</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>44811</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>4</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>6</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2</v>
+      </c>
+      <c r="S17" t="n">
+        <v>11</v>
+      </c>
+      <c r="T17" t="n">
         <v>13</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U17" t="n">
         <v>12</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Ask
 Grov gulmossa
@@ -2422,107 +2656,107 @@
 Gullviva</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 38039-2022 artfynd.xlsx", "A 38039-2022")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 38039-2022 karta.png", "A 38039-2022")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 38039-2022 georefererad karta.tif", "A 38039-2022")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 38039-2022 FSC-klagomål.docx", "A 38039-2022")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 38039-2022 FSC-klagomål mail.docx", "A 38039-2022")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 38039-2022 tillsynsbegäran.docx", "A 38039-2022")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 38039-2022 tillsynsbegäran mail.docx", "A 38039-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>A 27636-2023</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D16" s="1" t="n">
+      <c r="D18" s="1" t="n">
         <v>45097</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="E18" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I16" t="n">
+      <c r="I18" t="n">
         <v>7.4</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J18" t="n">
         <v>4</v>
       </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
         <v>4</v>
       </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
         <v>6</v>
       </c>
-      <c r="R16" t="n">
+      <c r="R18" t="n">
         <v>2</v>
       </c>
-      <c r="S16" t="n">
+      <c r="S18" t="n">
         <v>11</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T18" t="n">
         <v>13</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U18" t="n">
         <v>11</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Ask
 Grov gulmossa
@@ -2537,266 +2771,32 @@
 Gullviva</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 27636-2023 artfynd.xlsx", "A 27636-2023")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 27636-2023 karta.png", "A 27636-2023")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 27636-2023 georefererad karta.tif", "A 27636-2023")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 27636-2023 FSC-klagomål.docx", "A 27636-2023")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 27636-2023 FSC-klagomål mail.docx", "A 27636-2023")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 27636-2023 tillsynsbegäran.docx", "A 27636-2023")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 27636-2023 tillsynsbegäran mail.docx", "A 27636-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 60875-2025</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45999</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J17" t="n">
-        <v>8</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>5</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>7</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2</v>
-      </c>
-      <c r="S17" t="n">
-        <v>11</v>
-      </c>
-      <c r="T17" t="n">
-        <v>12</v>
-      </c>
-      <c r="U17" t="n">
-        <v>3</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Järnek
-Mosippa
-Grönsångare
-Gulsparv
-Göktyta
-Mindre hackspett
-Svinrot
-Murgröna
-Spillkråka
-Kråka
-Skogsduva</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 60875-2025 artfynd.xlsx", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 60875-2025 karta.png", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 60875-2025 georefererad karta.tif", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 60875-2025 FSC-klagomål.docx", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 60875-2025 FSC-klagomål mail.docx", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 60875-2025 tillsynsbegäran.docx", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 60875-2025 tillsynsbegäran mail.docx", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 60875-2025 prioriterade fågelarter.docx", "A 60875-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 24778-2022</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>44728</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2</v>
-      </c>
-      <c r="L18" t="n">
-        <v>7</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>8</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1</v>
-      </c>
-      <c r="S18" t="n">
-        <v>11</v>
-      </c>
-      <c r="T18" t="n">
-        <v>20</v>
-      </c>
-      <c r="U18" t="n">
-        <v>20</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Tofsäxing
-Backtimjan
-Flentimotej
-Grådådra
-Poppeltofsskivling
-Slåtterfibbla
-Sminkrot
-Solvända
-Kalktallört
-Murgröna
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24778-2022 artfynd.xlsx", "A 24778-2022")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24778-2022 karta.png", "A 24778-2022")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24778-2022 georefererad karta.tif", "A 24778-2022")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24778-2022 FSC-klagomål.docx", "A 24778-2022")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24778-2022 FSC-klagomål mail.docx", "A 24778-2022")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24778-2022 tillsynsbegäran.docx", "A 24778-2022")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24778-2022 tillsynsbegäran mail.docx", "A 24778-2022")</f>
         <v/>
       </c>
     </row>
@@ -2820,7 +2820,7 @@
         <v>45551</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>44616</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>45000</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3094,10 +3094,10 @@
         <v>9</v>
       </c>
       <c r="T21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="U21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>45530</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>45223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>45075</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>45169</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 43714-2025</t>
+          <t>A 43704-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3620,7 +3620,7 @@
         <v>45912</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3633,19 +3633,19 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>7.9</v>
+        <v>2.7</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -3657,21 +3657,131 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>6</v>
       </c>
       <c r="T26" t="n">
+        <v>6</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp
+Långbensgroda
+Större vattensalamander
+Åkergroda
+Mindre vattensalamander
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43704-2025 artfynd.xlsx", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="X26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43704-2025 karta.png", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="Y26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43704-2025 georefererad karta.tif", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="AA26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43704-2025 FSC-klagomål.docx", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="AB26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43704-2025 FSC-klagomål mail.docx", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="AC26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43704-2025 tillsynsbegäran.docx", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="AD26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43704-2025 tillsynsbegäran mail.docx", "A 43704-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 43714-2025</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>45912</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2</v>
+      </c>
+      <c r="S27" t="n">
+        <v>6</v>
+      </c>
+      <c r="T27" t="n">
         <v>8</v>
       </c>
-      <c r="U26" t="n">
+      <c r="U27" t="n">
         <v>2</v>
       </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>Mindre bastardsvärmare
 Sexfläckig bastardsvärmare
@@ -3681,146 +3791,36 @@
 Trädporella</t>
         </is>
       </c>
-      <c r="W26">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43714-2025 artfynd.xlsx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="X26">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43714-2025 karta.png", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="Y26">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43714-2025 georefererad karta.tif", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AA26">
+      <c r="AA27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43714-2025 FSC-klagomål.docx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AB26">
+      <c r="AB27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43714-2025 FSC-klagomål mail.docx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AC26">
+      <c r="AC27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43714-2025 tillsynsbegäran.docx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AD26">
+      <c r="AD27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43714-2025 tillsynsbegäran mail.docx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AE26">
+      <c r="AE27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 43714-2025 prioriterade fågelarter.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 43704-2025</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>45912</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J27" t="n">
-        <v>5</v>
-      </c>
-      <c r="K27" t="n">
-        <v>1</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>6</v>
-      </c>
-      <c r="T27" t="n">
-        <v>6</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Blomkålssvamp
-Långbensgroda
-Större vattensalamander
-Åkergroda
-Mindre vattensalamander
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43704-2025 artfynd.xlsx", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43704-2025 karta.png", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43704-2025 georefererad karta.tif", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43704-2025 FSC-klagomål.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43704-2025 FSC-klagomål mail.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43704-2025 tillsynsbegäran.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43704-2025 tillsynsbegäran mail.docx", "A 43704-2025")</f>
         <v/>
       </c>
     </row>
@@ -3844,7 +3844,7 @@
         <v>46190</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>46003</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>46038</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 19459-2023</t>
+          <t>A 54167-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4173,14 +4173,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45049</v>
+        <v>45616</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4193,22 +4193,22 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4217,21 +4217,129 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
       </c>
       <c r="T31" t="n">
+        <v>8</v>
+      </c>
+      <c r="U31" t="n">
+        <v>8</v>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Murgröna
+Tvåblad
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 54167-2024 artfynd.xlsx", "A 54167-2024")</f>
+        <v/>
+      </c>
+      <c r="X31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 54167-2024 karta.png", "A 54167-2024")</f>
+        <v/>
+      </c>
+      <c r="Y31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 54167-2024 georefererad karta.tif", "A 54167-2024")</f>
+        <v/>
+      </c>
+      <c r="AA31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 54167-2024 FSC-klagomål.docx", "A 54167-2024")</f>
+        <v/>
+      </c>
+      <c r="AB31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 54167-2024 FSC-klagomål mail.docx", "A 54167-2024")</f>
+        <v/>
+      </c>
+      <c r="AC31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 54167-2024 tillsynsbegäran.docx", "A 54167-2024")</f>
+        <v/>
+      </c>
+      <c r="AD31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 54167-2024 tillsynsbegäran mail.docx", "A 54167-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>A 19459-2023</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="n">
+        <v>45049</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
         <v>4</v>
       </c>
-      <c r="U31" t="n">
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
         <v>4</v>
       </c>
-      <c r="V31" s="2" t="inlineStr">
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>4</v>
+      </c>
+      <c r="T32" t="n">
+        <v>4</v>
+      </c>
+      <c r="U32" t="n">
+        <v>4</v>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>Kavelhirs
 Kösa
@@ -4239,140 +4347,32 @@
 Riddarsporre</t>
         </is>
       </c>
-      <c r="W31">
+      <c r="W32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 19459-2023 artfynd.xlsx", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="X31">
+      <c r="X32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 19459-2023 karta.png", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="Y31">
+      <c r="Y32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 19459-2023 georefererad karta.tif", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="AA31">
+      <c r="AA32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 19459-2023 FSC-klagomål.docx", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="AB31">
+      <c r="AB32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 19459-2023 FSC-klagomål mail.docx", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="AC31">
+      <c r="AC32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 19459-2023 tillsynsbegäran.docx", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="AD31">
+      <c r="AD32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 19459-2023 tillsynsbegäran mail.docx", "A 19459-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>A 54167-2024</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D32" s="1" t="n">
-        <v>45616</v>
-      </c>
-      <c r="E32" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J32" t="n">
-        <v>2</v>
-      </c>
-      <c r="K32" t="n">
-        <v>2</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>1</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>1</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1</v>
-      </c>
-      <c r="S32" t="n">
-        <v>4</v>
-      </c>
-      <c r="T32" t="n">
-        <v>8</v>
-      </c>
-      <c r="U32" t="n">
-        <v>8</v>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Murgröna
-Tvåblad
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 54167-2024 artfynd.xlsx", "A 54167-2024")</f>
-        <v/>
-      </c>
-      <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 54167-2024 karta.png", "A 54167-2024")</f>
-        <v/>
-      </c>
-      <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 54167-2024 georefererad karta.tif", "A 54167-2024")</f>
-        <v/>
-      </c>
-      <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 54167-2024 FSC-klagomål.docx", "A 54167-2024")</f>
-        <v/>
-      </c>
-      <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 54167-2024 FSC-klagomål mail.docx", "A 54167-2024")</f>
-        <v/>
-      </c>
-      <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 54167-2024 tillsynsbegäran.docx", "A 54167-2024")</f>
-        <v/>
-      </c>
-      <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 54167-2024 tillsynsbegäran mail.docx", "A 54167-2024")</f>
         <v/>
       </c>
     </row>
@@ -4396,7 +4396,7 @@
         <v>46183</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>46254</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4616,7 +4616,7 @@
         <v>44460</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>45912</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 15600-2025</t>
+          <t>A 29360-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4827,10 +4827,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45747</v>
+        <v>46203</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4843,19 +4843,19 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -4867,10 +4867,10 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S37" t="n">
         <v>3</v>
@@ -4882,145 +4882,145 @@
         <v>1</v>
       </c>
       <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>Mindre blåvinge
+Silversmygare
+Ekoxe</t>
+        </is>
+      </c>
+      <c r="W37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 29360-2026 artfynd.xlsx", "A 29360-2026")</f>
+        <v/>
+      </c>
+      <c r="X37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 29360-2026 karta.png", "A 29360-2026")</f>
+        <v/>
+      </c>
+      <c r="Y37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 29360-2026 georefererad karta.tif", "A 29360-2026")</f>
+        <v/>
+      </c>
+      <c r="AA37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 29360-2026 FSC-klagomål.docx", "A 29360-2026")</f>
+        <v/>
+      </c>
+      <c r="AB37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 29360-2026 FSC-klagomål mail.docx", "A 29360-2026")</f>
+        <v/>
+      </c>
+      <c r="AC37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 29360-2026 tillsynsbegäran.docx", "A 29360-2026")</f>
+        <v/>
+      </c>
+      <c r="AD37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 29360-2026 tillsynsbegäran mail.docx", "A 29360-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>A 15600-2025</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D38" s="1" t="n">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
         <is>
           <t>Kragjordstjärna
 Murgröna
 Scharlakansvårskål agg.</t>
         </is>
       </c>
-      <c r="W37">
+      <c r="W38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 15600-2025 artfynd.xlsx", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="X37">
+      <c r="X38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 15600-2025 karta.png", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="Y37">
+      <c r="Y38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 15600-2025 georefererad karta.tif", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="AA37">
+      <c r="AA38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 15600-2025 FSC-klagomål.docx", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="AB37">
+      <c r="AB38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 15600-2025 FSC-klagomål mail.docx", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="AC37">
+      <c r="AC38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 15600-2025 tillsynsbegäran.docx", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="AD37">
+      <c r="AD38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 15600-2025 tillsynsbegäran mail.docx", "A 15600-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>A 29360-2026</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D38" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="E38" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I38" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J38" t="n">
-        <v>1</v>
-      </c>
-      <c r="K38" t="n">
-        <v>1</v>
-      </c>
-      <c r="L38" t="n">
-        <v>1</v>
-      </c>
-      <c r="M38" t="n">
-        <v>1</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>2</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1</v>
-      </c>
-      <c r="S38" t="n">
-        <v>3</v>
-      </c>
-      <c r="T38" t="n">
-        <v>3</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1</v>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t>Mindre blåvinge
-Silversmygare
-Ekoxe</t>
-        </is>
-      </c>
-      <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 29360-2026 artfynd.xlsx", "A 29360-2026")</f>
-        <v/>
-      </c>
-      <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 29360-2026 karta.png", "A 29360-2026")</f>
-        <v/>
-      </c>
-      <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 29360-2026 georefererad karta.tif", "A 29360-2026")</f>
-        <v/>
-      </c>
-      <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 29360-2026 FSC-klagomål.docx", "A 29360-2026")</f>
-        <v/>
-      </c>
-      <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 29360-2026 FSC-klagomål mail.docx", "A 29360-2026")</f>
-        <v/>
-      </c>
-      <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 29360-2026 tillsynsbegäran.docx", "A 29360-2026")</f>
-        <v/>
-      </c>
-      <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 29360-2026 tillsynsbegäran mail.docx", "A 29360-2026")</f>
         <v/>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
         <v>44470</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         <v>45267</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
         <v>44544</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         <v>46246</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 13040-2024</t>
+          <t>A 24698-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5465,14 +5465,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45385</v>
+        <v>45084</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.2</v>
+        <v>5.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5494,13 +5494,13 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5512,7 +5512,7 @@
         <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5525,42 +5525,42 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13040-2024 artfynd.xlsx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24698-2023 artfynd.xlsx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13040-2024 karta.png", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24698-2023 karta.png", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13040-2024 georefererad karta.tif", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24698-2023 georefererad karta.tif", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13040-2024 FSC-klagomål.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24698-2023 FSC-klagomål.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13040-2024 FSC-klagomål mail.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24698-2023 FSC-klagomål mail.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13040-2024 tillsynsbegäran.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24698-2023 tillsynsbegäran.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13040-2024 tillsynsbegäran mail.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24698-2023 tillsynsbegäran mail.docx", "A 24698-2023")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 13384-2023</t>
+          <t>A 62183-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5574,10 +5574,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45005</v>
+        <v>46006</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5590,16 +5590,16 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -5614,7 +5614,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -5626,46 +5626,46 @@
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13384-2023 artfynd.xlsx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62183-2025 artfynd.xlsx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13384-2023 karta.png", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62183-2025 karta.png", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13384-2023 georefererad karta.tif", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62183-2025 georefererad karta.tif", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13384-2023 FSC-klagomål.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62183-2025 FSC-klagomål.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13384-2023 FSC-klagomål mail.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62183-2025 FSC-klagomål mail.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13384-2023 tillsynsbegäran.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62183-2025 tillsynsbegäran.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13384-2023 tillsynsbegäran mail.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62183-2025 tillsynsbegäran mail.docx", "A 62183-2025")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 62183-2025</t>
+          <t>A 13040-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5675,14 +5675,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46006</v>
+        <v>45385</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5704,13 +5704,13 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5722,7 +5722,7 @@
         <v>1</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5731,46 +5731,46 @@
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62183-2025 artfynd.xlsx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13040-2024 artfynd.xlsx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62183-2025 karta.png", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13040-2024 karta.png", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62183-2025 georefererad karta.tif", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13040-2024 georefererad karta.tif", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62183-2025 FSC-klagomål.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13040-2024 FSC-klagomål.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62183-2025 FSC-klagomål mail.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13040-2024 FSC-klagomål mail.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62183-2025 tillsynsbegäran.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13040-2024 tillsynsbegäran.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62183-2025 tillsynsbegäran mail.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13040-2024 tillsynsbegäran mail.docx", "A 13040-2024")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 30492-2026</t>
+          <t>A 13384-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5780,14 +5780,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46210</v>
+        <v>45005</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5800,16 +5800,16 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -5824,7 +5824,7 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -5836,46 +5836,46 @@
         <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 30492-2026 artfynd.xlsx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13384-2023 artfynd.xlsx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 30492-2026 karta.png", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13384-2023 karta.png", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 30492-2026 georefererad karta.tif", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13384-2023 georefererad karta.tif", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 30492-2026 FSC-klagomål.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13384-2023 FSC-klagomål.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 30492-2026 FSC-klagomål mail.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13384-2023 FSC-klagomål mail.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 30492-2026 tillsynsbegäran.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13384-2023 tillsynsbegäran.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 30492-2026 tillsynsbegäran mail.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13384-2023 tillsynsbegäran mail.docx", "A 13384-2023")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 36928-2026</t>
+          <t>A 30492-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5885,14 +5885,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46273</v>
+        <v>46210</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5905,16 +5905,16 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -5929,7 +5929,7 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
@@ -5945,42 +5945,42 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 36928-2026 artfynd.xlsx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 30492-2026 artfynd.xlsx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 36928-2026 karta.png", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 30492-2026 karta.png", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 36928-2026 georefererad karta.tif", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 30492-2026 georefererad karta.tif", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 36928-2026 FSC-klagomål.docx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 30492-2026 FSC-klagomål.docx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 36928-2026 FSC-klagomål mail.docx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 30492-2026 FSC-klagomål mail.docx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 36928-2026 tillsynsbegäran.docx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 30492-2026 tillsynsbegäran.docx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 36928-2026 tillsynsbegäran mail.docx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 30492-2026 tillsynsbegäran mail.docx", "A 30492-2026")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 24698-2023</t>
+          <t>A 36928-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5994,10 +5994,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45084</v>
+        <v>46273</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6010,16 +6010,16 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>5.5</v>
+        <v>1.3</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -6034,7 +6034,7 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
@@ -6046,39 +6046,39 @@
         <v>1</v>
       </c>
       <c r="U48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="W48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24698-2023 artfynd.xlsx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 36928-2026 artfynd.xlsx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="X48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24698-2023 karta.png", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 36928-2026 karta.png", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="Y48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24698-2023 georefererad karta.tif", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 36928-2026 georefererad karta.tif", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AA48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24698-2023 FSC-klagomål.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 36928-2026 FSC-klagomål.docx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AB48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24698-2023 FSC-klagomål mail.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 36928-2026 FSC-klagomål mail.docx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AC48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24698-2023 tillsynsbegäran.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 36928-2026 tillsynsbegäran.docx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AD48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24698-2023 tillsynsbegäran mail.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 36928-2026 tillsynsbegäran mail.docx", "A 36928-2026")</f>
         <v/>
       </c>
     </row>
@@ -6102,7 +6102,7 @@
         <v>44740</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>45980</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>46171</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>

--- a/Översikt MÖRBYLÅNGA.xlsx
+++ b/Översikt MÖRBYLÅNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44964</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>44655</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>45177</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45096</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45685</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>45475</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>45062</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>46195</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>46189</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>45254</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>45062</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>44508</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>44467</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 60875-2025</t>
+          <t>A 38039-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2349,14 +2349,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45999</v>
+        <v>44811</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2369,31 +2369,31 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.1</v>
+        <v>7.4</v>
       </c>
       <c r="J15" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
         <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R15" t="n">
         <v>2</v>
@@ -2402,12 +2402,242 @@
         <v>11</v>
       </c>
       <c r="T15" t="n">
+        <v>13</v>
+      </c>
+      <c r="U15" t="n">
         <v>12</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Grov gulmossa
+Backtimjan
+Dvärgjordstjärna
+Solvända
+Ängsstarr
+Murgröna
+Alvarmalört
+Grönvit nattviol
+Krutbrännare
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 38039-2022 artfynd.xlsx", "A 38039-2022")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 38039-2022 karta.png", "A 38039-2022")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 38039-2022 georefererad karta.tif", "A 38039-2022")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 38039-2022 FSC-klagomål.docx", "A 38039-2022")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 38039-2022 FSC-klagomål mail.docx", "A 38039-2022")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 38039-2022 tillsynsbegäran.docx", "A 38039-2022")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 38039-2022 tillsynsbegäran mail.docx", "A 38039-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 27636-2023</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45097</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>4</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>6</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2</v>
+      </c>
+      <c r="S16" t="n">
+        <v>11</v>
+      </c>
+      <c r="T16" t="n">
+        <v>13</v>
+      </c>
+      <c r="U16" t="n">
+        <v>11</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Grov gulmossa
+Backtimjan
+Dvärgjordstjärna
+Solvända
+Ängsstarr
+Murgröna
+Alvarmalört
+Grönvit nattviol
+Krutbrännare
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 27636-2023 artfynd.xlsx", "A 27636-2023")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 27636-2023 karta.png", "A 27636-2023")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 27636-2023 georefererad karta.tif", "A 27636-2023")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 27636-2023 FSC-klagomål.docx", "A 27636-2023")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 27636-2023 FSC-klagomål mail.docx", "A 27636-2023")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 27636-2023 tillsynsbegäran.docx", "A 27636-2023")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 27636-2023 tillsynsbegäran mail.docx", "A 27636-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 60875-2025</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45999</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>8</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>5</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>7</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2</v>
+      </c>
+      <c r="S17" t="n">
+        <v>11</v>
+      </c>
+      <c r="T17" t="n">
+        <v>12</v>
+      </c>
+      <c r="U17" t="n">
         <v>3</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Järnek
 Mosippa
@@ -2422,111 +2652,111 @@
 Skogsduva</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 60875-2025 artfynd.xlsx", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 60875-2025 karta.png", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 60875-2025 georefererad karta.tif", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 60875-2025 FSC-klagomål.docx", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 60875-2025 FSC-klagomål mail.docx", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 60875-2025 tillsynsbegäran.docx", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 60875-2025 tillsynsbegäran mail.docx", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 60875-2025 prioriterade fågelarter.docx", "A 60875-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>A 24778-2022</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D16" s="1" t="n">
+      <c r="D18" s="1" t="n">
         <v>44728</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="E18" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I16" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
         <v>2</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L18" t="n">
         <v>7</v>
       </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
         <v>8</v>
       </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" t="n">
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
         <v>11</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T18" t="n">
         <v>20</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U18" t="n">
         <v>20</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Tofsäxing
 Backtimjan
@@ -2541,262 +2771,32 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24778-2022 artfynd.xlsx", "A 24778-2022")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24778-2022 karta.png", "A 24778-2022")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24778-2022 georefererad karta.tif", "A 24778-2022")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24778-2022 FSC-klagomål.docx", "A 24778-2022")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24778-2022 FSC-klagomål mail.docx", "A 24778-2022")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24778-2022 tillsynsbegäran.docx", "A 24778-2022")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24778-2022 tillsynsbegäran mail.docx", "A 24778-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 38039-2022</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>44811</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="J17" t="n">
-        <v>4</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>4</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>6</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2</v>
-      </c>
-      <c r="S17" t="n">
-        <v>11</v>
-      </c>
-      <c r="T17" t="n">
-        <v>13</v>
-      </c>
-      <c r="U17" t="n">
-        <v>12</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Grov gulmossa
-Backtimjan
-Dvärgjordstjärna
-Solvända
-Ängsstarr
-Murgröna
-Alvarmalört
-Grönvit nattviol
-Krutbrännare
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 38039-2022 artfynd.xlsx", "A 38039-2022")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 38039-2022 karta.png", "A 38039-2022")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 38039-2022 georefererad karta.tif", "A 38039-2022")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 38039-2022 FSC-klagomål.docx", "A 38039-2022")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 38039-2022 FSC-klagomål mail.docx", "A 38039-2022")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 38039-2022 tillsynsbegäran.docx", "A 38039-2022")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 38039-2022 tillsynsbegäran mail.docx", "A 38039-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 27636-2023</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45097</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="J18" t="n">
-        <v>4</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>4</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>6</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2</v>
-      </c>
-      <c r="S18" t="n">
-        <v>11</v>
-      </c>
-      <c r="T18" t="n">
-        <v>13</v>
-      </c>
-      <c r="U18" t="n">
-        <v>11</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Grov gulmossa
-Backtimjan
-Dvärgjordstjärna
-Solvända
-Ängsstarr
-Murgröna
-Alvarmalört
-Grönvit nattviol
-Krutbrännare
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 27636-2023 artfynd.xlsx", "A 27636-2023")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 27636-2023 karta.png", "A 27636-2023")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 27636-2023 georefererad karta.tif", "A 27636-2023")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 27636-2023 FSC-klagomål.docx", "A 27636-2023")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 27636-2023 FSC-klagomål mail.docx", "A 27636-2023")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 27636-2023 tillsynsbegäran.docx", "A 27636-2023")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 27636-2023 tillsynsbegäran mail.docx", "A 27636-2023")</f>
         <v/>
       </c>
     </row>
@@ -2820,7 +2820,7 @@
         <v>45551</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>44616</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>45000</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>45530</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>45223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>45075</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>45169</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 43704-2025</t>
+          <t>A 43714-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3620,7 +3620,7 @@
         <v>45912</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3633,19 +3633,19 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.7</v>
+        <v>7.9</v>
       </c>
       <c r="J26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -3657,21 +3657,135 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S26" t="n">
         <v>6</v>
       </c>
       <c r="T26" t="n">
+        <v>8</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Mindre bastardsvärmare
+Sexfläckig bastardsvärmare
+Grönsångare
+Murgröna
+Tibast
+Trädporella</t>
+        </is>
+      </c>
+      <c r="W26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43714-2025 artfynd.xlsx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="X26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43714-2025 karta.png", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="Y26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43714-2025 georefererad karta.tif", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AA26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43714-2025 FSC-klagomål.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AB26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43714-2025 FSC-klagomål mail.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AC26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43714-2025 tillsynsbegäran.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AD26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43714-2025 tillsynsbegäran mail.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 43714-2025 prioriterade fågelarter.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 43704-2025</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>45912</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J27" t="n">
+        <v>5</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
         <v>6</v>
       </c>
-      <c r="U26" t="n">
-        <v>1</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="T27" t="n">
+        <v>6</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>Blomkålssvamp
 Långbensgroda
@@ -3681,146 +3795,32 @@
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W26">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43704-2025 artfynd.xlsx", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="X26">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43704-2025 karta.png", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="Y26">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43704-2025 georefererad karta.tif", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="AA26">
+      <c r="AA27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43704-2025 FSC-klagomål.docx", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="AB26">
+      <c r="AB27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43704-2025 FSC-klagomål mail.docx", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="AC26">
+      <c r="AC27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43704-2025 tillsynsbegäran.docx", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="AD26">
+      <c r="AD27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43704-2025 tillsynsbegäran mail.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 43714-2025</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>45912</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="J27" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>3</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1</v>
-      </c>
-      <c r="M27" t="n">
-        <v>2</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>3</v>
-      </c>
-      <c r="R27" t="n">
-        <v>2</v>
-      </c>
-      <c r="S27" t="n">
-        <v>6</v>
-      </c>
-      <c r="T27" t="n">
-        <v>8</v>
-      </c>
-      <c r="U27" t="n">
-        <v>2</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Mindre bastardsvärmare
-Sexfläckig bastardsvärmare
-Grönsångare
-Murgröna
-Tibast
-Trädporella</t>
-        </is>
-      </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43714-2025 artfynd.xlsx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43714-2025 karta.png", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43714-2025 georefererad karta.tif", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43714-2025 FSC-klagomål.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43714-2025 FSC-klagomål mail.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43714-2025 tillsynsbegäran.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43714-2025 tillsynsbegäran mail.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 43714-2025 prioriterade fågelarter.docx", "A 43714-2025")</f>
         <v/>
       </c>
     </row>
@@ -3844,7 +3844,7 @@
         <v>46190</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>46003</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>46038</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         <v>45616</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 19459-2023</t>
+          <t>A 26440-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4285,10 +4285,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45049</v>
+        <v>46183</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4301,16 +4301,16 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4325,7 +4325,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -4334,12 +4334,232 @@
         <v>4</v>
       </c>
       <c r="T32" t="n">
+        <v>5</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>Backstarr
+Murgröna
+Nästrot
+Vätteros</t>
+        </is>
+      </c>
+      <c r="W32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 26440-2026 artfynd.xlsx", "A 26440-2026")</f>
+        <v/>
+      </c>
+      <c r="X32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 26440-2026 karta.png", "A 26440-2026")</f>
+        <v/>
+      </c>
+      <c r="Y32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 26440-2026 georefererad karta.tif", "A 26440-2026")</f>
+        <v/>
+      </c>
+      <c r="AA32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 26440-2026 FSC-klagomål.docx", "A 26440-2026")</f>
+        <v/>
+      </c>
+      <c r="AB32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 26440-2026 FSC-klagomål mail.docx", "A 26440-2026")</f>
+        <v/>
+      </c>
+      <c r="AC32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 26440-2026 tillsynsbegäran.docx", "A 26440-2026")</f>
+        <v/>
+      </c>
+      <c r="AD32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 26440-2026 tillsynsbegäran mail.docx", "A 26440-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>A 34431-2026</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" t="n">
+        <v>3</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>3</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
         <v>4</v>
       </c>
-      <c r="U32" t="n">
+      <c r="T33" t="n">
+        <v>5</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Mindre hackspett
+Sandtimotej
+Murgröna</t>
+        </is>
+      </c>
+      <c r="W33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 34431-2026 artfynd.xlsx", "A 34431-2026")</f>
+        <v/>
+      </c>
+      <c r="X33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 34431-2026 karta.png", "A 34431-2026")</f>
+        <v/>
+      </c>
+      <c r="Y33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 34431-2026 georefererad karta.tif", "A 34431-2026")</f>
+        <v/>
+      </c>
+      <c r="AA33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 34431-2026 FSC-klagomål.docx", "A 34431-2026")</f>
+        <v/>
+      </c>
+      <c r="AB33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 34431-2026 FSC-klagomål mail.docx", "A 34431-2026")</f>
+        <v/>
+      </c>
+      <c r="AC33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 34431-2026 tillsynsbegäran.docx", "A 34431-2026")</f>
+        <v/>
+      </c>
+      <c r="AD33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 34431-2026 tillsynsbegäran mail.docx", "A 34431-2026")</f>
+        <v/>
+      </c>
+      <c r="AE33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 34431-2026 prioriterade fågelarter.docx", "A 34431-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>A 19459-2023</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="n">
+        <v>45049</v>
+      </c>
+      <c r="E34" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
         <v>4</v>
       </c>
-      <c r="V32" s="2" t="inlineStr">
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>4</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>4</v>
+      </c>
+      <c r="T34" t="n">
+        <v>4</v>
+      </c>
+      <c r="U34" t="n">
+        <v>4</v>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>Kavelhirs
 Kösa
@@ -4347,252 +4567,32 @@
 Riddarsporre</t>
         </is>
       </c>
-      <c r="W32">
+      <c r="W34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 19459-2023 artfynd.xlsx", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="X32">
+      <c r="X34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 19459-2023 karta.png", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="Y32">
+      <c r="Y34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 19459-2023 georefererad karta.tif", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="AA32">
+      <c r="AA34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 19459-2023 FSC-klagomål.docx", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="AB32">
+      <c r="AB34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 19459-2023 FSC-klagomål mail.docx", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="AC32">
+      <c r="AC34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 19459-2023 tillsynsbegäran.docx", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="AD32">
+      <c r="AD34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 19459-2023 tillsynsbegäran mail.docx", "A 19459-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>A 26440-2026</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D33" s="1" t="n">
-        <v>46183</v>
-      </c>
-      <c r="E33" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J33" t="n">
-        <v>1</v>
-      </c>
-      <c r="K33" t="n">
-        <v>3</v>
-      </c>
-      <c r="L33" t="n">
-        <v>1</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>4</v>
-      </c>
-      <c r="T33" t="n">
-        <v>5</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
-        <is>
-          <t>Backstarr
-Murgröna
-Nästrot
-Vätteros</t>
-        </is>
-      </c>
-      <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 26440-2026 artfynd.xlsx", "A 26440-2026")</f>
-        <v/>
-      </c>
-      <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 26440-2026 karta.png", "A 26440-2026")</f>
-        <v/>
-      </c>
-      <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 26440-2026 georefererad karta.tif", "A 26440-2026")</f>
-        <v/>
-      </c>
-      <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 26440-2026 FSC-klagomål.docx", "A 26440-2026")</f>
-        <v/>
-      </c>
-      <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 26440-2026 FSC-klagomål mail.docx", "A 26440-2026")</f>
-        <v/>
-      </c>
-      <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 26440-2026 tillsynsbegäran.docx", "A 26440-2026")</f>
-        <v/>
-      </c>
-      <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 26440-2026 tillsynsbegäran mail.docx", "A 26440-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>A 34431-2026</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="n">
-        <v>46254</v>
-      </c>
-      <c r="E34" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="J34" t="n">
-        <v>2</v>
-      </c>
-      <c r="K34" t="n">
-        <v>1</v>
-      </c>
-      <c r="L34" t="n">
-        <v>3</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>3</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>4</v>
-      </c>
-      <c r="T34" t="n">
-        <v>5</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1</v>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Mindre hackspett
-Sandtimotej
-Murgröna</t>
-        </is>
-      </c>
-      <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 34431-2026 artfynd.xlsx", "A 34431-2026")</f>
-        <v/>
-      </c>
-      <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 34431-2026 karta.png", "A 34431-2026")</f>
-        <v/>
-      </c>
-      <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 34431-2026 georefererad karta.tif", "A 34431-2026")</f>
-        <v/>
-      </c>
-      <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 34431-2026 FSC-klagomål.docx", "A 34431-2026")</f>
-        <v/>
-      </c>
-      <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 34431-2026 FSC-klagomål mail.docx", "A 34431-2026")</f>
-        <v/>
-      </c>
-      <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 34431-2026 tillsynsbegäran.docx", "A 34431-2026")</f>
-        <v/>
-      </c>
-      <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 34431-2026 tillsynsbegäran mail.docx", "A 34431-2026")</f>
-        <v/>
-      </c>
-      <c r="AE34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 34431-2026 prioriterade fågelarter.docx", "A 34431-2026")</f>
         <v/>
       </c>
     </row>
@@ -4616,7 +4616,7 @@
         <v>44460</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>45912</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 29360-2026</t>
+          <t>A 15600-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4827,10 +4827,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46203</v>
+        <v>45747</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4843,19 +4843,19 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -4867,10 +4867,10 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>3</v>
@@ -4882,145 +4882,145 @@
         <v>1</v>
       </c>
       <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>Kragjordstjärna
+Murgröna
+Scharlakansvårskål agg.</t>
+        </is>
+      </c>
+      <c r="W37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 15600-2025 artfynd.xlsx", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="X37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 15600-2025 karta.png", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="Y37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 15600-2025 georefererad karta.tif", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="AA37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 15600-2025 FSC-klagomål.docx", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="AB37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 15600-2025 FSC-klagomål mail.docx", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="AC37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 15600-2025 tillsynsbegäran.docx", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="AD37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 15600-2025 tillsynsbegäran mail.docx", "A 15600-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>A 29360-2026</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D38" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
         <is>
           <t>Mindre blåvinge
 Silversmygare
 Ekoxe</t>
         </is>
       </c>
-      <c r="W37">
+      <c r="W38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 29360-2026 artfynd.xlsx", "A 29360-2026")</f>
         <v/>
       </c>
-      <c r="X37">
+      <c r="X38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 29360-2026 karta.png", "A 29360-2026")</f>
         <v/>
       </c>
-      <c r="Y37">
+      <c r="Y38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 29360-2026 georefererad karta.tif", "A 29360-2026")</f>
         <v/>
       </c>
-      <c r="AA37">
+      <c r="AA38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 29360-2026 FSC-klagomål.docx", "A 29360-2026")</f>
         <v/>
       </c>
-      <c r="AB37">
+      <c r="AB38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 29360-2026 FSC-klagomål mail.docx", "A 29360-2026")</f>
         <v/>
       </c>
-      <c r="AC37">
+      <c r="AC38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 29360-2026 tillsynsbegäran.docx", "A 29360-2026")</f>
         <v/>
       </c>
-      <c r="AD37">
+      <c r="AD38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 29360-2026 tillsynsbegäran mail.docx", "A 29360-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>A 15600-2025</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D38" s="1" t="n">
-        <v>45747</v>
-      </c>
-      <c r="E38" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I38" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="n">
-        <v>3</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>3</v>
-      </c>
-      <c r="T38" t="n">
-        <v>3</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1</v>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t>Kragjordstjärna
-Murgröna
-Scharlakansvårskål agg.</t>
-        </is>
-      </c>
-      <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 15600-2025 artfynd.xlsx", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 15600-2025 karta.png", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 15600-2025 georefererad karta.tif", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 15600-2025 FSC-klagomål.docx", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 15600-2025 FSC-klagomål mail.docx", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 15600-2025 tillsynsbegäran.docx", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 15600-2025 tillsynsbegäran mail.docx", "A 15600-2025")</f>
         <v/>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
         <v>44470</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 62231-2023</t>
+          <t>A 72167-2021</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5143,14 +5143,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45267</v>
+        <v>44544</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J40" t="n">
         <v>1</v>
@@ -5204,42 +5204,46 @@
       <c r="V40" s="2" t="inlineStr">
         <is>
           <t>Murgröna
-Blåsippa</t>
+Röd glada</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62231-2023 artfynd.xlsx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 72167-2021 artfynd.xlsx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62231-2023 karta.png", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 72167-2021 karta.png", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62231-2023 georefererad karta.tif", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 72167-2021 georefererad karta.tif", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62231-2023 FSC-klagomål.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 72167-2021 FSC-klagomål.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62231-2023 FSC-klagomål mail.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 72167-2021 FSC-klagomål mail.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62231-2023 tillsynsbegäran.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 72167-2021 tillsynsbegäran.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62231-2023 tillsynsbegäran mail.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 72167-2021 tillsynsbegäran mail.docx", "A 72167-2021")</f>
+        <v/>
+      </c>
+      <c r="AE40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 72167-2021 prioriterade fågelarter.docx", "A 72167-2021")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 72167-2021</t>
+          <t>A 62231-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5249,14 +5253,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44544</v>
+        <v>45267</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5269,7 +5273,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J41" t="n">
         <v>1</v>
@@ -5310,39 +5314,35 @@
       <c r="V41" s="2" t="inlineStr">
         <is>
           <t>Murgröna
-Röd glada</t>
+Blåsippa</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 72167-2021 artfynd.xlsx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62231-2023 artfynd.xlsx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 72167-2021 karta.png", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62231-2023 karta.png", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 72167-2021 georefererad karta.tif", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62231-2023 georefererad karta.tif", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 72167-2021 FSC-klagomål.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62231-2023 FSC-klagomål.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 72167-2021 FSC-klagomål mail.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62231-2023 FSC-klagomål mail.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 72167-2021 tillsynsbegäran.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62231-2023 tillsynsbegäran.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 72167-2021 tillsynsbegäran mail.docx", "A 72167-2021")</f>
-        <v/>
-      </c>
-      <c r="AE41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 72167-2021 prioriterade fågelarter.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62231-2023 tillsynsbegäran mail.docx", "A 62231-2023")</f>
         <v/>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
         <v>46246</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 24698-2023</t>
+          <t>A 13040-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5465,14 +5465,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45084</v>
+        <v>45385</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>5.5</v>
+        <v>1.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5494,13 +5494,13 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5512,7 +5512,7 @@
         <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5525,42 +5525,42 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24698-2023 artfynd.xlsx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13040-2024 artfynd.xlsx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24698-2023 karta.png", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13040-2024 karta.png", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24698-2023 georefererad karta.tif", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13040-2024 georefererad karta.tif", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24698-2023 FSC-klagomål.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13040-2024 FSC-klagomål.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24698-2023 FSC-klagomål mail.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13040-2024 FSC-klagomål mail.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24698-2023 tillsynsbegäran.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13040-2024 tillsynsbegäran.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24698-2023 tillsynsbegäran mail.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13040-2024 tillsynsbegäran mail.docx", "A 13040-2024")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 62183-2025</t>
+          <t>A 13384-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5574,10 +5574,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46006</v>
+        <v>45005</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5590,16 +5590,16 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -5614,7 +5614,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -5626,46 +5626,46 @@
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62183-2025 artfynd.xlsx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13384-2023 artfynd.xlsx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62183-2025 karta.png", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13384-2023 karta.png", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62183-2025 georefererad karta.tif", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13384-2023 georefererad karta.tif", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62183-2025 FSC-klagomål.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13384-2023 FSC-klagomål.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62183-2025 FSC-klagomål mail.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13384-2023 FSC-klagomål mail.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62183-2025 tillsynsbegäran.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13384-2023 tillsynsbegäran.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62183-2025 tillsynsbegäran mail.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13384-2023 tillsynsbegäran mail.docx", "A 13384-2023")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 13040-2024</t>
+          <t>A 30492-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5679,10 +5679,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45385</v>
+        <v>46210</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5704,13 +5704,13 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5722,7 +5722,7 @@
         <v>1</v>
       </c>
       <c r="R45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5731,46 +5731,46 @@
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13040-2024 artfynd.xlsx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 30492-2026 artfynd.xlsx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13040-2024 karta.png", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 30492-2026 karta.png", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13040-2024 georefererad karta.tif", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 30492-2026 georefererad karta.tif", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13040-2024 FSC-klagomål.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 30492-2026 FSC-klagomål.docx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13040-2024 FSC-klagomål mail.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 30492-2026 FSC-klagomål mail.docx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13040-2024 tillsynsbegäran.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 30492-2026 tillsynsbegäran.docx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13040-2024 tillsynsbegäran mail.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 30492-2026 tillsynsbegäran mail.docx", "A 30492-2026")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 13384-2023</t>
+          <t>A 62183-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5784,10 +5784,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45005</v>
+        <v>46006</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5800,16 +5800,16 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -5824,7 +5824,7 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -5836,46 +5836,46 @@
         <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13384-2023 artfynd.xlsx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62183-2025 artfynd.xlsx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13384-2023 karta.png", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62183-2025 karta.png", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13384-2023 georefererad karta.tif", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62183-2025 georefererad karta.tif", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13384-2023 FSC-klagomål.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62183-2025 FSC-klagomål.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13384-2023 FSC-klagomål mail.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62183-2025 FSC-klagomål mail.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13384-2023 tillsynsbegäran.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62183-2025 tillsynsbegäran.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13384-2023 tillsynsbegäran mail.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62183-2025 tillsynsbegäran mail.docx", "A 62183-2025")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 30492-2026</t>
+          <t>A 36928-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5885,14 +5885,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46210</v>
+        <v>46273</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5905,16 +5905,16 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -5929,7 +5929,7 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
@@ -5945,42 +5945,42 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 30492-2026 artfynd.xlsx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 36928-2026 artfynd.xlsx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 30492-2026 karta.png", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 36928-2026 karta.png", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 30492-2026 georefererad karta.tif", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 36928-2026 georefererad karta.tif", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 30492-2026 FSC-klagomål.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 36928-2026 FSC-klagomål.docx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 30492-2026 FSC-klagomål mail.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 36928-2026 FSC-klagomål mail.docx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 30492-2026 tillsynsbegäran.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 36928-2026 tillsynsbegäran.docx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 30492-2026 tillsynsbegäran mail.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 36928-2026 tillsynsbegäran mail.docx", "A 36928-2026")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 36928-2026</t>
+          <t>A 24698-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5994,10 +5994,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46273</v>
+        <v>45084</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6010,16 +6010,16 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.3</v>
+        <v>5.5</v>
       </c>
       <c r="J48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -6034,7 +6034,7 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
@@ -6046,39 +6046,39 @@
         <v>1</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="W48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 36928-2026 artfynd.xlsx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24698-2023 artfynd.xlsx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="X48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 36928-2026 karta.png", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24698-2023 karta.png", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="Y48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 36928-2026 georefererad karta.tif", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24698-2023 georefererad karta.tif", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AA48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 36928-2026 FSC-klagomål.docx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24698-2023 FSC-klagomål.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AB48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 36928-2026 FSC-klagomål mail.docx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24698-2023 FSC-klagomål mail.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AC48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 36928-2026 tillsynsbegäran.docx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24698-2023 tillsynsbegäran.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AD48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 36928-2026 tillsynsbegäran mail.docx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24698-2023 tillsynsbegäran mail.docx", "A 24698-2023")</f>
         <v/>
       </c>
     </row>
@@ -6102,7 +6102,7 @@
         <v>44740</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>45980</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>46171</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>

--- a/Översikt MÖRBYLÅNGA.xlsx
+++ b/Översikt MÖRBYLÅNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44964</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>44655</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>45177</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45096</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45685</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>45475</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>45062</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>46195</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>46189</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>45254</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>45062</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>44508</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>44467</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>44811</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>45097</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 60875-2025</t>
+          <t>A 24778-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2583,10 +2583,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45999</v>
+        <v>44728</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2599,45 +2599,160 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L17" t="n">
+        <v>7</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>8</v>
       </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>5</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>7</v>
-      </c>
       <c r="R17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>11</v>
       </c>
       <c r="T17" t="n">
+        <v>20</v>
+      </c>
+      <c r="U17" t="n">
+        <v>20</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Tofsäxing
+Backtimjan
+Flentimotej
+Grådådra
+Poppeltofsskivling
+Slåtterfibbla
+Sminkrot
+Solvända
+Kalktallört
+Murgröna
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24778-2022 artfynd.xlsx", "A 24778-2022")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24778-2022 karta.png", "A 24778-2022")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24778-2022 georefererad karta.tif", "A 24778-2022")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24778-2022 FSC-klagomål.docx", "A 24778-2022")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24778-2022 FSC-klagomål mail.docx", "A 24778-2022")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24778-2022 tillsynsbegäran.docx", "A 24778-2022")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24778-2022 tillsynsbegäran mail.docx", "A 24778-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 60875-2025</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45999</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>8</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>5</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>7</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2</v>
+      </c>
+      <c r="S18" t="n">
+        <v>11</v>
+      </c>
+      <c r="T18" t="n">
         <v>12</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U18" t="n">
         <v>3</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Järnek
 Mosippa
@@ -2652,151 +2767,36 @@
 Skogsduva</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 60875-2025 artfynd.xlsx", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 60875-2025 karta.png", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 60875-2025 georefererad karta.tif", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 60875-2025 FSC-klagomål.docx", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 60875-2025 FSC-klagomål mail.docx", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 60875-2025 tillsynsbegäran.docx", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 60875-2025 tillsynsbegäran mail.docx", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="AE17">
+      <c r="AE18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 60875-2025 prioriterade fågelarter.docx", "A 60875-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 24778-2022</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>44728</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2</v>
-      </c>
-      <c r="L18" t="n">
-        <v>7</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>8</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1</v>
-      </c>
-      <c r="S18" t="n">
-        <v>11</v>
-      </c>
-      <c r="T18" t="n">
-        <v>20</v>
-      </c>
-      <c r="U18" t="n">
-        <v>20</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Tofsäxing
-Backtimjan
-Flentimotej
-Grådådra
-Poppeltofsskivling
-Slåtterfibbla
-Sminkrot
-Solvända
-Kalktallört
-Murgröna
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24778-2022 artfynd.xlsx", "A 24778-2022")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24778-2022 karta.png", "A 24778-2022")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24778-2022 georefererad karta.tif", "A 24778-2022")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24778-2022 FSC-klagomål.docx", "A 24778-2022")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24778-2022 FSC-klagomål mail.docx", "A 24778-2022")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24778-2022 tillsynsbegäran.docx", "A 24778-2022")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24778-2022 tillsynsbegäran mail.docx", "A 24778-2022")</f>
         <v/>
       </c>
     </row>
@@ -2820,7 +2820,7 @@
         <v>45551</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>44616</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>45000</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>45530</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>45223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>45075</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>45169</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 43714-2025</t>
+          <t>A 43704-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3620,7 +3620,7 @@
         <v>45912</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3633,19 +3633,19 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>7.9</v>
+        <v>2.7</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -3657,21 +3657,131 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>6</v>
       </c>
       <c r="T26" t="n">
+        <v>6</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp
+Långbensgroda
+Större vattensalamander
+Åkergroda
+Mindre vattensalamander
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43704-2025 artfynd.xlsx", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="X26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43704-2025 karta.png", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="Y26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43704-2025 georefererad karta.tif", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="AA26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43704-2025 FSC-klagomål.docx", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="AB26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43704-2025 FSC-klagomål mail.docx", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="AC26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43704-2025 tillsynsbegäran.docx", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="AD26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43704-2025 tillsynsbegäran mail.docx", "A 43704-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 43714-2025</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>45912</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2</v>
+      </c>
+      <c r="S27" t="n">
+        <v>6</v>
+      </c>
+      <c r="T27" t="n">
         <v>8</v>
       </c>
-      <c r="U26" t="n">
+      <c r="U27" t="n">
         <v>2</v>
       </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>Mindre bastardsvärmare
 Sexfläckig bastardsvärmare
@@ -3681,146 +3791,36 @@
 Trädporella</t>
         </is>
       </c>
-      <c r="W26">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43714-2025 artfynd.xlsx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="X26">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43714-2025 karta.png", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="Y26">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43714-2025 georefererad karta.tif", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AA26">
+      <c r="AA27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43714-2025 FSC-klagomål.docx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AB26">
+      <c r="AB27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43714-2025 FSC-klagomål mail.docx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AC26">
+      <c r="AC27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43714-2025 tillsynsbegäran.docx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AD26">
+      <c r="AD27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43714-2025 tillsynsbegäran mail.docx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AE26">
+      <c r="AE27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 43714-2025 prioriterade fågelarter.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 43704-2025</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>45912</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J27" t="n">
-        <v>5</v>
-      </c>
-      <c r="K27" t="n">
-        <v>1</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>6</v>
-      </c>
-      <c r="T27" t="n">
-        <v>6</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Blomkålssvamp
-Långbensgroda
-Större vattensalamander
-Åkergroda
-Mindre vattensalamander
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43704-2025 artfynd.xlsx", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43704-2025 karta.png", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43704-2025 georefererad karta.tif", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43704-2025 FSC-klagomål.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43704-2025 FSC-klagomål mail.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43704-2025 tillsynsbegäran.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43704-2025 tillsynsbegäran mail.docx", "A 43704-2025")</f>
         <v/>
       </c>
     </row>
@@ -3844,7 +3844,7 @@
         <v>46190</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>46003</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>46038</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         <v>45616</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 26440-2026</t>
+          <t>A 19459-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4285,10 +4285,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46183</v>
+        <v>45049</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4301,16 +4301,16 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4325,7 +4325,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -4334,12 +4334,120 @@
         <v>4</v>
       </c>
       <c r="T32" t="n">
+        <v>4</v>
+      </c>
+      <c r="U32" t="n">
+        <v>4</v>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>Kavelhirs
+Kösa
+Luddvicker
+Riddarsporre</t>
+        </is>
+      </c>
+      <c r="W32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 19459-2023 artfynd.xlsx", "A 19459-2023")</f>
+        <v/>
+      </c>
+      <c r="X32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 19459-2023 karta.png", "A 19459-2023")</f>
+        <v/>
+      </c>
+      <c r="Y32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 19459-2023 georefererad karta.tif", "A 19459-2023")</f>
+        <v/>
+      </c>
+      <c r="AA32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 19459-2023 FSC-klagomål.docx", "A 19459-2023")</f>
+        <v/>
+      </c>
+      <c r="AB32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 19459-2023 FSC-klagomål mail.docx", "A 19459-2023")</f>
+        <v/>
+      </c>
+      <c r="AC32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 19459-2023 tillsynsbegäran.docx", "A 19459-2023")</f>
+        <v/>
+      </c>
+      <c r="AD32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 19459-2023 tillsynsbegäran mail.docx", "A 19459-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>A 26440-2026</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>4</v>
+      </c>
+      <c r="T33" t="n">
         <v>5</v>
       </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
         <is>
           <t>Backstarr
 Murgröna
@@ -4347,107 +4455,107 @@
 Vätteros</t>
         </is>
       </c>
-      <c r="W32">
+      <c r="W33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 26440-2026 artfynd.xlsx", "A 26440-2026")</f>
         <v/>
       </c>
-      <c r="X32">
+      <c r="X33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 26440-2026 karta.png", "A 26440-2026")</f>
         <v/>
       </c>
-      <c r="Y32">
+      <c r="Y33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 26440-2026 georefererad karta.tif", "A 26440-2026")</f>
         <v/>
       </c>
-      <c r="AA32">
+      <c r="AA33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 26440-2026 FSC-klagomål.docx", "A 26440-2026")</f>
         <v/>
       </c>
-      <c r="AB32">
+      <c r="AB33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 26440-2026 FSC-klagomål mail.docx", "A 26440-2026")</f>
         <v/>
       </c>
-      <c r="AC32">
+      <c r="AC33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 26440-2026 tillsynsbegäran.docx", "A 26440-2026")</f>
         <v/>
       </c>
-      <c r="AD32">
+      <c r="AD33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 26440-2026 tillsynsbegäran mail.docx", "A 26440-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>A 34431-2026</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D33" s="1" t="n">
+      <c r="D34" s="1" t="n">
         <v>46254</v>
       </c>
-      <c r="E33" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F33" t="inlineStr">
+      <c r="E34" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I33" t="n">
+      <c r="I34" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="J33" t="n">
+      <c r="J34" t="n">
         <v>2</v>
       </c>
-      <c r="K33" t="n">
-        <v>1</v>
-      </c>
-      <c r="L33" t="n">
+      <c r="K34" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" t="n">
         <v>3</v>
       </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
         <v>3</v>
       </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
         <v>4</v>
       </c>
-      <c r="T33" t="n">
+      <c r="T34" t="n">
         <v>5</v>
       </c>
-      <c r="U33" t="n">
-        <v>1</v>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
+      <c r="U34" t="n">
+        <v>1</v>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>Entita
 Mindre hackspett
@@ -4455,144 +4563,36 @@
 Murgröna</t>
         </is>
       </c>
-      <c r="W33">
+      <c r="W34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 34431-2026 artfynd.xlsx", "A 34431-2026")</f>
         <v/>
       </c>
-      <c r="X33">
+      <c r="X34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 34431-2026 karta.png", "A 34431-2026")</f>
         <v/>
       </c>
-      <c r="Y33">
+      <c r="Y34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 34431-2026 georefererad karta.tif", "A 34431-2026")</f>
         <v/>
       </c>
-      <c r="AA33">
+      <c r="AA34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 34431-2026 FSC-klagomål.docx", "A 34431-2026")</f>
         <v/>
       </c>
-      <c r="AB33">
+      <c r="AB34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 34431-2026 FSC-klagomål mail.docx", "A 34431-2026")</f>
         <v/>
       </c>
-      <c r="AC33">
+      <c r="AC34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 34431-2026 tillsynsbegäran.docx", "A 34431-2026")</f>
         <v/>
       </c>
-      <c r="AD33">
+      <c r="AD34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 34431-2026 tillsynsbegäran mail.docx", "A 34431-2026")</f>
         <v/>
       </c>
-      <c r="AE33">
+      <c r="AE34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 34431-2026 prioriterade fågelarter.docx", "A 34431-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>A 19459-2023</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="n">
-        <v>45049</v>
-      </c>
-      <c r="E34" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>4</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>4</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>4</v>
-      </c>
-      <c r="T34" t="n">
-        <v>4</v>
-      </c>
-      <c r="U34" t="n">
-        <v>4</v>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>Kavelhirs
-Kösa
-Luddvicker
-Riddarsporre</t>
-        </is>
-      </c>
-      <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 19459-2023 artfynd.xlsx", "A 19459-2023")</f>
-        <v/>
-      </c>
-      <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 19459-2023 karta.png", "A 19459-2023")</f>
-        <v/>
-      </c>
-      <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 19459-2023 georefererad karta.tif", "A 19459-2023")</f>
-        <v/>
-      </c>
-      <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 19459-2023 FSC-klagomål.docx", "A 19459-2023")</f>
-        <v/>
-      </c>
-      <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 19459-2023 FSC-klagomål mail.docx", "A 19459-2023")</f>
-        <v/>
-      </c>
-      <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 19459-2023 tillsynsbegäran.docx", "A 19459-2023")</f>
-        <v/>
-      </c>
-      <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 19459-2023 tillsynsbegäran mail.docx", "A 19459-2023")</f>
         <v/>
       </c>
     </row>
@@ -4616,7 +4616,7 @@
         <v>44460</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>45912</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 15600-2025</t>
+          <t>A 29360-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4827,10 +4827,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45747</v>
+        <v>46203</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4843,19 +4843,19 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -4867,10 +4867,10 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S37" t="n">
         <v>3</v>
@@ -4882,145 +4882,145 @@
         <v>1</v>
       </c>
       <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>Mindre blåvinge
+Silversmygare
+Ekoxe</t>
+        </is>
+      </c>
+      <c r="W37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 29360-2026 artfynd.xlsx", "A 29360-2026")</f>
+        <v/>
+      </c>
+      <c r="X37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 29360-2026 karta.png", "A 29360-2026")</f>
+        <v/>
+      </c>
+      <c r="Y37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 29360-2026 georefererad karta.tif", "A 29360-2026")</f>
+        <v/>
+      </c>
+      <c r="AA37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 29360-2026 FSC-klagomål.docx", "A 29360-2026")</f>
+        <v/>
+      </c>
+      <c r="AB37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 29360-2026 FSC-klagomål mail.docx", "A 29360-2026")</f>
+        <v/>
+      </c>
+      <c r="AC37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 29360-2026 tillsynsbegäran.docx", "A 29360-2026")</f>
+        <v/>
+      </c>
+      <c r="AD37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 29360-2026 tillsynsbegäran mail.docx", "A 29360-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>A 15600-2025</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D38" s="1" t="n">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
         <is>
           <t>Kragjordstjärna
 Murgröna
 Scharlakansvårskål agg.</t>
         </is>
       </c>
-      <c r="W37">
+      <c r="W38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 15600-2025 artfynd.xlsx", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="X37">
+      <c r="X38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 15600-2025 karta.png", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="Y37">
+      <c r="Y38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 15600-2025 georefererad karta.tif", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="AA37">
+      <c r="AA38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 15600-2025 FSC-klagomål.docx", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="AB37">
+      <c r="AB38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 15600-2025 FSC-klagomål mail.docx", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="AC37">
+      <c r="AC38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 15600-2025 tillsynsbegäran.docx", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="AD37">
+      <c r="AD38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 15600-2025 tillsynsbegäran mail.docx", "A 15600-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>A 29360-2026</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D38" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="E38" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I38" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J38" t="n">
-        <v>1</v>
-      </c>
-      <c r="K38" t="n">
-        <v>1</v>
-      </c>
-      <c r="L38" t="n">
-        <v>1</v>
-      </c>
-      <c r="M38" t="n">
-        <v>1</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>2</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1</v>
-      </c>
-      <c r="S38" t="n">
-        <v>3</v>
-      </c>
-      <c r="T38" t="n">
-        <v>3</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1</v>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t>Mindre blåvinge
-Silversmygare
-Ekoxe</t>
-        </is>
-      </c>
-      <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 29360-2026 artfynd.xlsx", "A 29360-2026")</f>
-        <v/>
-      </c>
-      <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 29360-2026 karta.png", "A 29360-2026")</f>
-        <v/>
-      </c>
-      <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 29360-2026 georefererad karta.tif", "A 29360-2026")</f>
-        <v/>
-      </c>
-      <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 29360-2026 FSC-klagomål.docx", "A 29360-2026")</f>
-        <v/>
-      </c>
-      <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 29360-2026 FSC-klagomål mail.docx", "A 29360-2026")</f>
-        <v/>
-      </c>
-      <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 29360-2026 tillsynsbegäran.docx", "A 29360-2026")</f>
-        <v/>
-      </c>
-      <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 29360-2026 tillsynsbegäran mail.docx", "A 29360-2026")</f>
         <v/>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
         <v>44470</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 72167-2021</t>
+          <t>A 62231-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5143,14 +5143,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44544</v>
+        <v>45267</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J40" t="n">
         <v>1</v>
@@ -5204,46 +5204,42 @@
       <c r="V40" s="2" t="inlineStr">
         <is>
           <t>Murgröna
-Röd glada</t>
+Blåsippa</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 72167-2021 artfynd.xlsx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62231-2023 artfynd.xlsx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 72167-2021 karta.png", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62231-2023 karta.png", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 72167-2021 georefererad karta.tif", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62231-2023 georefererad karta.tif", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 72167-2021 FSC-klagomål.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62231-2023 FSC-klagomål.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 72167-2021 FSC-klagomål mail.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62231-2023 FSC-klagomål mail.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 72167-2021 tillsynsbegäran.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62231-2023 tillsynsbegäran.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 72167-2021 tillsynsbegäran mail.docx", "A 72167-2021")</f>
-        <v/>
-      </c>
-      <c r="AE40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 72167-2021 prioriterade fågelarter.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62231-2023 tillsynsbegäran mail.docx", "A 62231-2023")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 62231-2023</t>
+          <t>A 72167-2021</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5253,14 +5249,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45267</v>
+        <v>44544</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5273,7 +5269,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J41" t="n">
         <v>1</v>
@@ -5314,35 +5310,39 @@
       <c r="V41" s="2" t="inlineStr">
         <is>
           <t>Murgröna
-Blåsippa</t>
+Röd glada</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62231-2023 artfynd.xlsx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 72167-2021 artfynd.xlsx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62231-2023 karta.png", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 72167-2021 karta.png", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62231-2023 georefererad karta.tif", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 72167-2021 georefererad karta.tif", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62231-2023 FSC-klagomål.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 72167-2021 FSC-klagomål.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62231-2023 FSC-klagomål mail.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 72167-2021 FSC-klagomål mail.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62231-2023 tillsynsbegäran.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 72167-2021 tillsynsbegäran.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62231-2023 tillsynsbegäran mail.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 72167-2021 tillsynsbegäran mail.docx", "A 72167-2021")</f>
+        <v/>
+      </c>
+      <c r="AE41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 72167-2021 prioriterade fågelarter.docx", "A 72167-2021")</f>
         <v/>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
         <v>46246</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>45385</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>45005</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 30492-2026</t>
+          <t>A 62183-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5675,14 +5675,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46210</v>
+        <v>46006</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5735,42 +5735,42 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 30492-2026 artfynd.xlsx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62183-2025 artfynd.xlsx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 30492-2026 karta.png", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62183-2025 karta.png", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 30492-2026 georefererad karta.tif", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62183-2025 georefererad karta.tif", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 30492-2026 FSC-klagomål.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62183-2025 FSC-klagomål.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 30492-2026 FSC-klagomål mail.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62183-2025 FSC-klagomål mail.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 30492-2026 tillsynsbegäran.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62183-2025 tillsynsbegäran.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 30492-2026 tillsynsbegäran mail.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62183-2025 tillsynsbegäran mail.docx", "A 62183-2025")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 62183-2025</t>
+          <t>A 30492-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5780,14 +5780,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46006</v>
+        <v>46210</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5840,35 +5840,35 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62183-2025 artfynd.xlsx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 30492-2026 artfynd.xlsx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62183-2025 karta.png", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 30492-2026 karta.png", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62183-2025 georefererad karta.tif", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 30492-2026 georefererad karta.tif", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62183-2025 FSC-klagomål.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 30492-2026 FSC-klagomål.docx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62183-2025 FSC-klagomål mail.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 30492-2026 FSC-klagomål mail.docx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62183-2025 tillsynsbegäran.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 30492-2026 tillsynsbegäran.docx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62183-2025 tillsynsbegäran mail.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 30492-2026 tillsynsbegäran mail.docx", "A 30492-2026")</f>
         <v/>
       </c>
     </row>
@@ -5892,7 +5892,7 @@
         <v>46273</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>45084</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>44740</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>45980</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>46171</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>

--- a/Översikt MÖRBYLÅNGA.xlsx
+++ b/Översikt MÖRBYLÅNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44964</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>44655</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>45177</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45096</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45685</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>45475</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>45062</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>46195</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>46189</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>45254</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>45062</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>44508</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>44467</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>44811</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>45097</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>44728</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>45999</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>45551</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>44616</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>45000</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>45530</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>45223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>45075</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>45169</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>45912</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>45912</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>46190</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>46003</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>46038</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         <v>45616</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>45049</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>46183</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>46254</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4616,7 +4616,7 @@
         <v>44460</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>45912</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         <v>46203</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>45747</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5044,7 +5044,7 @@
         <v>44470</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         <v>45267</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
         <v>44544</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         <v>46246</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>45385</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>45005</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         <v>46006</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>46210</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         <v>46273</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>45084</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>44740</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>45980</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>46171</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>

--- a/Översikt MÖRBYLÅNGA.xlsx
+++ b/Översikt MÖRBYLÅNGA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE51"/>
+  <dimension ref="A1:AE50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44964</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>44655</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>45177</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45096</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45685</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>45475</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>45062</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>46195</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>46189</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>45254</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>45062</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>44508</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>44467</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>44811</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>45097</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 24778-2022</t>
+          <t>A 60875-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2583,10 +2583,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44728</v>
+        <v>45999</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2599,45 +2599,164 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>5</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>7</v>
+      </c>
+      <c r="R17" t="n">
         <v>2</v>
-      </c>
-      <c r="L17" t="n">
-        <v>7</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>8</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>11</v>
       </c>
       <c r="T17" t="n">
+        <v>12</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Järnek
+Mosippa
+Grönsångare
+Gulsparv
+Göktyta
+Mindre hackspett
+Svinrot
+Murgröna
+Spillkråka
+Kråka
+Skogsduva</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 60875-2025 artfynd.xlsx", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 60875-2025 karta.png", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 60875-2025 georefererad karta.tif", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 60875-2025 FSC-klagomål.docx", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 60875-2025 FSC-klagomål mail.docx", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 60875-2025 tillsynsbegäran.docx", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 60875-2025 tillsynsbegäran mail.docx", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 60875-2025 prioriterade fågelarter.docx", "A 60875-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 24778-2022</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>44728</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" t="n">
+        <v>7</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>8</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>11</v>
+      </c>
+      <c r="T18" t="n">
         <v>20</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U18" t="n">
         <v>20</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Tofsäxing
 Backtimjan
@@ -2652,151 +2771,32 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24778-2022 artfynd.xlsx", "A 24778-2022")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24778-2022 karta.png", "A 24778-2022")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24778-2022 georefererad karta.tif", "A 24778-2022")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24778-2022 FSC-klagomål.docx", "A 24778-2022")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24778-2022 FSC-klagomål mail.docx", "A 24778-2022")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24778-2022 tillsynsbegäran.docx", "A 24778-2022")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24778-2022 tillsynsbegäran mail.docx", "A 24778-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 60875-2025</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45999</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J18" t="n">
-        <v>8</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>5</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>7</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2</v>
-      </c>
-      <c r="S18" t="n">
-        <v>11</v>
-      </c>
-      <c r="T18" t="n">
-        <v>12</v>
-      </c>
-      <c r="U18" t="n">
-        <v>3</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Järnek
-Mosippa
-Grönsångare
-Gulsparv
-Göktyta
-Mindre hackspett
-Svinrot
-Murgröna
-Spillkråka
-Kråka
-Skogsduva</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 60875-2025 artfynd.xlsx", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 60875-2025 karta.png", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 60875-2025 georefererad karta.tif", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 60875-2025 FSC-klagomål.docx", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 60875-2025 FSC-klagomål mail.docx", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 60875-2025 tillsynsbegäran.docx", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 60875-2025 tillsynsbegäran mail.docx", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 60875-2025 prioriterade fågelarter.docx", "A 60875-2025")</f>
         <v/>
       </c>
     </row>
@@ -2820,7 +2820,7 @@
         <v>45551</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>44616</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>45000</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>45530</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>45223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>45075</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>45169</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>45912</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>45912</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>46190</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>46003</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>46038</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         <v>45616</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>45049</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>46183</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>46254</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 51244-2021</t>
+          <t>A 43702-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4609,14 +4609,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44460</v>
+        <v>45912</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4629,19 +4629,19 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -4653,60 +4653,60 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>3</v>
       </c>
       <c r="T35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Stäppbandbi
-Vittåtel
-Älg</t>
+          <t>Sårläka
+Murgröna
+Tibast</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 51244-2021 artfynd.xlsx", "A 51244-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43702-2025 artfynd.xlsx", "A 43702-2025")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 51244-2021 karta.png", "A 51244-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43702-2025 karta.png", "A 43702-2025")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 51244-2021 georefererad karta.tif", "A 51244-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43702-2025 georefererad karta.tif", "A 43702-2025")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 51244-2021 FSC-klagomål.docx", "A 51244-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43702-2025 FSC-klagomål.docx", "A 43702-2025")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 51244-2021 FSC-klagomål mail.docx", "A 51244-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43702-2025 FSC-klagomål mail.docx", "A 43702-2025")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 51244-2021 tillsynsbegäran.docx", "A 51244-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43702-2025 tillsynsbegäran.docx", "A 43702-2025")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 51244-2021 tillsynsbegäran mail.docx", "A 51244-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43702-2025 tillsynsbegäran mail.docx", "A 43702-2025")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 43702-2025</t>
+          <t>A 29360-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4716,14 +4716,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45912</v>
+        <v>46203</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4736,34 +4736,34 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
+        <v>1</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
         <v>2</v>
       </c>
-      <c r="L36" t="n">
-        <v>1</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>1</v>
-      </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S36" t="n">
         <v>3</v>
@@ -4772,48 +4772,48 @@
         <v>3</v>
       </c>
       <c r="U36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Sårläka
-Murgröna
-Tibast</t>
+          <t>Mindre blåvinge
+Silversmygare
+Ekoxe</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43702-2025 artfynd.xlsx", "A 43702-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 29360-2026 artfynd.xlsx", "A 29360-2026")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43702-2025 karta.png", "A 43702-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 29360-2026 karta.png", "A 29360-2026")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43702-2025 georefererad karta.tif", "A 43702-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 29360-2026 georefererad karta.tif", "A 29360-2026")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43702-2025 FSC-klagomål.docx", "A 43702-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 29360-2026 FSC-klagomål.docx", "A 29360-2026")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43702-2025 FSC-klagomål mail.docx", "A 43702-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 29360-2026 FSC-klagomål mail.docx", "A 29360-2026")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43702-2025 tillsynsbegäran.docx", "A 43702-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 29360-2026 tillsynsbegäran.docx", "A 29360-2026")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43702-2025 tillsynsbegäran mail.docx", "A 43702-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 29360-2026 tillsynsbegäran mail.docx", "A 29360-2026")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 29360-2026</t>
+          <t>A 15600-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4827,10 +4827,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46203</v>
+        <v>45747</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4843,19 +4843,19 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -4867,10 +4867,10 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>3</v>
@@ -4883,44 +4883,44 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Mindre blåvinge
-Silversmygare
-Ekoxe</t>
+          <t>Kragjordstjärna
+Murgröna
+Scharlakansvårskål agg.</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 29360-2026 artfynd.xlsx", "A 29360-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 15600-2025 artfynd.xlsx", "A 15600-2025")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 29360-2026 karta.png", "A 29360-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 15600-2025 karta.png", "A 15600-2025")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 29360-2026 georefererad karta.tif", "A 29360-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 15600-2025 georefererad karta.tif", "A 15600-2025")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 29360-2026 FSC-klagomål.docx", "A 29360-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 15600-2025 FSC-klagomål.docx", "A 15600-2025")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 29360-2026 FSC-klagomål mail.docx", "A 29360-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 15600-2025 FSC-klagomål mail.docx", "A 15600-2025")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 29360-2026 tillsynsbegäran.docx", "A 29360-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 15600-2025 tillsynsbegäran.docx", "A 15600-2025")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 29360-2026 tillsynsbegäran mail.docx", "A 29360-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 15600-2025 tillsynsbegäran mail.docx", "A 15600-2025")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 15600-2025</t>
+          <t>A 54192-2021</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4930,14 +4930,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45747</v>
+        <v>44470</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4950,16 +4950,16 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -4974,60 +4974,59 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Kragjordstjärna
-Murgröna
-Scharlakansvårskål agg.</t>
+          <t>Ladusvala
+Sminkrot</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 15600-2025 artfynd.xlsx", "A 15600-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 54192-2021 artfynd.xlsx", "A 54192-2021")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 15600-2025 karta.png", "A 15600-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 54192-2021 karta.png", "A 54192-2021")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 15600-2025 georefererad karta.tif", "A 15600-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 54192-2021 georefererad karta.tif", "A 54192-2021")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 15600-2025 FSC-klagomål.docx", "A 15600-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 54192-2021 FSC-klagomål.docx", "A 54192-2021")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 15600-2025 FSC-klagomål mail.docx", "A 15600-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 54192-2021 FSC-klagomål mail.docx", "A 54192-2021")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 15600-2025 tillsynsbegäran.docx", "A 15600-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 54192-2021 tillsynsbegäran.docx", "A 54192-2021")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 15600-2025 tillsynsbegäran mail.docx", "A 15600-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 54192-2021 tillsynsbegäran mail.docx", "A 54192-2021")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 54192-2021</t>
+          <t>A 62231-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5037,14 +5036,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44470</v>
+        <v>45267</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5057,16 +5056,16 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J39" t="n">
         <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -5081,7 +5080,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -5097,43 +5096,43 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Ladusvala
-Sminkrot</t>
+          <t>Murgröna
+Blåsippa</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 54192-2021 artfynd.xlsx", "A 54192-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62231-2023 artfynd.xlsx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 54192-2021 karta.png", "A 54192-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62231-2023 karta.png", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 54192-2021 georefererad karta.tif", "A 54192-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62231-2023 georefererad karta.tif", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 54192-2021 FSC-klagomål.docx", "A 54192-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62231-2023 FSC-klagomål.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 54192-2021 FSC-klagomål mail.docx", "A 54192-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62231-2023 FSC-klagomål mail.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 54192-2021 tillsynsbegäran.docx", "A 54192-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62231-2023 tillsynsbegäran.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 54192-2021 tillsynsbegäran mail.docx", "A 54192-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62231-2023 tillsynsbegäran mail.docx", "A 62231-2023")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 62231-2023</t>
+          <t>A 72167-2021</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5143,14 +5142,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45267</v>
+        <v>44544</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5163,7 +5162,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J40" t="n">
         <v>1</v>
@@ -5204,59 +5203,63 @@
       <c r="V40" s="2" t="inlineStr">
         <is>
           <t>Murgröna
-Blåsippa</t>
+Röd glada</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62231-2023 artfynd.xlsx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 72167-2021 artfynd.xlsx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62231-2023 karta.png", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 72167-2021 karta.png", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62231-2023 georefererad karta.tif", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 72167-2021 georefererad karta.tif", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62231-2023 FSC-klagomål.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 72167-2021 FSC-klagomål.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62231-2023 FSC-klagomål mail.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 72167-2021 FSC-klagomål mail.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62231-2023 tillsynsbegäran.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 72167-2021 tillsynsbegäran.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62231-2023 tillsynsbegäran mail.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 72167-2021 tillsynsbegäran mail.docx", "A 72167-2021")</f>
+        <v/>
+      </c>
+      <c r="AE40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 72167-2021 prioriterade fågelarter.docx", "A 72167-2021")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 72167-2021</t>
+          <t>S 2138-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44544</v>
+        <v>46246</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5269,7 +5272,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.5</v>
+        <v>5.4</v>
       </c>
       <c r="J41" t="n">
         <v>1</v>
@@ -5284,7 +5287,7 @@
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5293,10 +5296,10 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S41" t="n">
         <v>2</v>
@@ -5305,68 +5308,64 @@
         <v>2</v>
       </c>
       <c r="U41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Murgröna
-Röd glada</t>
+          <t>Ask
+Ekoxe</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 72167-2021 artfynd.xlsx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/S 2138-2026 artfynd.xlsx", "S 2138-2026")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 72167-2021 karta.png", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/S 2138-2026 karta.png", "S 2138-2026")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 72167-2021 georefererad karta.tif", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/S 2138-2026 georefererad karta.tif", "S 2138-2026")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 72167-2021 FSC-klagomål.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/S 2138-2026 FSC-klagomål.docx", "S 2138-2026")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 72167-2021 FSC-klagomål mail.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/S 2138-2026 FSC-klagomål mail.docx", "S 2138-2026")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 72167-2021 tillsynsbegäran.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/S 2138-2026 tillsynsbegäran.docx", "S 2138-2026")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 72167-2021 tillsynsbegäran mail.docx", "A 72167-2021")</f>
-        <v/>
-      </c>
-      <c r="AE41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 72167-2021 prioriterade fågelarter.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/S 2138-2026 tillsynsbegäran mail.docx", "S 2138-2026")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S 2138-2026</t>
+          <t>A 62183-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46246</v>
+        <v>46006</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5379,22 +5378,22 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>5.4</v>
+        <v>0.8</v>
       </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5406,49 +5405,48 @@
         <v>1</v>
       </c>
       <c r="R42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Ask
-Ekoxe</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/S 2138-2026 artfynd.xlsx", "S 2138-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62183-2025 artfynd.xlsx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/S 2138-2026 karta.png", "S 2138-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62183-2025 karta.png", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/S 2138-2026 georefererad karta.tif", "S 2138-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62183-2025 georefererad karta.tif", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/S 2138-2026 FSC-klagomål.docx", "S 2138-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62183-2025 FSC-klagomål.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/S 2138-2026 FSC-klagomål mail.docx", "S 2138-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62183-2025 FSC-klagomål mail.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/S 2138-2026 tillsynsbegäran.docx", "S 2138-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62183-2025 tillsynsbegäran.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/S 2138-2026 tillsynsbegäran mail.docx", "S 2138-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62183-2025 tillsynsbegäran mail.docx", "A 62183-2025")</f>
         <v/>
       </c>
     </row>
@@ -5472,7 +5470,7 @@
         <v>45385</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5577,7 +5575,7 @@
         <v>45005</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5665,7 +5663,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 62183-2025</t>
+          <t>A 30492-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5675,14 +5673,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46006</v>
+        <v>46210</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5695,7 +5693,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5735,42 +5733,42 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62183-2025 artfynd.xlsx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 30492-2026 artfynd.xlsx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62183-2025 karta.png", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 30492-2026 karta.png", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62183-2025 georefererad karta.tif", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 30492-2026 georefererad karta.tif", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62183-2025 FSC-klagomål.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 30492-2026 FSC-klagomål.docx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62183-2025 FSC-klagomål mail.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 30492-2026 FSC-klagomål mail.docx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62183-2025 tillsynsbegäran.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 30492-2026 tillsynsbegäran.docx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62183-2025 tillsynsbegäran mail.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 30492-2026 tillsynsbegäran mail.docx", "A 30492-2026")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 30492-2026</t>
+          <t>A 36928-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5780,14 +5778,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46210</v>
+        <v>46273</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5800,16 +5798,16 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -5824,7 +5822,7 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -5840,42 +5838,42 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 30492-2026 artfynd.xlsx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 36928-2026 artfynd.xlsx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 30492-2026 karta.png", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 36928-2026 karta.png", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 30492-2026 georefererad karta.tif", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 36928-2026 georefererad karta.tif", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 30492-2026 FSC-klagomål.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 36928-2026 FSC-klagomål.docx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 30492-2026 FSC-klagomål mail.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 36928-2026 FSC-klagomål mail.docx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 30492-2026 tillsynsbegäran.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 36928-2026 tillsynsbegäran.docx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 30492-2026 tillsynsbegäran mail.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 36928-2026 tillsynsbegäran mail.docx", "A 36928-2026")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 36928-2026</t>
+          <t>A 24698-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5889,10 +5887,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46273</v>
+        <v>45084</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5905,16 +5903,16 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.3</v>
+        <v>5.5</v>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -5929,7 +5927,7 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
@@ -5941,46 +5939,46 @@
         <v>1</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 36928-2026 artfynd.xlsx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24698-2023 artfynd.xlsx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 36928-2026 karta.png", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24698-2023 karta.png", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 36928-2026 georefererad karta.tif", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24698-2023 georefererad karta.tif", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 36928-2026 FSC-klagomål.docx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24698-2023 FSC-klagomål.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 36928-2026 FSC-klagomål mail.docx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24698-2023 FSC-klagomål mail.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 36928-2026 tillsynsbegäran.docx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24698-2023 tillsynsbegäran.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 36928-2026 tillsynsbegäran mail.docx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24698-2023 tillsynsbegäran mail.docx", "A 24698-2023")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 24698-2023</t>
+          <t>A 26876-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5990,14 +5988,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45084</v>
+        <v>44740</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6010,7 +6008,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>5.5</v>
+        <v>0.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -6019,7 +6017,7 @@
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -6034,58 +6032,26 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>1</v>
-      </c>
-      <c r="V48" s="2" t="inlineStr">
-        <is>
-          <t>Sårläka</t>
-        </is>
-      </c>
-      <c r="W48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24698-2023 artfynd.xlsx", "A 24698-2023")</f>
-        <v/>
-      </c>
-      <c r="X48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24698-2023 karta.png", "A 24698-2023")</f>
-        <v/>
-      </c>
-      <c r="Y48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24698-2023 georefererad karta.tif", "A 24698-2023")</f>
-        <v/>
-      </c>
-      <c r="AA48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24698-2023 FSC-klagomål.docx", "A 24698-2023")</f>
-        <v/>
-      </c>
-      <c r="AB48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24698-2023 FSC-klagomål mail.docx", "A 24698-2023")</f>
-        <v/>
-      </c>
-      <c r="AC48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24698-2023 tillsynsbegäran.docx", "A 24698-2023")</f>
-        <v/>
-      </c>
-      <c r="AD48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24698-2023 tillsynsbegäran mail.docx", "A 24698-2023")</f>
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V48" s="2" t="inlineStr"/>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 26876-2022</t>
+          <t>A 57407-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6095,14 +6061,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44740</v>
+        <v>45980</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6115,7 +6081,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -6155,27 +6121,27 @@
       </c>
       <c r="V49" s="2" t="inlineStr"/>
     </row>
-    <row r="50" ht="15" customHeight="1">
+    <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 57407-2025</t>
+          <t>S 1602-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45980</v>
+        <v>46171</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6188,7 +6154,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -6227,79 +6193,6 @@
         <v>0</v>
       </c>
       <c r="V50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>S 1602-2026</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D51" s="1" t="n">
-        <v>46171</v>
-      </c>
-      <c r="E51" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I51" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt MÖRBYLÅNGA.xlsx
+++ b/Översikt MÖRBYLÅNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44964</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>44655</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>45177</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45096</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45685</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>45475</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>45062</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>46195</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>46189</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>45254</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>45062</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>44508</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>44467</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 38039-2022</t>
+          <t>A 60875-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2349,14 +2349,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44811</v>
+        <v>45999</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2369,31 +2369,31 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>7.4</v>
+        <v>2.1</v>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R15" t="n">
         <v>2</v>
@@ -2402,12 +2402,246 @@
         <v>11</v>
       </c>
       <c r="T15" t="n">
+        <v>12</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Järnek
+Mosippa
+Grönsångare
+Gulsparv
+Göktyta
+Mindre hackspett
+Svinrot
+Murgröna
+Spillkråka
+Kråka
+Skogsduva</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 60875-2025 artfynd.xlsx", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 60875-2025 karta.png", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 60875-2025 georefererad karta.tif", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 60875-2025 FSC-klagomål.docx", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 60875-2025 FSC-klagomål mail.docx", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 60875-2025 tillsynsbegäran.docx", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 60875-2025 tillsynsbegäran mail.docx", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 60875-2025 prioriterade fågelarter.docx", "A 60875-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 24778-2022</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>44728</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>7</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>8</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>11</v>
+      </c>
+      <c r="T16" t="n">
+        <v>20</v>
+      </c>
+      <c r="U16" t="n">
+        <v>20</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Tofsäxing
+Backtimjan
+Flentimotej
+Grådådra
+Poppeltofsskivling
+Slåtterfibbla
+Sminkrot
+Solvända
+Kalktallört
+Murgröna
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24778-2022 artfynd.xlsx", "A 24778-2022")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24778-2022 karta.png", "A 24778-2022")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24778-2022 georefererad karta.tif", "A 24778-2022")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24778-2022 FSC-klagomål.docx", "A 24778-2022")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24778-2022 FSC-klagomål mail.docx", "A 24778-2022")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24778-2022 tillsynsbegäran.docx", "A 24778-2022")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24778-2022 tillsynsbegäran mail.docx", "A 24778-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 38039-2022</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>44811</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>4</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>6</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2</v>
+      </c>
+      <c r="S17" t="n">
+        <v>11</v>
+      </c>
+      <c r="T17" t="n">
         <v>13</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U17" t="n">
         <v>12</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Ask
 Grov gulmossa
@@ -2422,107 +2656,107 @@
 Gullviva</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 38039-2022 artfynd.xlsx", "A 38039-2022")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 38039-2022 karta.png", "A 38039-2022")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 38039-2022 georefererad karta.tif", "A 38039-2022")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 38039-2022 FSC-klagomål.docx", "A 38039-2022")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 38039-2022 FSC-klagomål mail.docx", "A 38039-2022")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 38039-2022 tillsynsbegäran.docx", "A 38039-2022")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 38039-2022 tillsynsbegäran mail.docx", "A 38039-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>A 27636-2023</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D16" s="1" t="n">
+      <c r="D18" s="1" t="n">
         <v>45097</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="E18" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I16" t="n">
+      <c r="I18" t="n">
         <v>7.4</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J18" t="n">
         <v>4</v>
       </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
         <v>4</v>
       </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
         <v>6</v>
       </c>
-      <c r="R16" t="n">
+      <c r="R18" t="n">
         <v>2</v>
       </c>
-      <c r="S16" t="n">
+      <c r="S18" t="n">
         <v>11</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T18" t="n">
         <v>13</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U18" t="n">
         <v>11</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Ask
 Grov gulmossa
@@ -2537,266 +2771,32 @@
 Gullviva</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 27636-2023 artfynd.xlsx", "A 27636-2023")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 27636-2023 karta.png", "A 27636-2023")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 27636-2023 georefererad karta.tif", "A 27636-2023")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 27636-2023 FSC-klagomål.docx", "A 27636-2023")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 27636-2023 FSC-klagomål mail.docx", "A 27636-2023")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 27636-2023 tillsynsbegäran.docx", "A 27636-2023")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 27636-2023 tillsynsbegäran mail.docx", "A 27636-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 60875-2025</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45999</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J17" t="n">
-        <v>8</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>5</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>7</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2</v>
-      </c>
-      <c r="S17" t="n">
-        <v>11</v>
-      </c>
-      <c r="T17" t="n">
-        <v>12</v>
-      </c>
-      <c r="U17" t="n">
-        <v>3</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Järnek
-Mosippa
-Grönsångare
-Gulsparv
-Göktyta
-Mindre hackspett
-Svinrot
-Murgröna
-Spillkråka
-Kråka
-Skogsduva</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 60875-2025 artfynd.xlsx", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 60875-2025 karta.png", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 60875-2025 georefererad karta.tif", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 60875-2025 FSC-klagomål.docx", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 60875-2025 FSC-klagomål mail.docx", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 60875-2025 tillsynsbegäran.docx", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 60875-2025 tillsynsbegäran mail.docx", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 60875-2025 prioriterade fågelarter.docx", "A 60875-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 24778-2022</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>44728</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2</v>
-      </c>
-      <c r="L18" t="n">
-        <v>7</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>8</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1</v>
-      </c>
-      <c r="S18" t="n">
-        <v>11</v>
-      </c>
-      <c r="T18" t="n">
-        <v>20</v>
-      </c>
-      <c r="U18" t="n">
-        <v>20</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Tofsäxing
-Backtimjan
-Flentimotej
-Grådådra
-Poppeltofsskivling
-Slåtterfibbla
-Sminkrot
-Solvända
-Kalktallört
-Murgröna
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24778-2022 artfynd.xlsx", "A 24778-2022")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24778-2022 karta.png", "A 24778-2022")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24778-2022 georefererad karta.tif", "A 24778-2022")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24778-2022 FSC-klagomål.docx", "A 24778-2022")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24778-2022 FSC-klagomål mail.docx", "A 24778-2022")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24778-2022 tillsynsbegäran.docx", "A 24778-2022")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24778-2022 tillsynsbegäran mail.docx", "A 24778-2022")</f>
         <v/>
       </c>
     </row>
@@ -2820,7 +2820,7 @@
         <v>45551</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>44616</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>45000</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>45530</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>45223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>45075</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>45169</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 43704-2025</t>
+          <t>A 43714-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3620,7 +3620,7 @@
         <v>45912</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3633,19 +3633,19 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.7</v>
+        <v>7.9</v>
       </c>
       <c r="J26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -3657,21 +3657,135 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S26" t="n">
         <v>6</v>
       </c>
       <c r="T26" t="n">
+        <v>8</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Mindre bastardsvärmare
+Sexfläckig bastardsvärmare
+Grönsångare
+Murgröna
+Tibast
+Trädporella</t>
+        </is>
+      </c>
+      <c r="W26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43714-2025 artfynd.xlsx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="X26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43714-2025 karta.png", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="Y26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43714-2025 georefererad karta.tif", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AA26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43714-2025 FSC-klagomål.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AB26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43714-2025 FSC-klagomål mail.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AC26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43714-2025 tillsynsbegäran.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AD26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43714-2025 tillsynsbegäran mail.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 43714-2025 prioriterade fågelarter.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 43704-2025</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>45912</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J27" t="n">
+        <v>5</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
         <v>6</v>
       </c>
-      <c r="U26" t="n">
-        <v>1</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="T27" t="n">
+        <v>6</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>Blomkålssvamp
 Långbensgroda
@@ -3681,146 +3795,32 @@
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W26">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43704-2025 artfynd.xlsx", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="X26">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43704-2025 karta.png", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="Y26">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43704-2025 georefererad karta.tif", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="AA26">
+      <c r="AA27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43704-2025 FSC-klagomål.docx", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="AB26">
+      <c r="AB27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43704-2025 FSC-klagomål mail.docx", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="AC26">
+      <c r="AC27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43704-2025 tillsynsbegäran.docx", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="AD26">
+      <c r="AD27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43704-2025 tillsynsbegäran mail.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 43714-2025</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>45912</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="J27" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>3</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1</v>
-      </c>
-      <c r="M27" t="n">
-        <v>2</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>3</v>
-      </c>
-      <c r="R27" t="n">
-        <v>2</v>
-      </c>
-      <c r="S27" t="n">
-        <v>6</v>
-      </c>
-      <c r="T27" t="n">
-        <v>8</v>
-      </c>
-      <c r="U27" t="n">
-        <v>2</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Mindre bastardsvärmare
-Sexfläckig bastardsvärmare
-Grönsångare
-Murgröna
-Tibast
-Trädporella</t>
-        </is>
-      </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43714-2025 artfynd.xlsx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43714-2025 karta.png", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43714-2025 georefererad karta.tif", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43714-2025 FSC-klagomål.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43714-2025 FSC-klagomål mail.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43714-2025 tillsynsbegäran.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43714-2025 tillsynsbegäran mail.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 43714-2025 prioriterade fågelarter.docx", "A 43714-2025")</f>
         <v/>
       </c>
     </row>
@@ -3844,7 +3844,7 @@
         <v>46190</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>46003</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>46038</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         <v>45616</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>45049</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>46183</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>46254</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 43702-2025</t>
+          <t>A 15600-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4609,14 +4609,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45912</v>
+        <v>45747</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4629,16 +4629,16 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -4653,7 +4653,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -4665,255 +4665,255 @@
         <v>3</v>
       </c>
       <c r="U35" t="n">
+        <v>1</v>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>Kragjordstjärna
+Murgröna
+Scharlakansvårskål agg.</t>
+        </is>
+      </c>
+      <c r="W35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 15600-2025 artfynd.xlsx", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="X35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 15600-2025 karta.png", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="Y35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 15600-2025 georefererad karta.tif", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="AA35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 15600-2025 FSC-klagomål.docx", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="AB35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 15600-2025 FSC-klagomål mail.docx", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="AC35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 15600-2025 tillsynsbegäran.docx", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="AD35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 15600-2025 tillsynsbegäran mail.docx", "A 15600-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>A 43702-2025</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D36" s="1" t="n">
+        <v>45912</v>
+      </c>
+      <c r="E36" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
         <v>2</v>
       </c>
-      <c r="V35" s="2" t="inlineStr">
+      <c r="L36" t="n">
+        <v>1</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
         <is>
           <t>Sårläka
 Murgröna
 Tibast</t>
         </is>
       </c>
-      <c r="W35">
+      <c r="W36">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43702-2025 artfynd.xlsx", "A 43702-2025")</f>
         <v/>
       </c>
-      <c r="X35">
+      <c r="X36">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43702-2025 karta.png", "A 43702-2025")</f>
         <v/>
       </c>
-      <c r="Y35">
+      <c r="Y36">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43702-2025 georefererad karta.tif", "A 43702-2025")</f>
         <v/>
       </c>
-      <c r="AA35">
+      <c r="AA36">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43702-2025 FSC-klagomål.docx", "A 43702-2025")</f>
         <v/>
       </c>
-      <c r="AB35">
+      <c r="AB36">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43702-2025 FSC-klagomål mail.docx", "A 43702-2025")</f>
         <v/>
       </c>
-      <c r="AC35">
+      <c r="AC36">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43702-2025 tillsynsbegäran.docx", "A 43702-2025")</f>
         <v/>
       </c>
-      <c r="AD35">
+      <c r="AD36">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43702-2025 tillsynsbegäran mail.docx", "A 43702-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>A 29360-2026</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D36" s="1" t="n">
+      <c r="D37" s="1" t="n">
         <v>46203</v>
       </c>
-      <c r="E36" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F36" t="inlineStr">
+      <c r="E37" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I36" t="n">
+      <c r="I37" t="n">
         <v>2.9</v>
       </c>
-      <c r="J36" t="n">
-        <v>1</v>
-      </c>
-      <c r="K36" t="n">
-        <v>1</v>
-      </c>
-      <c r="L36" t="n">
-        <v>1</v>
-      </c>
-      <c r="M36" t="n">
-        <v>1</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
+      <c r="J37" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
         <v>2</v>
       </c>
-      <c r="R36" t="n">
-        <v>1</v>
-      </c>
-      <c r="S36" t="n">
+      <c r="R37" t="n">
+        <v>1</v>
+      </c>
+      <c r="S37" t="n">
         <v>3</v>
       </c>
-      <c r="T36" t="n">
+      <c r="T37" t="n">
         <v>3</v>
       </c>
-      <c r="U36" t="n">
-        <v>1</v>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
+      <c r="U37" t="n">
+        <v>1</v>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
         <is>
           <t>Mindre blåvinge
 Silversmygare
 Ekoxe</t>
         </is>
       </c>
-      <c r="W36">
+      <c r="W37">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 29360-2026 artfynd.xlsx", "A 29360-2026")</f>
         <v/>
       </c>
-      <c r="X36">
+      <c r="X37">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 29360-2026 karta.png", "A 29360-2026")</f>
         <v/>
       </c>
-      <c r="Y36">
+      <c r="Y37">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 29360-2026 georefererad karta.tif", "A 29360-2026")</f>
         <v/>
       </c>
-      <c r="AA36">
+      <c r="AA37">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 29360-2026 FSC-klagomål.docx", "A 29360-2026")</f>
         <v/>
       </c>
-      <c r="AB36">
+      <c r="AB37">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 29360-2026 FSC-klagomål mail.docx", "A 29360-2026")</f>
         <v/>
       </c>
-      <c r="AC36">
+      <c r="AC37">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 29360-2026 tillsynsbegäran.docx", "A 29360-2026")</f>
         <v/>
       </c>
-      <c r="AD36">
+      <c r="AD37">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 29360-2026 tillsynsbegäran mail.docx", "A 29360-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" ht="15" customHeight="1">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>A 15600-2025</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D37" s="1" t="n">
-        <v>45747</v>
-      </c>
-      <c r="E37" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="n">
-        <v>3</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="n">
-        <v>3</v>
-      </c>
-      <c r="T37" t="n">
-        <v>3</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1</v>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>Kragjordstjärna
-Murgröna
-Scharlakansvårskål agg.</t>
-        </is>
-      </c>
-      <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 15600-2025 artfynd.xlsx", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 15600-2025 karta.png", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 15600-2025 georefererad karta.tif", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 15600-2025 FSC-klagomål.docx", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 15600-2025 FSC-klagomål mail.docx", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 15600-2025 tillsynsbegäran.docx", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 15600-2025 tillsynsbegäran mail.docx", "A 15600-2025")</f>
         <v/>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
         <v>44470</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 62231-2023</t>
+          <t>A 72167-2021</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5036,14 +5036,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45267</v>
+        <v>44544</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J39" t="n">
         <v>1</v>
@@ -5097,42 +5097,46 @@
       <c r="V39" s="2" t="inlineStr">
         <is>
           <t>Murgröna
-Blåsippa</t>
+Röd glada</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62231-2023 artfynd.xlsx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 72167-2021 artfynd.xlsx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62231-2023 karta.png", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 72167-2021 karta.png", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62231-2023 georefererad karta.tif", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 72167-2021 georefererad karta.tif", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62231-2023 FSC-klagomål.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 72167-2021 FSC-klagomål.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62231-2023 FSC-klagomål mail.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 72167-2021 FSC-klagomål mail.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62231-2023 tillsynsbegäran.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 72167-2021 tillsynsbegäran.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62231-2023 tillsynsbegäran mail.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 72167-2021 tillsynsbegäran mail.docx", "A 72167-2021")</f>
+        <v/>
+      </c>
+      <c r="AE39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 72167-2021 prioriterade fågelarter.docx", "A 72167-2021")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 72167-2021</t>
+          <t>A 62231-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5142,14 +5146,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44544</v>
+        <v>45267</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5162,7 +5166,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J40" t="n">
         <v>1</v>
@@ -5203,39 +5207,35 @@
       <c r="V40" s="2" t="inlineStr">
         <is>
           <t>Murgröna
-Röd glada</t>
+Blåsippa</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 72167-2021 artfynd.xlsx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62231-2023 artfynd.xlsx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 72167-2021 karta.png", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62231-2023 karta.png", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 72167-2021 georefererad karta.tif", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62231-2023 georefererad karta.tif", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 72167-2021 FSC-klagomål.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62231-2023 FSC-klagomål.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 72167-2021 FSC-klagomål mail.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62231-2023 FSC-klagomål mail.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 72167-2021 tillsynsbegäran.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62231-2023 tillsynsbegäran.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 72167-2021 tillsynsbegäran mail.docx", "A 72167-2021")</f>
-        <v/>
-      </c>
-      <c r="AE40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 72167-2021 prioriterade fågelarter.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62231-2023 tillsynsbegäran mail.docx", "A 62231-2023")</f>
         <v/>
       </c>
     </row>
@@ -5259,7 +5259,7 @@
         <v>46246</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 62183-2025</t>
+          <t>A 13040-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5358,14 +5358,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46006</v>
+        <v>45385</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -5387,13 +5387,13 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5405,7 +5405,7 @@
         <v>1</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -5414,46 +5414,46 @@
         <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62183-2025 artfynd.xlsx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13040-2024 artfynd.xlsx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62183-2025 karta.png", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13040-2024 karta.png", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62183-2025 georefererad karta.tif", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13040-2024 georefererad karta.tif", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62183-2025 FSC-klagomål.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13040-2024 FSC-klagomål.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62183-2025 FSC-klagomål mail.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13040-2024 FSC-klagomål mail.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62183-2025 tillsynsbegäran.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13040-2024 tillsynsbegäran.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62183-2025 tillsynsbegäran mail.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13040-2024 tillsynsbegäran mail.docx", "A 13040-2024")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 13040-2024</t>
+          <t>A 24698-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5463,14 +5463,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45385</v>
+        <v>45084</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.2</v>
+        <v>5.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5492,13 +5492,13 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5510,7 +5510,7 @@
         <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5523,35 +5523,35 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13040-2024 artfynd.xlsx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24698-2023 artfynd.xlsx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13040-2024 karta.png", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24698-2023 karta.png", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13040-2024 georefererad karta.tif", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24698-2023 georefererad karta.tif", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13040-2024 FSC-klagomål.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24698-2023 FSC-klagomål.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13040-2024 FSC-klagomål mail.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24698-2023 FSC-klagomål mail.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13040-2024 tillsynsbegäran.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24698-2023 tillsynsbegäran.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13040-2024 tillsynsbegäran mail.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24698-2023 tillsynsbegäran mail.docx", "A 24698-2023")</f>
         <v/>
       </c>
     </row>
@@ -5575,7 +5575,7 @@
         <v>45005</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 30492-2026</t>
+          <t>A 62183-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5673,14 +5673,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46210</v>
+        <v>46006</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5733,42 +5733,42 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 30492-2026 artfynd.xlsx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62183-2025 artfynd.xlsx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 30492-2026 karta.png", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62183-2025 karta.png", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 30492-2026 georefererad karta.tif", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62183-2025 georefererad karta.tif", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 30492-2026 FSC-klagomål.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62183-2025 FSC-klagomål.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 30492-2026 FSC-klagomål mail.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62183-2025 FSC-klagomål mail.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 30492-2026 tillsynsbegäran.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62183-2025 tillsynsbegäran.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 30492-2026 tillsynsbegäran mail.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62183-2025 tillsynsbegäran mail.docx", "A 62183-2025")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 36928-2026</t>
+          <t>A 30492-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5778,14 +5778,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46273</v>
+        <v>46210</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5798,16 +5798,16 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -5822,7 +5822,7 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -5838,42 +5838,42 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 36928-2026 artfynd.xlsx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 30492-2026 artfynd.xlsx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 36928-2026 karta.png", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 30492-2026 karta.png", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 36928-2026 georefererad karta.tif", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 30492-2026 georefererad karta.tif", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 36928-2026 FSC-klagomål.docx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 30492-2026 FSC-klagomål.docx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 36928-2026 FSC-klagomål mail.docx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 30492-2026 FSC-klagomål mail.docx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 36928-2026 tillsynsbegäran.docx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 30492-2026 tillsynsbegäran.docx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 36928-2026 tillsynsbegäran mail.docx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 30492-2026 tillsynsbegäran mail.docx", "A 30492-2026")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 24698-2023</t>
+          <t>A 36928-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5887,10 +5887,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45084</v>
+        <v>46273</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5903,16 +5903,16 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>5.5</v>
+        <v>1.3</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -5927,7 +5927,7 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
@@ -5939,39 +5939,39 @@
         <v>1</v>
       </c>
       <c r="U47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24698-2023 artfynd.xlsx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 36928-2026 artfynd.xlsx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24698-2023 karta.png", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 36928-2026 karta.png", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24698-2023 georefererad karta.tif", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 36928-2026 georefererad karta.tif", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24698-2023 FSC-klagomål.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 36928-2026 FSC-klagomål.docx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24698-2023 FSC-klagomål mail.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 36928-2026 FSC-klagomål mail.docx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24698-2023 tillsynsbegäran.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 36928-2026 tillsynsbegäran.docx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24698-2023 tillsynsbegäran mail.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 36928-2026 tillsynsbegäran mail.docx", "A 36928-2026")</f>
         <v/>
       </c>
     </row>
@@ -5995,7 +5995,7 @@
         <v>44740</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>45980</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>46171</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>

--- a/Översikt MÖRBYLÅNGA.xlsx
+++ b/Översikt MÖRBYLÅNGA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE50"/>
+  <dimension ref="A1:AE51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44964</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>44655</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>45177</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45096</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45685</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1355,75 +1355,214 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
+          <t>A 39627-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>7</v>
+      </c>
+      <c r="J7" t="n">
+        <v>14</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L7" t="n">
+        <v>12</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>16</v>
+      </c>
+      <c r="R7" t="n">
+        <v>4</v>
+      </c>
+      <c r="S7" t="n">
+        <v>31</v>
+      </c>
+      <c r="T7" t="n">
+        <v>50</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Lundalm
+Skogsalm
+Toppjungfrulin
+Axveronika
+Backklöver
+Backtimjan
+Flentimotej
+Göktyta
+Jordtistel
+Jungfrulin
+Korskovall
+Solvända
+Sädesärla
+Sårläka
+Vårstarr
+Ekoxe
+Murgröna
+Skogsknipprot
+Strävlosta
+Blåsippa
+Skogsbingel
+Halsbandsflugsnappare
+Röd glada
+Huggorm
+Skogsödla
+Vanlig padda
+Vanlig snok
+Johannesnycklar
+Sankt pers nycklar
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 39627-2026 artfynd.xlsx", "A 39627-2026")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 39627-2026 karta.png", "A 39627-2026")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 39627-2026 georefererad karta.tif", "A 39627-2026")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 39627-2026 FSC-klagomål.docx", "A 39627-2026")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 39627-2026 FSC-klagomål mail.docx", "A 39627-2026")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 39627-2026 tillsynsbegäran.docx", "A 39627-2026")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 39627-2026 tillsynsbegäran mail.docx", "A 39627-2026")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 39627-2026 prioriterade fågelarter.docx", "A 39627-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>A 27865-2024</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D7" s="1" t="n">
+      <c r="D8" s="1" t="n">
         <v>45475</v>
       </c>
-      <c r="E7" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="E8" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I7" t="n">
+      <c r="I8" t="n">
         <v>0.7</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J8" t="n">
         <v>8</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K8" t="n">
         <v>7</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L8" t="n">
         <v>10</v>
       </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>10</v>
       </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
         <v>21</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T8" t="n">
         <v>43</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>34</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Bergjohannesört
 Blå slemspindling
@@ -1448,111 +1587,111 @@
 Grönvit nattviol</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 27865-2024 artfynd.xlsx", "A 27865-2024")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 27865-2024 karta.png", "A 27865-2024")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 27865-2024 georefererad karta.tif", "A 27865-2024")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 27865-2024 FSC-klagomål.docx", "A 27865-2024")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 27865-2024 FSC-klagomål mail.docx", "A 27865-2024")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 27865-2024 tillsynsbegäran.docx", "A 27865-2024")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 27865-2024 tillsynsbegäran mail.docx", "A 27865-2024")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 27865-2024 prioriterade fågelarter.docx", "A 27865-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>A 21219-2023</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="D9" s="1" t="n">
         <v>45062</v>
       </c>
-      <c r="E8" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="E9" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I8" t="n">
+      <c r="I9" t="n">
         <v>2.6</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J9" t="n">
         <v>7</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K9" t="n">
         <v>10</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L9" t="n">
         <v>5</v>
       </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>7</v>
       </c>
-      <c r="R8" t="n">
+      <c r="R9" t="n">
         <v>2</v>
       </c>
-      <c r="S8" t="n">
+      <c r="S9" t="n">
         <v>20</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T9" t="n">
         <v>94</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U9" t="n">
         <v>94</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Ask
 Mindre bastardsvärmare
@@ -1576,107 +1715,107 @@
 Gullviva</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 21219-2023 artfynd.xlsx", "A 21219-2023")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 21219-2023 karta.png", "A 21219-2023")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 21219-2023 georefererad karta.tif", "A 21219-2023")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 21219-2023 FSC-klagomål.docx", "A 21219-2023")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 21219-2023 FSC-klagomål mail.docx", "A 21219-2023")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 21219-2023 tillsynsbegäran.docx", "A 21219-2023")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 21219-2023 tillsynsbegäran mail.docx", "A 21219-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>A 28146-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D9" s="1" t="n">
+      <c r="D10" s="1" t="n">
         <v>46195</v>
       </c>
-      <c r="E9" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="E10" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I9" t="n">
+      <c r="I10" t="n">
         <v>8.4</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J10" t="n">
         <v>8</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K10" t="n">
         <v>2</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L10" t="n">
         <v>10</v>
       </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>10</v>
       </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>19</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T10" t="n">
         <v>20</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Askpraktbagge
 Hasselpraktbagge
@@ -1699,107 +1838,107 @@
 Vanliga ängsnycklar</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 28146-2026 artfynd.xlsx", "A 28146-2026")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 28146-2026 karta.png", "A 28146-2026")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 28146-2026 georefererad karta.tif", "A 28146-2026")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 28146-2026 FSC-klagomål.docx", "A 28146-2026")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 28146-2026 FSC-klagomål mail.docx", "A 28146-2026")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 28146-2026 tillsynsbegäran.docx", "A 28146-2026")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 28146-2026 tillsynsbegäran mail.docx", "A 28146-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>S 1766-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D11" s="1" t="n">
         <v>46189</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="E11" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I10" t="n">
+      <c r="I11" t="n">
         <v>4.1</v>
       </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
         <v>4</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L11" t="n">
         <v>6</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M11" t="n">
         <v>3</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N11" t="n">
         <v>5</v>
       </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>14</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R11" t="n">
         <v>8</v>
       </c>
-      <c r="S10" t="n">
+      <c r="S11" t="n">
         <v>19</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T11" t="n">
         <v>23</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Ask
 Fyllitspindling
@@ -1822,107 +1961,107 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/S 1766-2026 artfynd.xlsx", "S 1766-2026")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/S 1766-2026 karta.png", "S 1766-2026")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/S 1766-2026 georefererad karta.tif", "S 1766-2026")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/S 1766-2026 FSC-klagomål.docx", "S 1766-2026")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/S 1766-2026 FSC-klagomål mail.docx", "S 1766-2026")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/S 1766-2026 tillsynsbegäran.docx", "S 1766-2026")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/S 1766-2026 tillsynsbegäran mail.docx", "S 1766-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>A 59540-2023</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D11" s="1" t="n">
+      <c r="D12" s="1" t="n">
         <v>45254</v>
       </c>
-      <c r="E11" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="E12" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I11" t="n">
+      <c r="I12" t="n">
         <v>2.8</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J12" t="n">
         <v>16</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
         <v>6</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M12" t="n">
         <v>2</v>
       </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>8</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R12" t="n">
         <v>2</v>
       </c>
-      <c r="S11" t="n">
+      <c r="S12" t="n">
         <v>16</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T12" t="n">
         <v>16</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Grönfink
 Tornseglare
@@ -1942,111 +2081,111 @@
 Ärtsångare</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 59540-2023 artfynd.xlsx", "A 59540-2023")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 59540-2023 karta.png", "A 59540-2023")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 59540-2023 georefererad karta.tif", "A 59540-2023")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 59540-2023 FSC-klagomål.docx", "A 59540-2023")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 59540-2023 FSC-klagomål mail.docx", "A 59540-2023")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 59540-2023 tillsynsbegäran.docx", "A 59540-2023")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 59540-2023 tillsynsbegäran mail.docx", "A 59540-2023")</f>
         <v/>
       </c>
-      <c r="AE11">
+      <c r="AE12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 59540-2023 prioriterade fågelarter.docx", "A 59540-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>A 21214-2023</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D12" s="1" t="n">
+      <c r="D13" s="1" t="n">
         <v>45062</v>
       </c>
-      <c r="E12" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F12" t="inlineStr">
+      <c r="E13" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I12" t="n">
+      <c r="I13" t="n">
         <v>3.5</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J13" t="n">
         <v>4</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K13" t="n">
         <v>6</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L13" t="n">
         <v>5</v>
       </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>5</v>
       </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>14</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T13" t="n">
         <v>37</v>
       </c>
-      <c r="U12" t="n">
+      <c r="U13" t="n">
         <v>37</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Grisspindling
 Mjölspindling
@@ -2064,111 +2203,111 @@
 Gullviva</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 21214-2023 artfynd.xlsx", "A 21214-2023")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 21214-2023 karta.png", "A 21214-2023")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 21214-2023 georefererad karta.tif", "A 21214-2023")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 21214-2023 FSC-klagomål.docx", "A 21214-2023")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 21214-2023 FSC-klagomål mail.docx", "A 21214-2023")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 21214-2023 tillsynsbegäran.docx", "A 21214-2023")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 21214-2023 tillsynsbegäran mail.docx", "A 21214-2023")</f>
         <v/>
       </c>
-      <c r="AE12">
+      <c r="AE13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 21214-2023 prioriterade fågelarter.docx", "A 21214-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>A 63779-2021</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D13" s="1" t="n">
+      <c r="D14" s="1" t="n">
         <v>44508</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F13" t="inlineStr">
+      <c r="E14" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I13" t="n">
+      <c r="I14" t="n">
         <v>5.1</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J14" t="n">
         <v>8</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K14" t="n">
         <v>2</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L14" t="n">
         <v>2</v>
       </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>1</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>3</v>
       </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="n">
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
         <v>12</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T14" t="n">
         <v>16</v>
       </c>
-      <c r="U13" t="n">
+      <c r="U14" t="n">
         <v>8</v>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Skogsalm
 Entita
@@ -2184,111 +2323,111 @@
 Kopparödla</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 63779-2021 artfynd.xlsx", "A 63779-2021")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 63779-2021 karta.png", "A 63779-2021")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 63779-2021 georefererad karta.tif", "A 63779-2021")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 63779-2021 FSC-klagomål.docx", "A 63779-2021")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 63779-2021 FSC-klagomål mail.docx", "A 63779-2021")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 63779-2021 tillsynsbegäran.docx", "A 63779-2021")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 63779-2021 tillsynsbegäran mail.docx", "A 63779-2021")</f>
         <v/>
       </c>
-      <c r="AE13">
+      <c r="AE14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 63779-2021 prioriterade fågelarter.docx", "A 63779-2021")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>A 52906-2021</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D14" s="1" t="n">
+      <c r="D15" s="1" t="n">
         <v>44467</v>
       </c>
-      <c r="E14" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="E15" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I14" t="n">
+      <c r="I15" t="n">
         <v>2.1</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J15" t="n">
         <v>5</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K15" t="n">
         <v>2</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L15" t="n">
         <v>4</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M15" t="n">
         <v>2</v>
       </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
         <v>7</v>
       </c>
-      <c r="R14" t="n">
+      <c r="R15" t="n">
         <v>3</v>
       </c>
-      <c r="S14" t="n">
+      <c r="S15" t="n">
         <v>11</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T15" t="n">
         <v>13</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U15" t="n">
         <v>13</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Beryllspindling
 Elastisk spindling
@@ -2303,111 +2442,456 @@
 Näktergal</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 52906-2021 artfynd.xlsx", "A 52906-2021")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 52906-2021 karta.png", "A 52906-2021")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 52906-2021 georefererad karta.tif", "A 52906-2021")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 52906-2021 FSC-klagomål.docx", "A 52906-2021")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 52906-2021 FSC-klagomål mail.docx", "A 52906-2021")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 52906-2021 tillsynsbegäran.docx", "A 52906-2021")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 52906-2021 tillsynsbegäran mail.docx", "A 52906-2021")</f>
         <v/>
       </c>
-      <c r="AE14">
+      <c r="AE15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 52906-2021 prioriterade fågelarter.docx", "A 52906-2021")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 38039-2022</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>44811</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>4</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>6</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2</v>
+      </c>
+      <c r="S16" t="n">
+        <v>11</v>
+      </c>
+      <c r="T16" t="n">
+        <v>13</v>
+      </c>
+      <c r="U16" t="n">
+        <v>12</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Grov gulmossa
+Backtimjan
+Dvärgjordstjärna
+Solvända
+Ängsstarr
+Murgröna
+Alvarmalört
+Grönvit nattviol
+Krutbrännare
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 38039-2022 artfynd.xlsx", "A 38039-2022")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 38039-2022 karta.png", "A 38039-2022")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 38039-2022 georefererad karta.tif", "A 38039-2022")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 38039-2022 FSC-klagomål.docx", "A 38039-2022")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 38039-2022 FSC-klagomål mail.docx", "A 38039-2022")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 38039-2022 tillsynsbegäran.docx", "A 38039-2022")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 38039-2022 tillsynsbegäran mail.docx", "A 38039-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 27636-2023</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45097</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>4</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>6</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2</v>
+      </c>
+      <c r="S17" t="n">
+        <v>11</v>
+      </c>
+      <c r="T17" t="n">
+        <v>13</v>
+      </c>
+      <c r="U17" t="n">
+        <v>11</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Grov gulmossa
+Backtimjan
+Dvärgjordstjärna
+Solvända
+Ängsstarr
+Murgröna
+Alvarmalört
+Grönvit nattviol
+Krutbrännare
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 27636-2023 artfynd.xlsx", "A 27636-2023")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 27636-2023 karta.png", "A 27636-2023")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 27636-2023 georefererad karta.tif", "A 27636-2023")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 27636-2023 FSC-klagomål.docx", "A 27636-2023")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 27636-2023 FSC-klagomål mail.docx", "A 27636-2023")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 27636-2023 tillsynsbegäran.docx", "A 27636-2023")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 27636-2023 tillsynsbegäran mail.docx", "A 27636-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 24778-2022</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>44728</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" t="n">
+        <v>7</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>8</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>11</v>
+      </c>
+      <c r="T18" t="n">
+        <v>20</v>
+      </c>
+      <c r="U18" t="n">
+        <v>20</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Tofsäxing
+Backtimjan
+Flentimotej
+Grådådra
+Poppeltofsskivling
+Slåtterfibbla
+Sminkrot
+Solvända
+Kalktallört
+Murgröna
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24778-2022 artfynd.xlsx", "A 24778-2022")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24778-2022 karta.png", "A 24778-2022")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24778-2022 georefererad karta.tif", "A 24778-2022")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24778-2022 FSC-klagomål.docx", "A 24778-2022")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24778-2022 FSC-klagomål mail.docx", "A 24778-2022")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24778-2022 tillsynsbegäran.docx", "A 24778-2022")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24778-2022 tillsynsbegäran mail.docx", "A 24778-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>A 60875-2025</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D15" s="1" t="n">
+      <c r="D19" s="1" t="n">
         <v>45999</v>
       </c>
-      <c r="E15" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F15" t="inlineStr">
+      <c r="E19" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I15" t="n">
+      <c r="I19" t="n">
         <v>2.1</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J19" t="n">
         <v>8</v>
       </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
         <v>5</v>
       </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>7</v>
       </c>
-      <c r="R15" t="n">
+      <c r="R19" t="n">
         <v>2</v>
       </c>
-      <c r="S15" t="n">
+      <c r="S19" t="n">
         <v>11</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T19" t="n">
         <v>12</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U19" t="n">
         <v>3</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Järnek
 Mosippa
@@ -2422,456 +2906,111 @@
 Skogsduva</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 60875-2025 artfynd.xlsx", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 60875-2025 karta.png", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 60875-2025 georefererad karta.tif", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 60875-2025 FSC-klagomål.docx", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 60875-2025 FSC-klagomål mail.docx", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 60875-2025 tillsynsbegäran.docx", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 60875-2025 tillsynsbegäran mail.docx", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 60875-2025 prioriterade fågelarter.docx", "A 60875-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 24778-2022</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 39320-2024</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>44728</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45551</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I16" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
+      <c r="I20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
         <v>2</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L20" t="n">
+        <v>4</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
         <v>7</v>
       </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>8</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" t="n">
+      <c r="R20" t="n">
+        <v>3</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="n">
         <v>11</v>
       </c>
-      <c r="T16" t="n">
-        <v>20</v>
-      </c>
-      <c r="U16" t="n">
-        <v>20</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Tofsäxing
-Backtimjan
-Flentimotej
-Grådådra
-Poppeltofsskivling
-Slåtterfibbla
-Sminkrot
-Solvända
-Kalktallört
-Murgröna
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24778-2022 artfynd.xlsx", "A 24778-2022")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24778-2022 karta.png", "A 24778-2022")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24778-2022 georefererad karta.tif", "A 24778-2022")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24778-2022 FSC-klagomål.docx", "A 24778-2022")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24778-2022 FSC-klagomål mail.docx", "A 24778-2022")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24778-2022 tillsynsbegäran.docx", "A 24778-2022")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24778-2022 tillsynsbegäran mail.docx", "A 24778-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 38039-2022</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>44811</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="J17" t="n">
-        <v>4</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>4</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>6</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2</v>
-      </c>
-      <c r="S17" t="n">
-        <v>11</v>
-      </c>
-      <c r="T17" t="n">
-        <v>13</v>
-      </c>
-      <c r="U17" t="n">
-        <v>12</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Grov gulmossa
-Backtimjan
-Dvärgjordstjärna
-Solvända
-Ängsstarr
-Murgröna
-Alvarmalört
-Grönvit nattviol
-Krutbrännare
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 38039-2022 artfynd.xlsx", "A 38039-2022")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 38039-2022 karta.png", "A 38039-2022")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 38039-2022 georefererad karta.tif", "A 38039-2022")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 38039-2022 FSC-klagomål.docx", "A 38039-2022")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 38039-2022 FSC-klagomål mail.docx", "A 38039-2022")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 38039-2022 tillsynsbegäran.docx", "A 38039-2022")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 38039-2022 tillsynsbegäran mail.docx", "A 38039-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 27636-2023</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45097</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="J18" t="n">
-        <v>4</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>4</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>6</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2</v>
-      </c>
-      <c r="S18" t="n">
-        <v>11</v>
-      </c>
-      <c r="T18" t="n">
-        <v>13</v>
-      </c>
-      <c r="U18" t="n">
-        <v>11</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Grov gulmossa
-Backtimjan
-Dvärgjordstjärna
-Solvända
-Ängsstarr
-Murgröna
-Alvarmalört
-Grönvit nattviol
-Krutbrännare
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 27636-2023 artfynd.xlsx", "A 27636-2023")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 27636-2023 karta.png", "A 27636-2023")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 27636-2023 georefererad karta.tif", "A 27636-2023")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 27636-2023 FSC-klagomål.docx", "A 27636-2023")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 27636-2023 FSC-klagomål mail.docx", "A 27636-2023")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 27636-2023 tillsynsbegäran.docx", "A 27636-2023")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 27636-2023 tillsynsbegäran mail.docx", "A 27636-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 39320-2024</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45551</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>2</v>
-      </c>
-      <c r="L19" t="n">
-        <v>4</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N19" t="n">
-        <v>1</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>7</v>
-      </c>
-      <c r="R19" t="n">
-        <v>3</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="U20" t="n">
         <v>10</v>
       </c>
-      <c r="T19" t="n">
-        <v>11</v>
-      </c>
-      <c r="U19" t="n">
-        <v>10</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Vresalm
 Lundalm
@@ -2885,107 +3024,107 @@
 Skogsduva</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 39320-2024 artfynd.xlsx", "A 39320-2024")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 39320-2024 karta.png", "A 39320-2024")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 39320-2024 georefererad karta.tif", "A 39320-2024")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 39320-2024 FSC-klagomål.docx", "A 39320-2024")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 39320-2024 FSC-klagomål mail.docx", "A 39320-2024")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 39320-2024 tillsynsbegäran.docx", "A 39320-2024")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 39320-2024 tillsynsbegäran mail.docx", "A 39320-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>S 1122-2022</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D20" s="1" t="n">
+      <c r="D21" s="1" t="n">
         <v>44616</v>
       </c>
-      <c r="E20" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F20" t="inlineStr">
+      <c r="E21" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I20" t="n">
+      <c r="I21" t="n">
         <v>2.6</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J21" t="n">
         <v>2</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K21" t="n">
         <v>3</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L21" t="n">
         <v>3</v>
       </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
         <v>3</v>
       </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
         <v>6</v>
       </c>
-      <c r="R20" t="n">
+      <c r="R21" t="n">
         <v>3</v>
       </c>
-      <c r="S20" t="n">
+      <c r="S21" t="n">
         <v>10</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T21" t="n">
         <v>16</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U21" t="n">
         <v>15</v>
       </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Ask
 Lundalm
@@ -2999,107 +3138,107 @@
 Sankt pers nycklar</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/S 1122-2022 artfynd.xlsx", "S 1122-2022")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/S 1122-2022 karta.png", "S 1122-2022")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/S 1122-2022 georefererad karta.tif", "S 1122-2022")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/S 1122-2022 FSC-klagomål.docx", "S 1122-2022")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/S 1122-2022 FSC-klagomål mail.docx", "S 1122-2022")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/S 1122-2022 tillsynsbegäran.docx", "S 1122-2022")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/S 1122-2022 tillsynsbegäran mail.docx", "S 1122-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>S 929-2023</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D21" s="1" t="n">
+      <c r="D22" s="1" t="n">
         <v>45000</v>
       </c>
-      <c r="E21" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F21" t="inlineStr">
+      <c r="E22" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I21" t="n">
+      <c r="I22" t="n">
         <v>4.7</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J22" t="n">
         <v>4</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K22" t="n">
         <v>2</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L22" t="n">
         <v>3</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M22" t="n">
         <v>3</v>
       </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
         <v>6</v>
       </c>
-      <c r="R21" t="n">
+      <c r="R22" t="n">
         <v>3</v>
       </c>
-      <c r="S21" t="n">
+      <c r="S22" t="n">
         <v>9</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T22" t="n">
         <v>12</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U22" t="n">
         <v>8</v>
       </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Liten jordstjärna
 Stare
@@ -3112,111 +3251,111 @@
 Kopparödla</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/S 929-2023 artfynd.xlsx", "S 929-2023")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/S 929-2023 karta.png", "S 929-2023")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/S 929-2023 georefererad karta.tif", "S 929-2023")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/S 929-2023 FSC-klagomål.docx", "S 929-2023")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/S 929-2023 FSC-klagomål mail.docx", "S 929-2023")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/S 929-2023 tillsynsbegäran.docx", "S 929-2023")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/S 929-2023 tillsynsbegäran mail.docx", "S 929-2023")</f>
         <v/>
       </c>
-      <c r="AE21">
+      <c r="AE22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/S 929-2023 prioriterade fågelarter.docx", "S 929-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>A 35242-2024</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D22" s="1" t="n">
+      <c r="D23" s="1" t="n">
         <v>45530</v>
       </c>
-      <c r="E22" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F22" t="inlineStr">
+      <c r="E23" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I22" t="n">
+      <c r="I23" t="n">
         <v>0.9</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J23" t="n">
         <v>2</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K23" t="n">
         <v>3</v>
       </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>3</v>
       </c>
-      <c r="N22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="N23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
         <v>4</v>
       </c>
-      <c r="R22" t="n">
+      <c r="R23" t="n">
         <v>4</v>
       </c>
-      <c r="S22" t="n">
+      <c r="S23" t="n">
         <v>8</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T23" t="n">
         <v>12</v>
       </c>
-      <c r="U22" t="n">
+      <c r="U23" t="n">
         <v>6</v>
       </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Sandgeting
 Liten diskröksvamp
@@ -3228,111 +3367,111 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W22">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 35242-2024 artfynd.xlsx", "A 35242-2024")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 35242-2024 karta.png", "A 35242-2024")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 35242-2024 georefererad karta.tif", "A 35242-2024")</f>
         <v/>
       </c>
-      <c r="Z22">
+      <c r="Z23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/knärot/A 35242-2024 karta knärot.png", "A 35242-2024")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 35242-2024 FSC-klagomål.docx", "A 35242-2024")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 35242-2024 FSC-klagomål mail.docx", "A 35242-2024")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 35242-2024 tillsynsbegäran.docx", "A 35242-2024")</f>
         <v/>
       </c>
-      <c r="AD22">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 35242-2024 tillsynsbegäran mail.docx", "A 35242-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>S 3773-2023</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D23" s="1" t="n">
+      <c r="D24" s="1" t="n">
         <v>45223</v>
       </c>
-      <c r="E23" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F23" t="inlineStr">
+      <c r="E24" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I23" t="n">
+      <c r="I24" t="n">
         <v>0.3</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J24" t="n">
         <v>2</v>
       </c>
-      <c r="K23" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" t="n">
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
         <v>3</v>
       </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
         <v>2</v>
       </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
         <v>5</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R24" t="n">
         <v>2</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S24" t="n">
         <v>8</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T24" t="n">
         <v>9</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U24" t="n">
         <v>9</v>
       </c>
-      <c r="V23" s="2" t="inlineStr">
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>Ask
 Lundalm
@@ -3344,107 +3483,107 @@
 Gullviva</t>
         </is>
       </c>
-      <c r="W23">
+      <c r="W24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/S 3773-2023 artfynd.xlsx", "S 3773-2023")</f>
         <v/>
       </c>
-      <c r="X23">
+      <c r="X24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/S 3773-2023 karta.png", "S 3773-2023")</f>
         <v/>
       </c>
-      <c r="Y23">
+      <c r="Y24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/S 3773-2023 georefererad karta.tif", "S 3773-2023")</f>
         <v/>
       </c>
-      <c r="AA23">
+      <c r="AA24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/S 3773-2023 FSC-klagomål.docx", "S 3773-2023")</f>
         <v/>
       </c>
-      <c r="AB23">
+      <c r="AB24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/S 3773-2023 FSC-klagomål mail.docx", "S 3773-2023")</f>
         <v/>
       </c>
-      <c r="AC23">
+      <c r="AC24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/S 3773-2023 tillsynsbegäran.docx", "S 3773-2023")</f>
         <v/>
       </c>
-      <c r="AD23">
+      <c r="AD24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/S 3773-2023 tillsynsbegäran mail.docx", "S 3773-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>S 1833-2023</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D24" s="1" t="n">
+      <c r="D25" s="1" t="n">
         <v>45075</v>
       </c>
-      <c r="E24" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F24" t="inlineStr">
+      <c r="E25" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I24" t="n">
+      <c r="I25" t="n">
         <v>0.4</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J25" t="n">
         <v>3</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K25" t="n">
         <v>2</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L25" t="n">
         <v>3</v>
       </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
         <v>3</v>
       </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
         <v>8</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T25" t="n">
         <v>11</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U25" t="n">
         <v>10</v>
       </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Sårläka
 Vippärt
@@ -3456,107 +3595,107 @@
 Gullviva</t>
         </is>
       </c>
-      <c r="W24">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/S 1833-2023 artfynd.xlsx", "S 1833-2023")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/S 1833-2023 karta.png", "S 1833-2023")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/S 1833-2023 georefererad karta.tif", "S 1833-2023")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/S 1833-2023 FSC-klagomål.docx", "S 1833-2023")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/S 1833-2023 FSC-klagomål mail.docx", "S 1833-2023")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/S 1833-2023 tillsynsbegäran.docx", "S 1833-2023")</f>
         <v/>
       </c>
-      <c r="AD24">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/S 1833-2023 tillsynsbegäran mail.docx", "S 1833-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>A 40361-2023</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D25" s="1" t="n">
+      <c r="D26" s="1" t="n">
         <v>45169</v>
       </c>
-      <c r="E25" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F25" t="inlineStr">
+      <c r="E26" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I25" t="n">
+      <c r="I26" t="n">
         <v>1.1</v>
       </c>
-      <c r="J25" t="n">
-        <v>1</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
         <v>4</v>
       </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
         <v>2</v>
       </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
         <v>6</v>
       </c>
-      <c r="R25" t="n">
+      <c r="R26" t="n">
         <v>2</v>
       </c>
-      <c r="S25" t="n">
+      <c r="S26" t="n">
         <v>7</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T26" t="n">
         <v>11</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U26" t="n">
         <v>10</v>
       </c>
-      <c r="V25" s="2" t="inlineStr">
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Ask
 Lundalm
@@ -3567,111 +3706,221 @@
 Näktergal</t>
         </is>
       </c>
-      <c r="W25">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 40361-2023 artfynd.xlsx", "A 40361-2023")</f>
         <v/>
       </c>
-      <c r="X25">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 40361-2023 karta.png", "A 40361-2023")</f>
         <v/>
       </c>
-      <c r="Y25">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 40361-2023 georefererad karta.tif", "A 40361-2023")</f>
         <v/>
       </c>
-      <c r="AA25">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 40361-2023 FSC-klagomål.docx", "A 40361-2023")</f>
         <v/>
       </c>
-      <c r="AB25">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 40361-2023 FSC-klagomål mail.docx", "A 40361-2023")</f>
         <v/>
       </c>
-      <c r="AC25">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 40361-2023 tillsynsbegäran.docx", "A 40361-2023")</f>
         <v/>
       </c>
-      <c r="AD25">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 40361-2023 tillsynsbegäran mail.docx", "A 40361-2023")</f>
         <v/>
       </c>
-      <c r="AE25">
+      <c r="AE26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 40361-2023 prioriterade fågelarter.docx", "A 40361-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 43704-2025</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>45912</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J27" t="n">
+        <v>5</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>6</v>
+      </c>
+      <c r="T27" t="n">
+        <v>6</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp
+Långbensgroda
+Större vattensalamander
+Åkergroda
+Mindre vattensalamander
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43704-2025 artfynd.xlsx", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="X27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43704-2025 karta.png", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="Y27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43704-2025 georefererad karta.tif", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="AA27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43704-2025 FSC-klagomål.docx", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="AB27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43704-2025 FSC-klagomål mail.docx", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="AC27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43704-2025 tillsynsbegäran.docx", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="AD27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43704-2025 tillsynsbegäran mail.docx", "A 43704-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>A 43714-2025</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D26" s="1" t="n">
+      <c r="D28" s="1" t="n">
         <v>45912</v>
       </c>
-      <c r="E26" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F26" t="inlineStr">
+      <c r="E28" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I26" t="n">
+      <c r="I28" t="n">
         <v>7.9</v>
       </c>
-      <c r="J26" t="n">
-        <v>1</v>
-      </c>
-      <c r="K26" t="n">
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
         <v>3</v>
       </c>
-      <c r="L26" t="n">
-        <v>1</v>
-      </c>
-      <c r="M26" t="n">
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" t="n">
         <v>2</v>
       </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
         <v>3</v>
       </c>
-      <c r="R26" t="n">
+      <c r="R28" t="n">
         <v>2</v>
       </c>
-      <c r="S26" t="n">
+      <c r="S28" t="n">
         <v>6</v>
       </c>
-      <c r="T26" t="n">
+      <c r="T28" t="n">
         <v>8</v>
       </c>
-      <c r="U26" t="n">
+      <c r="U28" t="n">
         <v>2</v>
       </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>Mindre bastardsvärmare
 Sexfläckig bastardsvärmare
@@ -3681,221 +3930,111 @@
 Trädporella</t>
         </is>
       </c>
-      <c r="W26">
+      <c r="W28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43714-2025 artfynd.xlsx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="X26">
+      <c r="X28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43714-2025 karta.png", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="Y26">
+      <c r="Y28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43714-2025 georefererad karta.tif", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AA26">
+      <c r="AA28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43714-2025 FSC-klagomål.docx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AB26">
+      <c r="AB28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43714-2025 FSC-klagomål mail.docx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AC26">
+      <c r="AC28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43714-2025 tillsynsbegäran.docx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AD26">
+      <c r="AD28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43714-2025 tillsynsbegäran mail.docx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AE26">
+      <c r="AE28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 43714-2025 prioriterade fågelarter.docx", "A 43714-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 43704-2025</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>45912</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F27" t="inlineStr">
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>S 1814-2026</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I27" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J27" t="n">
-        <v>5</v>
-      </c>
-      <c r="K27" t="n">
-        <v>1</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
+      <c r="I29" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>2</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1</v>
+      </c>
+      <c r="S29" t="n">
         <v>6</v>
       </c>
-      <c r="T27" t="n">
-        <v>6</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Blomkålssvamp
-Långbensgroda
-Större vattensalamander
-Åkergroda
-Mindre vattensalamander
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43704-2025 artfynd.xlsx", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43704-2025 karta.png", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43704-2025 georefererad karta.tif", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43704-2025 FSC-klagomål.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43704-2025 FSC-klagomål mail.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43704-2025 tillsynsbegäran.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43704-2025 tillsynsbegäran mail.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>S 1814-2026</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>46190</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="J28" t="n">
-        <v>3</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>2</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>3</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1</v>
-      </c>
-      <c r="S28" t="n">
-        <v>6</v>
-      </c>
-      <c r="T28" t="n">
+      <c r="T29" t="n">
         <v>11</v>
       </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>Småvänderot
 Leopardsköldbagge
@@ -3905,107 +4044,107 @@
 Ängsnycklar</t>
         </is>
       </c>
-      <c r="W28">
+      <c r="W29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/S 1814-2026 artfynd.xlsx", "S 1814-2026")</f>
         <v/>
       </c>
-      <c r="X28">
+      <c r="X29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/S 1814-2026 karta.png", "S 1814-2026")</f>
         <v/>
       </c>
-      <c r="Y28">
+      <c r="Y29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/S 1814-2026 georefererad karta.tif", "S 1814-2026")</f>
         <v/>
       </c>
-      <c r="AA28">
+      <c r="AA29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/S 1814-2026 FSC-klagomål.docx", "S 1814-2026")</f>
         <v/>
       </c>
-      <c r="AB28">
+      <c r="AB29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/S 1814-2026 FSC-klagomål mail.docx", "S 1814-2026")</f>
         <v/>
       </c>
-      <c r="AC28">
+      <c r="AC29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/S 1814-2026 tillsynsbegäran.docx", "S 1814-2026")</f>
         <v/>
       </c>
-      <c r="AD28">
+      <c r="AD29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/S 1814-2026 tillsynsbegäran mail.docx", "S 1814-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>A 61963-2025</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D29" s="1" t="n">
+      <c r="D30" s="1" t="n">
         <v>46003</v>
       </c>
-      <c r="E29" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F29" t="inlineStr">
+      <c r="E30" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I29" t="n">
+      <c r="I30" t="n">
         <v>1.1</v>
       </c>
-      <c r="J29" t="n">
+      <c r="J30" t="n">
         <v>4</v>
       </c>
-      <c r="K29" t="n">
-        <v>1</v>
-      </c>
-      <c r="L29" t="n">
-        <v>1</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>1</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
+      <c r="K30" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
         <v>5</v>
       </c>
-      <c r="T29" t="n">
+      <c r="T30" t="n">
         <v>8</v>
       </c>
-      <c r="U29" t="n">
+      <c r="U30" t="n">
         <v>3</v>
       </c>
-      <c r="V29" s="2" t="inlineStr">
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>Gulsparv
 Mindre märgborre
@@ -4014,111 +4153,111 @@
 Röd glada</t>
         </is>
       </c>
-      <c r="W29">
+      <c r="W30">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 61963-2025 artfynd.xlsx", "A 61963-2025")</f>
         <v/>
       </c>
-      <c r="X29">
+      <c r="X30">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 61963-2025 karta.png", "A 61963-2025")</f>
         <v/>
       </c>
-      <c r="Y29">
+      <c r="Y30">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 61963-2025 georefererad karta.tif", "A 61963-2025")</f>
         <v/>
       </c>
-      <c r="AA29">
+      <c r="AA30">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 61963-2025 FSC-klagomål.docx", "A 61963-2025")</f>
         <v/>
       </c>
-      <c r="AB29">
+      <c r="AB30">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 61963-2025 FSC-klagomål mail.docx", "A 61963-2025")</f>
         <v/>
       </c>
-      <c r="AC29">
+      <c r="AC30">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 61963-2025 tillsynsbegäran.docx", "A 61963-2025")</f>
         <v/>
       </c>
-      <c r="AD29">
+      <c r="AD30">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 61963-2025 tillsynsbegäran mail.docx", "A 61963-2025")</f>
         <v/>
       </c>
-      <c r="AE29">
+      <c r="AE30">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 61963-2025 prioriterade fågelarter.docx", "A 61963-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>A 2864-2026</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D30" s="1" t="n">
+      <c r="D31" s="1" t="n">
         <v>46038</v>
       </c>
-      <c r="E30" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F30" t="inlineStr">
+      <c r="E31" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I30" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" t="n">
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="n">
         <v>4</v>
       </c>
-      <c r="K30" t="n">
-        <v>1</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
+      <c r="K31" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
         <v>5</v>
       </c>
-      <c r="T30" t="n">
+      <c r="T31" t="n">
         <v>8</v>
       </c>
-      <c r="U30" t="n">
+      <c r="U31" t="n">
         <v>3</v>
       </c>
-      <c r="V30" s="2" t="inlineStr">
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>Gulsparv
 Mindre märgborre
@@ -4127,111 +4266,111 @@
 Röd glada</t>
         </is>
       </c>
-      <c r="W30">
+      <c r="W31">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 2864-2026 artfynd.xlsx", "A 2864-2026")</f>
         <v/>
       </c>
-      <c r="X30">
+      <c r="X31">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 2864-2026 karta.png", "A 2864-2026")</f>
         <v/>
       </c>
-      <c r="Y30">
+      <c r="Y31">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 2864-2026 georefererad karta.tif", "A 2864-2026")</f>
         <v/>
       </c>
-      <c r="AA30">
+      <c r="AA31">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 2864-2026 FSC-klagomål.docx", "A 2864-2026")</f>
         <v/>
       </c>
-      <c r="AB30">
+      <c r="AB31">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 2864-2026 FSC-klagomål mail.docx", "A 2864-2026")</f>
         <v/>
       </c>
-      <c r="AC30">
+      <c r="AC31">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 2864-2026 tillsynsbegäran.docx", "A 2864-2026")</f>
         <v/>
       </c>
-      <c r="AD30">
+      <c r="AD31">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 2864-2026 tillsynsbegäran mail.docx", "A 2864-2026")</f>
         <v/>
       </c>
-      <c r="AE30">
+      <c r="AE31">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 2864-2026 prioriterade fågelarter.docx", "A 2864-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>A 54167-2024</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D31" s="1" t="n">
+      <c r="D32" s="1" t="n">
         <v>45616</v>
       </c>
-      <c r="E31" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F31" t="inlineStr">
+      <c r="E32" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I31" t="n">
+      <c r="I32" t="n">
         <v>1.5</v>
       </c>
-      <c r="J31" t="n">
+      <c r="J32" t="n">
         <v>2</v>
       </c>
-      <c r="K31" t="n">
+      <c r="K32" t="n">
         <v>2</v>
       </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>1</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>1</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1</v>
-      </c>
-      <c r="S31" t="n">
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1</v>
+      </c>
+      <c r="S32" t="n">
         <v>4</v>
       </c>
-      <c r="T31" t="n">
+      <c r="T32" t="n">
         <v>8</v>
       </c>
-      <c r="U31" t="n">
+      <c r="U32" t="n">
         <v>8</v>
       </c>
-      <c r="V31" s="2" t="inlineStr">
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>Ask
 Murgröna
@@ -4239,107 +4378,107 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W31">
+      <c r="W32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 54167-2024 artfynd.xlsx", "A 54167-2024")</f>
         <v/>
       </c>
-      <c r="X31">
+      <c r="X32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 54167-2024 karta.png", "A 54167-2024")</f>
         <v/>
       </c>
-      <c r="Y31">
+      <c r="Y32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 54167-2024 georefererad karta.tif", "A 54167-2024")</f>
         <v/>
       </c>
-      <c r="AA31">
+      <c r="AA32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 54167-2024 FSC-klagomål.docx", "A 54167-2024")</f>
         <v/>
       </c>
-      <c r="AB31">
+      <c r="AB32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 54167-2024 FSC-klagomål mail.docx", "A 54167-2024")</f>
         <v/>
       </c>
-      <c r="AC31">
+      <c r="AC32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 54167-2024 tillsynsbegäran.docx", "A 54167-2024")</f>
         <v/>
       </c>
-      <c r="AD31">
+      <c r="AD32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 54167-2024 tillsynsbegäran mail.docx", "A 54167-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>A 19459-2023</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D32" s="1" t="n">
+      <c r="D33" s="1" t="n">
         <v>45049</v>
       </c>
-      <c r="E32" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F32" t="inlineStr">
+      <c r="E33" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I32" t="n">
+      <c r="I33" t="n">
         <v>1.6</v>
       </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
         <v>4</v>
       </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
         <v>4</v>
       </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
         <v>4</v>
       </c>
-      <c r="T32" t="n">
+      <c r="T33" t="n">
         <v>4</v>
       </c>
-      <c r="U32" t="n">
+      <c r="U33" t="n">
         <v>4</v>
       </c>
-      <c r="V32" s="2" t="inlineStr">
+      <c r="V33" s="2" t="inlineStr">
         <is>
           <t>Kavelhirs
 Kösa
@@ -4347,107 +4486,107 @@
 Riddarsporre</t>
         </is>
       </c>
-      <c r="W32">
+      <c r="W33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 19459-2023 artfynd.xlsx", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="X32">
+      <c r="X33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 19459-2023 karta.png", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="Y32">
+      <c r="Y33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 19459-2023 georefererad karta.tif", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="AA32">
+      <c r="AA33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 19459-2023 FSC-klagomål.docx", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="AB32">
+      <c r="AB33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 19459-2023 FSC-klagomål mail.docx", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="AC32">
+      <c r="AC33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 19459-2023 tillsynsbegäran.docx", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="AD32">
+      <c r="AD33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 19459-2023 tillsynsbegäran mail.docx", "A 19459-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>A 26440-2026</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D33" s="1" t="n">
+      <c r="D34" s="1" t="n">
         <v>46183</v>
       </c>
-      <c r="E33" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F33" t="inlineStr">
+      <c r="E34" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I33" t="n">
+      <c r="I34" t="n">
         <v>1.1</v>
       </c>
-      <c r="J33" t="n">
-        <v>1</v>
-      </c>
-      <c r="K33" t="n">
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="n">
         <v>3</v>
       </c>
-      <c r="L33" t="n">
-        <v>1</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
+      <c r="L34" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
         <v>4</v>
       </c>
-      <c r="T33" t="n">
+      <c r="T34" t="n">
         <v>5</v>
       </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>Backstarr
 Murgröna
@@ -4455,107 +4594,107 @@
 Vätteros</t>
         </is>
       </c>
-      <c r="W33">
+      <c r="W34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 26440-2026 artfynd.xlsx", "A 26440-2026")</f>
         <v/>
       </c>
-      <c r="X33">
+      <c r="X34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 26440-2026 karta.png", "A 26440-2026")</f>
         <v/>
       </c>
-      <c r="Y33">
+      <c r="Y34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 26440-2026 georefererad karta.tif", "A 26440-2026")</f>
         <v/>
       </c>
-      <c r="AA33">
+      <c r="AA34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 26440-2026 FSC-klagomål.docx", "A 26440-2026")</f>
         <v/>
       </c>
-      <c r="AB33">
+      <c r="AB34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 26440-2026 FSC-klagomål mail.docx", "A 26440-2026")</f>
         <v/>
       </c>
-      <c r="AC33">
+      <c r="AC34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 26440-2026 tillsynsbegäran.docx", "A 26440-2026")</f>
         <v/>
       </c>
-      <c r="AD33">
+      <c r="AD34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 26440-2026 tillsynsbegäran mail.docx", "A 26440-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>A 34431-2026</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D34" s="1" t="n">
+      <c r="D35" s="1" t="n">
         <v>46254</v>
       </c>
-      <c r="E34" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F34" t="inlineStr">
+      <c r="E35" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I34" t="n">
+      <c r="I35" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="J34" t="n">
+      <c r="J35" t="n">
         <v>2</v>
       </c>
-      <c r="K34" t="n">
-        <v>1</v>
-      </c>
-      <c r="L34" t="n">
+      <c r="K35" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" t="n">
         <v>3</v>
       </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
         <v>3</v>
       </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
         <v>4</v>
       </c>
-      <c r="T34" t="n">
+      <c r="T35" t="n">
         <v>5</v>
       </c>
-      <c r="U34" t="n">
-        <v>1</v>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
+      <c r="U35" t="n">
+        <v>1</v>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
         <is>
           <t>Entita
 Mindre hackspett
@@ -4563,470 +4702,364 @@
 Murgröna</t>
         </is>
       </c>
-      <c r="W34">
+      <c r="W35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 34431-2026 artfynd.xlsx", "A 34431-2026")</f>
         <v/>
       </c>
-      <c r="X34">
+      <c r="X35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 34431-2026 karta.png", "A 34431-2026")</f>
         <v/>
       </c>
-      <c r="Y34">
+      <c r="Y35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 34431-2026 georefererad karta.tif", "A 34431-2026")</f>
         <v/>
       </c>
-      <c r="AA34">
+      <c r="AA35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 34431-2026 FSC-klagomål.docx", "A 34431-2026")</f>
         <v/>
       </c>
-      <c r="AB34">
+      <c r="AB35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 34431-2026 FSC-klagomål mail.docx", "A 34431-2026")</f>
         <v/>
       </c>
-      <c r="AC34">
+      <c r="AC35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 34431-2026 tillsynsbegäran.docx", "A 34431-2026")</f>
         <v/>
       </c>
-      <c r="AD34">
+      <c r="AD35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 34431-2026 tillsynsbegäran mail.docx", "A 34431-2026")</f>
         <v/>
       </c>
-      <c r="AE34">
+      <c r="AE35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 34431-2026 prioriterade fågelarter.docx", "A 34431-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>A 43702-2025</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D36" s="1" t="n">
+        <v>45912</v>
+      </c>
+      <c r="E36" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>Sårläka
+Murgröna
+Tibast</t>
+        </is>
+      </c>
+      <c r="W36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43702-2025 artfynd.xlsx", "A 43702-2025")</f>
+        <v/>
+      </c>
+      <c r="X36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43702-2025 karta.png", "A 43702-2025")</f>
+        <v/>
+      </c>
+      <c r="Y36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43702-2025 georefererad karta.tif", "A 43702-2025")</f>
+        <v/>
+      </c>
+      <c r="AA36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43702-2025 FSC-klagomål.docx", "A 43702-2025")</f>
+        <v/>
+      </c>
+      <c r="AB36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43702-2025 FSC-klagomål mail.docx", "A 43702-2025")</f>
+        <v/>
+      </c>
+      <c r="AC36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43702-2025 tillsynsbegäran.docx", "A 43702-2025")</f>
+        <v/>
+      </c>
+      <c r="AD36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43702-2025 tillsynsbegäran mail.docx", "A 43702-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>A 29360-2026</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D37" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="E37" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>Mindre blåvinge
+Silversmygare
+Ekoxe</t>
+        </is>
+      </c>
+      <c r="W37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 29360-2026 artfynd.xlsx", "A 29360-2026")</f>
+        <v/>
+      </c>
+      <c r="X37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 29360-2026 karta.png", "A 29360-2026")</f>
+        <v/>
+      </c>
+      <c r="Y37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 29360-2026 georefererad karta.tif", "A 29360-2026")</f>
+        <v/>
+      </c>
+      <c r="AA37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 29360-2026 FSC-klagomål.docx", "A 29360-2026")</f>
+        <v/>
+      </c>
+      <c r="AB37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 29360-2026 FSC-klagomål mail.docx", "A 29360-2026")</f>
+        <v/>
+      </c>
+      <c r="AC37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 29360-2026 tillsynsbegäran.docx", "A 29360-2026")</f>
+        <v/>
+      </c>
+      <c r="AD37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 29360-2026 tillsynsbegäran mail.docx", "A 29360-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>A 15600-2025</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D35" s="1" t="n">
+      <c r="D38" s="1" t="n">
         <v>45747</v>
       </c>
-      <c r="E35" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F35" t="inlineStr">
+      <c r="E38" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I35" t="n">
+      <c r="I38" t="n">
         <v>1.1</v>
       </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
         <v>3</v>
       </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
         <v>3</v>
       </c>
-      <c r="T35" t="n">
+      <c r="T38" t="n">
         <v>3</v>
       </c>
-      <c r="U35" t="n">
-        <v>1</v>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
+      <c r="U38" t="n">
+        <v>1</v>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
         <is>
           <t>Kragjordstjärna
 Murgröna
 Scharlakansvårskål agg.</t>
         </is>
       </c>
-      <c r="W35">
+      <c r="W38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 15600-2025 artfynd.xlsx", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="X35">
+      <c r="X38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 15600-2025 karta.png", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="Y35">
+      <c r="Y38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 15600-2025 georefererad karta.tif", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="AA35">
+      <c r="AA38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 15600-2025 FSC-klagomål.docx", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="AB35">
+      <c r="AB38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 15600-2025 FSC-klagomål mail.docx", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="AC35">
+      <c r="AC38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 15600-2025 tillsynsbegäran.docx", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="AD35">
+      <c r="AD38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 15600-2025 tillsynsbegäran mail.docx", "A 15600-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>A 43702-2025</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="n">
-        <v>45912</v>
-      </c>
-      <c r="E36" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>2</v>
-      </c>
-      <c r="L36" t="n">
-        <v>1</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>1</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>3</v>
-      </c>
-      <c r="T36" t="n">
-        <v>3</v>
-      </c>
-      <c r="U36" t="n">
-        <v>2</v>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>Sårläka
-Murgröna
-Tibast</t>
-        </is>
-      </c>
-      <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43702-2025 artfynd.xlsx", "A 43702-2025")</f>
-        <v/>
-      </c>
-      <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43702-2025 karta.png", "A 43702-2025")</f>
-        <v/>
-      </c>
-      <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43702-2025 georefererad karta.tif", "A 43702-2025")</f>
-        <v/>
-      </c>
-      <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43702-2025 FSC-klagomål.docx", "A 43702-2025")</f>
-        <v/>
-      </c>
-      <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43702-2025 FSC-klagomål mail.docx", "A 43702-2025")</f>
-        <v/>
-      </c>
-      <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43702-2025 tillsynsbegäran.docx", "A 43702-2025")</f>
-        <v/>
-      </c>
-      <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43702-2025 tillsynsbegäran mail.docx", "A 43702-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" ht="15" customHeight="1">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>A 29360-2026</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D37" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="E37" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J37" t="n">
-        <v>1</v>
-      </c>
-      <c r="K37" t="n">
-        <v>1</v>
-      </c>
-      <c r="L37" t="n">
-        <v>1</v>
-      </c>
-      <c r="M37" t="n">
-        <v>1</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>2</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1</v>
-      </c>
-      <c r="S37" t="n">
-        <v>3</v>
-      </c>
-      <c r="T37" t="n">
-        <v>3</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1</v>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>Mindre blåvinge
-Silversmygare
-Ekoxe</t>
-        </is>
-      </c>
-      <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 29360-2026 artfynd.xlsx", "A 29360-2026")</f>
-        <v/>
-      </c>
-      <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 29360-2026 karta.png", "A 29360-2026")</f>
-        <v/>
-      </c>
-      <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 29360-2026 georefererad karta.tif", "A 29360-2026")</f>
-        <v/>
-      </c>
-      <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 29360-2026 FSC-klagomål.docx", "A 29360-2026")</f>
-        <v/>
-      </c>
-      <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 29360-2026 FSC-klagomål mail.docx", "A 29360-2026")</f>
-        <v/>
-      </c>
-      <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 29360-2026 tillsynsbegäran.docx", "A 29360-2026")</f>
-        <v/>
-      </c>
-      <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 29360-2026 tillsynsbegäran mail.docx", "A 29360-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>A 54192-2021</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D38" s="1" t="n">
-        <v>44470</v>
-      </c>
-      <c r="E38" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I38" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J38" t="n">
-        <v>1</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
-        <v>2</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>2</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>2</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2</v>
-      </c>
-      <c r="U38" t="n">
-        <v>2</v>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t>Ladusvala
-Sminkrot</t>
-        </is>
-      </c>
-      <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 54192-2021 artfynd.xlsx", "A 54192-2021")</f>
-        <v/>
-      </c>
-      <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 54192-2021 karta.png", "A 54192-2021")</f>
-        <v/>
-      </c>
-      <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 54192-2021 georefererad karta.tif", "A 54192-2021")</f>
-        <v/>
-      </c>
-      <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 54192-2021 FSC-klagomål.docx", "A 54192-2021")</f>
-        <v/>
-      </c>
-      <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 54192-2021 FSC-klagomål mail.docx", "A 54192-2021")</f>
-        <v/>
-      </c>
-      <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 54192-2021 tillsynsbegäran.docx", "A 54192-2021")</f>
-        <v/>
-      </c>
-      <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 54192-2021 tillsynsbegäran mail.docx", "A 54192-2021")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 72167-2021</t>
+          <t>A 54192-2021</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5040,10 +5073,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44544</v>
+        <v>44470</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5056,16 +5089,16 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="J39" t="n">
         <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -5080,7 +5113,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -5096,40 +5129,36 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Murgröna
-Röd glada</t>
+          <t>Ladusvala
+Sminkrot</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 72167-2021 artfynd.xlsx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 54192-2021 artfynd.xlsx", "A 54192-2021")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 72167-2021 karta.png", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 54192-2021 karta.png", "A 54192-2021")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 72167-2021 georefererad karta.tif", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 54192-2021 georefererad karta.tif", "A 54192-2021")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 72167-2021 FSC-klagomål.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 54192-2021 FSC-klagomål.docx", "A 54192-2021")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 72167-2021 FSC-klagomål mail.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 54192-2021 FSC-klagomål mail.docx", "A 54192-2021")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 72167-2021 tillsynsbegäran.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 54192-2021 tillsynsbegäran.docx", "A 54192-2021")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 72167-2021 tillsynsbegäran mail.docx", "A 72167-2021")</f>
-        <v/>
-      </c>
-      <c r="AE39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 72167-2021 prioriterade fågelarter.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 54192-2021 tillsynsbegäran mail.docx", "A 54192-2021")</f>
         <v/>
       </c>
     </row>
@@ -5153,7 +5182,7 @@
         <v>45267</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5242,24 +5271,24 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S 2138-2026</t>
+          <t>A 72167-2021</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46246</v>
+        <v>44544</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5272,7 +5301,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>5.4</v>
+        <v>3.5</v>
       </c>
       <c r="J41" t="n">
         <v>1</v>
@@ -5287,7 +5316,7 @@
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5296,10 +5325,10 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>2</v>
@@ -5308,64 +5337,68 @@
         <v>2</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Ask
-Ekoxe</t>
+          <t>Murgröna
+Röd glada</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/S 2138-2026 artfynd.xlsx", "S 2138-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 72167-2021 artfynd.xlsx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/S 2138-2026 karta.png", "S 2138-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 72167-2021 karta.png", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/S 2138-2026 georefererad karta.tif", "S 2138-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 72167-2021 georefererad karta.tif", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/S 2138-2026 FSC-klagomål.docx", "S 2138-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 72167-2021 FSC-klagomål.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/S 2138-2026 FSC-klagomål mail.docx", "S 2138-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 72167-2021 FSC-klagomål mail.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/S 2138-2026 tillsynsbegäran.docx", "S 2138-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 72167-2021 tillsynsbegäran.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/S 2138-2026 tillsynsbegäran mail.docx", "S 2138-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 72167-2021 tillsynsbegäran mail.docx", "A 72167-2021")</f>
+        <v/>
+      </c>
+      <c r="AE41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 72167-2021 prioriterade fågelarter.docx", "A 72167-2021")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 13040-2024</t>
+          <t>S 2138-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45385</v>
+        <v>46246</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5378,13 +5411,13 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.2</v>
+        <v>5.4</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -5408,52 +5441,53 @@
         <v>1</v>
       </c>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Ask
+Ekoxe</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13040-2024 artfynd.xlsx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/S 2138-2026 artfynd.xlsx", "S 2138-2026")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13040-2024 karta.png", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/S 2138-2026 karta.png", "S 2138-2026")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13040-2024 georefererad karta.tif", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/S 2138-2026 georefererad karta.tif", "S 2138-2026")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13040-2024 FSC-klagomål.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/S 2138-2026 FSC-klagomål.docx", "S 2138-2026")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13040-2024 FSC-klagomål mail.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/S 2138-2026 FSC-klagomål mail.docx", "S 2138-2026")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13040-2024 tillsynsbegäran.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/S 2138-2026 tillsynsbegäran.docx", "S 2138-2026")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13040-2024 tillsynsbegäran mail.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/S 2138-2026 tillsynsbegäran mail.docx", "S 2138-2026")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 24698-2023</t>
+          <t>A 62183-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5467,10 +5501,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45084</v>
+        <v>46006</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5483,7 +5517,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>5.5</v>
+        <v>0.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5519,46 +5553,46 @@
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24698-2023 artfynd.xlsx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62183-2025 artfynd.xlsx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24698-2023 karta.png", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62183-2025 karta.png", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24698-2023 georefererad karta.tif", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62183-2025 georefererad karta.tif", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24698-2023 FSC-klagomål.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62183-2025 FSC-klagomål.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24698-2023 FSC-klagomål mail.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62183-2025 FSC-klagomål mail.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24698-2023 tillsynsbegäran.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62183-2025 tillsynsbegäran.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24698-2023 tillsynsbegäran mail.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62183-2025 tillsynsbegäran mail.docx", "A 62183-2025")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 13384-2023</t>
+          <t>A 13040-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5568,14 +5602,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45005</v>
+        <v>45385</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5588,10 +5622,10 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -5603,7 +5637,7 @@
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5612,10 +5646,10 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -5628,42 +5662,42 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13384-2023 artfynd.xlsx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13040-2024 artfynd.xlsx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13384-2023 karta.png", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13040-2024 karta.png", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13384-2023 georefererad karta.tif", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13040-2024 georefererad karta.tif", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13384-2023 FSC-klagomål.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13040-2024 FSC-klagomål.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13384-2023 FSC-klagomål mail.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13040-2024 FSC-klagomål mail.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13384-2023 tillsynsbegäran.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13040-2024 tillsynsbegäran.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13384-2023 tillsynsbegäran mail.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13040-2024 tillsynsbegäran mail.docx", "A 13040-2024")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 62183-2025</t>
+          <t>A 13384-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5677,10 +5711,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46006</v>
+        <v>45005</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5693,16 +5727,16 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -5717,7 +5751,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -5729,39 +5763,39 @@
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62183-2025 artfynd.xlsx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13384-2023 artfynd.xlsx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62183-2025 karta.png", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13384-2023 karta.png", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62183-2025 georefererad karta.tif", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13384-2023 georefererad karta.tif", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62183-2025 FSC-klagomål.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13384-2023 FSC-klagomål.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62183-2025 FSC-klagomål mail.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13384-2023 FSC-klagomål mail.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62183-2025 tillsynsbegäran.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13384-2023 tillsynsbegäran.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62183-2025 tillsynsbegäran mail.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13384-2023 tillsynsbegäran mail.docx", "A 13384-2023")</f>
         <v/>
       </c>
     </row>
@@ -5785,7 +5819,7 @@
         <v>46210</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5890,7 +5924,7 @@
         <v>46273</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5978,7 +6012,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 26876-2022</t>
+          <t>A 24698-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5988,14 +6022,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44740</v>
+        <v>45084</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6008,7 +6042,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.7</v>
+        <v>5.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -6017,7 +6051,7 @@
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -6032,26 +6066,58 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="W48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24698-2023 artfynd.xlsx", "A 24698-2023")</f>
+        <v/>
+      </c>
+      <c r="X48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24698-2023 karta.png", "A 24698-2023")</f>
+        <v/>
+      </c>
+      <c r="Y48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24698-2023 georefererad karta.tif", "A 24698-2023")</f>
+        <v/>
+      </c>
+      <c r="AA48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24698-2023 FSC-klagomål.docx", "A 24698-2023")</f>
+        <v/>
+      </c>
+      <c r="AB48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24698-2023 FSC-klagomål mail.docx", "A 24698-2023")</f>
+        <v/>
+      </c>
+      <c r="AC48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24698-2023 tillsynsbegäran.docx", "A 24698-2023")</f>
+        <v/>
+      </c>
+      <c r="AD48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24698-2023 tillsynsbegäran mail.docx", "A 24698-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 57407-2025</t>
+          <t>A 26876-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6061,14 +6127,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45980</v>
+        <v>44740</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6081,7 +6147,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -6121,78 +6187,151 @@
       </c>
       <c r="V49" s="2" t="inlineStr"/>
     </row>
-    <row r="50">
+    <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
+          <t>A 57407-2025</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D50" s="1" t="n">
+        <v>45980</v>
+      </c>
+      <c r="E50" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
           <t>S 1602-2026</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D50" s="1" t="n">
+      <c r="D51" s="1" t="n">
         <v>46171</v>
       </c>
-      <c r="E50" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F50" t="inlineStr">
+      <c r="E51" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F51" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I50" t="n">
+      <c r="I51" t="n">
         <v>2.1</v>
       </c>
-      <c r="J50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" t="n">
-        <v>0</v>
-      </c>
-      <c r="V50" s="2" t="inlineStr"/>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt MÖRBYLÅNGA.xlsx
+++ b/Översikt MÖRBYLÅNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44964</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>44655</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>45177</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45096</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45685</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>46289</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>45475</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>45062</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>46195</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>46189</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>45254</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>45062</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>44508</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>44467</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>44811</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>45097</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 24778-2022</t>
+          <t>A 60875-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2722,10 +2722,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44728</v>
+        <v>45999</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2738,45 +2738,164 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>5</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>7</v>
+      </c>
+      <c r="R18" t="n">
         <v>2</v>
-      </c>
-      <c r="L18" t="n">
-        <v>7</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>8</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1</v>
       </c>
       <c r="S18" t="n">
         <v>11</v>
       </c>
       <c r="T18" t="n">
+        <v>12</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Järnek
+Mosippa
+Grönsångare
+Gulsparv
+Göktyta
+Mindre hackspett
+Svinrot
+Murgröna
+Spillkråka
+Kråka
+Skogsduva</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 60875-2025 artfynd.xlsx", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 60875-2025 karta.png", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 60875-2025 georefererad karta.tif", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 60875-2025 FSC-klagomål.docx", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 60875-2025 FSC-klagomål mail.docx", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 60875-2025 tillsynsbegäran.docx", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 60875-2025 tillsynsbegäran mail.docx", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 60875-2025 prioriterade fågelarter.docx", "A 60875-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 24778-2022</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>44728</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>7</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>8</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" t="n">
+        <v>11</v>
+      </c>
+      <c r="T19" t="n">
         <v>20</v>
       </c>
-      <c r="U18" t="n">
+      <c r="U19" t="n">
         <v>20</v>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Tofsäxing
 Backtimjan
@@ -2791,151 +2910,32 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24778-2022 artfynd.xlsx", "A 24778-2022")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24778-2022 karta.png", "A 24778-2022")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24778-2022 georefererad karta.tif", "A 24778-2022")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24778-2022 FSC-klagomål.docx", "A 24778-2022")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24778-2022 FSC-klagomål mail.docx", "A 24778-2022")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24778-2022 tillsynsbegäran.docx", "A 24778-2022")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24778-2022 tillsynsbegäran mail.docx", "A 24778-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 60875-2025</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45999</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J19" t="n">
-        <v>8</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>5</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>1</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>7</v>
-      </c>
-      <c r="R19" t="n">
-        <v>2</v>
-      </c>
-      <c r="S19" t="n">
-        <v>11</v>
-      </c>
-      <c r="T19" t="n">
-        <v>12</v>
-      </c>
-      <c r="U19" t="n">
-        <v>3</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Järnek
-Mosippa
-Grönsångare
-Gulsparv
-Göktyta
-Mindre hackspett
-Svinrot
-Murgröna
-Spillkråka
-Kråka
-Skogsduva</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 60875-2025 artfynd.xlsx", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 60875-2025 karta.png", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 60875-2025 georefererad karta.tif", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 60875-2025 FSC-klagomål.docx", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 60875-2025 FSC-klagomål mail.docx", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 60875-2025 tillsynsbegäran.docx", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 60875-2025 tillsynsbegäran mail.docx", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 60875-2025 prioriterade fågelarter.docx", "A 60875-2025")</f>
         <v/>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
         <v>45551</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>44616</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>45000</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>45530</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>45223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>45075</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>45169</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3742,7 +3742,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 43704-2025</t>
+          <t>A 43714-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3759,7 +3759,7 @@
         <v>45912</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3772,19 +3772,19 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.7</v>
+        <v>7.9</v>
       </c>
       <c r="J27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3796,21 +3796,135 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S27" t="n">
         <v>6</v>
       </c>
       <c r="T27" t="n">
+        <v>8</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Mindre bastardsvärmare
+Sexfläckig bastardsvärmare
+Grönsångare
+Murgröna
+Tibast
+Trädporella</t>
+        </is>
+      </c>
+      <c r="W27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43714-2025 artfynd.xlsx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="X27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43714-2025 karta.png", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="Y27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43714-2025 georefererad karta.tif", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AA27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43714-2025 FSC-klagomål.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AB27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43714-2025 FSC-klagomål mail.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AC27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43714-2025 tillsynsbegäran.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AD27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43714-2025 tillsynsbegäran mail.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 43714-2025 prioriterade fågelarter.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A 43704-2025</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>45912</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J28" t="n">
+        <v>5</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
         <v>6</v>
       </c>
-      <c r="U27" t="n">
-        <v>1</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="T28" t="n">
+        <v>6</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>Blomkålssvamp
 Långbensgroda
@@ -3820,146 +3934,32 @@
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W27">
+      <c r="W28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43704-2025 artfynd.xlsx", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="X27">
+      <c r="X28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43704-2025 karta.png", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="Y27">
+      <c r="Y28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43704-2025 georefererad karta.tif", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="AA27">
+      <c r="AA28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43704-2025 FSC-klagomål.docx", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="AB27">
+      <c r="AB28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43704-2025 FSC-klagomål mail.docx", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="AC27">
+      <c r="AC28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43704-2025 tillsynsbegäran.docx", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="AD27">
+      <c r="AD28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43704-2025 tillsynsbegäran mail.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>A 43714-2025</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>45912</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="J28" t="n">
-        <v>1</v>
-      </c>
-      <c r="K28" t="n">
-        <v>3</v>
-      </c>
-      <c r="L28" t="n">
-        <v>1</v>
-      </c>
-      <c r="M28" t="n">
-        <v>2</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>3</v>
-      </c>
-      <c r="R28" t="n">
-        <v>2</v>
-      </c>
-      <c r="S28" t="n">
-        <v>6</v>
-      </c>
-      <c r="T28" t="n">
-        <v>8</v>
-      </c>
-      <c r="U28" t="n">
-        <v>2</v>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>Mindre bastardsvärmare
-Sexfläckig bastardsvärmare
-Grönsångare
-Murgröna
-Tibast
-Trädporella</t>
-        </is>
-      </c>
-      <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43714-2025 artfynd.xlsx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43714-2025 karta.png", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43714-2025 georefererad karta.tif", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43714-2025 FSC-klagomål.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43714-2025 FSC-klagomål mail.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43714-2025 tillsynsbegäran.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43714-2025 tillsynsbegäran mail.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 43714-2025 prioriterade fågelarter.docx", "A 43714-2025")</f>
         <v/>
       </c>
     </row>
@@ -3983,7 +3983,7 @@
         <v>46190</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>46003</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>46038</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         <v>45616</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 19459-2023</t>
+          <t>A 26440-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45049</v>
+        <v>46183</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4440,16 +4440,16 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -4464,7 +4464,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -4473,12 +4473,232 @@
         <v>4</v>
       </c>
       <c r="T33" t="n">
+        <v>5</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>Backstarr
+Murgröna
+Nästrot
+Vätteros</t>
+        </is>
+      </c>
+      <c r="W33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 26440-2026 artfynd.xlsx", "A 26440-2026")</f>
+        <v/>
+      </c>
+      <c r="X33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 26440-2026 karta.png", "A 26440-2026")</f>
+        <v/>
+      </c>
+      <c r="Y33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 26440-2026 georefererad karta.tif", "A 26440-2026")</f>
+        <v/>
+      </c>
+      <c r="AA33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 26440-2026 FSC-klagomål.docx", "A 26440-2026")</f>
+        <v/>
+      </c>
+      <c r="AB33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 26440-2026 FSC-klagomål mail.docx", "A 26440-2026")</f>
+        <v/>
+      </c>
+      <c r="AC33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 26440-2026 tillsynsbegäran.docx", "A 26440-2026")</f>
+        <v/>
+      </c>
+      <c r="AD33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 26440-2026 tillsynsbegäran mail.docx", "A 26440-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>A 34431-2026</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="E34" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" t="n">
+        <v>3</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
         <v>4</v>
       </c>
-      <c r="U33" t="n">
+      <c r="T34" t="n">
+        <v>5</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Mindre hackspett
+Sandtimotej
+Murgröna</t>
+        </is>
+      </c>
+      <c r="W34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 34431-2026 artfynd.xlsx", "A 34431-2026")</f>
+        <v/>
+      </c>
+      <c r="X34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 34431-2026 karta.png", "A 34431-2026")</f>
+        <v/>
+      </c>
+      <c r="Y34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 34431-2026 georefererad karta.tif", "A 34431-2026")</f>
+        <v/>
+      </c>
+      <c r="AA34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 34431-2026 FSC-klagomål.docx", "A 34431-2026")</f>
+        <v/>
+      </c>
+      <c r="AB34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 34431-2026 FSC-klagomål mail.docx", "A 34431-2026")</f>
+        <v/>
+      </c>
+      <c r="AC34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 34431-2026 tillsynsbegäran.docx", "A 34431-2026")</f>
+        <v/>
+      </c>
+      <c r="AD34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 34431-2026 tillsynsbegäran mail.docx", "A 34431-2026")</f>
+        <v/>
+      </c>
+      <c r="AE34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 34431-2026 prioriterade fågelarter.docx", "A 34431-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>A 19459-2023</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D35" s="1" t="n">
+        <v>45049</v>
+      </c>
+      <c r="E35" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
         <v>4</v>
       </c>
-      <c r="V33" s="2" t="inlineStr">
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>4</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>4</v>
+      </c>
+      <c r="T35" t="n">
+        <v>4</v>
+      </c>
+      <c r="U35" t="n">
+        <v>4</v>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
         <is>
           <t>Kavelhirs
 Kösa
@@ -4486,252 +4706,32 @@
 Riddarsporre</t>
         </is>
       </c>
-      <c r="W33">
+      <c r="W35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 19459-2023 artfynd.xlsx", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="X33">
+      <c r="X35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 19459-2023 karta.png", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="Y33">
+      <c r="Y35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 19459-2023 georefererad karta.tif", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="AA33">
+      <c r="AA35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 19459-2023 FSC-klagomål.docx", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="AB33">
+      <c r="AB35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 19459-2023 FSC-klagomål mail.docx", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="AC33">
+      <c r="AC35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 19459-2023 tillsynsbegäran.docx", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="AD33">
+      <c r="AD35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 19459-2023 tillsynsbegäran mail.docx", "A 19459-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>A 26440-2026</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="n">
-        <v>46183</v>
-      </c>
-      <c r="E34" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J34" t="n">
-        <v>1</v>
-      </c>
-      <c r="K34" t="n">
-        <v>3</v>
-      </c>
-      <c r="L34" t="n">
-        <v>1</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>1</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>4</v>
-      </c>
-      <c r="T34" t="n">
-        <v>5</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>Backstarr
-Murgröna
-Nästrot
-Vätteros</t>
-        </is>
-      </c>
-      <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 26440-2026 artfynd.xlsx", "A 26440-2026")</f>
-        <v/>
-      </c>
-      <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 26440-2026 karta.png", "A 26440-2026")</f>
-        <v/>
-      </c>
-      <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 26440-2026 georefererad karta.tif", "A 26440-2026")</f>
-        <v/>
-      </c>
-      <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 26440-2026 FSC-klagomål.docx", "A 26440-2026")</f>
-        <v/>
-      </c>
-      <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 26440-2026 FSC-klagomål mail.docx", "A 26440-2026")</f>
-        <v/>
-      </c>
-      <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 26440-2026 tillsynsbegäran.docx", "A 26440-2026")</f>
-        <v/>
-      </c>
-      <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 26440-2026 tillsynsbegäran mail.docx", "A 26440-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>A 34431-2026</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="n">
-        <v>46254</v>
-      </c>
-      <c r="E35" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="J35" t="n">
-        <v>2</v>
-      </c>
-      <c r="K35" t="n">
-        <v>1</v>
-      </c>
-      <c r="L35" t="n">
-        <v>3</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>3</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>4</v>
-      </c>
-      <c r="T35" t="n">
-        <v>5</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1</v>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Mindre hackspett
-Sandtimotej
-Murgröna</t>
-        </is>
-      </c>
-      <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 34431-2026 artfynd.xlsx", "A 34431-2026")</f>
-        <v/>
-      </c>
-      <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 34431-2026 karta.png", "A 34431-2026")</f>
-        <v/>
-      </c>
-      <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 34431-2026 georefererad karta.tif", "A 34431-2026")</f>
-        <v/>
-      </c>
-      <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 34431-2026 FSC-klagomål.docx", "A 34431-2026")</f>
-        <v/>
-      </c>
-      <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 34431-2026 FSC-klagomål mail.docx", "A 34431-2026")</f>
-        <v/>
-      </c>
-      <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 34431-2026 tillsynsbegäran.docx", "A 34431-2026")</f>
-        <v/>
-      </c>
-      <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 34431-2026 tillsynsbegäran mail.docx", "A 34431-2026")</f>
-        <v/>
-      </c>
-      <c r="AE35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 34431-2026 prioriterade fågelarter.docx", "A 34431-2026")</f>
         <v/>
       </c>
     </row>
@@ -4755,7 +4755,7 @@
         <v>45912</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 29360-2026</t>
+          <t>A 15600-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4859,10 +4859,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46203</v>
+        <v>45747</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4875,19 +4875,19 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -4899,10 +4899,10 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>3</v>
@@ -4914,145 +4914,145 @@
         <v>1</v>
       </c>
       <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>Kragjordstjärna
+Murgröna
+Scharlakansvårskål agg.</t>
+        </is>
+      </c>
+      <c r="W37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 15600-2025 artfynd.xlsx", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="X37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 15600-2025 karta.png", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="Y37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 15600-2025 georefererad karta.tif", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="AA37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 15600-2025 FSC-klagomål.docx", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="AB37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 15600-2025 FSC-klagomål mail.docx", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="AC37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 15600-2025 tillsynsbegäran.docx", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="AD37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 15600-2025 tillsynsbegäran mail.docx", "A 15600-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>A 29360-2026</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D38" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
         <is>
           <t>Mindre blåvinge
 Silversmygare
 Ekoxe</t>
         </is>
       </c>
-      <c r="W37">
+      <c r="W38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 29360-2026 artfynd.xlsx", "A 29360-2026")</f>
         <v/>
       </c>
-      <c r="X37">
+      <c r="X38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 29360-2026 karta.png", "A 29360-2026")</f>
         <v/>
       </c>
-      <c r="Y37">
+      <c r="Y38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 29360-2026 georefererad karta.tif", "A 29360-2026")</f>
         <v/>
       </c>
-      <c r="AA37">
+      <c r="AA38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 29360-2026 FSC-klagomål.docx", "A 29360-2026")</f>
         <v/>
       </c>
-      <c r="AB37">
+      <c r="AB38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 29360-2026 FSC-klagomål mail.docx", "A 29360-2026")</f>
         <v/>
       </c>
-      <c r="AC37">
+      <c r="AC38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 29360-2026 tillsynsbegäran.docx", "A 29360-2026")</f>
         <v/>
       </c>
-      <c r="AD37">
+      <c r="AD38">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 29360-2026 tillsynsbegäran mail.docx", "A 29360-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>A 15600-2025</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D38" s="1" t="n">
-        <v>45747</v>
-      </c>
-      <c r="E38" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I38" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="n">
-        <v>3</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>3</v>
-      </c>
-      <c r="T38" t="n">
-        <v>3</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1</v>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t>Kragjordstjärna
-Murgröna
-Scharlakansvårskål agg.</t>
-        </is>
-      </c>
-      <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 15600-2025 artfynd.xlsx", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 15600-2025 karta.png", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 15600-2025 georefererad karta.tif", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 15600-2025 FSC-klagomål.docx", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 15600-2025 FSC-klagomål mail.docx", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 15600-2025 tillsynsbegäran.docx", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 15600-2025 tillsynsbegäran mail.docx", "A 15600-2025")</f>
         <v/>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
         <v>44470</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 62231-2023</t>
+          <t>A 72167-2021</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5175,14 +5175,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45267</v>
+        <v>44544</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J40" t="n">
         <v>1</v>
@@ -5236,42 +5236,46 @@
       <c r="V40" s="2" t="inlineStr">
         <is>
           <t>Murgröna
-Blåsippa</t>
+Röd glada</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62231-2023 artfynd.xlsx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 72167-2021 artfynd.xlsx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62231-2023 karta.png", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 72167-2021 karta.png", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62231-2023 georefererad karta.tif", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 72167-2021 georefererad karta.tif", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62231-2023 FSC-klagomål.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 72167-2021 FSC-klagomål.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62231-2023 FSC-klagomål mail.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 72167-2021 FSC-klagomål mail.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62231-2023 tillsynsbegäran.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 72167-2021 tillsynsbegäran.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62231-2023 tillsynsbegäran mail.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 72167-2021 tillsynsbegäran mail.docx", "A 72167-2021")</f>
+        <v/>
+      </c>
+      <c r="AE40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 72167-2021 prioriterade fågelarter.docx", "A 72167-2021")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 72167-2021</t>
+          <t>A 62231-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5281,14 +5285,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44544</v>
+        <v>45267</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5301,7 +5305,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J41" t="n">
         <v>1</v>
@@ -5342,39 +5346,35 @@
       <c r="V41" s="2" t="inlineStr">
         <is>
           <t>Murgröna
-Röd glada</t>
+Blåsippa</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 72167-2021 artfynd.xlsx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62231-2023 artfynd.xlsx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 72167-2021 karta.png", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62231-2023 karta.png", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 72167-2021 georefererad karta.tif", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62231-2023 georefererad karta.tif", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 72167-2021 FSC-klagomål.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62231-2023 FSC-klagomål.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 72167-2021 FSC-klagomål mail.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62231-2023 FSC-klagomål mail.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 72167-2021 tillsynsbegäran.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62231-2023 tillsynsbegäran.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 72167-2021 tillsynsbegäran mail.docx", "A 72167-2021")</f>
-        <v/>
-      </c>
-      <c r="AE41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 72167-2021 prioriterade fågelarter.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62231-2023 tillsynsbegäran mail.docx", "A 62231-2023")</f>
         <v/>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
         <v>46246</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 62183-2025</t>
+          <t>A 13040-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5497,14 +5497,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46006</v>
+        <v>45385</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5526,13 +5526,13 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5544,7 +5544,7 @@
         <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5553,46 +5553,46 @@
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62183-2025 artfynd.xlsx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13040-2024 artfynd.xlsx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62183-2025 karta.png", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13040-2024 karta.png", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62183-2025 georefererad karta.tif", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13040-2024 georefererad karta.tif", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62183-2025 FSC-klagomål.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13040-2024 FSC-klagomål.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62183-2025 FSC-klagomål mail.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13040-2024 FSC-klagomål mail.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62183-2025 tillsynsbegäran.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13040-2024 tillsynsbegäran.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62183-2025 tillsynsbegäran mail.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13040-2024 tillsynsbegäran mail.docx", "A 13040-2024")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 13040-2024</t>
+          <t>A 13384-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5602,14 +5602,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45385</v>
+        <v>45005</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5622,10 +5622,10 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -5637,7 +5637,7 @@
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5646,10 +5646,10 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -5662,42 +5662,42 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13040-2024 artfynd.xlsx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13384-2023 artfynd.xlsx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13040-2024 karta.png", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13384-2023 karta.png", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13040-2024 georefererad karta.tif", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13384-2023 georefererad karta.tif", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13040-2024 FSC-klagomål.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13384-2023 FSC-klagomål.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13040-2024 FSC-klagomål mail.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13384-2023 FSC-klagomål mail.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13040-2024 tillsynsbegäran.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13384-2023 tillsynsbegäran.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13040-2024 tillsynsbegäran mail.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13384-2023 tillsynsbegäran mail.docx", "A 13384-2023")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 13384-2023</t>
+          <t>A 24698-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45005</v>
+        <v>45084</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5727,16 +5727,16 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.9</v>
+        <v>5.5</v>
       </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -5751,7 +5751,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -5767,42 +5767,42 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13384-2023 artfynd.xlsx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24698-2023 artfynd.xlsx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13384-2023 karta.png", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24698-2023 karta.png", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13384-2023 georefererad karta.tif", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24698-2023 georefererad karta.tif", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13384-2023 FSC-klagomål.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24698-2023 FSC-klagomål.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13384-2023 FSC-klagomål mail.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24698-2023 FSC-klagomål mail.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13384-2023 tillsynsbegäran.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24698-2023 tillsynsbegäran.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13384-2023 tillsynsbegäran mail.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24698-2023 tillsynsbegäran mail.docx", "A 24698-2023")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 30492-2026</t>
+          <t>A 62183-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5812,14 +5812,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46210</v>
+        <v>46006</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5872,42 +5872,42 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 30492-2026 artfynd.xlsx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62183-2025 artfynd.xlsx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 30492-2026 karta.png", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62183-2025 karta.png", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 30492-2026 georefererad karta.tif", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62183-2025 georefererad karta.tif", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 30492-2026 FSC-klagomål.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62183-2025 FSC-klagomål.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 30492-2026 FSC-klagomål mail.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62183-2025 FSC-klagomål mail.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 30492-2026 tillsynsbegäran.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62183-2025 tillsynsbegäran.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 30492-2026 tillsynsbegäran mail.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62183-2025 tillsynsbegäran mail.docx", "A 62183-2025")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 36928-2026</t>
+          <t>A 30492-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5917,14 +5917,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46273</v>
+        <v>46210</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5937,16 +5937,16 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -5961,7 +5961,7 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
@@ -5977,42 +5977,42 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 36928-2026 artfynd.xlsx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 30492-2026 artfynd.xlsx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 36928-2026 karta.png", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 30492-2026 karta.png", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 36928-2026 georefererad karta.tif", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 30492-2026 georefererad karta.tif", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 36928-2026 FSC-klagomål.docx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 30492-2026 FSC-klagomål.docx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 36928-2026 FSC-klagomål mail.docx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 30492-2026 FSC-klagomål mail.docx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 36928-2026 tillsynsbegäran.docx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 30492-2026 tillsynsbegäran.docx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 36928-2026 tillsynsbegäran mail.docx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 30492-2026 tillsynsbegäran mail.docx", "A 30492-2026")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 24698-2023</t>
+          <t>A 36928-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6026,10 +6026,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45084</v>
+        <v>46273</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6042,16 +6042,16 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>5.5</v>
+        <v>1.3</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -6066,7 +6066,7 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
@@ -6078,39 +6078,39 @@
         <v>1</v>
       </c>
       <c r="U48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="W48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24698-2023 artfynd.xlsx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 36928-2026 artfynd.xlsx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="X48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24698-2023 karta.png", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 36928-2026 karta.png", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="Y48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24698-2023 georefererad karta.tif", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 36928-2026 georefererad karta.tif", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AA48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24698-2023 FSC-klagomål.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 36928-2026 FSC-klagomål.docx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AB48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24698-2023 FSC-klagomål mail.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 36928-2026 FSC-klagomål mail.docx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AC48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24698-2023 tillsynsbegäran.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 36928-2026 tillsynsbegäran.docx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AD48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24698-2023 tillsynsbegäran mail.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 36928-2026 tillsynsbegäran mail.docx", "A 36928-2026")</f>
         <v/>
       </c>
     </row>
@@ -6134,7 +6134,7 @@
         <v>44740</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6207,7 +6207,7 @@
         <v>45980</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
         <v>46171</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>

--- a/Översikt MÖRBYLÅNGA.xlsx
+++ b/Översikt MÖRBYLÅNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44964</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>44655</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>45177</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45096</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45685</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>46289</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>45475</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>45062</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>46195</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>46189</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>45254</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>45062</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>44508</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>44467</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>44811</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>45097</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>45999</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>44728</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>45551</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>44616</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>45000</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>45530</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>45223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>45075</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>45169</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>45912</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>45912</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
         <v>46190</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>46003</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>46038</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         <v>45616</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4427,7 +4427,7 @@
         <v>46183</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>46254</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>45049</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>45912</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>45747</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>46203</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         <v>44470</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         <v>44544</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         <v>45267</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         <v>46246</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>45385</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>45005</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         <v>45084</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         <v>46006</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>46210</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>46273</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>44740</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6207,7 +6207,7 @@
         <v>45980</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
         <v>46171</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>

--- a/Översikt MÖRBYLÅNGA.xlsx
+++ b/Översikt MÖRBYLÅNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44964</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>44655</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>45177</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45096</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45685</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>46289</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>45475</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>45062</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>46195</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>46189</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>45254</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>45062</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>44508</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>44467</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>44811</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>45097</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>45999</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>44728</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>45551</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>44616</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>45000</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>45530</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>45223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>45075</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>45169</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>45912</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>45912</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
         <v>46190</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>46003</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>46038</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         <v>45616</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4427,7 +4427,7 @@
         <v>46183</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>46254</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>45049</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>45912</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>45747</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>46203</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         <v>44470</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         <v>44544</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         <v>45267</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         <v>46246</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>45385</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>45005</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         <v>45084</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         <v>46006</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>46210</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>46273</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>44740</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6207,7 +6207,7 @@
         <v>45980</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
         <v>46171</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>

--- a/Översikt MÖRBYLÅNGA.xlsx
+++ b/Översikt MÖRBYLÅNGA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE51"/>
+  <dimension ref="A1:AE50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44964</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>44655</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>45177</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45096</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45685</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>46289</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>45475</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>45062</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>46195</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>46189</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>45254</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>45062</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>44508</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 52906-2021</t>
+          <t>A 60875-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2373,10 +2373,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44467</v>
+        <v>45999</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2392,22 +2392,22 @@
         <v>2.1</v>
       </c>
       <c r="J15" t="n">
+        <v>8</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
         <v>5</v>
       </c>
-      <c r="K15" t="n">
-        <v>2</v>
-      </c>
-      <c r="L15" t="n">
-        <v>4</v>
-      </c>
       <c r="M15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -2416,69 +2416,69 @@
         <v>7</v>
       </c>
       <c r="R15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S15" t="n">
         <v>11</v>
       </c>
       <c r="T15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="U15" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Beryllspindling
-Elastisk spindling
-Grönkantad spindling
-Gulprickig vaxskivling
+          <t>Järnek
+Mosippa
+Grönsångare
 Gulsparv
-Järnsparv
-Rödvingetrast
-Lindspindling
+Göktyta
+Mindre hackspett
+Svinrot
 Murgröna
-Blåsippa
-Näktergal</t>
+Spillkråka
+Kråka
+Skogsduva</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 52906-2021 artfynd.xlsx", "A 52906-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 60875-2025 artfynd.xlsx", "A 60875-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 52906-2021 karta.png", "A 52906-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 60875-2025 karta.png", "A 60875-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 52906-2021 georefererad karta.tif", "A 52906-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 60875-2025 georefererad karta.tif", "A 60875-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 52906-2021 FSC-klagomål.docx", "A 52906-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 60875-2025 FSC-klagomål.docx", "A 60875-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 52906-2021 FSC-klagomål mail.docx", "A 52906-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 60875-2025 FSC-klagomål mail.docx", "A 60875-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 52906-2021 tillsynsbegäran.docx", "A 52906-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 60875-2025 tillsynsbegäran.docx", "A 60875-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 52906-2021 tillsynsbegäran mail.docx", "A 52906-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 60875-2025 tillsynsbegäran mail.docx", "A 60875-2025")</f>
         <v/>
       </c>
       <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 52906-2021 prioriterade fågelarter.docx", "A 52906-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 60875-2025 prioriterade fågelarter.docx", "A 60875-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 38039-2022</t>
+          <t>A 24778-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2488,14 +2488,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44811</v>
+        <v>44728</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2508,19 +2508,19 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>7.4</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L16" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>1</v>
@@ -2532,21 +2532,136 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>11</v>
       </c>
       <c r="T16" t="n">
+        <v>20</v>
+      </c>
+      <c r="U16" t="n">
+        <v>20</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Tofsäxing
+Backtimjan
+Flentimotej
+Grådådra
+Poppeltofsskivling
+Slåtterfibbla
+Sminkrot
+Solvända
+Kalktallört
+Murgröna
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24778-2022 artfynd.xlsx", "A 24778-2022")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24778-2022 karta.png", "A 24778-2022")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24778-2022 georefererad karta.tif", "A 24778-2022")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24778-2022 FSC-klagomål.docx", "A 24778-2022")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24778-2022 FSC-klagomål mail.docx", "A 24778-2022")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24778-2022 tillsynsbegäran.docx", "A 24778-2022")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24778-2022 tillsynsbegäran mail.docx", "A 24778-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 38039-2022</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>44811</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>4</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>6</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2</v>
+      </c>
+      <c r="S17" t="n">
+        <v>11</v>
+      </c>
+      <c r="T17" t="n">
         <v>13</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U17" t="n">
         <v>12</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Ask
 Grov gulmossa
@@ -2561,107 +2676,107 @@
 Gullviva</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 38039-2022 artfynd.xlsx", "A 38039-2022")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 38039-2022 karta.png", "A 38039-2022")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 38039-2022 georefererad karta.tif", "A 38039-2022")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 38039-2022 FSC-klagomål.docx", "A 38039-2022")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 38039-2022 FSC-klagomål mail.docx", "A 38039-2022")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 38039-2022 tillsynsbegäran.docx", "A 38039-2022")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 38039-2022 tillsynsbegäran mail.docx", "A 38039-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>A 27636-2023</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D17" s="1" t="n">
+      <c r="D18" s="1" t="n">
         <v>45097</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F17" t="inlineStr">
+      <c r="E18" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I17" t="n">
+      <c r="I18" t="n">
         <v>7.4</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J18" t="n">
         <v>4</v>
       </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
         <v>4</v>
       </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
         <v>6</v>
       </c>
-      <c r="R17" t="n">
+      <c r="R18" t="n">
         <v>2</v>
       </c>
-      <c r="S17" t="n">
+      <c r="S18" t="n">
         <v>11</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T18" t="n">
         <v>13</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U18" t="n">
         <v>11</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Ask
 Grov gulmossa
@@ -2676,158 +2791,39 @@
 Gullviva</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 27636-2023 artfynd.xlsx", "A 27636-2023")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 27636-2023 karta.png", "A 27636-2023")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 27636-2023 georefererad karta.tif", "A 27636-2023")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 27636-2023 FSC-klagomål.docx", "A 27636-2023")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 27636-2023 FSC-klagomål mail.docx", "A 27636-2023")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 27636-2023 tillsynsbegäran.docx", "A 27636-2023")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 27636-2023 tillsynsbegäran mail.docx", "A 27636-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 60875-2025</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45999</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J18" t="n">
-        <v>8</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>5</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>7</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2</v>
-      </c>
-      <c r="S18" t="n">
-        <v>11</v>
-      </c>
-      <c r="T18" t="n">
-        <v>12</v>
-      </c>
-      <c r="U18" t="n">
-        <v>3</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Järnek
-Mosippa
-Grönsångare
-Gulsparv
-Göktyta
-Mindre hackspett
-Svinrot
-Murgröna
-Spillkråka
-Kråka
-Skogsduva</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 60875-2025 artfynd.xlsx", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 60875-2025 karta.png", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 60875-2025 georefererad karta.tif", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 60875-2025 FSC-klagomål.docx", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 60875-2025 FSC-klagomål mail.docx", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 60875-2025 tillsynsbegäran.docx", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 60875-2025 tillsynsbegäran mail.docx", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 60875-2025 prioriterade fågelarter.docx", "A 60875-2025")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 24778-2022</t>
+          <t>A 39320-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2837,14 +2833,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44728</v>
+        <v>45551</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2857,7 +2853,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2866,151 +2862,36 @@
         <v>2</v>
       </c>
       <c r="L19" t="n">
+        <v>4</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>7</v>
       </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>1</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>8</v>
-      </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="n">
         <v>11</v>
       </c>
-      <c r="T19" t="n">
-        <v>20</v>
-      </c>
       <c r="U19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Tofsäxing
-Backtimjan
-Flentimotej
-Grådådra
-Poppeltofsskivling
-Slåtterfibbla
-Sminkrot
-Solvända
-Kalktallört
-Murgröna
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24778-2022 artfynd.xlsx", "A 24778-2022")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24778-2022 karta.png", "A 24778-2022")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24778-2022 georefererad karta.tif", "A 24778-2022")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24778-2022 FSC-klagomål.docx", "A 24778-2022")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24778-2022 FSC-klagomål mail.docx", "A 24778-2022")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24778-2022 tillsynsbegäran.docx", "A 24778-2022")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24778-2022 tillsynsbegäran mail.docx", "A 24778-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 39320-2024</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45551</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>2</v>
-      </c>
-      <c r="L20" t="n">
-        <v>4</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N20" t="n">
-        <v>1</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>7</v>
-      </c>
-      <c r="R20" t="n">
-        <v>3</v>
-      </c>
-      <c r="S20" t="n">
-        <v>10</v>
-      </c>
-      <c r="T20" t="n">
-        <v>11</v>
-      </c>
-      <c r="U20" t="n">
-        <v>10</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Vresalm
 Lundalm
@@ -3024,107 +2905,107 @@
 Skogsduva</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 39320-2024 artfynd.xlsx", "A 39320-2024")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 39320-2024 karta.png", "A 39320-2024")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 39320-2024 georefererad karta.tif", "A 39320-2024")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 39320-2024 FSC-klagomål.docx", "A 39320-2024")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 39320-2024 FSC-klagomål mail.docx", "A 39320-2024")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 39320-2024 tillsynsbegäran.docx", "A 39320-2024")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 39320-2024 tillsynsbegäran mail.docx", "A 39320-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>S 1122-2022</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D21" s="1" t="n">
+      <c r="D20" s="1" t="n">
         <v>44616</v>
       </c>
-      <c r="E21" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F21" t="inlineStr">
+      <c r="E20" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I21" t="n">
+      <c r="I20" t="n">
         <v>2.6</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J20" t="n">
         <v>2</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K20" t="n">
         <v>3</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L20" t="n">
         <v>3</v>
       </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
         <v>3</v>
       </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
         <v>6</v>
       </c>
-      <c r="R21" t="n">
+      <c r="R20" t="n">
         <v>3</v>
       </c>
-      <c r="S21" t="n">
+      <c r="S20" t="n">
         <v>10</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T20" t="n">
         <v>16</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U20" t="n">
         <v>15</v>
       </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Ask
 Lundalm
@@ -3138,107 +3019,107 @@
 Sankt pers nycklar</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/S 1122-2022 artfynd.xlsx", "S 1122-2022")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/S 1122-2022 karta.png", "S 1122-2022")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/S 1122-2022 georefererad karta.tif", "S 1122-2022")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/S 1122-2022 FSC-klagomål.docx", "S 1122-2022")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/S 1122-2022 FSC-klagomål mail.docx", "S 1122-2022")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/S 1122-2022 tillsynsbegäran.docx", "S 1122-2022")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/S 1122-2022 tillsynsbegäran mail.docx", "S 1122-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>S 929-2023</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D22" s="1" t="n">
+      <c r="D21" s="1" t="n">
         <v>45000</v>
       </c>
-      <c r="E22" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F22" t="inlineStr">
+      <c r="E21" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I22" t="n">
+      <c r="I21" t="n">
         <v>4.7</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J21" t="n">
         <v>4</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K21" t="n">
         <v>2</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L21" t="n">
         <v>3</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M21" t="n">
         <v>3</v>
       </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
         <v>6</v>
       </c>
-      <c r="R22" t="n">
+      <c r="R21" t="n">
         <v>3</v>
       </c>
-      <c r="S22" t="n">
+      <c r="S21" t="n">
         <v>9</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T21" t="n">
         <v>12</v>
       </c>
-      <c r="U22" t="n">
+      <c r="U21" t="n">
         <v>8</v>
       </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Liten jordstjärna
 Stare
@@ -3251,111 +3132,111 @@
 Kopparödla</t>
         </is>
       </c>
-      <c r="W22">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/S 929-2023 artfynd.xlsx", "S 929-2023")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/S 929-2023 karta.png", "S 929-2023")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/S 929-2023 georefererad karta.tif", "S 929-2023")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/S 929-2023 FSC-klagomål.docx", "S 929-2023")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/S 929-2023 FSC-klagomål mail.docx", "S 929-2023")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/S 929-2023 tillsynsbegäran.docx", "S 929-2023")</f>
         <v/>
       </c>
-      <c r="AD22">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/S 929-2023 tillsynsbegäran mail.docx", "S 929-2023")</f>
         <v/>
       </c>
-      <c r="AE22">
+      <c r="AE21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/S 929-2023 prioriterade fågelarter.docx", "S 929-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>A 35242-2024</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D23" s="1" t="n">
+      <c r="D22" s="1" t="n">
         <v>45530</v>
       </c>
-      <c r="E23" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F23" t="inlineStr">
+      <c r="E22" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I23" t="n">
+      <c r="I22" t="n">
         <v>0.9</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J22" t="n">
         <v>2</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K22" t="n">
         <v>3</v>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>3</v>
       </c>
-      <c r="N23" t="n">
-        <v>1</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
+      <c r="N22" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
         <v>4</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R22" t="n">
         <v>4</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S22" t="n">
         <v>8</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T22" t="n">
         <v>12</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U22" t="n">
         <v>6</v>
       </c>
-      <c r="V23" s="2" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Sandgeting
 Liten diskröksvamp
@@ -3367,111 +3248,111 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W23">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 35242-2024 artfynd.xlsx", "A 35242-2024")</f>
         <v/>
       </c>
-      <c r="X23">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 35242-2024 karta.png", "A 35242-2024")</f>
         <v/>
       </c>
-      <c r="Y23">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 35242-2024 georefererad karta.tif", "A 35242-2024")</f>
         <v/>
       </c>
-      <c r="Z23">
+      <c r="Z22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/knärot/A 35242-2024 karta knärot.png", "A 35242-2024")</f>
         <v/>
       </c>
-      <c r="AA23">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 35242-2024 FSC-klagomål.docx", "A 35242-2024")</f>
         <v/>
       </c>
-      <c r="AB23">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 35242-2024 FSC-klagomål mail.docx", "A 35242-2024")</f>
         <v/>
       </c>
-      <c r="AC23">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 35242-2024 tillsynsbegäran.docx", "A 35242-2024")</f>
         <v/>
       </c>
-      <c r="AD23">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 35242-2024 tillsynsbegäran mail.docx", "A 35242-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>S 3773-2023</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D24" s="1" t="n">
+      <c r="D23" s="1" t="n">
         <v>45223</v>
       </c>
-      <c r="E24" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F24" t="inlineStr">
+      <c r="E23" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I24" t="n">
+      <c r="I23" t="n">
         <v>0.3</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J23" t="n">
         <v>2</v>
       </c>
-      <c r="K24" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" t="n">
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
         <v>3</v>
       </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
         <v>2</v>
       </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
         <v>5</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R23" t="n">
         <v>2</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S23" t="n">
         <v>8</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T23" t="n">
         <v>9</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U23" t="n">
         <v>9</v>
       </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Ask
 Lundalm
@@ -3483,107 +3364,107 @@
 Gullviva</t>
         </is>
       </c>
-      <c r="W24">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/S 3773-2023 artfynd.xlsx", "S 3773-2023")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/S 3773-2023 karta.png", "S 3773-2023")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/S 3773-2023 georefererad karta.tif", "S 3773-2023")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/S 3773-2023 FSC-klagomål.docx", "S 3773-2023")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/S 3773-2023 FSC-klagomål mail.docx", "S 3773-2023")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/S 3773-2023 tillsynsbegäran.docx", "S 3773-2023")</f>
         <v/>
       </c>
-      <c r="AD24">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/S 3773-2023 tillsynsbegäran mail.docx", "S 3773-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>S 1833-2023</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D25" s="1" t="n">
+      <c r="D24" s="1" t="n">
         <v>45075</v>
       </c>
-      <c r="E25" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F25" t="inlineStr">
+      <c r="E24" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I25" t="n">
+      <c r="I24" t="n">
         <v>0.4</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J24" t="n">
         <v>3</v>
       </c>
-      <c r="K25" t="n">
+      <c r="K24" t="n">
         <v>2</v>
       </c>
-      <c r="L25" t="n">
+      <c r="L24" t="n">
         <v>3</v>
       </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
         <v>3</v>
       </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
         <v>8</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T24" t="n">
         <v>11</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U24" t="n">
         <v>10</v>
       </c>
-      <c r="V25" s="2" t="inlineStr">
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>Sårläka
 Vippärt
@@ -3595,107 +3476,107 @@
 Gullviva</t>
         </is>
       </c>
-      <c r="W25">
+      <c r="W24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/S 1833-2023 artfynd.xlsx", "S 1833-2023")</f>
         <v/>
       </c>
-      <c r="X25">
+      <c r="X24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/S 1833-2023 karta.png", "S 1833-2023")</f>
         <v/>
       </c>
-      <c r="Y25">
+      <c r="Y24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/S 1833-2023 georefererad karta.tif", "S 1833-2023")</f>
         <v/>
       </c>
-      <c r="AA25">
+      <c r="AA24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/S 1833-2023 FSC-klagomål.docx", "S 1833-2023")</f>
         <v/>
       </c>
-      <c r="AB25">
+      <c r="AB24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/S 1833-2023 FSC-klagomål mail.docx", "S 1833-2023")</f>
         <v/>
       </c>
-      <c r="AC25">
+      <c r="AC24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/S 1833-2023 tillsynsbegäran.docx", "S 1833-2023")</f>
         <v/>
       </c>
-      <c r="AD25">
+      <c r="AD24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/S 1833-2023 tillsynsbegäran mail.docx", "S 1833-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>A 40361-2023</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D26" s="1" t="n">
+      <c r="D25" s="1" t="n">
         <v>45169</v>
       </c>
-      <c r="E26" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F26" t="inlineStr">
+      <c r="E25" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I26" t="n">
+      <c r="I25" t="n">
         <v>1.1</v>
       </c>
-      <c r="J26" t="n">
-        <v>1</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
         <v>4</v>
       </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
         <v>2</v>
       </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
         <v>6</v>
       </c>
-      <c r="R26" t="n">
+      <c r="R25" t="n">
         <v>2</v>
       </c>
-      <c r="S26" t="n">
+      <c r="S25" t="n">
         <v>7</v>
       </c>
-      <c r="T26" t="n">
+      <c r="T25" t="n">
         <v>11</v>
       </c>
-      <c r="U26" t="n">
+      <c r="U25" t="n">
         <v>10</v>
       </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Ask
 Lundalm
@@ -3706,36 +3587,146 @@
 Näktergal</t>
         </is>
       </c>
+      <c r="W25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 40361-2023 artfynd.xlsx", "A 40361-2023")</f>
+        <v/>
+      </c>
+      <c r="X25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 40361-2023 karta.png", "A 40361-2023")</f>
+        <v/>
+      </c>
+      <c r="Y25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 40361-2023 georefererad karta.tif", "A 40361-2023")</f>
+        <v/>
+      </c>
+      <c r="AA25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 40361-2023 FSC-klagomål.docx", "A 40361-2023")</f>
+        <v/>
+      </c>
+      <c r="AB25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 40361-2023 FSC-klagomål mail.docx", "A 40361-2023")</f>
+        <v/>
+      </c>
+      <c r="AC25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 40361-2023 tillsynsbegäran.docx", "A 40361-2023")</f>
+        <v/>
+      </c>
+      <c r="AD25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 40361-2023 tillsynsbegäran mail.docx", "A 40361-2023")</f>
+        <v/>
+      </c>
+      <c r="AE25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 40361-2023 prioriterade fågelarter.docx", "A 40361-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A 43704-2025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>45912</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>6</v>
+      </c>
+      <c r="T26" t="n">
+        <v>6</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp
+Långbensgroda
+Större vattensalamander
+Åkergroda
+Mindre vattensalamander
+Vanlig padda</t>
+        </is>
+      </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 40361-2023 artfynd.xlsx", "A 40361-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43704-2025 artfynd.xlsx", "A 43704-2025")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 40361-2023 karta.png", "A 40361-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43704-2025 karta.png", "A 43704-2025")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 40361-2023 georefererad karta.tif", "A 40361-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43704-2025 georefererad karta.tif", "A 43704-2025")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 40361-2023 FSC-klagomål.docx", "A 40361-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43704-2025 FSC-klagomål.docx", "A 43704-2025")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 40361-2023 FSC-klagomål mail.docx", "A 40361-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43704-2025 FSC-klagomål mail.docx", "A 43704-2025")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 40361-2023 tillsynsbegäran.docx", "A 40361-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43704-2025 tillsynsbegäran.docx", "A 43704-2025")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 40361-2023 tillsynsbegäran mail.docx", "A 40361-2023")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 40361-2023 prioriterade fågelarter.docx", "A 40361-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43704-2025 tillsynsbegäran mail.docx", "A 43704-2025")</f>
         <v/>
       </c>
     </row>
@@ -3759,7 +3750,7 @@
         <v>45912</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3856,24 +3847,24 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 43704-2025</t>
+          <t>S 1814-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45912</v>
+        <v>46190</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3886,19 +3877,19 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.7</v>
+        <v>10.7</v>
       </c>
       <c r="J28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -3910,131 +3901,21 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
         <v>6</v>
       </c>
       <c r="T28" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>Blomkålssvamp
-Långbensgroda
-Större vattensalamander
-Åkergroda
-Mindre vattensalamander
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43704-2025 artfynd.xlsx", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43704-2025 karta.png", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43704-2025 georefererad karta.tif", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43704-2025 FSC-klagomål.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43704-2025 FSC-klagomål mail.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43704-2025 tillsynsbegäran.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43704-2025 tillsynsbegäran mail.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>S 1814-2026</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="n">
-        <v>46190</v>
-      </c>
-      <c r="E29" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="J29" t="n">
-        <v>3</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>2</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>3</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1</v>
-      </c>
-      <c r="S29" t="n">
-        <v>6</v>
-      </c>
-      <c r="T29" t="n">
-        <v>11</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>Småvänderot
 Leopardsköldbagge
@@ -4044,107 +3925,107 @@
 Ängsnycklar</t>
         </is>
       </c>
-      <c r="W29">
+      <c r="W28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/S 1814-2026 artfynd.xlsx", "S 1814-2026")</f>
         <v/>
       </c>
-      <c r="X29">
+      <c r="X28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/S 1814-2026 karta.png", "S 1814-2026")</f>
         <v/>
       </c>
-      <c r="Y29">
+      <c r="Y28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/S 1814-2026 georefererad karta.tif", "S 1814-2026")</f>
         <v/>
       </c>
-      <c r="AA29">
+      <c r="AA28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/S 1814-2026 FSC-klagomål.docx", "S 1814-2026")</f>
         <v/>
       </c>
-      <c r="AB29">
+      <c r="AB28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/S 1814-2026 FSC-klagomål mail.docx", "S 1814-2026")</f>
         <v/>
       </c>
-      <c r="AC29">
+      <c r="AC28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/S 1814-2026 tillsynsbegäran.docx", "S 1814-2026")</f>
         <v/>
       </c>
-      <c r="AD29">
+      <c r="AD28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/S 1814-2026 tillsynsbegäran mail.docx", "S 1814-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>A 61963-2025</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D30" s="1" t="n">
+      <c r="D29" s="1" t="n">
         <v>46003</v>
       </c>
-      <c r="E30" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F30" t="inlineStr">
+      <c r="E29" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I30" t="n">
+      <c r="I29" t="n">
         <v>1.1</v>
       </c>
-      <c r="J30" t="n">
+      <c r="J29" t="n">
         <v>4</v>
       </c>
-      <c r="K30" t="n">
-        <v>1</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
+      <c r="K29" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
         <v>5</v>
       </c>
-      <c r="T30" t="n">
+      <c r="T29" t="n">
         <v>8</v>
       </c>
-      <c r="U30" t="n">
+      <c r="U29" t="n">
         <v>3</v>
       </c>
-      <c r="V30" s="2" t="inlineStr">
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>Gulsparv
 Mindre märgborre
@@ -4153,111 +4034,111 @@
 Röd glada</t>
         </is>
       </c>
-      <c r="W30">
+      <c r="W29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 61963-2025 artfynd.xlsx", "A 61963-2025")</f>
         <v/>
       </c>
-      <c r="X30">
+      <c r="X29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 61963-2025 karta.png", "A 61963-2025")</f>
         <v/>
       </c>
-      <c r="Y30">
+      <c r="Y29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 61963-2025 georefererad karta.tif", "A 61963-2025")</f>
         <v/>
       </c>
-      <c r="AA30">
+      <c r="AA29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 61963-2025 FSC-klagomål.docx", "A 61963-2025")</f>
         <v/>
       </c>
-      <c r="AB30">
+      <c r="AB29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 61963-2025 FSC-klagomål mail.docx", "A 61963-2025")</f>
         <v/>
       </c>
-      <c r="AC30">
+      <c r="AC29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 61963-2025 tillsynsbegäran.docx", "A 61963-2025")</f>
         <v/>
       </c>
-      <c r="AD30">
+      <c r="AD29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 61963-2025 tillsynsbegäran mail.docx", "A 61963-2025")</f>
         <v/>
       </c>
-      <c r="AE30">
+      <c r="AE29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 61963-2025 prioriterade fågelarter.docx", "A 61963-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>A 2864-2026</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D31" s="1" t="n">
+      <c r="D30" s="1" t="n">
         <v>46038</v>
       </c>
-      <c r="E31" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F31" t="inlineStr">
+      <c r="E30" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I31" t="n">
-        <v>1</v>
-      </c>
-      <c r="J31" t="n">
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="n">
         <v>4</v>
       </c>
-      <c r="K31" t="n">
-        <v>1</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>1</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
+      <c r="K30" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
         <v>5</v>
       </c>
-      <c r="T31" t="n">
+      <c r="T30" t="n">
         <v>8</v>
       </c>
-      <c r="U31" t="n">
+      <c r="U30" t="n">
         <v>3</v>
       </c>
-      <c r="V31" s="2" t="inlineStr">
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>Gulsparv
 Mindre märgborre
@@ -4266,111 +4147,111 @@
 Röd glada</t>
         </is>
       </c>
-      <c r="W31">
+      <c r="W30">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 2864-2026 artfynd.xlsx", "A 2864-2026")</f>
         <v/>
       </c>
-      <c r="X31">
+      <c r="X30">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 2864-2026 karta.png", "A 2864-2026")</f>
         <v/>
       </c>
-      <c r="Y31">
+      <c r="Y30">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 2864-2026 georefererad karta.tif", "A 2864-2026")</f>
         <v/>
       </c>
-      <c r="AA31">
+      <c r="AA30">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 2864-2026 FSC-klagomål.docx", "A 2864-2026")</f>
         <v/>
       </c>
-      <c r="AB31">
+      <c r="AB30">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 2864-2026 FSC-klagomål mail.docx", "A 2864-2026")</f>
         <v/>
       </c>
-      <c r="AC31">
+      <c r="AC30">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 2864-2026 tillsynsbegäran.docx", "A 2864-2026")</f>
         <v/>
       </c>
-      <c r="AD31">
+      <c r="AD30">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 2864-2026 tillsynsbegäran mail.docx", "A 2864-2026")</f>
         <v/>
       </c>
-      <c r="AE31">
+      <c r="AE30">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 2864-2026 prioriterade fågelarter.docx", "A 2864-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>A 54167-2024</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D32" s="1" t="n">
+      <c r="D31" s="1" t="n">
         <v>45616</v>
       </c>
-      <c r="E32" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F32" t="inlineStr">
+      <c r="E31" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I32" t="n">
+      <c r="I31" t="n">
         <v>1.5</v>
       </c>
-      <c r="J32" t="n">
+      <c r="J31" t="n">
         <v>2</v>
       </c>
-      <c r="K32" t="n">
+      <c r="K31" t="n">
         <v>2</v>
       </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>1</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>1</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1</v>
-      </c>
-      <c r="S32" t="n">
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1</v>
+      </c>
+      <c r="S31" t="n">
         <v>4</v>
       </c>
-      <c r="T32" t="n">
+      <c r="T31" t="n">
         <v>8</v>
       </c>
-      <c r="U32" t="n">
+      <c r="U31" t="n">
         <v>8</v>
       </c>
-      <c r="V32" s="2" t="inlineStr">
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>Ask
 Murgröna
@@ -4378,32 +4259,140 @@
 Blåsippa</t>
         </is>
       </c>
+      <c r="W31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 54167-2024 artfynd.xlsx", "A 54167-2024")</f>
+        <v/>
+      </c>
+      <c r="X31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 54167-2024 karta.png", "A 54167-2024")</f>
+        <v/>
+      </c>
+      <c r="Y31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 54167-2024 georefererad karta.tif", "A 54167-2024")</f>
+        <v/>
+      </c>
+      <c r="AA31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 54167-2024 FSC-klagomål.docx", "A 54167-2024")</f>
+        <v/>
+      </c>
+      <c r="AB31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 54167-2024 FSC-klagomål mail.docx", "A 54167-2024")</f>
+        <v/>
+      </c>
+      <c r="AC31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 54167-2024 tillsynsbegäran.docx", "A 54167-2024")</f>
+        <v/>
+      </c>
+      <c r="AD31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 54167-2024 tillsynsbegäran mail.docx", "A 54167-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>A 19459-2023</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="n">
+        <v>45049</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>4</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>4</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>4</v>
+      </c>
+      <c r="T32" t="n">
+        <v>4</v>
+      </c>
+      <c r="U32" t="n">
+        <v>4</v>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>Kavelhirs
+Kösa
+Luddvicker
+Riddarsporre</t>
+        </is>
+      </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 54167-2024 artfynd.xlsx", "A 54167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 19459-2023 artfynd.xlsx", "A 19459-2023")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 54167-2024 karta.png", "A 54167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 19459-2023 karta.png", "A 19459-2023")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 54167-2024 georefererad karta.tif", "A 54167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 19459-2023 georefererad karta.tif", "A 19459-2023")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 54167-2024 FSC-klagomål.docx", "A 54167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 19459-2023 FSC-klagomål.docx", "A 19459-2023")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 54167-2024 FSC-klagomål mail.docx", "A 54167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 19459-2023 FSC-klagomål mail.docx", "A 19459-2023")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 54167-2024 tillsynsbegäran.docx", "A 54167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 19459-2023 tillsynsbegäran.docx", "A 19459-2023")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 54167-2024 tillsynsbegäran mail.docx", "A 54167-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 19459-2023 tillsynsbegäran mail.docx", "A 19459-2023")</f>
         <v/>
       </c>
     </row>
@@ -4427,7 +4416,7 @@
         <v>46183</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4535,7 +4524,7 @@
         <v>46254</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4630,7 +4619,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 19459-2023</t>
+          <t>A 43702-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4640,14 +4629,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45049</v>
+        <v>45912</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4660,16 +4649,16 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L35" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -4684,61 +4673,60 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Kavelhirs
-Kösa
-Luddvicker
-Riddarsporre</t>
+          <t>Sårläka
+Murgröna
+Tibast</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 19459-2023 artfynd.xlsx", "A 19459-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43702-2025 artfynd.xlsx", "A 43702-2025")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 19459-2023 karta.png", "A 19459-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43702-2025 karta.png", "A 43702-2025")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 19459-2023 georefererad karta.tif", "A 19459-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43702-2025 georefererad karta.tif", "A 43702-2025")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 19459-2023 FSC-klagomål.docx", "A 19459-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43702-2025 FSC-klagomål.docx", "A 43702-2025")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 19459-2023 FSC-klagomål mail.docx", "A 19459-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43702-2025 FSC-klagomål mail.docx", "A 43702-2025")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 19459-2023 tillsynsbegäran.docx", "A 19459-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43702-2025 tillsynsbegäran.docx", "A 43702-2025")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 19459-2023 tillsynsbegäran mail.docx", "A 19459-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43702-2025 tillsynsbegäran mail.docx", "A 43702-2025")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 43702-2025</t>
+          <t>A 29360-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4748,14 +4736,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45912</v>
+        <v>46203</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4768,34 +4756,34 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
+        <v>1</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
         <v>2</v>
       </c>
-      <c r="L36" t="n">
-        <v>1</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>1</v>
-      </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S36" t="n">
         <v>3</v>
@@ -4804,41 +4792,41 @@
         <v>3</v>
       </c>
       <c r="U36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Sårläka
-Murgröna
-Tibast</t>
+          <t>Mindre blåvinge
+Silversmygare
+Ekoxe</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43702-2025 artfynd.xlsx", "A 43702-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 29360-2026 artfynd.xlsx", "A 29360-2026")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43702-2025 karta.png", "A 43702-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 29360-2026 karta.png", "A 29360-2026")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43702-2025 georefererad karta.tif", "A 43702-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 29360-2026 georefererad karta.tif", "A 29360-2026")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43702-2025 FSC-klagomål.docx", "A 43702-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 29360-2026 FSC-klagomål.docx", "A 29360-2026")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43702-2025 FSC-klagomål mail.docx", "A 43702-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 29360-2026 FSC-klagomål mail.docx", "A 29360-2026")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43702-2025 tillsynsbegäran.docx", "A 43702-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 29360-2026 tillsynsbegäran.docx", "A 29360-2026")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43702-2025 tillsynsbegäran mail.docx", "A 43702-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 29360-2026 tillsynsbegäran mail.docx", "A 29360-2026")</f>
         <v/>
       </c>
     </row>
@@ -4862,7 +4850,7 @@
         <v>45747</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4952,7 +4940,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 29360-2026</t>
+          <t>A 54192-2021</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4962,14 +4950,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46203</v>
+        <v>44470</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4982,19 +4970,19 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J38" t="n">
         <v>1</v>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -5009,57 +4997,56 @@
         <v>2</v>
       </c>
       <c r="R38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Mindre blåvinge
-Silversmygare
-Ekoxe</t>
+          <t>Ladusvala
+Sminkrot</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 29360-2026 artfynd.xlsx", "A 29360-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 54192-2021 artfynd.xlsx", "A 54192-2021")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 29360-2026 karta.png", "A 29360-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 54192-2021 karta.png", "A 54192-2021")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 29360-2026 georefererad karta.tif", "A 29360-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 54192-2021 georefererad karta.tif", "A 54192-2021")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 29360-2026 FSC-klagomål.docx", "A 29360-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 54192-2021 FSC-klagomål.docx", "A 54192-2021")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 29360-2026 FSC-klagomål mail.docx", "A 29360-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 54192-2021 FSC-klagomål mail.docx", "A 54192-2021")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 29360-2026 tillsynsbegäran.docx", "A 29360-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 54192-2021 tillsynsbegäran.docx", "A 54192-2021")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 29360-2026 tillsynsbegäran mail.docx", "A 29360-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 54192-2021 tillsynsbegäran mail.docx", "A 54192-2021")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 54192-2021</t>
+          <t>A 62231-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5069,14 +5056,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44470</v>
+        <v>45267</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5089,16 +5076,16 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J39" t="n">
         <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -5113,7 +5100,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -5129,36 +5116,36 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Ladusvala
-Sminkrot</t>
+          <t>Murgröna
+Blåsippa</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 54192-2021 artfynd.xlsx", "A 54192-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62231-2023 artfynd.xlsx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 54192-2021 karta.png", "A 54192-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62231-2023 karta.png", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 54192-2021 georefererad karta.tif", "A 54192-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62231-2023 georefererad karta.tif", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 54192-2021 FSC-klagomål.docx", "A 54192-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62231-2023 FSC-klagomål.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 54192-2021 FSC-klagomål mail.docx", "A 54192-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62231-2023 FSC-klagomål mail.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 54192-2021 tillsynsbegäran.docx", "A 54192-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62231-2023 tillsynsbegäran.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 54192-2021 tillsynsbegäran mail.docx", "A 54192-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62231-2023 tillsynsbegäran mail.docx", "A 62231-2023")</f>
         <v/>
       </c>
     </row>
@@ -5182,7 +5169,7 @@
         <v>44544</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5275,24 +5262,24 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 62231-2023</t>
+          <t>S 2138-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45267</v>
+        <v>46246</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5305,7 +5292,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.6</v>
+        <v>5.4</v>
       </c>
       <c r="J41" t="n">
         <v>1</v>
@@ -5320,7 +5307,7 @@
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5329,10 +5316,10 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S41" t="n">
         <v>2</v>
@@ -5341,64 +5328,64 @@
         <v>2</v>
       </c>
       <c r="U41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Murgröna
-Blåsippa</t>
+          <t>Ask
+Ekoxe</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62231-2023 artfynd.xlsx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/S 2138-2026 artfynd.xlsx", "S 2138-2026")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62231-2023 karta.png", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/S 2138-2026 karta.png", "S 2138-2026")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62231-2023 georefererad karta.tif", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/S 2138-2026 georefererad karta.tif", "S 2138-2026")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62231-2023 FSC-klagomål.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/S 2138-2026 FSC-klagomål.docx", "S 2138-2026")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62231-2023 FSC-klagomål mail.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/S 2138-2026 FSC-klagomål mail.docx", "S 2138-2026")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62231-2023 tillsynsbegäran.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/S 2138-2026 tillsynsbegäran.docx", "S 2138-2026")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62231-2023 tillsynsbegäran mail.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/S 2138-2026 tillsynsbegäran mail.docx", "S 2138-2026")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S 2138-2026</t>
+          <t>A 62183-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46246</v>
+        <v>46006</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5411,22 +5398,22 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>5.4</v>
+        <v>0.8</v>
       </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5438,56 +5425,55 @@
         <v>1</v>
       </c>
       <c r="R42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Ask
-Ekoxe</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/S 2138-2026 artfynd.xlsx", "S 2138-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62183-2025 artfynd.xlsx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/S 2138-2026 karta.png", "S 2138-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62183-2025 karta.png", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/S 2138-2026 georefererad karta.tif", "S 2138-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62183-2025 georefererad karta.tif", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/S 2138-2026 FSC-klagomål.docx", "S 2138-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62183-2025 FSC-klagomål.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/S 2138-2026 FSC-klagomål mail.docx", "S 2138-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62183-2025 FSC-klagomål mail.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/S 2138-2026 tillsynsbegäran.docx", "S 2138-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62183-2025 tillsynsbegäran.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/S 2138-2026 tillsynsbegäran mail.docx", "S 2138-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62183-2025 tillsynsbegäran mail.docx", "A 62183-2025")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 13040-2024</t>
+          <t>A 24698-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5497,14 +5483,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45385</v>
+        <v>45084</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5517,7 +5503,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.2</v>
+        <v>5.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5526,13 +5512,13 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5544,7 +5530,7 @@
         <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5557,42 +5543,42 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13040-2024 artfynd.xlsx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24698-2023 artfynd.xlsx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13040-2024 karta.png", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24698-2023 karta.png", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13040-2024 georefererad karta.tif", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24698-2023 georefererad karta.tif", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13040-2024 FSC-klagomål.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24698-2023 FSC-klagomål.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13040-2024 FSC-klagomål mail.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24698-2023 FSC-klagomål mail.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13040-2024 tillsynsbegäran.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24698-2023 tillsynsbegäran.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13040-2024 tillsynsbegäran mail.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24698-2023 tillsynsbegäran mail.docx", "A 24698-2023")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 13384-2023</t>
+          <t>A 13040-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5602,14 +5588,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45005</v>
+        <v>45385</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5622,10 +5608,10 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -5637,7 +5623,7 @@
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5646,10 +5632,10 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -5662,42 +5648,42 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13384-2023 artfynd.xlsx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13040-2024 artfynd.xlsx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13384-2023 karta.png", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13040-2024 karta.png", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13384-2023 georefererad karta.tif", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13040-2024 georefererad karta.tif", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13384-2023 FSC-klagomål.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13040-2024 FSC-klagomål.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13384-2023 FSC-klagomål mail.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13040-2024 FSC-klagomål mail.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13384-2023 tillsynsbegäran.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13040-2024 tillsynsbegäran.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13384-2023 tillsynsbegäran mail.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13040-2024 tillsynsbegäran mail.docx", "A 13040-2024")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 24698-2023</t>
+          <t>A 13384-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5711,10 +5697,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45084</v>
+        <v>45005</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5727,16 +5713,16 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>5.5</v>
+        <v>0.9</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -5751,7 +5737,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -5767,42 +5753,42 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24698-2023 artfynd.xlsx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13384-2023 artfynd.xlsx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24698-2023 karta.png", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13384-2023 karta.png", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24698-2023 georefererad karta.tif", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13384-2023 georefererad karta.tif", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24698-2023 FSC-klagomål.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13384-2023 FSC-klagomål.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24698-2023 FSC-klagomål mail.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13384-2023 FSC-klagomål mail.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24698-2023 tillsynsbegäran.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13384-2023 tillsynsbegäran.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24698-2023 tillsynsbegäran mail.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13384-2023 tillsynsbegäran mail.docx", "A 13384-2023")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 62183-2025</t>
+          <t>A 30492-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5812,14 +5798,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46006</v>
+        <v>46210</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5832,7 +5818,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5872,42 +5858,42 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62183-2025 artfynd.xlsx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 30492-2026 artfynd.xlsx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62183-2025 karta.png", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 30492-2026 karta.png", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62183-2025 georefererad karta.tif", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 30492-2026 georefererad karta.tif", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62183-2025 FSC-klagomål.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 30492-2026 FSC-klagomål.docx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62183-2025 FSC-klagomål mail.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 30492-2026 FSC-klagomål mail.docx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62183-2025 tillsynsbegäran.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 30492-2026 tillsynsbegäran.docx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62183-2025 tillsynsbegäran mail.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 30492-2026 tillsynsbegäran mail.docx", "A 30492-2026")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 30492-2026</t>
+          <t>A 36928-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5917,14 +5903,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46210</v>
+        <v>46273</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5937,16 +5923,16 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -5961,7 +5947,7 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
@@ -5977,42 +5963,42 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 30492-2026 artfynd.xlsx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 36928-2026 artfynd.xlsx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 30492-2026 karta.png", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 36928-2026 karta.png", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 30492-2026 georefererad karta.tif", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 36928-2026 georefererad karta.tif", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 30492-2026 FSC-klagomål.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 36928-2026 FSC-klagomål.docx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 30492-2026 FSC-klagomål mail.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 36928-2026 FSC-klagomål mail.docx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 30492-2026 tillsynsbegäran.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 36928-2026 tillsynsbegäran.docx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 30492-2026 tillsynsbegäran mail.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 36928-2026 tillsynsbegäran mail.docx", "A 36928-2026")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 36928-2026</t>
+          <t>A 26876-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6022,14 +6008,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46273</v>
+        <v>44740</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6042,13 +6028,13 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -6072,52 +6058,20 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
         <v>0</v>
       </c>
-      <c r="V48" s="2" t="inlineStr">
-        <is>
-          <t>Tvåblad</t>
-        </is>
-      </c>
-      <c r="W48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 36928-2026 artfynd.xlsx", "A 36928-2026")</f>
-        <v/>
-      </c>
-      <c r="X48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 36928-2026 karta.png", "A 36928-2026")</f>
-        <v/>
-      </c>
-      <c r="Y48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 36928-2026 georefererad karta.tif", "A 36928-2026")</f>
-        <v/>
-      </c>
-      <c r="AA48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 36928-2026 FSC-klagomål.docx", "A 36928-2026")</f>
-        <v/>
-      </c>
-      <c r="AB48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 36928-2026 FSC-klagomål mail.docx", "A 36928-2026")</f>
-        <v/>
-      </c>
-      <c r="AC48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 36928-2026 tillsynsbegäran.docx", "A 36928-2026")</f>
-        <v/>
-      </c>
-      <c r="AD48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 36928-2026 tillsynsbegäran mail.docx", "A 36928-2026")</f>
-        <v/>
-      </c>
+      <c r="V48" s="2" t="inlineStr"/>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 26876-2022</t>
+          <t>A 57407-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6127,14 +6081,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44740</v>
+        <v>45980</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6147,7 +6101,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -6187,27 +6141,27 @@
       </c>
       <c r="V49" s="2" t="inlineStr"/>
     </row>
-    <row r="50" ht="15" customHeight="1">
+    <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 57407-2025</t>
+          <t>S 1602-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45980</v>
+        <v>46171</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6220,7 +6174,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -6259,79 +6213,6 @@
         <v>0</v>
       </c>
       <c r="V50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>S 1602-2026</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D51" s="1" t="n">
-        <v>46171</v>
-      </c>
-      <c r="E51" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I51" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt MÖRBYLÅNGA.xlsx
+++ b/Översikt MÖRBYLÅNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44964</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>44655</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>45177</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45096</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45685</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>46289</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>45475</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>45062</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>46195</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>46189</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>45254</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>45062</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>44508</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>45999</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 24778-2022</t>
+          <t>A 38039-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2488,14 +2488,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44728</v>
+        <v>44811</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2508,45 +2508,275 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>7.4</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>4</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>6</v>
+      </c>
+      <c r="R16" t="n">
         <v>2</v>
-      </c>
-      <c r="L16" t="n">
-        <v>7</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>8</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>11</v>
       </c>
       <c r="T16" t="n">
+        <v>13</v>
+      </c>
+      <c r="U16" t="n">
+        <v>12</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Grov gulmossa
+Backtimjan
+Dvärgjordstjärna
+Solvända
+Ängsstarr
+Murgröna
+Alvarmalört
+Grönvit nattviol
+Krutbrännare
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 38039-2022 artfynd.xlsx", "A 38039-2022")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 38039-2022 karta.png", "A 38039-2022")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 38039-2022 georefererad karta.tif", "A 38039-2022")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 38039-2022 FSC-klagomål.docx", "A 38039-2022")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 38039-2022 FSC-klagomål mail.docx", "A 38039-2022")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 38039-2022 tillsynsbegäran.docx", "A 38039-2022")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 38039-2022 tillsynsbegäran mail.docx", "A 38039-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 27636-2023</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45097</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>4</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>6</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2</v>
+      </c>
+      <c r="S17" t="n">
+        <v>11</v>
+      </c>
+      <c r="T17" t="n">
+        <v>13</v>
+      </c>
+      <c r="U17" t="n">
+        <v>11</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Grov gulmossa
+Backtimjan
+Dvärgjordstjärna
+Solvända
+Ängsstarr
+Murgröna
+Alvarmalört
+Grönvit nattviol
+Krutbrännare
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 27636-2023 artfynd.xlsx", "A 27636-2023")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 27636-2023 karta.png", "A 27636-2023")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 27636-2023 georefererad karta.tif", "A 27636-2023")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 27636-2023 FSC-klagomål.docx", "A 27636-2023")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 27636-2023 FSC-klagomål mail.docx", "A 27636-2023")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 27636-2023 tillsynsbegäran.docx", "A 27636-2023")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 27636-2023 tillsynsbegäran mail.docx", "A 27636-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 24778-2022</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>44728</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" t="n">
+        <v>7</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>8</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>11</v>
+      </c>
+      <c r="T18" t="n">
         <v>20</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U18" t="n">
         <v>20</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Tofsäxing
 Backtimjan
@@ -2561,262 +2791,32 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24778-2022 artfynd.xlsx", "A 24778-2022")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24778-2022 karta.png", "A 24778-2022")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24778-2022 georefererad karta.tif", "A 24778-2022")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24778-2022 FSC-klagomål.docx", "A 24778-2022")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24778-2022 FSC-klagomål mail.docx", "A 24778-2022")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24778-2022 tillsynsbegäran.docx", "A 24778-2022")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24778-2022 tillsynsbegäran mail.docx", "A 24778-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 38039-2022</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>44811</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="J17" t="n">
-        <v>4</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>4</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>6</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2</v>
-      </c>
-      <c r="S17" t="n">
-        <v>11</v>
-      </c>
-      <c r="T17" t="n">
-        <v>13</v>
-      </c>
-      <c r="U17" t="n">
-        <v>12</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Grov gulmossa
-Backtimjan
-Dvärgjordstjärna
-Solvända
-Ängsstarr
-Murgröna
-Alvarmalört
-Grönvit nattviol
-Krutbrännare
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 38039-2022 artfynd.xlsx", "A 38039-2022")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 38039-2022 karta.png", "A 38039-2022")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 38039-2022 georefererad karta.tif", "A 38039-2022")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 38039-2022 FSC-klagomål.docx", "A 38039-2022")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 38039-2022 FSC-klagomål mail.docx", "A 38039-2022")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 38039-2022 tillsynsbegäran.docx", "A 38039-2022")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 38039-2022 tillsynsbegäran mail.docx", "A 38039-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 27636-2023</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45097</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="J18" t="n">
-        <v>4</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>4</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>6</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2</v>
-      </c>
-      <c r="S18" t="n">
-        <v>11</v>
-      </c>
-      <c r="T18" t="n">
-        <v>13</v>
-      </c>
-      <c r="U18" t="n">
-        <v>11</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Grov gulmossa
-Backtimjan
-Dvärgjordstjärna
-Solvända
-Ängsstarr
-Murgröna
-Alvarmalört
-Grönvit nattviol
-Krutbrännare
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 27636-2023 artfynd.xlsx", "A 27636-2023")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 27636-2023 karta.png", "A 27636-2023")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 27636-2023 georefererad karta.tif", "A 27636-2023")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 27636-2023 FSC-klagomål.docx", "A 27636-2023")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 27636-2023 FSC-klagomål mail.docx", "A 27636-2023")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 27636-2023 tillsynsbegäran.docx", "A 27636-2023")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 27636-2023 tillsynsbegäran mail.docx", "A 27636-2023")</f>
         <v/>
       </c>
     </row>
@@ -2840,7 +2840,7 @@
         <v>45551</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>44616</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>45000</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         <v>45530</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>45223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>45075</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>45169</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 43704-2025</t>
+          <t>A 43714-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3640,7 +3640,7 @@
         <v>45912</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3653,19 +3653,19 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.7</v>
+        <v>7.9</v>
       </c>
       <c r="J26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -3677,21 +3677,135 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S26" t="n">
         <v>6</v>
       </c>
       <c r="T26" t="n">
+        <v>8</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Mindre bastardsvärmare
+Sexfläckig bastardsvärmare
+Grönsångare
+Murgröna
+Tibast
+Trädporella</t>
+        </is>
+      </c>
+      <c r="W26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43714-2025 artfynd.xlsx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="X26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43714-2025 karta.png", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="Y26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43714-2025 georefererad karta.tif", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AA26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43714-2025 FSC-klagomål.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AB26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43714-2025 FSC-klagomål mail.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AC26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43714-2025 tillsynsbegäran.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AD26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43714-2025 tillsynsbegäran mail.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 43714-2025 prioriterade fågelarter.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 43704-2025</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>45912</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J27" t="n">
+        <v>5</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
         <v>6</v>
       </c>
-      <c r="U26" t="n">
-        <v>1</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="T27" t="n">
+        <v>6</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>Blomkålssvamp
 Långbensgroda
@@ -3701,146 +3815,32 @@
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W26">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43704-2025 artfynd.xlsx", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="X26">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43704-2025 karta.png", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="Y26">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43704-2025 georefererad karta.tif", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="AA26">
+      <c r="AA27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43704-2025 FSC-klagomål.docx", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="AB26">
+      <c r="AB27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43704-2025 FSC-klagomål mail.docx", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="AC26">
+      <c r="AC27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43704-2025 tillsynsbegäran.docx", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="AD26">
+      <c r="AD27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43704-2025 tillsynsbegäran mail.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 43714-2025</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>45912</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="J27" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>3</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1</v>
-      </c>
-      <c r="M27" t="n">
-        <v>2</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>3</v>
-      </c>
-      <c r="R27" t="n">
-        <v>2</v>
-      </c>
-      <c r="S27" t="n">
-        <v>6</v>
-      </c>
-      <c r="T27" t="n">
-        <v>8</v>
-      </c>
-      <c r="U27" t="n">
-        <v>2</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Mindre bastardsvärmare
-Sexfläckig bastardsvärmare
-Grönsångare
-Murgröna
-Tibast
-Trädporella</t>
-        </is>
-      </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43714-2025 artfynd.xlsx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43714-2025 karta.png", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43714-2025 georefererad karta.tif", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43714-2025 FSC-klagomål.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43714-2025 FSC-klagomål mail.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43714-2025 tillsynsbegäran.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43714-2025 tillsynsbegäran mail.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 43714-2025 prioriterade fågelarter.docx", "A 43714-2025")</f>
         <v/>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
         <v>46190</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>46003</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>46038</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>45616</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>45049</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
         <v>46183</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         <v>46254</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         <v>45912</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 29360-2026</t>
+          <t>A 15600-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4740,10 +4740,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46203</v>
+        <v>45747</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4756,19 +4756,19 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -4780,10 +4780,10 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>3</v>
@@ -4795,145 +4795,145 @@
         <v>1</v>
       </c>
       <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>Kragjordstjärna
+Murgröna
+Scharlakansvårskål agg.</t>
+        </is>
+      </c>
+      <c r="W36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 15600-2025 artfynd.xlsx", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="X36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 15600-2025 karta.png", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="Y36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 15600-2025 georefererad karta.tif", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="AA36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 15600-2025 FSC-klagomål.docx", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="AB36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 15600-2025 FSC-klagomål mail.docx", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="AC36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 15600-2025 tillsynsbegäran.docx", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="AD36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 15600-2025 tillsynsbegäran mail.docx", "A 15600-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>A 29360-2026</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D37" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="E37" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
         <is>
           <t>Mindre blåvinge
 Silversmygare
 Ekoxe</t>
         </is>
       </c>
-      <c r="W36">
+      <c r="W37">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 29360-2026 artfynd.xlsx", "A 29360-2026")</f>
         <v/>
       </c>
-      <c r="X36">
+      <c r="X37">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 29360-2026 karta.png", "A 29360-2026")</f>
         <v/>
       </c>
-      <c r="Y36">
+      <c r="Y37">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 29360-2026 georefererad karta.tif", "A 29360-2026")</f>
         <v/>
       </c>
-      <c r="AA36">
+      <c r="AA37">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 29360-2026 FSC-klagomål.docx", "A 29360-2026")</f>
         <v/>
       </c>
-      <c r="AB36">
+      <c r="AB37">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 29360-2026 FSC-klagomål mail.docx", "A 29360-2026")</f>
         <v/>
       </c>
-      <c r="AC36">
+      <c r="AC37">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 29360-2026 tillsynsbegäran.docx", "A 29360-2026")</f>
         <v/>
       </c>
-      <c r="AD36">
+      <c r="AD37">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 29360-2026 tillsynsbegäran mail.docx", "A 29360-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" ht="15" customHeight="1">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>A 15600-2025</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D37" s="1" t="n">
-        <v>45747</v>
-      </c>
-      <c r="E37" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="n">
-        <v>3</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="n">
-        <v>3</v>
-      </c>
-      <c r="T37" t="n">
-        <v>3</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1</v>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>Kragjordstjärna
-Murgröna
-Scharlakansvårskål agg.</t>
-        </is>
-      </c>
-      <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 15600-2025 artfynd.xlsx", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 15600-2025 karta.png", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 15600-2025 georefererad karta.tif", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 15600-2025 FSC-klagomål.docx", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 15600-2025 FSC-klagomål mail.docx", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 15600-2025 tillsynsbegäran.docx", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 15600-2025 tillsynsbegäran mail.docx", "A 15600-2025")</f>
         <v/>
       </c>
     </row>
@@ -4957,7 +4957,7 @@
         <v>44470</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 62231-2023</t>
+          <t>A 72167-2021</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5056,14 +5056,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45267</v>
+        <v>44544</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J39" t="n">
         <v>1</v>
@@ -5117,42 +5117,46 @@
       <c r="V39" s="2" t="inlineStr">
         <is>
           <t>Murgröna
-Blåsippa</t>
+Röd glada</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62231-2023 artfynd.xlsx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 72167-2021 artfynd.xlsx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62231-2023 karta.png", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 72167-2021 karta.png", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62231-2023 georefererad karta.tif", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 72167-2021 georefererad karta.tif", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62231-2023 FSC-klagomål.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 72167-2021 FSC-klagomål.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62231-2023 FSC-klagomål mail.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 72167-2021 FSC-klagomål mail.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62231-2023 tillsynsbegäran.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 72167-2021 tillsynsbegäran.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62231-2023 tillsynsbegäran mail.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 72167-2021 tillsynsbegäran mail.docx", "A 72167-2021")</f>
+        <v/>
+      </c>
+      <c r="AE39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 72167-2021 prioriterade fågelarter.docx", "A 72167-2021")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 72167-2021</t>
+          <t>A 62231-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5162,14 +5166,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44544</v>
+        <v>45267</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5182,7 +5186,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J40" t="n">
         <v>1</v>
@@ -5223,39 +5227,35 @@
       <c r="V40" s="2" t="inlineStr">
         <is>
           <t>Murgröna
-Röd glada</t>
+Blåsippa</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 72167-2021 artfynd.xlsx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62231-2023 artfynd.xlsx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 72167-2021 karta.png", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62231-2023 karta.png", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 72167-2021 georefererad karta.tif", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62231-2023 georefererad karta.tif", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 72167-2021 FSC-klagomål.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62231-2023 FSC-klagomål.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 72167-2021 FSC-klagomål mail.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62231-2023 FSC-klagomål mail.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 72167-2021 tillsynsbegäran.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62231-2023 tillsynsbegäran.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 72167-2021 tillsynsbegäran mail.docx", "A 72167-2021")</f>
-        <v/>
-      </c>
-      <c r="AE40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 72167-2021 prioriterade fågelarter.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62231-2023 tillsynsbegäran mail.docx", "A 62231-2023")</f>
         <v/>
       </c>
     </row>
@@ -5279,7 +5279,7 @@
         <v>46246</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 62183-2025</t>
+          <t>A 13040-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5378,14 +5378,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46006</v>
+        <v>45385</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -5407,13 +5407,13 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5425,7 +5425,7 @@
         <v>1</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -5434,46 +5434,46 @@
         <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62183-2025 artfynd.xlsx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13040-2024 artfynd.xlsx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62183-2025 karta.png", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13040-2024 karta.png", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62183-2025 georefererad karta.tif", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13040-2024 georefererad karta.tif", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62183-2025 FSC-klagomål.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13040-2024 FSC-klagomål.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62183-2025 FSC-klagomål mail.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13040-2024 FSC-klagomål mail.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62183-2025 tillsynsbegäran.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13040-2024 tillsynsbegäran.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62183-2025 tillsynsbegäran mail.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13040-2024 tillsynsbegäran mail.docx", "A 13040-2024")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 24698-2023</t>
+          <t>A 13384-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5487,10 +5487,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45084</v>
+        <v>45005</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5503,16 +5503,16 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>5.5</v>
+        <v>0.9</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -5527,7 +5527,7 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -5543,42 +5543,42 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24698-2023 artfynd.xlsx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13384-2023 artfynd.xlsx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24698-2023 karta.png", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13384-2023 karta.png", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24698-2023 georefererad karta.tif", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13384-2023 georefererad karta.tif", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24698-2023 FSC-klagomål.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13384-2023 FSC-klagomål.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24698-2023 FSC-klagomål mail.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13384-2023 FSC-klagomål mail.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24698-2023 tillsynsbegäran.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13384-2023 tillsynsbegäran.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24698-2023 tillsynsbegäran mail.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13384-2023 tillsynsbegäran mail.docx", "A 13384-2023")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 13040-2024</t>
+          <t>A 24698-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5588,14 +5588,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45385</v>
+        <v>45084</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.2</v>
+        <v>5.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5617,13 +5617,13 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5635,7 +5635,7 @@
         <v>1</v>
       </c>
       <c r="R44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -5648,42 +5648,42 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13040-2024 artfynd.xlsx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24698-2023 artfynd.xlsx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13040-2024 karta.png", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24698-2023 karta.png", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13040-2024 georefererad karta.tif", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24698-2023 georefererad karta.tif", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13040-2024 FSC-klagomål.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24698-2023 FSC-klagomål.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13040-2024 FSC-klagomål mail.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24698-2023 FSC-klagomål mail.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13040-2024 tillsynsbegäran.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24698-2023 tillsynsbegäran.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13040-2024 tillsynsbegäran mail.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24698-2023 tillsynsbegäran mail.docx", "A 24698-2023")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 13384-2023</t>
+          <t>A 62183-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5697,10 +5697,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45005</v>
+        <v>46006</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5713,16 +5713,16 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -5737,7 +5737,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -5749,39 +5749,39 @@
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13384-2023 artfynd.xlsx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62183-2025 artfynd.xlsx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13384-2023 karta.png", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62183-2025 karta.png", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13384-2023 georefererad karta.tif", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62183-2025 georefererad karta.tif", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13384-2023 FSC-klagomål.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62183-2025 FSC-klagomål.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13384-2023 FSC-klagomål mail.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62183-2025 FSC-klagomål mail.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13384-2023 tillsynsbegäran.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62183-2025 tillsynsbegäran.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13384-2023 tillsynsbegäran mail.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62183-2025 tillsynsbegäran mail.docx", "A 62183-2025")</f>
         <v/>
       </c>
     </row>
@@ -5805,7 +5805,7 @@
         <v>46210</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>46273</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>44740</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         <v>45980</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>46171</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>

--- a/Översikt MÖRBYLÅNGA.xlsx
+++ b/Översikt MÖRBYLÅNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44964</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>44655</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>45177</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45096</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45685</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>46289</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>45475</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>45062</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>46195</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>46189</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>45254</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>45062</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>44508</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 60875-2025</t>
+          <t>A 24778-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2373,10 +2373,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45999</v>
+        <v>44728</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2389,45 +2389,160 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>7</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
         <v>8</v>
       </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>5</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>7</v>
-      </c>
       <c r="R15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>11</v>
       </c>
       <c r="T15" t="n">
+        <v>20</v>
+      </c>
+      <c r="U15" t="n">
+        <v>20</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Tofsäxing
+Backtimjan
+Flentimotej
+Grådådra
+Poppeltofsskivling
+Slåtterfibbla
+Sminkrot
+Solvända
+Kalktallört
+Murgröna
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24778-2022 artfynd.xlsx", "A 24778-2022")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24778-2022 karta.png", "A 24778-2022")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24778-2022 georefererad karta.tif", "A 24778-2022")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24778-2022 FSC-klagomål.docx", "A 24778-2022")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24778-2022 FSC-klagomål mail.docx", "A 24778-2022")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24778-2022 tillsynsbegäran.docx", "A 24778-2022")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24778-2022 tillsynsbegäran mail.docx", "A 24778-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 60875-2025</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45999</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>8</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>5</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>7</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2</v>
+      </c>
+      <c r="S16" t="n">
+        <v>11</v>
+      </c>
+      <c r="T16" t="n">
         <v>12</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U16" t="n">
         <v>3</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Järnek
 Mosippa
@@ -2442,111 +2557,111 @@
 Skogsduva</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 60875-2025 artfynd.xlsx", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 60875-2025 karta.png", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 60875-2025 georefererad karta.tif", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 60875-2025 FSC-klagomål.docx", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 60875-2025 FSC-klagomål mail.docx", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 60875-2025 tillsynsbegäran.docx", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 60875-2025 tillsynsbegäran mail.docx", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 60875-2025 prioriterade fågelarter.docx", "A 60875-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>A 38039-2022</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D16" s="1" t="n">
+      <c r="D17" s="1" t="n">
         <v>44811</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="E17" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I16" t="n">
+      <c r="I17" t="n">
         <v>7.4</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J17" t="n">
         <v>4</v>
       </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
         <v>4</v>
       </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>6</v>
       </c>
-      <c r="R16" t="n">
+      <c r="R17" t="n">
         <v>2</v>
       </c>
-      <c r="S16" t="n">
+      <c r="S17" t="n">
         <v>11</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T17" t="n">
         <v>13</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U17" t="n">
         <v>12</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Ask
 Grov gulmossa
@@ -2561,107 +2676,107 @@
 Gullviva</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 38039-2022 artfynd.xlsx", "A 38039-2022")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 38039-2022 karta.png", "A 38039-2022")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 38039-2022 georefererad karta.tif", "A 38039-2022")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 38039-2022 FSC-klagomål.docx", "A 38039-2022")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 38039-2022 FSC-klagomål mail.docx", "A 38039-2022")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 38039-2022 tillsynsbegäran.docx", "A 38039-2022")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 38039-2022 tillsynsbegäran mail.docx", "A 38039-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>A 27636-2023</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D17" s="1" t="n">
+      <c r="D18" s="1" t="n">
         <v>45097</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F17" t="inlineStr">
+      <c r="E18" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I17" t="n">
+      <c r="I18" t="n">
         <v>7.4</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J18" t="n">
         <v>4</v>
       </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
         <v>4</v>
       </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
         <v>6</v>
       </c>
-      <c r="R17" t="n">
+      <c r="R18" t="n">
         <v>2</v>
       </c>
-      <c r="S17" t="n">
+      <c r="S18" t="n">
         <v>11</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T18" t="n">
         <v>13</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U18" t="n">
         <v>11</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Ask
 Grov gulmossa
@@ -2676,147 +2791,32 @@
 Gullviva</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 27636-2023 artfynd.xlsx", "A 27636-2023")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 27636-2023 karta.png", "A 27636-2023")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 27636-2023 georefererad karta.tif", "A 27636-2023")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 27636-2023 FSC-klagomål.docx", "A 27636-2023")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 27636-2023 FSC-klagomål mail.docx", "A 27636-2023")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 27636-2023 tillsynsbegäran.docx", "A 27636-2023")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 27636-2023 tillsynsbegäran mail.docx", "A 27636-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 24778-2022</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>44728</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2</v>
-      </c>
-      <c r="L18" t="n">
-        <v>7</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>8</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1</v>
-      </c>
-      <c r="S18" t="n">
-        <v>11</v>
-      </c>
-      <c r="T18" t="n">
-        <v>20</v>
-      </c>
-      <c r="U18" t="n">
-        <v>20</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Tofsäxing
-Backtimjan
-Flentimotej
-Grådådra
-Poppeltofsskivling
-Slåtterfibbla
-Sminkrot
-Solvända
-Kalktallört
-Murgröna
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24778-2022 artfynd.xlsx", "A 24778-2022")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24778-2022 karta.png", "A 24778-2022")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24778-2022 georefererad karta.tif", "A 24778-2022")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24778-2022 FSC-klagomål.docx", "A 24778-2022")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24778-2022 FSC-klagomål mail.docx", "A 24778-2022")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24778-2022 tillsynsbegäran.docx", "A 24778-2022")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24778-2022 tillsynsbegäran mail.docx", "A 24778-2022")</f>
         <v/>
       </c>
     </row>
@@ -2840,7 +2840,7 @@
         <v>45551</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>44616</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>45000</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         <v>45530</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>45223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>45075</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>45169</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 43714-2025</t>
+          <t>A 43704-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3640,7 +3640,7 @@
         <v>45912</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3653,19 +3653,19 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>7.9</v>
+        <v>2.7</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -3677,21 +3677,131 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>6</v>
       </c>
       <c r="T26" t="n">
+        <v>6</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp
+Långbensgroda
+Större vattensalamander
+Åkergroda
+Mindre vattensalamander
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43704-2025 artfynd.xlsx", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="X26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43704-2025 karta.png", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="Y26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43704-2025 georefererad karta.tif", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="AA26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43704-2025 FSC-klagomål.docx", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="AB26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43704-2025 FSC-klagomål mail.docx", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="AC26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43704-2025 tillsynsbegäran.docx", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="AD26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43704-2025 tillsynsbegäran mail.docx", "A 43704-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 43714-2025</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>45912</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2</v>
+      </c>
+      <c r="S27" t="n">
+        <v>6</v>
+      </c>
+      <c r="T27" t="n">
         <v>8</v>
       </c>
-      <c r="U26" t="n">
+      <c r="U27" t="n">
         <v>2</v>
       </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>Mindre bastardsvärmare
 Sexfläckig bastardsvärmare
@@ -3701,146 +3811,36 @@
 Trädporella</t>
         </is>
       </c>
-      <c r="W26">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43714-2025 artfynd.xlsx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="X26">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43714-2025 karta.png", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="Y26">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43714-2025 georefererad karta.tif", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AA26">
+      <c r="AA27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43714-2025 FSC-klagomål.docx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AB26">
+      <c r="AB27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43714-2025 FSC-klagomål mail.docx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AC26">
+      <c r="AC27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43714-2025 tillsynsbegäran.docx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AD26">
+      <c r="AD27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43714-2025 tillsynsbegäran mail.docx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AE26">
+      <c r="AE27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 43714-2025 prioriterade fågelarter.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 43704-2025</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>45912</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J27" t="n">
-        <v>5</v>
-      </c>
-      <c r="K27" t="n">
-        <v>1</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>6</v>
-      </c>
-      <c r="T27" t="n">
-        <v>6</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Blomkålssvamp
-Långbensgroda
-Större vattensalamander
-Åkergroda
-Mindre vattensalamander
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43704-2025 artfynd.xlsx", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43704-2025 karta.png", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43704-2025 georefererad karta.tif", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43704-2025 FSC-klagomål.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43704-2025 FSC-klagomål mail.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43704-2025 tillsynsbegäran.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43704-2025 tillsynsbegäran mail.docx", "A 43704-2025")</f>
         <v/>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
         <v>46190</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>46003</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>46038</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 54167-2024</t>
+          <t>A 19459-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4193,14 +4193,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45616</v>
+        <v>45049</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4213,22 +4213,22 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4237,21 +4237,129 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
       </c>
       <c r="T31" t="n">
+        <v>4</v>
+      </c>
+      <c r="U31" t="n">
+        <v>4</v>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>Kavelhirs
+Kösa
+Luddvicker
+Riddarsporre</t>
+        </is>
+      </c>
+      <c r="W31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 19459-2023 artfynd.xlsx", "A 19459-2023")</f>
+        <v/>
+      </c>
+      <c r="X31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 19459-2023 karta.png", "A 19459-2023")</f>
+        <v/>
+      </c>
+      <c r="Y31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 19459-2023 georefererad karta.tif", "A 19459-2023")</f>
+        <v/>
+      </c>
+      <c r="AA31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 19459-2023 FSC-klagomål.docx", "A 19459-2023")</f>
+        <v/>
+      </c>
+      <c r="AB31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 19459-2023 FSC-klagomål mail.docx", "A 19459-2023")</f>
+        <v/>
+      </c>
+      <c r="AC31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 19459-2023 tillsynsbegäran.docx", "A 19459-2023")</f>
+        <v/>
+      </c>
+      <c r="AD31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 19459-2023 tillsynsbegäran mail.docx", "A 19459-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>A 54167-2024</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="n">
+        <v>45616</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1</v>
+      </c>
+      <c r="S32" t="n">
+        <v>4</v>
+      </c>
+      <c r="T32" t="n">
         <v>8</v>
       </c>
-      <c r="U31" t="n">
+      <c r="U32" t="n">
         <v>8</v>
       </c>
-      <c r="V31" s="2" t="inlineStr">
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>Ask
 Murgröna
@@ -4259,140 +4367,32 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W31">
+      <c r="W32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 54167-2024 artfynd.xlsx", "A 54167-2024")</f>
         <v/>
       </c>
-      <c r="X31">
+      <c r="X32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 54167-2024 karta.png", "A 54167-2024")</f>
         <v/>
       </c>
-      <c r="Y31">
+      <c r="Y32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 54167-2024 georefererad karta.tif", "A 54167-2024")</f>
         <v/>
       </c>
-      <c r="AA31">
+      <c r="AA32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 54167-2024 FSC-klagomål.docx", "A 54167-2024")</f>
         <v/>
       </c>
-      <c r="AB31">
+      <c r="AB32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 54167-2024 FSC-klagomål mail.docx", "A 54167-2024")</f>
         <v/>
       </c>
-      <c r="AC31">
+      <c r="AC32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 54167-2024 tillsynsbegäran.docx", "A 54167-2024")</f>
         <v/>
       </c>
-      <c r="AD31">
+      <c r="AD32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 54167-2024 tillsynsbegäran mail.docx", "A 54167-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>A 19459-2023</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D32" s="1" t="n">
-        <v>45049</v>
-      </c>
-      <c r="E32" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>4</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>4</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>4</v>
-      </c>
-      <c r="T32" t="n">
-        <v>4</v>
-      </c>
-      <c r="U32" t="n">
-        <v>4</v>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>Kavelhirs
-Kösa
-Luddvicker
-Riddarsporre</t>
-        </is>
-      </c>
-      <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 19459-2023 artfynd.xlsx", "A 19459-2023")</f>
-        <v/>
-      </c>
-      <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 19459-2023 karta.png", "A 19459-2023")</f>
-        <v/>
-      </c>
-      <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 19459-2023 georefererad karta.tif", "A 19459-2023")</f>
-        <v/>
-      </c>
-      <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 19459-2023 FSC-klagomål.docx", "A 19459-2023")</f>
-        <v/>
-      </c>
-      <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 19459-2023 FSC-klagomål mail.docx", "A 19459-2023")</f>
-        <v/>
-      </c>
-      <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 19459-2023 tillsynsbegäran.docx", "A 19459-2023")</f>
-        <v/>
-      </c>
-      <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 19459-2023 tillsynsbegäran mail.docx", "A 19459-2023")</f>
         <v/>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
         <v>46183</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         <v>46254</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 43702-2025</t>
+          <t>A 15600-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4629,14 +4629,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45912</v>
+        <v>45747</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4649,16 +4649,16 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -4673,7 +4673,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -4685,148 +4685,148 @@
         <v>3</v>
       </c>
       <c r="U35" t="n">
+        <v>1</v>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>Kragjordstjärna
+Murgröna
+Scharlakansvårskål agg.</t>
+        </is>
+      </c>
+      <c r="W35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 15600-2025 artfynd.xlsx", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="X35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 15600-2025 karta.png", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="Y35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 15600-2025 georefererad karta.tif", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="AA35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 15600-2025 FSC-klagomål.docx", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="AB35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 15600-2025 FSC-klagomål mail.docx", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="AC35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 15600-2025 tillsynsbegäran.docx", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="AD35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 15600-2025 tillsynsbegäran mail.docx", "A 15600-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>A 43702-2025</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D36" s="1" t="n">
+        <v>45912</v>
+      </c>
+      <c r="E36" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
         <v>2</v>
       </c>
-      <c r="V35" s="2" t="inlineStr">
+      <c r="L36" t="n">
+        <v>1</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
         <is>
           <t>Sårläka
 Murgröna
 Tibast</t>
         </is>
       </c>
-      <c r="W35">
+      <c r="W36">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43702-2025 artfynd.xlsx", "A 43702-2025")</f>
         <v/>
       </c>
-      <c r="X35">
+      <c r="X36">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43702-2025 karta.png", "A 43702-2025")</f>
         <v/>
       </c>
-      <c r="Y35">
+      <c r="Y36">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43702-2025 georefererad karta.tif", "A 43702-2025")</f>
         <v/>
       </c>
-      <c r="AA35">
+      <c r="AA36">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43702-2025 FSC-klagomål.docx", "A 43702-2025")</f>
         <v/>
       </c>
-      <c r="AB35">
+      <c r="AB36">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43702-2025 FSC-klagomål mail.docx", "A 43702-2025")</f>
         <v/>
       </c>
-      <c r="AC35">
+      <c r="AC36">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43702-2025 tillsynsbegäran.docx", "A 43702-2025")</f>
         <v/>
       </c>
-      <c r="AD35">
+      <c r="AD36">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43702-2025 tillsynsbegäran mail.docx", "A 43702-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>A 15600-2025</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="n">
-        <v>45747</v>
-      </c>
-      <c r="E36" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>3</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>3</v>
-      </c>
-      <c r="T36" t="n">
-        <v>3</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1</v>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>Kragjordstjärna
-Murgröna
-Scharlakansvårskål agg.</t>
-        </is>
-      </c>
-      <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 15600-2025 artfynd.xlsx", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 15600-2025 karta.png", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 15600-2025 georefererad karta.tif", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 15600-2025 FSC-klagomål.docx", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 15600-2025 FSC-klagomål mail.docx", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 15600-2025 tillsynsbegäran.docx", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 15600-2025 tillsynsbegäran mail.docx", "A 15600-2025")</f>
         <v/>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
         <v>46203</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>44470</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 72167-2021</t>
+          <t>A 62231-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5056,14 +5056,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44544</v>
+        <v>45267</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J39" t="n">
         <v>1</v>
@@ -5117,46 +5117,42 @@
       <c r="V39" s="2" t="inlineStr">
         <is>
           <t>Murgröna
-Röd glada</t>
+Blåsippa</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 72167-2021 artfynd.xlsx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62231-2023 artfynd.xlsx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 72167-2021 karta.png", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62231-2023 karta.png", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 72167-2021 georefererad karta.tif", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62231-2023 georefererad karta.tif", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 72167-2021 FSC-klagomål.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62231-2023 FSC-klagomål.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 72167-2021 FSC-klagomål mail.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62231-2023 FSC-klagomål mail.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 72167-2021 tillsynsbegäran.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62231-2023 tillsynsbegäran.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 72167-2021 tillsynsbegäran mail.docx", "A 72167-2021")</f>
-        <v/>
-      </c>
-      <c r="AE39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 72167-2021 prioriterade fågelarter.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62231-2023 tillsynsbegäran mail.docx", "A 62231-2023")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 62231-2023</t>
+          <t>A 72167-2021</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5166,14 +5162,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45267</v>
+        <v>44544</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5186,7 +5182,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J40" t="n">
         <v>1</v>
@@ -5227,35 +5223,39 @@
       <c r="V40" s="2" t="inlineStr">
         <is>
           <t>Murgröna
-Blåsippa</t>
+Röd glada</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62231-2023 artfynd.xlsx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 72167-2021 artfynd.xlsx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62231-2023 karta.png", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 72167-2021 karta.png", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62231-2023 georefererad karta.tif", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 72167-2021 georefererad karta.tif", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62231-2023 FSC-klagomål.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 72167-2021 FSC-klagomål.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62231-2023 FSC-klagomål mail.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 72167-2021 FSC-klagomål mail.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62231-2023 tillsynsbegäran.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 72167-2021 tillsynsbegäran.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62231-2023 tillsynsbegäran mail.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 72167-2021 tillsynsbegäran mail.docx", "A 72167-2021")</f>
+        <v/>
+      </c>
+      <c r="AE40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 72167-2021 prioriterade fågelarter.docx", "A 72167-2021")</f>
         <v/>
       </c>
     </row>
@@ -5279,7 +5279,7 @@
         <v>46246</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 13040-2024</t>
+          <t>A 24698-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5378,14 +5378,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45385</v>
+        <v>45084</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.2</v>
+        <v>5.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -5407,13 +5407,13 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5425,7 +5425,7 @@
         <v>1</v>
       </c>
       <c r="R42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -5438,42 +5438,42 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13040-2024 artfynd.xlsx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24698-2023 artfynd.xlsx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13040-2024 karta.png", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24698-2023 karta.png", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13040-2024 georefererad karta.tif", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24698-2023 georefererad karta.tif", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13040-2024 FSC-klagomål.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24698-2023 FSC-klagomål.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13040-2024 FSC-klagomål mail.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24698-2023 FSC-klagomål mail.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13040-2024 tillsynsbegäran.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24698-2023 tillsynsbegäran.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13040-2024 tillsynsbegäran mail.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24698-2023 tillsynsbegäran mail.docx", "A 24698-2023")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 13384-2023</t>
+          <t>A 13040-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5483,14 +5483,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45005</v>
+        <v>45385</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5503,10 +5503,10 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -5518,7 +5518,7 @@
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5527,10 +5527,10 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5543,42 +5543,42 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13384-2023 artfynd.xlsx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13040-2024 artfynd.xlsx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13384-2023 karta.png", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13040-2024 karta.png", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13384-2023 georefererad karta.tif", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13040-2024 georefererad karta.tif", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13384-2023 FSC-klagomål.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13040-2024 FSC-klagomål.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13384-2023 FSC-klagomål mail.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13040-2024 FSC-klagomål mail.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13384-2023 tillsynsbegäran.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13040-2024 tillsynsbegäran.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13384-2023 tillsynsbegäran mail.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13040-2024 tillsynsbegäran mail.docx", "A 13040-2024")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 24698-2023</t>
+          <t>A 13384-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5592,10 +5592,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45084</v>
+        <v>45005</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5608,16 +5608,16 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>5.5</v>
+        <v>0.9</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -5632,7 +5632,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -5648,35 +5648,35 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24698-2023 artfynd.xlsx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13384-2023 artfynd.xlsx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24698-2023 karta.png", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13384-2023 karta.png", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24698-2023 georefererad karta.tif", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13384-2023 georefererad karta.tif", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24698-2023 FSC-klagomål.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13384-2023 FSC-klagomål.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24698-2023 FSC-klagomål mail.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13384-2023 FSC-klagomål mail.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24698-2023 tillsynsbegäran.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13384-2023 tillsynsbegäran.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24698-2023 tillsynsbegäran mail.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13384-2023 tillsynsbegäran mail.docx", "A 13384-2023")</f>
         <v/>
       </c>
     </row>
@@ -5700,7 +5700,7 @@
         <v>46006</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         <v>46210</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>46273</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>44740</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         <v>45980</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>46171</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>

--- a/Översikt MÖRBYLÅNGA.xlsx
+++ b/Översikt MÖRBYLÅNGA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE50"/>
+  <dimension ref="A1:AE49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44964</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>44655</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>45177</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45096</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45685</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>46289</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>45475</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>45062</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>46195</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>46189</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>45254</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>45062</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>44508</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 24778-2022</t>
+          <t>A 38039-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2369,14 +2369,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44728</v>
+        <v>44811</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2389,45 +2389,394 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>7.4</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>4</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>6</v>
+      </c>
+      <c r="R15" t="n">
         <v>2</v>
-      </c>
-      <c r="L15" t="n">
-        <v>7</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>8</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>11</v>
       </c>
       <c r="T15" t="n">
+        <v>13</v>
+      </c>
+      <c r="U15" t="n">
+        <v>12</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Grov gulmossa
+Backtimjan
+Dvärgjordstjärna
+Solvända
+Ängsstarr
+Murgröna
+Alvarmalört
+Grönvit nattviol
+Krutbrännare
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 38039-2022 artfynd.xlsx", "A 38039-2022")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 38039-2022 karta.png", "A 38039-2022")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 38039-2022 georefererad karta.tif", "A 38039-2022")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 38039-2022 FSC-klagomål.docx", "A 38039-2022")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 38039-2022 FSC-klagomål mail.docx", "A 38039-2022")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 38039-2022 tillsynsbegäran.docx", "A 38039-2022")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 38039-2022 tillsynsbegäran mail.docx", "A 38039-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 27636-2023</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45097</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>4</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>6</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2</v>
+      </c>
+      <c r="S16" t="n">
+        <v>11</v>
+      </c>
+      <c r="T16" t="n">
+        <v>13</v>
+      </c>
+      <c r="U16" t="n">
+        <v>11</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Grov gulmossa
+Backtimjan
+Dvärgjordstjärna
+Solvända
+Ängsstarr
+Murgröna
+Alvarmalört
+Grönvit nattviol
+Krutbrännare
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 27636-2023 artfynd.xlsx", "A 27636-2023")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 27636-2023 karta.png", "A 27636-2023")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 27636-2023 georefererad karta.tif", "A 27636-2023")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 27636-2023 FSC-klagomål.docx", "A 27636-2023")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 27636-2023 FSC-klagomål mail.docx", "A 27636-2023")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 27636-2023 tillsynsbegäran.docx", "A 27636-2023")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 27636-2023 tillsynsbegäran mail.docx", "A 27636-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 60875-2025</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45999</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>8</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>5</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>7</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2</v>
+      </c>
+      <c r="S17" t="n">
+        <v>11</v>
+      </c>
+      <c r="T17" t="n">
+        <v>12</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Järnek
+Mosippa
+Grönsångare
+Gulsparv
+Göktyta
+Mindre hackspett
+Svinrot
+Murgröna
+Spillkråka
+Kråka
+Skogsduva</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 60875-2025 artfynd.xlsx", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 60875-2025 karta.png", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 60875-2025 georefererad karta.tif", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 60875-2025 FSC-klagomål.docx", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 60875-2025 FSC-klagomål mail.docx", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 60875-2025 tillsynsbegäran.docx", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 60875-2025 tillsynsbegäran mail.docx", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 60875-2025 prioriterade fågelarter.docx", "A 60875-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 24778-2022</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>44728</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" t="n">
+        <v>7</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>8</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>11</v>
+      </c>
+      <c r="T18" t="n">
         <v>20</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U18" t="n">
         <v>20</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Tofsäxing
 Backtimjan
@@ -2442,381 +2791,32 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24778-2022 artfynd.xlsx", "A 24778-2022")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24778-2022 karta.png", "A 24778-2022")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24778-2022 georefererad karta.tif", "A 24778-2022")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24778-2022 FSC-klagomål.docx", "A 24778-2022")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24778-2022 FSC-klagomål mail.docx", "A 24778-2022")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24778-2022 tillsynsbegäran.docx", "A 24778-2022")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24778-2022 tillsynsbegäran mail.docx", "A 24778-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 60875-2025</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45999</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J16" t="n">
-        <v>8</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>5</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>7</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2</v>
-      </c>
-      <c r="S16" t="n">
-        <v>11</v>
-      </c>
-      <c r="T16" t="n">
-        <v>12</v>
-      </c>
-      <c r="U16" t="n">
-        <v>3</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Järnek
-Mosippa
-Grönsångare
-Gulsparv
-Göktyta
-Mindre hackspett
-Svinrot
-Murgröna
-Spillkråka
-Kråka
-Skogsduva</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 60875-2025 artfynd.xlsx", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 60875-2025 karta.png", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 60875-2025 georefererad karta.tif", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 60875-2025 FSC-klagomål.docx", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 60875-2025 FSC-klagomål mail.docx", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 60875-2025 tillsynsbegäran.docx", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 60875-2025 tillsynsbegäran mail.docx", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 60875-2025 prioriterade fågelarter.docx", "A 60875-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 38039-2022</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>44811</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="J17" t="n">
-        <v>4</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>4</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>6</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2</v>
-      </c>
-      <c r="S17" t="n">
-        <v>11</v>
-      </c>
-      <c r="T17" t="n">
-        <v>13</v>
-      </c>
-      <c r="U17" t="n">
-        <v>12</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Grov gulmossa
-Backtimjan
-Dvärgjordstjärna
-Solvända
-Ängsstarr
-Murgröna
-Alvarmalört
-Grönvit nattviol
-Krutbrännare
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 38039-2022 artfynd.xlsx", "A 38039-2022")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 38039-2022 karta.png", "A 38039-2022")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 38039-2022 georefererad karta.tif", "A 38039-2022")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 38039-2022 FSC-klagomål.docx", "A 38039-2022")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 38039-2022 FSC-klagomål mail.docx", "A 38039-2022")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 38039-2022 tillsynsbegäran.docx", "A 38039-2022")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 38039-2022 tillsynsbegäran mail.docx", "A 38039-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 27636-2023</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45097</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="J18" t="n">
-        <v>4</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>4</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>6</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2</v>
-      </c>
-      <c r="S18" t="n">
-        <v>11</v>
-      </c>
-      <c r="T18" t="n">
-        <v>13</v>
-      </c>
-      <c r="U18" t="n">
-        <v>11</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Grov gulmossa
-Backtimjan
-Dvärgjordstjärna
-Solvända
-Ängsstarr
-Murgröna
-Alvarmalört
-Grönvit nattviol
-Krutbrännare
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 27636-2023 artfynd.xlsx", "A 27636-2023")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 27636-2023 karta.png", "A 27636-2023")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 27636-2023 georefererad karta.tif", "A 27636-2023")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 27636-2023 FSC-klagomål.docx", "A 27636-2023")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 27636-2023 FSC-klagomål mail.docx", "A 27636-2023")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 27636-2023 tillsynsbegäran.docx", "A 27636-2023")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 27636-2023 tillsynsbegäran mail.docx", "A 27636-2023")</f>
         <v/>
       </c>
     </row>
@@ -2840,7 +2840,7 @@
         <v>45551</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>44616</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>45000</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         <v>45530</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>45223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>45075</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>45169</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 43704-2025</t>
+          <t>A 43714-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3640,7 +3640,7 @@
         <v>45912</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3653,19 +3653,19 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.7</v>
+        <v>7.9</v>
       </c>
       <c r="J26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -3677,21 +3677,135 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S26" t="n">
         <v>6</v>
       </c>
       <c r="T26" t="n">
+        <v>8</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Mindre bastardsvärmare
+Sexfläckig bastardsvärmare
+Grönsångare
+Murgröna
+Tibast
+Trädporella</t>
+        </is>
+      </c>
+      <c r="W26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43714-2025 artfynd.xlsx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="X26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43714-2025 karta.png", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="Y26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43714-2025 georefererad karta.tif", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AA26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43714-2025 FSC-klagomål.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AB26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43714-2025 FSC-klagomål mail.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AC26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43714-2025 tillsynsbegäran.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AD26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43714-2025 tillsynsbegäran mail.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 43714-2025 prioriterade fågelarter.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 43704-2025</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>45912</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J27" t="n">
+        <v>5</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
         <v>6</v>
       </c>
-      <c r="U26" t="n">
-        <v>1</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="T27" t="n">
+        <v>6</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>Blomkålssvamp
 Långbensgroda
@@ -3701,146 +3815,32 @@
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W26">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43704-2025 artfynd.xlsx", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="X26">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43704-2025 karta.png", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="Y26">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43704-2025 georefererad karta.tif", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="AA26">
+      <c r="AA27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43704-2025 FSC-klagomål.docx", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="AB26">
+      <c r="AB27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43704-2025 FSC-klagomål mail.docx", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="AC26">
+      <c r="AC27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43704-2025 tillsynsbegäran.docx", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="AD26">
+      <c r="AD27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43704-2025 tillsynsbegäran mail.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 43714-2025</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>45912</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="J27" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>3</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1</v>
-      </c>
-      <c r="M27" t="n">
-        <v>2</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>3</v>
-      </c>
-      <c r="R27" t="n">
-        <v>2</v>
-      </c>
-      <c r="S27" t="n">
-        <v>6</v>
-      </c>
-      <c r="T27" t="n">
-        <v>8</v>
-      </c>
-      <c r="U27" t="n">
-        <v>2</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Mindre bastardsvärmare
-Sexfläckig bastardsvärmare
-Grönsångare
-Murgröna
-Tibast
-Trädporella</t>
-        </is>
-      </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43714-2025 artfynd.xlsx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43714-2025 karta.png", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43714-2025 georefererad karta.tif", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43714-2025 FSC-klagomål.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43714-2025 FSC-klagomål mail.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43714-2025 tillsynsbegäran.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43714-2025 tillsynsbegäran mail.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 43714-2025 prioriterade fågelarter.docx", "A 43714-2025")</f>
         <v/>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
         <v>46190</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>46003</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>46038</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 19459-2023</t>
+          <t>A 54167-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4193,14 +4193,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45049</v>
+        <v>45616</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4213,22 +4213,22 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4237,21 +4237,237 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
       </c>
       <c r="T31" t="n">
+        <v>8</v>
+      </c>
+      <c r="U31" t="n">
+        <v>8</v>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Murgröna
+Tvåblad
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 54167-2024 artfynd.xlsx", "A 54167-2024")</f>
+        <v/>
+      </c>
+      <c r="X31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 54167-2024 karta.png", "A 54167-2024")</f>
+        <v/>
+      </c>
+      <c r="Y31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 54167-2024 georefererad karta.tif", "A 54167-2024")</f>
+        <v/>
+      </c>
+      <c r="AA31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 54167-2024 FSC-klagomål.docx", "A 54167-2024")</f>
+        <v/>
+      </c>
+      <c r="AB31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 54167-2024 FSC-klagomål mail.docx", "A 54167-2024")</f>
+        <v/>
+      </c>
+      <c r="AC31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 54167-2024 tillsynsbegäran.docx", "A 54167-2024")</f>
+        <v/>
+      </c>
+      <c r="AD31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 54167-2024 tillsynsbegäran mail.docx", "A 54167-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>A 26440-2026</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
         <v>4</v>
       </c>
-      <c r="U31" t="n">
+      <c r="T32" t="n">
+        <v>5</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>Backstarr
+Murgröna
+Nästrot
+Vätteros</t>
+        </is>
+      </c>
+      <c r="W32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 26440-2026 artfynd.xlsx", "A 26440-2026")</f>
+        <v/>
+      </c>
+      <c r="X32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 26440-2026 karta.png", "A 26440-2026")</f>
+        <v/>
+      </c>
+      <c r="Y32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 26440-2026 georefererad karta.tif", "A 26440-2026")</f>
+        <v/>
+      </c>
+      <c r="AA32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 26440-2026 FSC-klagomål.docx", "A 26440-2026")</f>
+        <v/>
+      </c>
+      <c r="AB32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 26440-2026 FSC-klagomål mail.docx", "A 26440-2026")</f>
+        <v/>
+      </c>
+      <c r="AC32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 26440-2026 tillsynsbegäran.docx", "A 26440-2026")</f>
+        <v/>
+      </c>
+      <c r="AD32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 26440-2026 tillsynsbegäran mail.docx", "A 26440-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>A 19459-2023</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="n">
+        <v>45049</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
         <v>4</v>
       </c>
-      <c r="V31" s="2" t="inlineStr">
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>4</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>4</v>
+      </c>
+      <c r="T33" t="n">
+        <v>4</v>
+      </c>
+      <c r="U33" t="n">
+        <v>4</v>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
         <is>
           <t>Kavelhirs
 Kösa
@@ -4259,248 +4475,32 @@
 Riddarsporre</t>
         </is>
       </c>
-      <c r="W31">
+      <c r="W33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 19459-2023 artfynd.xlsx", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="X31">
+      <c r="X33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 19459-2023 karta.png", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="Y31">
+      <c r="Y33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 19459-2023 georefererad karta.tif", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="AA31">
+      <c r="AA33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 19459-2023 FSC-klagomål.docx", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="AB31">
+      <c r="AB33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 19459-2023 FSC-klagomål mail.docx", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="AC31">
+      <c r="AC33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 19459-2023 tillsynsbegäran.docx", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="AD31">
+      <c r="AD33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 19459-2023 tillsynsbegäran mail.docx", "A 19459-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>A 54167-2024</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D32" s="1" t="n">
-        <v>45616</v>
-      </c>
-      <c r="E32" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J32" t="n">
-        <v>2</v>
-      </c>
-      <c r="K32" t="n">
-        <v>2</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>1</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>1</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1</v>
-      </c>
-      <c r="S32" t="n">
-        <v>4</v>
-      </c>
-      <c r="T32" t="n">
-        <v>8</v>
-      </c>
-      <c r="U32" t="n">
-        <v>8</v>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Murgröna
-Tvåblad
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 54167-2024 artfynd.xlsx", "A 54167-2024")</f>
-        <v/>
-      </c>
-      <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 54167-2024 karta.png", "A 54167-2024")</f>
-        <v/>
-      </c>
-      <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 54167-2024 georefererad karta.tif", "A 54167-2024")</f>
-        <v/>
-      </c>
-      <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 54167-2024 FSC-klagomål.docx", "A 54167-2024")</f>
-        <v/>
-      </c>
-      <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 54167-2024 FSC-klagomål mail.docx", "A 54167-2024")</f>
-        <v/>
-      </c>
-      <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 54167-2024 tillsynsbegäran.docx", "A 54167-2024")</f>
-        <v/>
-      </c>
-      <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 54167-2024 tillsynsbegäran mail.docx", "A 54167-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>A 26440-2026</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D33" s="1" t="n">
-        <v>46183</v>
-      </c>
-      <c r="E33" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J33" t="n">
-        <v>1</v>
-      </c>
-      <c r="K33" t="n">
-        <v>3</v>
-      </c>
-      <c r="L33" t="n">
-        <v>1</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>4</v>
-      </c>
-      <c r="T33" t="n">
-        <v>5</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
-        <is>
-          <t>Backstarr
-Murgröna
-Nästrot
-Vätteros</t>
-        </is>
-      </c>
-      <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 26440-2026 artfynd.xlsx", "A 26440-2026")</f>
-        <v/>
-      </c>
-      <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 26440-2026 karta.png", "A 26440-2026")</f>
-        <v/>
-      </c>
-      <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 26440-2026 georefererad karta.tif", "A 26440-2026")</f>
-        <v/>
-      </c>
-      <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 26440-2026 FSC-klagomål.docx", "A 26440-2026")</f>
-        <v/>
-      </c>
-      <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 26440-2026 FSC-klagomål mail.docx", "A 26440-2026")</f>
-        <v/>
-      </c>
-      <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 26440-2026 tillsynsbegäran.docx", "A 26440-2026")</f>
-        <v/>
-      </c>
-      <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 26440-2026 tillsynsbegäran mail.docx", "A 26440-2026")</f>
         <v/>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
         <v>46254</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 15600-2025</t>
+          <t>A 43702-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4629,14 +4629,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45747</v>
+        <v>45912</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4649,16 +4649,16 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -4673,7 +4673,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -4685,148 +4685,148 @@
         <v>3</v>
       </c>
       <c r="U35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>Sårläka
+Murgröna
+Tibast</t>
+        </is>
+      </c>
+      <c r="W35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43702-2025 artfynd.xlsx", "A 43702-2025")</f>
+        <v/>
+      </c>
+      <c r="X35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43702-2025 karta.png", "A 43702-2025")</f>
+        <v/>
+      </c>
+      <c r="Y35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43702-2025 georefererad karta.tif", "A 43702-2025")</f>
+        <v/>
+      </c>
+      <c r="AA35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43702-2025 FSC-klagomål.docx", "A 43702-2025")</f>
+        <v/>
+      </c>
+      <c r="AB35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43702-2025 FSC-klagomål mail.docx", "A 43702-2025")</f>
+        <v/>
+      </c>
+      <c r="AC35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43702-2025 tillsynsbegäran.docx", "A 43702-2025")</f>
+        <v/>
+      </c>
+      <c r="AD35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43702-2025 tillsynsbegäran mail.docx", "A 43702-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>A 15600-2025</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D36" s="1" t="n">
+        <v>45747</v>
+      </c>
+      <c r="E36" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
         <is>
           <t>Kragjordstjärna
 Murgröna
 Scharlakansvårskål agg.</t>
         </is>
       </c>
-      <c r="W35">
+      <c r="W36">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 15600-2025 artfynd.xlsx", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="X35">
+      <c r="X36">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 15600-2025 karta.png", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="Y35">
+      <c r="Y36">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 15600-2025 georefererad karta.tif", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="AA35">
+      <c r="AA36">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 15600-2025 FSC-klagomål.docx", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="AB35">
+      <c r="AB36">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 15600-2025 FSC-klagomål mail.docx", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="AC35">
+      <c r="AC36">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 15600-2025 tillsynsbegäran.docx", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="AD35">
+      <c r="AD36">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 15600-2025 tillsynsbegäran mail.docx", "A 15600-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>A 43702-2025</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="n">
-        <v>45912</v>
-      </c>
-      <c r="E36" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>2</v>
-      </c>
-      <c r="L36" t="n">
-        <v>1</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>1</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>3</v>
-      </c>
-      <c r="T36" t="n">
-        <v>3</v>
-      </c>
-      <c r="U36" t="n">
-        <v>2</v>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>Sårläka
-Murgröna
-Tibast</t>
-        </is>
-      </c>
-      <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43702-2025 artfynd.xlsx", "A 43702-2025")</f>
-        <v/>
-      </c>
-      <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43702-2025 karta.png", "A 43702-2025")</f>
-        <v/>
-      </c>
-      <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43702-2025 georefererad karta.tif", "A 43702-2025")</f>
-        <v/>
-      </c>
-      <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43702-2025 FSC-klagomål.docx", "A 43702-2025")</f>
-        <v/>
-      </c>
-      <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43702-2025 FSC-klagomål mail.docx", "A 43702-2025")</f>
-        <v/>
-      </c>
-      <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43702-2025 tillsynsbegäran.docx", "A 43702-2025")</f>
-        <v/>
-      </c>
-      <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43702-2025 tillsynsbegäran mail.docx", "A 43702-2025")</f>
         <v/>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
         <v>46203</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 54192-2021</t>
+          <t>A 72167-2021</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4954,10 +4954,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44470</v>
+        <v>44544</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4970,16 +4970,16 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J38" t="n">
         <v>1</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -5010,36 +5010,40 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Ladusvala
-Sminkrot</t>
+          <t>Murgröna
+Röd glada</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 54192-2021 artfynd.xlsx", "A 54192-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 72167-2021 artfynd.xlsx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 54192-2021 karta.png", "A 54192-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 72167-2021 karta.png", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 54192-2021 georefererad karta.tif", "A 54192-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 72167-2021 georefererad karta.tif", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 54192-2021 FSC-klagomål.docx", "A 54192-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 72167-2021 FSC-klagomål.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 54192-2021 FSC-klagomål mail.docx", "A 54192-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 72167-2021 FSC-klagomål mail.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 54192-2021 tillsynsbegäran.docx", "A 54192-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 72167-2021 tillsynsbegäran.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 54192-2021 tillsynsbegäran mail.docx", "A 54192-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 72167-2021 tillsynsbegäran mail.docx", "A 72167-2021")</f>
+        <v/>
+      </c>
+      <c r="AE38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 72167-2021 prioriterade fågelarter.docx", "A 72167-2021")</f>
         <v/>
       </c>
     </row>
@@ -5063,7 +5067,7 @@
         <v>45267</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5152,24 +5156,24 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 72167-2021</t>
+          <t>S 2138-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44544</v>
+        <v>46246</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5182,7 +5186,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.5</v>
+        <v>5.4</v>
       </c>
       <c r="J40" t="n">
         <v>1</v>
@@ -5197,7 +5201,7 @@
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5206,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S40" t="n">
         <v>2</v>
@@ -5218,68 +5222,64 @@
         <v>2</v>
       </c>
       <c r="U40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Murgröna
-Röd glada</t>
+          <t>Ask
+Ekoxe</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 72167-2021 artfynd.xlsx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/S 2138-2026 artfynd.xlsx", "S 2138-2026")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 72167-2021 karta.png", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/S 2138-2026 karta.png", "S 2138-2026")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 72167-2021 georefererad karta.tif", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/S 2138-2026 georefererad karta.tif", "S 2138-2026")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 72167-2021 FSC-klagomål.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/S 2138-2026 FSC-klagomål.docx", "S 2138-2026")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 72167-2021 FSC-klagomål mail.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/S 2138-2026 FSC-klagomål mail.docx", "S 2138-2026")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 72167-2021 tillsynsbegäran.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/S 2138-2026 tillsynsbegäran.docx", "S 2138-2026")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 72167-2021 tillsynsbegäran mail.docx", "A 72167-2021")</f>
-        <v/>
-      </c>
-      <c r="AE40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 72167-2021 prioriterade fågelarter.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/S 2138-2026 tillsynsbegäran mail.docx", "S 2138-2026")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S 2138-2026</t>
+          <t>A 13040-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46246</v>
+        <v>45385</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5292,13 +5292,13 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>5.4</v>
+        <v>1.2</v>
       </c>
       <c r="J41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -5322,53 +5322,52 @@
         <v>1</v>
       </c>
       <c r="S41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Ask
-Ekoxe</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/S 2138-2026 artfynd.xlsx", "S 2138-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13040-2024 artfynd.xlsx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/S 2138-2026 karta.png", "S 2138-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13040-2024 karta.png", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/S 2138-2026 georefererad karta.tif", "S 2138-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13040-2024 georefererad karta.tif", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/S 2138-2026 FSC-klagomål.docx", "S 2138-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13040-2024 FSC-klagomål.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/S 2138-2026 FSC-klagomål mail.docx", "S 2138-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13040-2024 FSC-klagomål mail.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/S 2138-2026 tillsynsbegäran.docx", "S 2138-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13040-2024 tillsynsbegäran.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/S 2138-2026 tillsynsbegäran mail.docx", "S 2138-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13040-2024 tillsynsbegäran mail.docx", "A 13040-2024")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 24698-2023</t>
+          <t>A 13384-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5382,10 +5381,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45084</v>
+        <v>45005</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5398,16 +5397,16 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>5.5</v>
+        <v>0.9</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -5422,7 +5421,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -5438,42 +5437,42 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24698-2023 artfynd.xlsx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13384-2023 artfynd.xlsx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24698-2023 karta.png", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13384-2023 karta.png", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24698-2023 georefererad karta.tif", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13384-2023 georefererad karta.tif", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24698-2023 FSC-klagomål.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13384-2023 FSC-klagomål.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24698-2023 FSC-klagomål mail.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13384-2023 FSC-klagomål mail.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24698-2023 tillsynsbegäran.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13384-2023 tillsynsbegäran.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24698-2023 tillsynsbegäran mail.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13384-2023 tillsynsbegäran mail.docx", "A 13384-2023")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 13040-2024</t>
+          <t>A 24698-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5483,14 +5482,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45385</v>
+        <v>45084</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5503,7 +5502,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.2</v>
+        <v>5.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5512,13 +5511,13 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5530,7 +5529,7 @@
         <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5543,42 +5542,42 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13040-2024 artfynd.xlsx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24698-2023 artfynd.xlsx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13040-2024 karta.png", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24698-2023 karta.png", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13040-2024 georefererad karta.tif", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24698-2023 georefererad karta.tif", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13040-2024 FSC-klagomål.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24698-2023 FSC-klagomål.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13040-2024 FSC-klagomål mail.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24698-2023 FSC-klagomål mail.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13040-2024 tillsynsbegäran.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24698-2023 tillsynsbegäran.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13040-2024 tillsynsbegäran mail.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24698-2023 tillsynsbegäran mail.docx", "A 24698-2023")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 13384-2023</t>
+          <t>A 62183-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5592,10 +5591,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45005</v>
+        <v>46006</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5608,16 +5607,16 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -5632,7 +5631,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -5644,46 +5643,46 @@
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13384-2023 artfynd.xlsx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62183-2025 artfynd.xlsx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13384-2023 karta.png", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62183-2025 karta.png", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13384-2023 georefererad karta.tif", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62183-2025 georefererad karta.tif", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13384-2023 FSC-klagomål.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62183-2025 FSC-klagomål.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13384-2023 FSC-klagomål mail.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62183-2025 FSC-klagomål mail.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13384-2023 tillsynsbegäran.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62183-2025 tillsynsbegäran.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13384-2023 tillsynsbegäran mail.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62183-2025 tillsynsbegäran mail.docx", "A 62183-2025")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 62183-2025</t>
+          <t>A 30492-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5693,14 +5692,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46006</v>
+        <v>46210</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5713,7 +5712,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5753,42 +5752,42 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62183-2025 artfynd.xlsx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 30492-2026 artfynd.xlsx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62183-2025 karta.png", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 30492-2026 karta.png", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62183-2025 georefererad karta.tif", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 30492-2026 georefererad karta.tif", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62183-2025 FSC-klagomål.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 30492-2026 FSC-klagomål.docx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62183-2025 FSC-klagomål mail.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 30492-2026 FSC-klagomål mail.docx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62183-2025 tillsynsbegäran.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 30492-2026 tillsynsbegäran.docx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62183-2025 tillsynsbegäran mail.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 30492-2026 tillsynsbegäran mail.docx", "A 30492-2026")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 30492-2026</t>
+          <t>A 36928-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5798,14 +5797,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46210</v>
+        <v>46273</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5818,16 +5817,16 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -5842,7 +5841,7 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -5858,42 +5857,42 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 30492-2026 artfynd.xlsx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 36928-2026 artfynd.xlsx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 30492-2026 karta.png", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 36928-2026 karta.png", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 30492-2026 georefererad karta.tif", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 36928-2026 georefererad karta.tif", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 30492-2026 FSC-klagomål.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 36928-2026 FSC-klagomål.docx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 30492-2026 FSC-klagomål mail.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 36928-2026 FSC-klagomål mail.docx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 30492-2026 tillsynsbegäran.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 36928-2026 tillsynsbegäran.docx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 30492-2026 tillsynsbegäran mail.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 36928-2026 tillsynsbegäran mail.docx", "A 36928-2026")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 36928-2026</t>
+          <t>A 26876-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5903,14 +5902,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46273</v>
+        <v>44740</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5923,13 +5922,13 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -5953,52 +5952,20 @@
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
       </c>
-      <c r="V47" s="2" t="inlineStr">
-        <is>
-          <t>Tvåblad</t>
-        </is>
-      </c>
-      <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 36928-2026 artfynd.xlsx", "A 36928-2026")</f>
-        <v/>
-      </c>
-      <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 36928-2026 karta.png", "A 36928-2026")</f>
-        <v/>
-      </c>
-      <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 36928-2026 georefererad karta.tif", "A 36928-2026")</f>
-        <v/>
-      </c>
-      <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 36928-2026 FSC-klagomål.docx", "A 36928-2026")</f>
-        <v/>
-      </c>
-      <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 36928-2026 FSC-klagomål mail.docx", "A 36928-2026")</f>
-        <v/>
-      </c>
-      <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 36928-2026 tillsynsbegäran.docx", "A 36928-2026")</f>
-        <v/>
-      </c>
-      <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 36928-2026 tillsynsbegäran mail.docx", "A 36928-2026")</f>
-        <v/>
-      </c>
+      <c r="V47" s="2" t="inlineStr"/>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 26876-2022</t>
+          <t>A 57407-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6008,14 +5975,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44740</v>
+        <v>45980</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6028,7 +5995,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -6068,27 +6035,27 @@
       </c>
       <c r="V48" s="2" t="inlineStr"/>
     </row>
-    <row r="49" ht="15" customHeight="1">
+    <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 57407-2025</t>
+          <t>S 1602-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45980</v>
+        <v>46171</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6101,7 +6068,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -6140,79 +6107,6 @@
         <v>0</v>
       </c>
       <c r="V49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>S 1602-2026</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D50" s="1" t="n">
-        <v>46171</v>
-      </c>
-      <c r="E50" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I50" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" t="n">
-        <v>0</v>
-      </c>
-      <c r="V50" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt MÖRBYLÅNGA.xlsx
+++ b/Översikt MÖRBYLÅNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44964</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>44655</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>45177</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45096</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45685</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>46289</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>45475</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>45062</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>46195</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>46189</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>45254</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>45062</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>44508</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 38039-2022</t>
+          <t>A 60875-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2369,14 +2369,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44811</v>
+        <v>45999</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2389,31 +2389,31 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>7.4</v>
+        <v>2.1</v>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R15" t="n">
         <v>2</v>
@@ -2422,12 +2422,131 @@
         <v>11</v>
       </c>
       <c r="T15" t="n">
+        <v>12</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Järnek
+Mosippa
+Grönsångare
+Gulsparv
+Göktyta
+Mindre hackspett
+Svinrot
+Murgröna
+Spillkråka
+Kråka
+Skogsduva</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 60875-2025 artfynd.xlsx", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 60875-2025 karta.png", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 60875-2025 georefererad karta.tif", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 60875-2025 FSC-klagomål.docx", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 60875-2025 FSC-klagomål mail.docx", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 60875-2025 tillsynsbegäran.docx", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 60875-2025 tillsynsbegäran mail.docx", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 60875-2025 prioriterade fågelarter.docx", "A 60875-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 38039-2022</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>44811</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>4</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>6</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2</v>
+      </c>
+      <c r="S16" t="n">
+        <v>11</v>
+      </c>
+      <c r="T16" t="n">
         <v>13</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U16" t="n">
         <v>12</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Ask
 Grov gulmossa
@@ -2442,107 +2561,107 @@
 Gullviva</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 38039-2022 artfynd.xlsx", "A 38039-2022")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 38039-2022 karta.png", "A 38039-2022")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 38039-2022 georefererad karta.tif", "A 38039-2022")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 38039-2022 FSC-klagomål.docx", "A 38039-2022")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 38039-2022 FSC-klagomål mail.docx", "A 38039-2022")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 38039-2022 tillsynsbegäran.docx", "A 38039-2022")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 38039-2022 tillsynsbegäran mail.docx", "A 38039-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>A 27636-2023</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D16" s="1" t="n">
+      <c r="D17" s="1" t="n">
         <v>45097</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="E17" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I16" t="n">
+      <c r="I17" t="n">
         <v>7.4</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J17" t="n">
         <v>4</v>
       </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
         <v>4</v>
       </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>6</v>
       </c>
-      <c r="R16" t="n">
+      <c r="R17" t="n">
         <v>2</v>
       </c>
-      <c r="S16" t="n">
+      <c r="S17" t="n">
         <v>11</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T17" t="n">
         <v>13</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U17" t="n">
         <v>11</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Ask
 Grov gulmossa
@@ -2557,151 +2676,32 @@
 Gullviva</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 27636-2023 artfynd.xlsx", "A 27636-2023")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 27636-2023 karta.png", "A 27636-2023")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 27636-2023 georefererad karta.tif", "A 27636-2023")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 27636-2023 FSC-klagomål.docx", "A 27636-2023")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 27636-2023 FSC-klagomål mail.docx", "A 27636-2023")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 27636-2023 tillsynsbegäran.docx", "A 27636-2023")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 27636-2023 tillsynsbegäran mail.docx", "A 27636-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 60875-2025</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45999</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J17" t="n">
-        <v>8</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>5</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>7</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2</v>
-      </c>
-      <c r="S17" t="n">
-        <v>11</v>
-      </c>
-      <c r="T17" t="n">
-        <v>12</v>
-      </c>
-      <c r="U17" t="n">
-        <v>3</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Järnek
-Mosippa
-Grönsångare
-Gulsparv
-Göktyta
-Mindre hackspett
-Svinrot
-Murgröna
-Spillkråka
-Kråka
-Skogsduva</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 60875-2025 artfynd.xlsx", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 60875-2025 karta.png", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 60875-2025 georefererad karta.tif", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 60875-2025 FSC-klagomål.docx", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 60875-2025 FSC-klagomål mail.docx", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 60875-2025 tillsynsbegäran.docx", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 60875-2025 tillsynsbegäran mail.docx", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 60875-2025 prioriterade fågelarter.docx", "A 60875-2025")</f>
         <v/>
       </c>
     </row>
@@ -2725,7 +2725,7 @@
         <v>44728</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>45551</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>44616</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>45000</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         <v>45530</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>45223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>45075</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>45169</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 43714-2025</t>
+          <t>A 43704-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3640,7 +3640,7 @@
         <v>45912</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3653,19 +3653,19 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>7.9</v>
+        <v>2.7</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -3677,21 +3677,131 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>6</v>
       </c>
       <c r="T26" t="n">
+        <v>6</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp
+Långbensgroda
+Större vattensalamander
+Åkergroda
+Mindre vattensalamander
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43704-2025 artfynd.xlsx", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="X26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43704-2025 karta.png", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="Y26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43704-2025 georefererad karta.tif", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="AA26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43704-2025 FSC-klagomål.docx", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="AB26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43704-2025 FSC-klagomål mail.docx", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="AC26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43704-2025 tillsynsbegäran.docx", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="AD26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43704-2025 tillsynsbegäran mail.docx", "A 43704-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 43714-2025</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>45912</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2</v>
+      </c>
+      <c r="S27" t="n">
+        <v>6</v>
+      </c>
+      <c r="T27" t="n">
         <v>8</v>
       </c>
-      <c r="U26" t="n">
+      <c r="U27" t="n">
         <v>2</v>
       </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>Mindre bastardsvärmare
 Sexfläckig bastardsvärmare
@@ -3701,146 +3811,36 @@
 Trädporella</t>
         </is>
       </c>
-      <c r="W26">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43714-2025 artfynd.xlsx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="X26">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43714-2025 karta.png", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="Y26">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43714-2025 georefererad karta.tif", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AA26">
+      <c r="AA27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43714-2025 FSC-klagomål.docx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AB26">
+      <c r="AB27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43714-2025 FSC-klagomål mail.docx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AC26">
+      <c r="AC27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43714-2025 tillsynsbegäran.docx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AD26">
+      <c r="AD27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43714-2025 tillsynsbegäran mail.docx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AE26">
+      <c r="AE27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 43714-2025 prioriterade fågelarter.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 43704-2025</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>45912</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J27" t="n">
-        <v>5</v>
-      </c>
-      <c r="K27" t="n">
-        <v>1</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>6</v>
-      </c>
-      <c r="T27" t="n">
-        <v>6</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Blomkålssvamp
-Långbensgroda
-Större vattensalamander
-Åkergroda
-Mindre vattensalamander
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43704-2025 artfynd.xlsx", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43704-2025 karta.png", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43704-2025 georefererad karta.tif", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43704-2025 FSC-klagomål.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43704-2025 FSC-klagomål mail.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43704-2025 tillsynsbegäran.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43704-2025 tillsynsbegäran mail.docx", "A 43704-2025")</f>
         <v/>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
         <v>46190</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>46003</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>46038</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>45616</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>46183</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
         <v>45049</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         <v>46254</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         <v>45912</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 15600-2025</t>
+          <t>A 29360-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4740,10 +4740,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45747</v>
+        <v>46203</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4756,19 +4756,19 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -4780,10 +4780,10 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S36" t="n">
         <v>3</v>
@@ -4795,152 +4795,152 @@
         <v>1</v>
       </c>
       <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>Mindre blåvinge
+Silversmygare
+Ekoxe</t>
+        </is>
+      </c>
+      <c r="W36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 29360-2026 artfynd.xlsx", "A 29360-2026")</f>
+        <v/>
+      </c>
+      <c r="X36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 29360-2026 karta.png", "A 29360-2026")</f>
+        <v/>
+      </c>
+      <c r="Y36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 29360-2026 georefererad karta.tif", "A 29360-2026")</f>
+        <v/>
+      </c>
+      <c r="AA36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 29360-2026 FSC-klagomål.docx", "A 29360-2026")</f>
+        <v/>
+      </c>
+      <c r="AB36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 29360-2026 FSC-klagomål mail.docx", "A 29360-2026")</f>
+        <v/>
+      </c>
+      <c r="AC36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 29360-2026 tillsynsbegäran.docx", "A 29360-2026")</f>
+        <v/>
+      </c>
+      <c r="AD36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 29360-2026 tillsynsbegäran mail.docx", "A 29360-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>A 15600-2025</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D37" s="1" t="n">
+        <v>45747</v>
+      </c>
+      <c r="E37" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
         <is>
           <t>Kragjordstjärna
 Murgröna
 Scharlakansvårskål agg.</t>
         </is>
       </c>
-      <c r="W36">
+      <c r="W37">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 15600-2025 artfynd.xlsx", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="X36">
+      <c r="X37">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 15600-2025 karta.png", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="Y36">
+      <c r="Y37">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 15600-2025 georefererad karta.tif", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="AA36">
+      <c r="AA37">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 15600-2025 FSC-klagomål.docx", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="AB36">
+      <c r="AB37">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 15600-2025 FSC-klagomål mail.docx", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="AC36">
+      <c r="AC37">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 15600-2025 tillsynsbegäran.docx", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="AD36">
+      <c r="AD37">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 15600-2025 tillsynsbegäran mail.docx", "A 15600-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" ht="15" customHeight="1">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>A 29360-2026</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D37" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="E37" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J37" t="n">
-        <v>1</v>
-      </c>
-      <c r="K37" t="n">
-        <v>1</v>
-      </c>
-      <c r="L37" t="n">
-        <v>1</v>
-      </c>
-      <c r="M37" t="n">
-        <v>1</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>2</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1</v>
-      </c>
-      <c r="S37" t="n">
-        <v>3</v>
-      </c>
-      <c r="T37" t="n">
-        <v>3</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1</v>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>Mindre blåvinge
-Silversmygare
-Ekoxe</t>
-        </is>
-      </c>
-      <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 29360-2026 artfynd.xlsx", "A 29360-2026")</f>
-        <v/>
-      </c>
-      <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 29360-2026 karta.png", "A 29360-2026")</f>
-        <v/>
-      </c>
-      <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 29360-2026 georefererad karta.tif", "A 29360-2026")</f>
-        <v/>
-      </c>
-      <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 29360-2026 FSC-klagomål.docx", "A 29360-2026")</f>
-        <v/>
-      </c>
-      <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 29360-2026 FSC-klagomål mail.docx", "A 29360-2026")</f>
-        <v/>
-      </c>
-      <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 29360-2026 tillsynsbegäran.docx", "A 29360-2026")</f>
-        <v/>
-      </c>
-      <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 29360-2026 tillsynsbegäran mail.docx", "A 29360-2026")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 72167-2021</t>
+          <t>A 62231-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4950,14 +4950,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44544</v>
+        <v>45267</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J38" t="n">
         <v>1</v>
@@ -5011,46 +5011,42 @@
       <c r="V38" s="2" t="inlineStr">
         <is>
           <t>Murgröna
-Röd glada</t>
+Blåsippa</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 72167-2021 artfynd.xlsx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62231-2023 artfynd.xlsx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 72167-2021 karta.png", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62231-2023 karta.png", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 72167-2021 georefererad karta.tif", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62231-2023 georefererad karta.tif", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 72167-2021 FSC-klagomål.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62231-2023 FSC-klagomål.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 72167-2021 FSC-klagomål mail.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62231-2023 FSC-klagomål mail.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 72167-2021 tillsynsbegäran.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62231-2023 tillsynsbegäran.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 72167-2021 tillsynsbegäran mail.docx", "A 72167-2021")</f>
-        <v/>
-      </c>
-      <c r="AE38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 72167-2021 prioriterade fågelarter.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62231-2023 tillsynsbegäran mail.docx", "A 62231-2023")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 62231-2023</t>
+          <t>A 72167-2021</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5060,14 +5056,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45267</v>
+        <v>44544</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5080,7 +5076,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J39" t="n">
         <v>1</v>
@@ -5121,35 +5117,39 @@
       <c r="V39" s="2" t="inlineStr">
         <is>
           <t>Murgröna
-Blåsippa</t>
+Röd glada</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62231-2023 artfynd.xlsx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 72167-2021 artfynd.xlsx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62231-2023 karta.png", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 72167-2021 karta.png", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62231-2023 georefererad karta.tif", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 72167-2021 georefererad karta.tif", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62231-2023 FSC-klagomål.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 72167-2021 FSC-klagomål.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62231-2023 FSC-klagomål mail.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 72167-2021 FSC-klagomål mail.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62231-2023 tillsynsbegäran.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 72167-2021 tillsynsbegäran.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62231-2023 tillsynsbegäran mail.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 72167-2021 tillsynsbegäran mail.docx", "A 72167-2021")</f>
+        <v/>
+      </c>
+      <c r="AE39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 72167-2021 prioriterade fågelarter.docx", "A 72167-2021")</f>
         <v/>
       </c>
     </row>
@@ -5173,7 +5173,7 @@
         <v>46246</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 13040-2024</t>
+          <t>A 62183-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5272,14 +5272,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45385</v>
+        <v>46006</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -5301,13 +5301,13 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5319,7 +5319,7 @@
         <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -5328,46 +5328,46 @@
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13040-2024 artfynd.xlsx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62183-2025 artfynd.xlsx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13040-2024 karta.png", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62183-2025 karta.png", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13040-2024 georefererad karta.tif", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62183-2025 georefererad karta.tif", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13040-2024 FSC-klagomål.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62183-2025 FSC-klagomål.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13040-2024 FSC-klagomål mail.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62183-2025 FSC-klagomål mail.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13040-2024 tillsynsbegäran.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62183-2025 tillsynsbegäran.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13040-2024 tillsynsbegäran mail.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62183-2025 tillsynsbegäran mail.docx", "A 62183-2025")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 13384-2023</t>
+          <t>A 24698-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5381,10 +5381,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45005</v>
+        <v>45084</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5397,16 +5397,16 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.9</v>
+        <v>5.5</v>
       </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -5421,7 +5421,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -5437,42 +5437,42 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13384-2023 artfynd.xlsx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24698-2023 artfynd.xlsx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13384-2023 karta.png", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24698-2023 karta.png", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13384-2023 georefererad karta.tif", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24698-2023 georefererad karta.tif", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13384-2023 FSC-klagomål.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24698-2023 FSC-klagomål.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13384-2023 FSC-klagomål mail.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24698-2023 FSC-klagomål mail.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13384-2023 tillsynsbegäran.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24698-2023 tillsynsbegäran.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13384-2023 tillsynsbegäran mail.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24698-2023 tillsynsbegäran mail.docx", "A 24698-2023")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 24698-2023</t>
+          <t>A 13040-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5482,14 +5482,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45084</v>
+        <v>45385</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>5.5</v>
+        <v>1.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5511,13 +5511,13 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5529,7 +5529,7 @@
         <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5542,42 +5542,42 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24698-2023 artfynd.xlsx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13040-2024 artfynd.xlsx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24698-2023 karta.png", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13040-2024 karta.png", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24698-2023 georefererad karta.tif", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13040-2024 georefererad karta.tif", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24698-2023 FSC-klagomål.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13040-2024 FSC-klagomål.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24698-2023 FSC-klagomål mail.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13040-2024 FSC-klagomål mail.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24698-2023 tillsynsbegäran.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13040-2024 tillsynsbegäran.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24698-2023 tillsynsbegäran mail.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13040-2024 tillsynsbegäran mail.docx", "A 13040-2024")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 62183-2025</t>
+          <t>A 13384-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5591,10 +5591,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46006</v>
+        <v>45005</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5607,16 +5607,16 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -5631,7 +5631,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -5643,39 +5643,39 @@
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62183-2025 artfynd.xlsx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13384-2023 artfynd.xlsx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62183-2025 karta.png", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13384-2023 karta.png", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62183-2025 georefererad karta.tif", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13384-2023 georefererad karta.tif", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62183-2025 FSC-klagomål.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13384-2023 FSC-klagomål.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62183-2025 FSC-klagomål mail.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13384-2023 FSC-klagomål mail.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62183-2025 tillsynsbegäran.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13384-2023 tillsynsbegäran.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62183-2025 tillsynsbegäran mail.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13384-2023 tillsynsbegäran mail.docx", "A 13384-2023")</f>
         <v/>
       </c>
     </row>
@@ -5699,7 +5699,7 @@
         <v>46210</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>46273</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         <v>44740</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         <v>45980</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         <v>46171</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>

--- a/Översikt MÖRBYLÅNGA.xlsx
+++ b/Översikt MÖRBYLÅNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44964</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>44655</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>45177</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45096</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45685</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>46289</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>45475</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>45062</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>46195</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>46189</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>45254</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>45062</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>44508</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>45999</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>44811</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>45097</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>44728</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>45551</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>44616</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>45000</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         <v>45530</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>45223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>45075</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>45169</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>45912</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>45912</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>46190</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>46003</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>46038</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>45616</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>46183</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
         <v>45049</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         <v>46254</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         <v>45912</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>46203</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4850,7 +4850,7 @@
         <v>45747</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>45267</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
         <v>44544</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>46246</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>46006</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         <v>45084</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>45385</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>45005</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>46210</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>46273</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         <v>44740</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         <v>45980</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         <v>46171</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>

--- a/Översikt MÖRBYLÅNGA.xlsx
+++ b/Översikt MÖRBYLÅNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44964</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>44655</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>45177</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45096</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45685</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>46289</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>45475</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>45062</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>46195</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>46189</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>45254</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>45062</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>44508</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>45999</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>44811</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>45097</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>44728</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>45551</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>44616</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>45000</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         <v>45530</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>45223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>45075</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>45169</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>45912</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>45912</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>46190</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>46003</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>46038</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>45616</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>46183</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
         <v>45049</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         <v>46254</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         <v>45912</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>46203</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4850,7 +4850,7 @@
         <v>45747</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>45267</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
         <v>44544</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>46246</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>46006</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         <v>45084</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>45385</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>45005</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>46210</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>46273</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         <v>44740</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         <v>45980</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         <v>46171</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>

--- a/Översikt MÖRBYLÅNGA.xlsx
+++ b/Översikt MÖRBYLÅNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44964</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>44655</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>45177</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45096</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45685</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>46289</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>45475</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>45062</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>46195</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>46189</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>45254</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>45062</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>44508</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>45999</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>44811</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>45097</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>44728</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>45551</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>44616</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>45000</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         <v>45530</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>45223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>45075</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>45169</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 43704-2025</t>
+          <t>A 43714-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3640,7 +3640,7 @@
         <v>45912</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3653,19 +3653,19 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.7</v>
+        <v>7.9</v>
       </c>
       <c r="J26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -3677,21 +3677,135 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S26" t="n">
         <v>6</v>
       </c>
       <c r="T26" t="n">
+        <v>8</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Mindre bastardsvärmare
+Sexfläckig bastardsvärmare
+Grönsångare
+Murgröna
+Tibast
+Trädporella</t>
+        </is>
+      </c>
+      <c r="W26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43714-2025 artfynd.xlsx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="X26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43714-2025 karta.png", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="Y26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43714-2025 georefererad karta.tif", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AA26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43714-2025 FSC-klagomål.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AB26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43714-2025 FSC-klagomål mail.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AC26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43714-2025 tillsynsbegäran.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AD26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43714-2025 tillsynsbegäran mail.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 43714-2025 prioriterade fågelarter.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 43704-2025</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>45912</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J27" t="n">
+        <v>5</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
         <v>6</v>
       </c>
-      <c r="U26" t="n">
-        <v>1</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="T27" t="n">
+        <v>6</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>Blomkålssvamp
 Långbensgroda
@@ -3701,146 +3815,32 @@
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W26">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43704-2025 artfynd.xlsx", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="X26">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43704-2025 karta.png", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="Y26">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43704-2025 georefererad karta.tif", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="AA26">
+      <c r="AA27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43704-2025 FSC-klagomål.docx", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="AB26">
+      <c r="AB27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43704-2025 FSC-klagomål mail.docx", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="AC26">
+      <c r="AC27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43704-2025 tillsynsbegäran.docx", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="AD26">
+      <c r="AD27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43704-2025 tillsynsbegäran mail.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 43714-2025</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>45912</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="J27" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>3</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1</v>
-      </c>
-      <c r="M27" t="n">
-        <v>2</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>3</v>
-      </c>
-      <c r="R27" t="n">
-        <v>2</v>
-      </c>
-      <c r="S27" t="n">
-        <v>6</v>
-      </c>
-      <c r="T27" t="n">
-        <v>8</v>
-      </c>
-      <c r="U27" t="n">
-        <v>2</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Mindre bastardsvärmare
-Sexfläckig bastardsvärmare
-Grönsångare
-Murgröna
-Tibast
-Trädporella</t>
-        </is>
-      </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43714-2025 artfynd.xlsx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43714-2025 karta.png", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43714-2025 georefererad karta.tif", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43714-2025 FSC-klagomål.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43714-2025 FSC-klagomål mail.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43714-2025 tillsynsbegäran.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43714-2025 tillsynsbegäran mail.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 43714-2025 prioriterade fågelarter.docx", "A 43714-2025")</f>
         <v/>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
         <v>46190</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>46003</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>46038</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>45616</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 26440-2026</t>
+          <t>A 19459-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4305,10 +4305,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46183</v>
+        <v>45049</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4321,16 +4321,16 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4345,7 +4345,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -4354,12 +4354,120 @@
         <v>4</v>
       </c>
       <c r="T32" t="n">
+        <v>4</v>
+      </c>
+      <c r="U32" t="n">
+        <v>4</v>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>Kavelhirs
+Kösa
+Luddvicker
+Riddarsporre</t>
+        </is>
+      </c>
+      <c r="W32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 19459-2023 artfynd.xlsx", "A 19459-2023")</f>
+        <v/>
+      </c>
+      <c r="X32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 19459-2023 karta.png", "A 19459-2023")</f>
+        <v/>
+      </c>
+      <c r="Y32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 19459-2023 georefererad karta.tif", "A 19459-2023")</f>
+        <v/>
+      </c>
+      <c r="AA32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 19459-2023 FSC-klagomål.docx", "A 19459-2023")</f>
+        <v/>
+      </c>
+      <c r="AB32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 19459-2023 FSC-klagomål mail.docx", "A 19459-2023")</f>
+        <v/>
+      </c>
+      <c r="AC32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 19459-2023 tillsynsbegäran.docx", "A 19459-2023")</f>
+        <v/>
+      </c>
+      <c r="AD32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 19459-2023 tillsynsbegäran mail.docx", "A 19459-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>A 26440-2026</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>4</v>
+      </c>
+      <c r="T33" t="n">
         <v>5</v>
       </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
         <is>
           <t>Backstarr
 Murgröna
@@ -4367,140 +4475,32 @@
 Vätteros</t>
         </is>
       </c>
-      <c r="W32">
+      <c r="W33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 26440-2026 artfynd.xlsx", "A 26440-2026")</f>
         <v/>
       </c>
-      <c r="X32">
+      <c r="X33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 26440-2026 karta.png", "A 26440-2026")</f>
         <v/>
       </c>
-      <c r="Y32">
+      <c r="Y33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 26440-2026 georefererad karta.tif", "A 26440-2026")</f>
         <v/>
       </c>
-      <c r="AA32">
+      <c r="AA33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 26440-2026 FSC-klagomål.docx", "A 26440-2026")</f>
         <v/>
       </c>
-      <c r="AB32">
+      <c r="AB33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 26440-2026 FSC-klagomål mail.docx", "A 26440-2026")</f>
         <v/>
       </c>
-      <c r="AC32">
+      <c r="AC33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 26440-2026 tillsynsbegäran.docx", "A 26440-2026")</f>
         <v/>
       </c>
-      <c r="AD32">
+      <c r="AD33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 26440-2026 tillsynsbegäran mail.docx", "A 26440-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>A 19459-2023</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D33" s="1" t="n">
-        <v>45049</v>
-      </c>
-      <c r="E33" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>4</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>4</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>4</v>
-      </c>
-      <c r="T33" t="n">
-        <v>4</v>
-      </c>
-      <c r="U33" t="n">
-        <v>4</v>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
-        <is>
-          <t>Kavelhirs
-Kösa
-Luddvicker
-Riddarsporre</t>
-        </is>
-      </c>
-      <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 19459-2023 artfynd.xlsx", "A 19459-2023")</f>
-        <v/>
-      </c>
-      <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 19459-2023 karta.png", "A 19459-2023")</f>
-        <v/>
-      </c>
-      <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 19459-2023 georefererad karta.tif", "A 19459-2023")</f>
-        <v/>
-      </c>
-      <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 19459-2023 FSC-klagomål.docx", "A 19459-2023")</f>
-        <v/>
-      </c>
-      <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 19459-2023 FSC-klagomål mail.docx", "A 19459-2023")</f>
-        <v/>
-      </c>
-      <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 19459-2023 tillsynsbegäran.docx", "A 19459-2023")</f>
-        <v/>
-      </c>
-      <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 19459-2023 tillsynsbegäran mail.docx", "A 19459-2023")</f>
         <v/>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
         <v>46254</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         <v>45912</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 29360-2026</t>
+          <t>A 15600-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4740,10 +4740,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46203</v>
+        <v>45747</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4756,19 +4756,19 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -4780,10 +4780,10 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>3</v>
@@ -4795,152 +4795,152 @@
         <v>1</v>
       </c>
       <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>Kragjordstjärna
+Murgröna
+Scharlakansvårskål agg.</t>
+        </is>
+      </c>
+      <c r="W36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 15600-2025 artfynd.xlsx", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="X36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 15600-2025 karta.png", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="Y36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 15600-2025 georefererad karta.tif", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="AA36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 15600-2025 FSC-klagomål.docx", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="AB36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 15600-2025 FSC-klagomål mail.docx", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="AC36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 15600-2025 tillsynsbegäran.docx", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="AD36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 15600-2025 tillsynsbegäran mail.docx", "A 15600-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>A 29360-2026</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D37" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="E37" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
         <is>
           <t>Mindre blåvinge
 Silversmygare
 Ekoxe</t>
         </is>
       </c>
-      <c r="W36">
+      <c r="W37">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 29360-2026 artfynd.xlsx", "A 29360-2026")</f>
         <v/>
       </c>
-      <c r="X36">
+      <c r="X37">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 29360-2026 karta.png", "A 29360-2026")</f>
         <v/>
       </c>
-      <c r="Y36">
+      <c r="Y37">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 29360-2026 georefererad karta.tif", "A 29360-2026")</f>
         <v/>
       </c>
-      <c r="AA36">
+      <c r="AA37">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 29360-2026 FSC-klagomål.docx", "A 29360-2026")</f>
         <v/>
       </c>
-      <c r="AB36">
+      <c r="AB37">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 29360-2026 FSC-klagomål mail.docx", "A 29360-2026")</f>
         <v/>
       </c>
-      <c r="AC36">
+      <c r="AC37">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 29360-2026 tillsynsbegäran.docx", "A 29360-2026")</f>
         <v/>
       </c>
-      <c r="AD36">
+      <c r="AD37">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 29360-2026 tillsynsbegäran mail.docx", "A 29360-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" ht="15" customHeight="1">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>A 15600-2025</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D37" s="1" t="n">
-        <v>45747</v>
-      </c>
-      <c r="E37" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="n">
-        <v>3</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="n">
-        <v>3</v>
-      </c>
-      <c r="T37" t="n">
-        <v>3</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1</v>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>Kragjordstjärna
-Murgröna
-Scharlakansvårskål agg.</t>
-        </is>
-      </c>
-      <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 15600-2025 artfynd.xlsx", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 15600-2025 karta.png", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 15600-2025 georefererad karta.tif", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 15600-2025 FSC-klagomål.docx", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 15600-2025 FSC-klagomål mail.docx", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 15600-2025 tillsynsbegäran.docx", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 15600-2025 tillsynsbegäran mail.docx", "A 15600-2025")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 62231-2023</t>
+          <t>A 72167-2021</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4950,14 +4950,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45267</v>
+        <v>44544</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J38" t="n">
         <v>1</v>
@@ -5011,42 +5011,46 @@
       <c r="V38" s="2" t="inlineStr">
         <is>
           <t>Murgröna
-Blåsippa</t>
+Röd glada</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62231-2023 artfynd.xlsx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 72167-2021 artfynd.xlsx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62231-2023 karta.png", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 72167-2021 karta.png", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62231-2023 georefererad karta.tif", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 72167-2021 georefererad karta.tif", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62231-2023 FSC-klagomål.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 72167-2021 FSC-klagomål.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62231-2023 FSC-klagomål mail.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 72167-2021 FSC-klagomål mail.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62231-2023 tillsynsbegäran.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 72167-2021 tillsynsbegäran.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62231-2023 tillsynsbegäran mail.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 72167-2021 tillsynsbegäran mail.docx", "A 72167-2021")</f>
+        <v/>
+      </c>
+      <c r="AE38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 72167-2021 prioriterade fågelarter.docx", "A 72167-2021")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 72167-2021</t>
+          <t>A 62231-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5056,14 +5060,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44544</v>
+        <v>45267</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5076,7 +5080,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J39" t="n">
         <v>1</v>
@@ -5117,39 +5121,35 @@
       <c r="V39" s="2" t="inlineStr">
         <is>
           <t>Murgröna
-Röd glada</t>
+Blåsippa</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 72167-2021 artfynd.xlsx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62231-2023 artfynd.xlsx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 72167-2021 karta.png", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62231-2023 karta.png", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 72167-2021 georefererad karta.tif", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62231-2023 georefererad karta.tif", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 72167-2021 FSC-klagomål.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62231-2023 FSC-klagomål.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 72167-2021 FSC-klagomål mail.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62231-2023 FSC-klagomål mail.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 72167-2021 tillsynsbegäran.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62231-2023 tillsynsbegäran.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 72167-2021 tillsynsbegäran mail.docx", "A 72167-2021")</f>
-        <v/>
-      </c>
-      <c r="AE39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 72167-2021 prioriterade fågelarter.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62231-2023 tillsynsbegäran mail.docx", "A 62231-2023")</f>
         <v/>
       </c>
     </row>
@@ -5173,7 +5173,7 @@
         <v>46246</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 62183-2025</t>
+          <t>A 13040-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5272,14 +5272,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46006</v>
+        <v>45385</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -5301,13 +5301,13 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5319,7 +5319,7 @@
         <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -5328,46 +5328,46 @@
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62183-2025 artfynd.xlsx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13040-2024 artfynd.xlsx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62183-2025 karta.png", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13040-2024 karta.png", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62183-2025 georefererad karta.tif", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13040-2024 georefererad karta.tif", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62183-2025 FSC-klagomål.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13040-2024 FSC-klagomål.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62183-2025 FSC-klagomål mail.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13040-2024 FSC-klagomål mail.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62183-2025 tillsynsbegäran.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13040-2024 tillsynsbegäran.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62183-2025 tillsynsbegäran mail.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13040-2024 tillsynsbegäran mail.docx", "A 13040-2024")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 24698-2023</t>
+          <t>A 13384-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5381,10 +5381,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45084</v>
+        <v>45005</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5397,16 +5397,16 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>5.5</v>
+        <v>0.9</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -5421,7 +5421,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -5437,42 +5437,42 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24698-2023 artfynd.xlsx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13384-2023 artfynd.xlsx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24698-2023 karta.png", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13384-2023 karta.png", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24698-2023 georefererad karta.tif", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13384-2023 georefererad karta.tif", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24698-2023 FSC-klagomål.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13384-2023 FSC-klagomål.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24698-2023 FSC-klagomål mail.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13384-2023 FSC-klagomål mail.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24698-2023 tillsynsbegäran.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13384-2023 tillsynsbegäran.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24698-2023 tillsynsbegäran mail.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13384-2023 tillsynsbegäran mail.docx", "A 13384-2023")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 13040-2024</t>
+          <t>A 62183-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5482,14 +5482,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45385</v>
+        <v>46006</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5511,13 +5511,13 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5529,7 +5529,7 @@
         <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5538,46 +5538,46 @@
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13040-2024 artfynd.xlsx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62183-2025 artfynd.xlsx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13040-2024 karta.png", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62183-2025 karta.png", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13040-2024 georefererad karta.tif", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62183-2025 georefererad karta.tif", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13040-2024 FSC-klagomål.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62183-2025 FSC-klagomål.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13040-2024 FSC-klagomål mail.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62183-2025 FSC-klagomål mail.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13040-2024 tillsynsbegäran.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62183-2025 tillsynsbegäran.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13040-2024 tillsynsbegäran mail.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62183-2025 tillsynsbegäran mail.docx", "A 62183-2025")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 13384-2023</t>
+          <t>A 30492-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5587,14 +5587,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45005</v>
+        <v>46210</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5607,16 +5607,16 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -5631,7 +5631,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -5643,46 +5643,46 @@
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13384-2023 artfynd.xlsx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 30492-2026 artfynd.xlsx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13384-2023 karta.png", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 30492-2026 karta.png", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13384-2023 georefererad karta.tif", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 30492-2026 georefererad karta.tif", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13384-2023 FSC-klagomål.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 30492-2026 FSC-klagomål.docx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13384-2023 FSC-klagomål mail.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 30492-2026 FSC-klagomål mail.docx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13384-2023 tillsynsbegäran.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 30492-2026 tillsynsbegäran.docx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13384-2023 tillsynsbegäran mail.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 30492-2026 tillsynsbegäran mail.docx", "A 30492-2026")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 30492-2026</t>
+          <t>A 36928-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5692,14 +5692,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46210</v>
+        <v>46273</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5712,16 +5712,16 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -5736,7 +5736,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -5752,42 +5752,42 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 30492-2026 artfynd.xlsx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 36928-2026 artfynd.xlsx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 30492-2026 karta.png", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 36928-2026 karta.png", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 30492-2026 georefererad karta.tif", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 36928-2026 georefererad karta.tif", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 30492-2026 FSC-klagomål.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 36928-2026 FSC-klagomål.docx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 30492-2026 FSC-klagomål mail.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 36928-2026 FSC-klagomål mail.docx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 30492-2026 tillsynsbegäran.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 36928-2026 tillsynsbegäran.docx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 30492-2026 tillsynsbegäran mail.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 36928-2026 tillsynsbegäran mail.docx", "A 36928-2026")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 36928-2026</t>
+          <t>A 24698-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5801,10 +5801,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46273</v>
+        <v>45084</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5817,16 +5817,16 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.3</v>
+        <v>5.5</v>
       </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -5841,7 +5841,7 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -5853,39 +5853,39 @@
         <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 36928-2026 artfynd.xlsx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24698-2023 artfynd.xlsx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 36928-2026 karta.png", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24698-2023 karta.png", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 36928-2026 georefererad karta.tif", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24698-2023 georefererad karta.tif", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 36928-2026 FSC-klagomål.docx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24698-2023 FSC-klagomål.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 36928-2026 FSC-klagomål mail.docx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24698-2023 FSC-klagomål mail.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 36928-2026 tillsynsbegäran.docx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24698-2023 tillsynsbegäran.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 36928-2026 tillsynsbegäran mail.docx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24698-2023 tillsynsbegäran mail.docx", "A 24698-2023")</f>
         <v/>
       </c>
     </row>
@@ -5909,7 +5909,7 @@
         <v>44740</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         <v>45980</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         <v>46171</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>

--- a/Översikt MÖRBYLÅNGA.xlsx
+++ b/Översikt MÖRBYLÅNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44964</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>44655</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>45177</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45096</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45685</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>46289</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>45475</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>45062</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>46195</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>46189</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>45254</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>45062</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>44508</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 60875-2025</t>
+          <t>A 38039-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2369,14 +2369,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45999</v>
+        <v>44811</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2389,31 +2389,31 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.1</v>
+        <v>7.4</v>
       </c>
       <c r="J15" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
         <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R15" t="n">
         <v>2</v>
@@ -2422,12 +2422,127 @@
         <v>11</v>
       </c>
       <c r="T15" t="n">
+        <v>13</v>
+      </c>
+      <c r="U15" t="n">
         <v>12</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Grov gulmossa
+Backtimjan
+Dvärgjordstjärna
+Solvända
+Ängsstarr
+Murgröna
+Alvarmalört
+Grönvit nattviol
+Krutbrännare
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 38039-2022 artfynd.xlsx", "A 38039-2022")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 38039-2022 karta.png", "A 38039-2022")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 38039-2022 georefererad karta.tif", "A 38039-2022")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 38039-2022 FSC-klagomål.docx", "A 38039-2022")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 38039-2022 FSC-klagomål mail.docx", "A 38039-2022")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 38039-2022 tillsynsbegäran.docx", "A 38039-2022")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 38039-2022 tillsynsbegäran mail.docx", "A 38039-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 60875-2025</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45999</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>8</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>5</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>7</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2</v>
+      </c>
+      <c r="S16" t="n">
+        <v>11</v>
+      </c>
+      <c r="T16" t="n">
+        <v>12</v>
+      </c>
+      <c r="U16" t="n">
         <v>3</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Järnek
 Mosippa
@@ -2442,111 +2557,111 @@
 Skogsduva</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 60875-2025 artfynd.xlsx", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 60875-2025 karta.png", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 60875-2025 georefererad karta.tif", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 60875-2025 FSC-klagomål.docx", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 60875-2025 FSC-klagomål mail.docx", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 60875-2025 tillsynsbegäran.docx", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 60875-2025 tillsynsbegäran mail.docx", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 60875-2025 prioriterade fågelarter.docx", "A 60875-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 38039-2022</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 27636-2023</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D16" s="1" t="n">
-        <v>44811</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="D17" s="1" t="n">
+        <v>45097</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I16" t="n">
+      <c r="I17" t="n">
         <v>7.4</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J17" t="n">
         <v>4</v>
       </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
         <v>4</v>
       </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>6</v>
       </c>
-      <c r="R16" t="n">
+      <c r="R17" t="n">
         <v>2</v>
       </c>
-      <c r="S16" t="n">
+      <c r="S17" t="n">
         <v>11</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T17" t="n">
         <v>13</v>
       </c>
-      <c r="U16" t="n">
-        <v>12</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="U17" t="n">
+        <v>11</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Ask
 Grov gulmossa
@@ -2561,121 +2676,6 @@
 Gullviva</t>
         </is>
       </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 38039-2022 artfynd.xlsx", "A 38039-2022")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 38039-2022 karta.png", "A 38039-2022")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 38039-2022 georefererad karta.tif", "A 38039-2022")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 38039-2022 FSC-klagomål.docx", "A 38039-2022")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 38039-2022 FSC-klagomål mail.docx", "A 38039-2022")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 38039-2022 tillsynsbegäran.docx", "A 38039-2022")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 38039-2022 tillsynsbegäran mail.docx", "A 38039-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 27636-2023</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45097</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="J17" t="n">
-        <v>4</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>4</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>6</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2</v>
-      </c>
-      <c r="S17" t="n">
-        <v>11</v>
-      </c>
-      <c r="T17" t="n">
-        <v>13</v>
-      </c>
-      <c r="U17" t="n">
-        <v>11</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Grov gulmossa
-Backtimjan
-Dvärgjordstjärna
-Solvända
-Ängsstarr
-Murgröna
-Alvarmalört
-Grönvit nattviol
-Krutbrännare
-Gullviva</t>
-        </is>
-      </c>
       <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 27636-2023 artfynd.xlsx", "A 27636-2023")</f>
         <v/>
@@ -2725,7 +2725,7 @@
         <v>44728</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>45551</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>44616</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>45000</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         <v>45530</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>45223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>45075</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>45169</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 43714-2025</t>
+          <t>A 43704-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3640,7 +3640,7 @@
         <v>45912</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3653,19 +3653,19 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>7.9</v>
+        <v>2.7</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -3677,21 +3677,131 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>6</v>
       </c>
       <c r="T26" t="n">
+        <v>6</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp
+Långbensgroda
+Större vattensalamander
+Åkergroda
+Mindre vattensalamander
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43704-2025 artfynd.xlsx", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="X26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43704-2025 karta.png", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="Y26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43704-2025 georefererad karta.tif", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="AA26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43704-2025 FSC-klagomål.docx", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="AB26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43704-2025 FSC-klagomål mail.docx", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="AC26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43704-2025 tillsynsbegäran.docx", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="AD26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43704-2025 tillsynsbegäran mail.docx", "A 43704-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 43714-2025</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>45912</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2</v>
+      </c>
+      <c r="S27" t="n">
+        <v>6</v>
+      </c>
+      <c r="T27" t="n">
         <v>8</v>
       </c>
-      <c r="U26" t="n">
+      <c r="U27" t="n">
         <v>2</v>
       </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>Mindre bastardsvärmare
 Sexfläckig bastardsvärmare
@@ -3701,146 +3811,36 @@
 Trädporella</t>
         </is>
       </c>
-      <c r="W26">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43714-2025 artfynd.xlsx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="X26">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43714-2025 karta.png", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="Y26">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43714-2025 georefererad karta.tif", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AA26">
+      <c r="AA27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43714-2025 FSC-klagomål.docx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AB26">
+      <c r="AB27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43714-2025 FSC-klagomål mail.docx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AC26">
+      <c r="AC27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43714-2025 tillsynsbegäran.docx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AD26">
+      <c r="AD27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43714-2025 tillsynsbegäran mail.docx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AE26">
+      <c r="AE27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 43714-2025 prioriterade fågelarter.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 43704-2025</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>45912</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J27" t="n">
-        <v>5</v>
-      </c>
-      <c r="K27" t="n">
-        <v>1</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>6</v>
-      </c>
-      <c r="T27" t="n">
-        <v>6</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Blomkålssvamp
-Långbensgroda
-Större vattensalamander
-Åkergroda
-Mindre vattensalamander
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43704-2025 artfynd.xlsx", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43704-2025 karta.png", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43704-2025 georefererad karta.tif", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43704-2025 FSC-klagomål.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43704-2025 FSC-klagomål mail.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43704-2025 tillsynsbegäran.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43704-2025 tillsynsbegäran mail.docx", "A 43704-2025")</f>
         <v/>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
         <v>46190</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>46003</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>46038</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>45616</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 19459-2023</t>
+          <t>A 26440-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4305,10 +4305,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45049</v>
+        <v>46183</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4321,16 +4321,16 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4345,7 +4345,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -4354,12 +4354,120 @@
         <v>4</v>
       </c>
       <c r="T32" t="n">
+        <v>5</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>Backstarr
+Murgröna
+Nästrot
+Vätteros</t>
+        </is>
+      </c>
+      <c r="W32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 26440-2026 artfynd.xlsx", "A 26440-2026")</f>
+        <v/>
+      </c>
+      <c r="X32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 26440-2026 karta.png", "A 26440-2026")</f>
+        <v/>
+      </c>
+      <c r="Y32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 26440-2026 georefererad karta.tif", "A 26440-2026")</f>
+        <v/>
+      </c>
+      <c r="AA32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 26440-2026 FSC-klagomål.docx", "A 26440-2026")</f>
+        <v/>
+      </c>
+      <c r="AB32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 26440-2026 FSC-klagomål mail.docx", "A 26440-2026")</f>
+        <v/>
+      </c>
+      <c r="AC32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 26440-2026 tillsynsbegäran.docx", "A 26440-2026")</f>
+        <v/>
+      </c>
+      <c r="AD32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 26440-2026 tillsynsbegäran mail.docx", "A 26440-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>A 19459-2023</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="n">
+        <v>45049</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
         <v>4</v>
       </c>
-      <c r="U32" t="n">
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
         <v>4</v>
       </c>
-      <c r="V32" s="2" t="inlineStr">
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>4</v>
+      </c>
+      <c r="T33" t="n">
+        <v>4</v>
+      </c>
+      <c r="U33" t="n">
+        <v>4</v>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
         <is>
           <t>Kavelhirs
 Kösa
@@ -4367,140 +4475,32 @@
 Riddarsporre</t>
         </is>
       </c>
-      <c r="W32">
+      <c r="W33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 19459-2023 artfynd.xlsx", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="X32">
+      <c r="X33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 19459-2023 karta.png", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="Y32">
+      <c r="Y33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 19459-2023 georefererad karta.tif", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="AA32">
+      <c r="AA33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 19459-2023 FSC-klagomål.docx", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="AB32">
+      <c r="AB33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 19459-2023 FSC-klagomål mail.docx", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="AC32">
+      <c r="AC33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 19459-2023 tillsynsbegäran.docx", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="AD32">
+      <c r="AD33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 19459-2023 tillsynsbegäran mail.docx", "A 19459-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>A 26440-2026</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D33" s="1" t="n">
-        <v>46183</v>
-      </c>
-      <c r="E33" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J33" t="n">
-        <v>1</v>
-      </c>
-      <c r="K33" t="n">
-        <v>3</v>
-      </c>
-      <c r="L33" t="n">
-        <v>1</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>4</v>
-      </c>
-      <c r="T33" t="n">
-        <v>5</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
-        <is>
-          <t>Backstarr
-Murgröna
-Nästrot
-Vätteros</t>
-        </is>
-      </c>
-      <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 26440-2026 artfynd.xlsx", "A 26440-2026")</f>
-        <v/>
-      </c>
-      <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 26440-2026 karta.png", "A 26440-2026")</f>
-        <v/>
-      </c>
-      <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 26440-2026 georefererad karta.tif", "A 26440-2026")</f>
-        <v/>
-      </c>
-      <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 26440-2026 FSC-klagomål.docx", "A 26440-2026")</f>
-        <v/>
-      </c>
-      <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 26440-2026 FSC-klagomål mail.docx", "A 26440-2026")</f>
-        <v/>
-      </c>
-      <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 26440-2026 tillsynsbegäran.docx", "A 26440-2026")</f>
-        <v/>
-      </c>
-      <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 26440-2026 tillsynsbegäran mail.docx", "A 26440-2026")</f>
         <v/>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
         <v>46254</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         <v>45912</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 15600-2025</t>
+          <t>A 29360-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4740,10 +4740,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45747</v>
+        <v>46203</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4756,19 +4756,19 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -4780,10 +4780,10 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S36" t="n">
         <v>3</v>
@@ -4795,152 +4795,152 @@
         <v>1</v>
       </c>
       <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>Mindre blåvinge
+Silversmygare
+Ekoxe</t>
+        </is>
+      </c>
+      <c r="W36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 29360-2026 artfynd.xlsx", "A 29360-2026")</f>
+        <v/>
+      </c>
+      <c r="X36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 29360-2026 karta.png", "A 29360-2026")</f>
+        <v/>
+      </c>
+      <c r="Y36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 29360-2026 georefererad karta.tif", "A 29360-2026")</f>
+        <v/>
+      </c>
+      <c r="AA36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 29360-2026 FSC-klagomål.docx", "A 29360-2026")</f>
+        <v/>
+      </c>
+      <c r="AB36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 29360-2026 FSC-klagomål mail.docx", "A 29360-2026")</f>
+        <v/>
+      </c>
+      <c r="AC36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 29360-2026 tillsynsbegäran.docx", "A 29360-2026")</f>
+        <v/>
+      </c>
+      <c r="AD36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 29360-2026 tillsynsbegäran mail.docx", "A 29360-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>A 15600-2025</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D37" s="1" t="n">
+        <v>45747</v>
+      </c>
+      <c r="E37" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
         <is>
           <t>Kragjordstjärna
 Murgröna
 Scharlakansvårskål agg.</t>
         </is>
       </c>
-      <c r="W36">
+      <c r="W37">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 15600-2025 artfynd.xlsx", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="X36">
+      <c r="X37">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 15600-2025 karta.png", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="Y36">
+      <c r="Y37">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 15600-2025 georefererad karta.tif", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="AA36">
+      <c r="AA37">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 15600-2025 FSC-klagomål.docx", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="AB36">
+      <c r="AB37">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 15600-2025 FSC-klagomål mail.docx", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="AC36">
+      <c r="AC37">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 15600-2025 tillsynsbegäran.docx", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="AD36">
+      <c r="AD37">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 15600-2025 tillsynsbegäran mail.docx", "A 15600-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" ht="15" customHeight="1">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>A 29360-2026</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D37" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="E37" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J37" t="n">
-        <v>1</v>
-      </c>
-      <c r="K37" t="n">
-        <v>1</v>
-      </c>
-      <c r="L37" t="n">
-        <v>1</v>
-      </c>
-      <c r="M37" t="n">
-        <v>1</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>2</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1</v>
-      </c>
-      <c r="S37" t="n">
-        <v>3</v>
-      </c>
-      <c r="T37" t="n">
-        <v>3</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1</v>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>Mindre blåvinge
-Silversmygare
-Ekoxe</t>
-        </is>
-      </c>
-      <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 29360-2026 artfynd.xlsx", "A 29360-2026")</f>
-        <v/>
-      </c>
-      <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 29360-2026 karta.png", "A 29360-2026")</f>
-        <v/>
-      </c>
-      <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 29360-2026 georefererad karta.tif", "A 29360-2026")</f>
-        <v/>
-      </c>
-      <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 29360-2026 FSC-klagomål.docx", "A 29360-2026")</f>
-        <v/>
-      </c>
-      <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 29360-2026 FSC-klagomål mail.docx", "A 29360-2026")</f>
-        <v/>
-      </c>
-      <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 29360-2026 tillsynsbegäran.docx", "A 29360-2026")</f>
-        <v/>
-      </c>
-      <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 29360-2026 tillsynsbegäran mail.docx", "A 29360-2026")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 72167-2021</t>
+          <t>A 62231-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4950,14 +4950,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44544</v>
+        <v>45267</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J38" t="n">
         <v>1</v>
@@ -5011,46 +5011,42 @@
       <c r="V38" s="2" t="inlineStr">
         <is>
           <t>Murgröna
-Röd glada</t>
+Blåsippa</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 72167-2021 artfynd.xlsx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62231-2023 artfynd.xlsx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 72167-2021 karta.png", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62231-2023 karta.png", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 72167-2021 georefererad karta.tif", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62231-2023 georefererad karta.tif", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 72167-2021 FSC-klagomål.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62231-2023 FSC-klagomål.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 72167-2021 FSC-klagomål mail.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62231-2023 FSC-klagomål mail.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 72167-2021 tillsynsbegäran.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62231-2023 tillsynsbegäran.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 72167-2021 tillsynsbegäran mail.docx", "A 72167-2021")</f>
-        <v/>
-      </c>
-      <c r="AE38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 72167-2021 prioriterade fågelarter.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62231-2023 tillsynsbegäran mail.docx", "A 62231-2023")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 62231-2023</t>
+          <t>A 72167-2021</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5060,14 +5056,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45267</v>
+        <v>44544</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5080,7 +5076,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J39" t="n">
         <v>1</v>
@@ -5121,35 +5117,39 @@
       <c r="V39" s="2" t="inlineStr">
         <is>
           <t>Murgröna
-Blåsippa</t>
+Röd glada</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62231-2023 artfynd.xlsx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 72167-2021 artfynd.xlsx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62231-2023 karta.png", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 72167-2021 karta.png", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62231-2023 georefererad karta.tif", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 72167-2021 georefererad karta.tif", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62231-2023 FSC-klagomål.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 72167-2021 FSC-klagomål.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62231-2023 FSC-klagomål mail.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 72167-2021 FSC-klagomål mail.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62231-2023 tillsynsbegäran.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 72167-2021 tillsynsbegäran.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62231-2023 tillsynsbegäran mail.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 72167-2021 tillsynsbegäran mail.docx", "A 72167-2021")</f>
+        <v/>
+      </c>
+      <c r="AE39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 72167-2021 prioriterade fågelarter.docx", "A 72167-2021")</f>
         <v/>
       </c>
     </row>
@@ -5173,7 +5173,7 @@
         <v>46246</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 13040-2024</t>
+          <t>A 24698-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5272,14 +5272,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45385</v>
+        <v>45084</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.2</v>
+        <v>5.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -5301,13 +5301,13 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5319,7 +5319,7 @@
         <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -5332,42 +5332,42 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13040-2024 artfynd.xlsx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24698-2023 artfynd.xlsx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13040-2024 karta.png", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24698-2023 karta.png", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13040-2024 georefererad karta.tif", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24698-2023 georefererad karta.tif", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13040-2024 FSC-klagomål.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24698-2023 FSC-klagomål.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13040-2024 FSC-klagomål mail.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24698-2023 FSC-klagomål mail.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13040-2024 tillsynsbegäran.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24698-2023 tillsynsbegäran.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13040-2024 tillsynsbegäran mail.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24698-2023 tillsynsbegäran mail.docx", "A 24698-2023")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 13384-2023</t>
+          <t>A 62183-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5381,10 +5381,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45005</v>
+        <v>46006</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5397,16 +5397,16 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -5421,7 +5421,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -5433,46 +5433,46 @@
         <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13384-2023 artfynd.xlsx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62183-2025 artfynd.xlsx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13384-2023 karta.png", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62183-2025 karta.png", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13384-2023 georefererad karta.tif", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62183-2025 georefererad karta.tif", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13384-2023 FSC-klagomål.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62183-2025 FSC-klagomål.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13384-2023 FSC-klagomål mail.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62183-2025 FSC-klagomål mail.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13384-2023 tillsynsbegäran.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62183-2025 tillsynsbegäran.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13384-2023 tillsynsbegäran mail.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62183-2025 tillsynsbegäran mail.docx", "A 62183-2025")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 62183-2025</t>
+          <t>A 13040-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5482,14 +5482,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46006</v>
+        <v>45385</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5511,13 +5511,13 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5529,7 +5529,7 @@
         <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5538,39 +5538,39 @@
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62183-2025 artfynd.xlsx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13040-2024 artfynd.xlsx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62183-2025 karta.png", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13040-2024 karta.png", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62183-2025 georefererad karta.tif", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13040-2024 georefererad karta.tif", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62183-2025 FSC-klagomål.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13040-2024 FSC-klagomål.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62183-2025 FSC-klagomål mail.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13040-2024 FSC-klagomål mail.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62183-2025 tillsynsbegäran.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13040-2024 tillsynsbegäran.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62183-2025 tillsynsbegäran mail.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13040-2024 tillsynsbegäran mail.docx", "A 13040-2024")</f>
         <v/>
       </c>
     </row>
@@ -5594,7 +5594,7 @@
         <v>46210</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 36928-2026</t>
+          <t>A 13384-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5696,10 +5696,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46273</v>
+        <v>45005</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5712,13 +5712,13 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J45" t="n">
         <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -5748,46 +5748,46 @@
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 36928-2026 artfynd.xlsx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13384-2023 artfynd.xlsx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 36928-2026 karta.png", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13384-2023 karta.png", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 36928-2026 georefererad karta.tif", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13384-2023 georefererad karta.tif", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 36928-2026 FSC-klagomål.docx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13384-2023 FSC-klagomål.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 36928-2026 FSC-klagomål mail.docx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13384-2023 FSC-klagomål mail.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 36928-2026 tillsynsbegäran.docx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13384-2023 tillsynsbegäran.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 36928-2026 tillsynsbegäran mail.docx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13384-2023 tillsynsbegäran mail.docx", "A 13384-2023")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 24698-2023</t>
+          <t>A 36928-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5801,10 +5801,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45084</v>
+        <v>46273</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5817,16 +5817,16 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>5.5</v>
+        <v>1.3</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -5841,7 +5841,7 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -5853,39 +5853,39 @@
         <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24698-2023 artfynd.xlsx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 36928-2026 artfynd.xlsx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24698-2023 karta.png", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 36928-2026 karta.png", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24698-2023 georefererad karta.tif", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 36928-2026 georefererad karta.tif", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24698-2023 FSC-klagomål.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 36928-2026 FSC-klagomål.docx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24698-2023 FSC-klagomål mail.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 36928-2026 FSC-klagomål mail.docx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24698-2023 tillsynsbegäran.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 36928-2026 tillsynsbegäran.docx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24698-2023 tillsynsbegäran mail.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 36928-2026 tillsynsbegäran mail.docx", "A 36928-2026")</f>
         <v/>
       </c>
     </row>
@@ -5909,7 +5909,7 @@
         <v>44740</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         <v>45980</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         <v>46171</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>

--- a/Översikt MÖRBYLÅNGA.xlsx
+++ b/Översikt MÖRBYLÅNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44964</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>44655</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>45177</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45096</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45685</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>46289</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>45475</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>45062</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>46195</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>46189</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>45254</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>45062</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>44508</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 38039-2022</t>
+          <t>A 60875-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2369,14 +2369,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44811</v>
+        <v>45999</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2389,31 +2389,31 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>7.4</v>
+        <v>2.1</v>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R15" t="n">
         <v>2</v>
@@ -2422,12 +2422,246 @@
         <v>11</v>
       </c>
       <c r="T15" t="n">
+        <v>12</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Järnek
+Mosippa
+Grönsångare
+Gulsparv
+Göktyta
+Mindre hackspett
+Svinrot
+Murgröna
+Spillkråka
+Kråka
+Skogsduva</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 60875-2025 artfynd.xlsx", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 60875-2025 karta.png", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 60875-2025 georefererad karta.tif", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 60875-2025 FSC-klagomål.docx", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 60875-2025 FSC-klagomål mail.docx", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 60875-2025 tillsynsbegäran.docx", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 60875-2025 tillsynsbegäran mail.docx", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 60875-2025 prioriterade fågelarter.docx", "A 60875-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 24778-2022</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>44728</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>7</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>8</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>11</v>
+      </c>
+      <c r="T16" t="n">
+        <v>20</v>
+      </c>
+      <c r="U16" t="n">
+        <v>20</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Tofsäxing
+Backtimjan
+Flentimotej
+Grådådra
+Poppeltofsskivling
+Slåtterfibbla
+Sminkrot
+Solvända
+Kalktallört
+Murgröna
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24778-2022 artfynd.xlsx", "A 24778-2022")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24778-2022 karta.png", "A 24778-2022")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24778-2022 georefererad karta.tif", "A 24778-2022")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24778-2022 FSC-klagomål.docx", "A 24778-2022")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24778-2022 FSC-klagomål mail.docx", "A 24778-2022")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24778-2022 tillsynsbegäran.docx", "A 24778-2022")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24778-2022 tillsynsbegäran mail.docx", "A 24778-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 38039-2022</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>44811</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>4</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>6</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2</v>
+      </c>
+      <c r="S17" t="n">
+        <v>11</v>
+      </c>
+      <c r="T17" t="n">
         <v>13</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U17" t="n">
         <v>12</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Ask
 Grov gulmossa
@@ -2442,226 +2676,107 @@
 Gullviva</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 38039-2022 artfynd.xlsx", "A 38039-2022")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 38039-2022 karta.png", "A 38039-2022")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 38039-2022 georefererad karta.tif", "A 38039-2022")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 38039-2022 FSC-klagomål.docx", "A 38039-2022")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 38039-2022 FSC-klagomål mail.docx", "A 38039-2022")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 38039-2022 tillsynsbegäran.docx", "A 38039-2022")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 38039-2022 tillsynsbegäran mail.docx", "A 38039-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 60875-2025</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 27636-2023</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45999</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45097</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J16" t="n">
-        <v>8</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>5</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>7</v>
-      </c>
-      <c r="R16" t="n">
+      <c r="I18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J18" t="n">
+        <v>4</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>4</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>6</v>
+      </c>
+      <c r="R18" t="n">
         <v>2</v>
       </c>
-      <c r="S16" t="n">
+      <c r="S18" t="n">
         <v>11</v>
       </c>
-      <c r="T16" t="n">
-        <v>12</v>
-      </c>
-      <c r="U16" t="n">
-        <v>3</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Järnek
-Mosippa
-Grönsångare
-Gulsparv
-Göktyta
-Mindre hackspett
-Svinrot
-Murgröna
-Spillkråka
-Kråka
-Skogsduva</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 60875-2025 artfynd.xlsx", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 60875-2025 karta.png", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 60875-2025 georefererad karta.tif", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 60875-2025 FSC-klagomål.docx", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 60875-2025 FSC-klagomål mail.docx", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 60875-2025 tillsynsbegäran.docx", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 60875-2025 tillsynsbegäran mail.docx", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 60875-2025 prioriterade fågelarter.docx", "A 60875-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 27636-2023</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45097</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="J17" t="n">
-        <v>4</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>4</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>6</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="T18" t="n">
+        <v>13</v>
+      </c>
+      <c r="U18" t="n">
         <v>11</v>
       </c>
-      <c r="T17" t="n">
-        <v>13</v>
-      </c>
-      <c r="U17" t="n">
-        <v>11</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Ask
 Grov gulmossa
@@ -2676,147 +2791,32 @@
 Gullviva</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 27636-2023 artfynd.xlsx", "A 27636-2023")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 27636-2023 karta.png", "A 27636-2023")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 27636-2023 georefererad karta.tif", "A 27636-2023")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 27636-2023 FSC-klagomål.docx", "A 27636-2023")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 27636-2023 FSC-klagomål mail.docx", "A 27636-2023")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 27636-2023 tillsynsbegäran.docx", "A 27636-2023")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 27636-2023 tillsynsbegäran mail.docx", "A 27636-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 24778-2022</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>44728</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2</v>
-      </c>
-      <c r="L18" t="n">
-        <v>7</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>8</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1</v>
-      </c>
-      <c r="S18" t="n">
-        <v>11</v>
-      </c>
-      <c r="T18" t="n">
-        <v>20</v>
-      </c>
-      <c r="U18" t="n">
-        <v>20</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Tofsäxing
-Backtimjan
-Flentimotej
-Grådådra
-Poppeltofsskivling
-Slåtterfibbla
-Sminkrot
-Solvända
-Kalktallört
-Murgröna
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24778-2022 artfynd.xlsx", "A 24778-2022")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24778-2022 karta.png", "A 24778-2022")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24778-2022 georefererad karta.tif", "A 24778-2022")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24778-2022 FSC-klagomål.docx", "A 24778-2022")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24778-2022 FSC-klagomål mail.docx", "A 24778-2022")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24778-2022 tillsynsbegäran.docx", "A 24778-2022")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24778-2022 tillsynsbegäran mail.docx", "A 24778-2022")</f>
         <v/>
       </c>
     </row>
@@ -2840,7 +2840,7 @@
         <v>45551</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>44616</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>45000</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         <v>45530</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>45223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>45075</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>45169</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 43704-2025</t>
+          <t>A 43714-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3640,7 +3640,7 @@
         <v>45912</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3653,19 +3653,19 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.7</v>
+        <v>7.9</v>
       </c>
       <c r="J26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -3677,21 +3677,135 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S26" t="n">
         <v>6</v>
       </c>
       <c r="T26" t="n">
+        <v>8</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Mindre bastardsvärmare
+Sexfläckig bastardsvärmare
+Grönsångare
+Murgröna
+Tibast
+Trädporella</t>
+        </is>
+      </c>
+      <c r="W26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43714-2025 artfynd.xlsx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="X26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43714-2025 karta.png", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="Y26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43714-2025 georefererad karta.tif", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AA26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43714-2025 FSC-klagomål.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AB26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43714-2025 FSC-klagomål mail.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AC26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43714-2025 tillsynsbegäran.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AD26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43714-2025 tillsynsbegäran mail.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 43714-2025 prioriterade fågelarter.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 43704-2025</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>45912</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J27" t="n">
+        <v>5</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
         <v>6</v>
       </c>
-      <c r="U26" t="n">
-        <v>1</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="T27" t="n">
+        <v>6</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>Blomkålssvamp
 Långbensgroda
@@ -3701,146 +3815,32 @@
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W26">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43704-2025 artfynd.xlsx", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="X26">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43704-2025 karta.png", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="Y26">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43704-2025 georefererad karta.tif", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="AA26">
+      <c r="AA27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43704-2025 FSC-klagomål.docx", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="AB26">
+      <c r="AB27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43704-2025 FSC-klagomål mail.docx", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="AC26">
+      <c r="AC27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43704-2025 tillsynsbegäran.docx", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="AD26">
+      <c r="AD27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43704-2025 tillsynsbegäran mail.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 43714-2025</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>45912</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="J27" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>3</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1</v>
-      </c>
-      <c r="M27" t="n">
-        <v>2</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>3</v>
-      </c>
-      <c r="R27" t="n">
-        <v>2</v>
-      </c>
-      <c r="S27" t="n">
-        <v>6</v>
-      </c>
-      <c r="T27" t="n">
-        <v>8</v>
-      </c>
-      <c r="U27" t="n">
-        <v>2</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Mindre bastardsvärmare
-Sexfläckig bastardsvärmare
-Grönsångare
-Murgröna
-Tibast
-Trädporella</t>
-        </is>
-      </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43714-2025 artfynd.xlsx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43714-2025 karta.png", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43714-2025 georefererad karta.tif", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43714-2025 FSC-klagomål.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43714-2025 FSC-klagomål mail.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43714-2025 tillsynsbegäran.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43714-2025 tillsynsbegäran mail.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 43714-2025 prioriterade fågelarter.docx", "A 43714-2025")</f>
         <v/>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
         <v>46190</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>46003</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>46038</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>45616</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 26440-2026</t>
+          <t>A 19459-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4305,10 +4305,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46183</v>
+        <v>45049</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4321,16 +4321,16 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4345,7 +4345,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -4354,12 +4354,120 @@
         <v>4</v>
       </c>
       <c r="T32" t="n">
+        <v>4</v>
+      </c>
+      <c r="U32" t="n">
+        <v>4</v>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>Kavelhirs
+Kösa
+Luddvicker
+Riddarsporre</t>
+        </is>
+      </c>
+      <c r="W32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 19459-2023 artfynd.xlsx", "A 19459-2023")</f>
+        <v/>
+      </c>
+      <c r="X32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 19459-2023 karta.png", "A 19459-2023")</f>
+        <v/>
+      </c>
+      <c r="Y32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 19459-2023 georefererad karta.tif", "A 19459-2023")</f>
+        <v/>
+      </c>
+      <c r="AA32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 19459-2023 FSC-klagomål.docx", "A 19459-2023")</f>
+        <v/>
+      </c>
+      <c r="AB32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 19459-2023 FSC-klagomål mail.docx", "A 19459-2023")</f>
+        <v/>
+      </c>
+      <c r="AC32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 19459-2023 tillsynsbegäran.docx", "A 19459-2023")</f>
+        <v/>
+      </c>
+      <c r="AD32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 19459-2023 tillsynsbegäran mail.docx", "A 19459-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>A 26440-2026</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>4</v>
+      </c>
+      <c r="T33" t="n">
         <v>5</v>
       </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
         <is>
           <t>Backstarr
 Murgröna
@@ -4367,140 +4475,32 @@
 Vätteros</t>
         </is>
       </c>
-      <c r="W32">
+      <c r="W33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 26440-2026 artfynd.xlsx", "A 26440-2026")</f>
         <v/>
       </c>
-      <c r="X32">
+      <c r="X33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 26440-2026 karta.png", "A 26440-2026")</f>
         <v/>
       </c>
-      <c r="Y32">
+      <c r="Y33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 26440-2026 georefererad karta.tif", "A 26440-2026")</f>
         <v/>
       </c>
-      <c r="AA32">
+      <c r="AA33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 26440-2026 FSC-klagomål.docx", "A 26440-2026")</f>
         <v/>
       </c>
-      <c r="AB32">
+      <c r="AB33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 26440-2026 FSC-klagomål mail.docx", "A 26440-2026")</f>
         <v/>
       </c>
-      <c r="AC32">
+      <c r="AC33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 26440-2026 tillsynsbegäran.docx", "A 26440-2026")</f>
         <v/>
       </c>
-      <c r="AD32">
+      <c r="AD33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 26440-2026 tillsynsbegäran mail.docx", "A 26440-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>A 19459-2023</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D33" s="1" t="n">
-        <v>45049</v>
-      </c>
-      <c r="E33" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>4</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>4</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>4</v>
-      </c>
-      <c r="T33" t="n">
-        <v>4</v>
-      </c>
-      <c r="U33" t="n">
-        <v>4</v>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
-        <is>
-          <t>Kavelhirs
-Kösa
-Luddvicker
-Riddarsporre</t>
-        </is>
-      </c>
-      <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 19459-2023 artfynd.xlsx", "A 19459-2023")</f>
-        <v/>
-      </c>
-      <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 19459-2023 karta.png", "A 19459-2023")</f>
-        <v/>
-      </c>
-      <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 19459-2023 georefererad karta.tif", "A 19459-2023")</f>
-        <v/>
-      </c>
-      <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 19459-2023 FSC-klagomål.docx", "A 19459-2023")</f>
-        <v/>
-      </c>
-      <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 19459-2023 FSC-klagomål mail.docx", "A 19459-2023")</f>
-        <v/>
-      </c>
-      <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 19459-2023 tillsynsbegäran.docx", "A 19459-2023")</f>
-        <v/>
-      </c>
-      <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 19459-2023 tillsynsbegäran mail.docx", "A 19459-2023")</f>
         <v/>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
         <v>46254</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 43702-2025</t>
+          <t>A 15600-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4629,14 +4629,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45912</v>
+        <v>45747</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4649,16 +4649,16 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -4673,7 +4673,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -4685,262 +4685,262 @@
         <v>3</v>
       </c>
       <c r="U35" t="n">
+        <v>1</v>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>Kragjordstjärna
+Murgröna
+Scharlakansvårskål agg.</t>
+        </is>
+      </c>
+      <c r="W35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 15600-2025 artfynd.xlsx", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="X35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 15600-2025 karta.png", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="Y35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 15600-2025 georefererad karta.tif", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="AA35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 15600-2025 FSC-klagomål.docx", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="AB35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 15600-2025 FSC-klagomål mail.docx", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="AC35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 15600-2025 tillsynsbegäran.docx", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="AD35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 15600-2025 tillsynsbegäran mail.docx", "A 15600-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>A 43702-2025</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D36" s="1" t="n">
+        <v>45912</v>
+      </c>
+      <c r="E36" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
         <v>2</v>
       </c>
-      <c r="V35" s="2" t="inlineStr">
+      <c r="L36" t="n">
+        <v>1</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
         <is>
           <t>Sårläka
 Murgröna
 Tibast</t>
         </is>
       </c>
-      <c r="W35">
+      <c r="W36">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43702-2025 artfynd.xlsx", "A 43702-2025")</f>
         <v/>
       </c>
-      <c r="X35">
+      <c r="X36">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43702-2025 karta.png", "A 43702-2025")</f>
         <v/>
       </c>
-      <c r="Y35">
+      <c r="Y36">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43702-2025 georefererad karta.tif", "A 43702-2025")</f>
         <v/>
       </c>
-      <c r="AA35">
+      <c r="AA36">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43702-2025 FSC-klagomål.docx", "A 43702-2025")</f>
         <v/>
       </c>
-      <c r="AB35">
+      <c r="AB36">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43702-2025 FSC-klagomål mail.docx", "A 43702-2025")</f>
         <v/>
       </c>
-      <c r="AC35">
+      <c r="AC36">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43702-2025 tillsynsbegäran.docx", "A 43702-2025")</f>
         <v/>
       </c>
-      <c r="AD35">
+      <c r="AD36">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43702-2025 tillsynsbegäran mail.docx", "A 43702-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>A 29360-2026</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D36" s="1" t="n">
+      <c r="D37" s="1" t="n">
         <v>46203</v>
       </c>
-      <c r="E36" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F36" t="inlineStr">
+      <c r="E37" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I36" t="n">
+      <c r="I37" t="n">
         <v>2.9</v>
       </c>
-      <c r="J36" t="n">
-        <v>1</v>
-      </c>
-      <c r="K36" t="n">
-        <v>1</v>
-      </c>
-      <c r="L36" t="n">
-        <v>1</v>
-      </c>
-      <c r="M36" t="n">
-        <v>1</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
+      <c r="J37" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
         <v>2</v>
       </c>
-      <c r="R36" t="n">
-        <v>1</v>
-      </c>
-      <c r="S36" t="n">
+      <c r="R37" t="n">
+        <v>1</v>
+      </c>
+      <c r="S37" t="n">
         <v>3</v>
       </c>
-      <c r="T36" t="n">
+      <c r="T37" t="n">
         <v>3</v>
       </c>
-      <c r="U36" t="n">
-        <v>1</v>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
+      <c r="U37" t="n">
+        <v>1</v>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
         <is>
           <t>Mindre blåvinge
 Silversmygare
 Ekoxe</t>
         </is>
       </c>
-      <c r="W36">
+      <c r="W37">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 29360-2026 artfynd.xlsx", "A 29360-2026")</f>
         <v/>
       </c>
-      <c r="X36">
+      <c r="X37">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 29360-2026 karta.png", "A 29360-2026")</f>
         <v/>
       </c>
-      <c r="Y36">
+      <c r="Y37">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 29360-2026 georefererad karta.tif", "A 29360-2026")</f>
         <v/>
       </c>
-      <c r="AA36">
+      <c r="AA37">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 29360-2026 FSC-klagomål.docx", "A 29360-2026")</f>
         <v/>
       </c>
-      <c r="AB36">
+      <c r="AB37">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 29360-2026 FSC-klagomål mail.docx", "A 29360-2026")</f>
         <v/>
       </c>
-      <c r="AC36">
+      <c r="AC37">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 29360-2026 tillsynsbegäran.docx", "A 29360-2026")</f>
         <v/>
       </c>
-      <c r="AD36">
+      <c r="AD37">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 29360-2026 tillsynsbegäran mail.docx", "A 29360-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" ht="15" customHeight="1">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>A 15600-2025</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D37" s="1" t="n">
-        <v>45747</v>
-      </c>
-      <c r="E37" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="n">
-        <v>3</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="n">
-        <v>3</v>
-      </c>
-      <c r="T37" t="n">
-        <v>3</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1</v>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>Kragjordstjärna
-Murgröna
-Scharlakansvårskål agg.</t>
-        </is>
-      </c>
-      <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 15600-2025 artfynd.xlsx", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 15600-2025 karta.png", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 15600-2025 georefererad karta.tif", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 15600-2025 FSC-klagomål.docx", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 15600-2025 FSC-klagomål mail.docx", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 15600-2025 tillsynsbegäran.docx", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 15600-2025 tillsynsbegäran mail.docx", "A 15600-2025")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 62231-2023</t>
+          <t>A 72167-2021</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4950,14 +4950,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45267</v>
+        <v>44544</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J38" t="n">
         <v>1</v>
@@ -5011,42 +5011,46 @@
       <c r="V38" s="2" t="inlineStr">
         <is>
           <t>Murgröna
-Blåsippa</t>
+Röd glada</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62231-2023 artfynd.xlsx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 72167-2021 artfynd.xlsx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62231-2023 karta.png", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 72167-2021 karta.png", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62231-2023 georefererad karta.tif", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 72167-2021 georefererad karta.tif", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62231-2023 FSC-klagomål.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 72167-2021 FSC-klagomål.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62231-2023 FSC-klagomål mail.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 72167-2021 FSC-klagomål mail.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62231-2023 tillsynsbegäran.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 72167-2021 tillsynsbegäran.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62231-2023 tillsynsbegäran mail.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 72167-2021 tillsynsbegäran mail.docx", "A 72167-2021")</f>
+        <v/>
+      </c>
+      <c r="AE38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 72167-2021 prioriterade fågelarter.docx", "A 72167-2021")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 72167-2021</t>
+          <t>A 62231-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5056,14 +5060,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44544</v>
+        <v>45267</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5076,7 +5080,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J39" t="n">
         <v>1</v>
@@ -5117,39 +5121,35 @@
       <c r="V39" s="2" t="inlineStr">
         <is>
           <t>Murgröna
-Röd glada</t>
+Blåsippa</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 72167-2021 artfynd.xlsx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62231-2023 artfynd.xlsx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 72167-2021 karta.png", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62231-2023 karta.png", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 72167-2021 georefererad karta.tif", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62231-2023 georefererad karta.tif", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 72167-2021 FSC-klagomål.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62231-2023 FSC-klagomål.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 72167-2021 FSC-klagomål mail.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62231-2023 FSC-klagomål mail.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 72167-2021 tillsynsbegäran.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62231-2023 tillsynsbegäran.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 72167-2021 tillsynsbegäran mail.docx", "A 72167-2021")</f>
-        <v/>
-      </c>
-      <c r="AE39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 72167-2021 prioriterade fågelarter.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62231-2023 tillsynsbegäran mail.docx", "A 62231-2023")</f>
         <v/>
       </c>
     </row>
@@ -5173,7 +5173,7 @@
         <v>46246</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 24698-2023</t>
+          <t>A 13040-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5272,14 +5272,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45084</v>
+        <v>45385</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>5.5</v>
+        <v>1.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -5301,13 +5301,13 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5319,7 +5319,7 @@
         <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -5332,42 +5332,42 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24698-2023 artfynd.xlsx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13040-2024 artfynd.xlsx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24698-2023 karta.png", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13040-2024 karta.png", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24698-2023 georefererad karta.tif", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13040-2024 georefererad karta.tif", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24698-2023 FSC-klagomål.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13040-2024 FSC-klagomål.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24698-2023 FSC-klagomål mail.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13040-2024 FSC-klagomål mail.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24698-2023 tillsynsbegäran.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13040-2024 tillsynsbegäran.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24698-2023 tillsynsbegäran mail.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13040-2024 tillsynsbegäran mail.docx", "A 13040-2024")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 62183-2025</t>
+          <t>A 24698-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5381,10 +5381,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46006</v>
+        <v>45084</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.8</v>
+        <v>5.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -5433,46 +5433,46 @@
         <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62183-2025 artfynd.xlsx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24698-2023 artfynd.xlsx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62183-2025 karta.png", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24698-2023 karta.png", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62183-2025 georefererad karta.tif", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24698-2023 georefererad karta.tif", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62183-2025 FSC-klagomål.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24698-2023 FSC-klagomål.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62183-2025 FSC-klagomål mail.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24698-2023 FSC-klagomål mail.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62183-2025 tillsynsbegäran.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24698-2023 tillsynsbegäran.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62183-2025 tillsynsbegäran mail.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24698-2023 tillsynsbegäran mail.docx", "A 24698-2023")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 13040-2024</t>
+          <t>A 13384-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5482,14 +5482,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45385</v>
+        <v>45005</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5502,10 +5502,10 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -5517,7 +5517,7 @@
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5526,10 +5526,10 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5542,42 +5542,42 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13040-2024 artfynd.xlsx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13384-2023 artfynd.xlsx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13040-2024 karta.png", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13384-2023 karta.png", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13040-2024 georefererad karta.tif", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13384-2023 georefererad karta.tif", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13040-2024 FSC-klagomål.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13384-2023 FSC-klagomål.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13040-2024 FSC-klagomål mail.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13384-2023 FSC-klagomål mail.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13040-2024 tillsynsbegäran.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13384-2023 tillsynsbegäran.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13040-2024 tillsynsbegäran mail.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13384-2023 tillsynsbegäran mail.docx", "A 13384-2023")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 30492-2026</t>
+          <t>A 62183-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5587,14 +5587,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46210</v>
+        <v>46006</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5647,42 +5647,42 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 30492-2026 artfynd.xlsx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62183-2025 artfynd.xlsx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 30492-2026 karta.png", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62183-2025 karta.png", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 30492-2026 georefererad karta.tif", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62183-2025 georefererad karta.tif", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 30492-2026 FSC-klagomål.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62183-2025 FSC-klagomål.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 30492-2026 FSC-klagomål mail.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62183-2025 FSC-klagomål mail.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 30492-2026 tillsynsbegäran.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62183-2025 tillsynsbegäran.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 30492-2026 tillsynsbegäran mail.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62183-2025 tillsynsbegäran mail.docx", "A 62183-2025")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 13384-2023</t>
+          <t>A 30492-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5692,14 +5692,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45005</v>
+        <v>46210</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5712,16 +5712,16 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -5736,7 +5736,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -5748,39 +5748,39 @@
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13384-2023 artfynd.xlsx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 30492-2026 artfynd.xlsx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13384-2023 karta.png", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 30492-2026 karta.png", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13384-2023 georefererad karta.tif", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 30492-2026 georefererad karta.tif", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13384-2023 FSC-klagomål.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 30492-2026 FSC-klagomål.docx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13384-2023 FSC-klagomål mail.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 30492-2026 FSC-klagomål mail.docx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13384-2023 tillsynsbegäran.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 30492-2026 tillsynsbegäran.docx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13384-2023 tillsynsbegäran mail.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 30492-2026 tillsynsbegäran mail.docx", "A 30492-2026")</f>
         <v/>
       </c>
     </row>
@@ -5804,7 +5804,7 @@
         <v>46273</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         <v>44740</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         <v>45980</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         <v>46171</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>

--- a/Översikt MÖRBYLÅNGA.xlsx
+++ b/Översikt MÖRBYLÅNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44964</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>44655</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>45177</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45096</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45685</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>46289</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>45475</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>45062</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>46195</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>46189</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>45254</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>45062</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>44508</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>45999</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>44728</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>44811</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>45097</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>45551</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2937,24 +2937,24 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S 1122-2022</t>
+          <t>A 15600-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44616</v>
+        <v>45747</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2967,22 +2967,22 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2991,21 +2991,139 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
       </c>
       <c r="T20" t="n">
+        <v>20</v>
+      </c>
+      <c r="U20" t="n">
+        <v>18</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Kragjordstjärna
+Murgröna
+Scharlakansvårskål agg.
+Tibast
+Blåsippa
+Skärmstarr
+Spillkråka
+Storrams
+Röd glada</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 15600-2025 artfynd.xlsx", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 15600-2025 karta.png", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 15600-2025 georefererad karta.tif", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 15600-2025 FSC-klagomål.docx", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 15600-2025 FSC-klagomål mail.docx", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 15600-2025 tillsynsbegäran.docx", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 15600-2025 tillsynsbegäran mail.docx", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 15600-2025 prioriterade fågelarter.docx", "A 15600-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>S 1122-2022</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>44616</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L21" t="n">
+        <v>3</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>6</v>
+      </c>
+      <c r="R21" t="n">
+        <v>3</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="n">
         <v>16</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U21" t="n">
         <v>15</v>
       </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Ask
 Lundalm
@@ -3019,107 +3137,107 @@
 Sankt pers nycklar</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/S 1122-2022 artfynd.xlsx", "S 1122-2022")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/S 1122-2022 karta.png", "S 1122-2022")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/S 1122-2022 georefererad karta.tif", "S 1122-2022")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/S 1122-2022 FSC-klagomål.docx", "S 1122-2022")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/S 1122-2022 FSC-klagomål mail.docx", "S 1122-2022")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/S 1122-2022 tillsynsbegäran.docx", "S 1122-2022")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/S 1122-2022 tillsynsbegäran mail.docx", "S 1122-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>S 929-2023</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D21" s="1" t="n">
+      <c r="D22" s="1" t="n">
         <v>45000</v>
       </c>
-      <c r="E21" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F21" t="inlineStr">
+      <c r="E22" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I21" t="n">
+      <c r="I22" t="n">
         <v>4.7</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J22" t="n">
         <v>4</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K22" t="n">
         <v>2</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L22" t="n">
         <v>3</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M22" t="n">
         <v>3</v>
       </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
         <v>6</v>
       </c>
-      <c r="R21" t="n">
+      <c r="R22" t="n">
         <v>3</v>
       </c>
-      <c r="S21" t="n">
+      <c r="S22" t="n">
         <v>9</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T22" t="n">
         <v>12</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U22" t="n">
         <v>8</v>
       </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Liten jordstjärna
 Stare
@@ -3132,111 +3250,111 @@
 Kopparödla</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/S 929-2023 artfynd.xlsx", "S 929-2023")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/S 929-2023 karta.png", "S 929-2023")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/S 929-2023 georefererad karta.tif", "S 929-2023")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/S 929-2023 FSC-klagomål.docx", "S 929-2023")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/S 929-2023 FSC-klagomål mail.docx", "S 929-2023")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/S 929-2023 tillsynsbegäran.docx", "S 929-2023")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/S 929-2023 tillsynsbegäran mail.docx", "S 929-2023")</f>
         <v/>
       </c>
-      <c r="AE21">
+      <c r="AE22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/S 929-2023 prioriterade fågelarter.docx", "S 929-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>A 35242-2024</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D22" s="1" t="n">
+      <c r="D23" s="1" t="n">
         <v>45530</v>
       </c>
-      <c r="E22" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F22" t="inlineStr">
+      <c r="E23" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I22" t="n">
+      <c r="I23" t="n">
         <v>0.9</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J23" t="n">
         <v>2</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K23" t="n">
         <v>3</v>
       </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>3</v>
       </c>
-      <c r="N22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="N23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
         <v>4</v>
       </c>
-      <c r="R22" t="n">
+      <c r="R23" t="n">
         <v>4</v>
       </c>
-      <c r="S22" t="n">
+      <c r="S23" t="n">
         <v>8</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T23" t="n">
         <v>12</v>
       </c>
-      <c r="U22" t="n">
+      <c r="U23" t="n">
         <v>6</v>
       </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Sandgeting
 Liten diskröksvamp
@@ -3248,111 +3366,111 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W22">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 35242-2024 artfynd.xlsx", "A 35242-2024")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 35242-2024 karta.png", "A 35242-2024")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 35242-2024 georefererad karta.tif", "A 35242-2024")</f>
         <v/>
       </c>
-      <c r="Z22">
+      <c r="Z23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/knärot/A 35242-2024 karta knärot.png", "A 35242-2024")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 35242-2024 FSC-klagomål.docx", "A 35242-2024")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 35242-2024 FSC-klagomål mail.docx", "A 35242-2024")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 35242-2024 tillsynsbegäran.docx", "A 35242-2024")</f>
         <v/>
       </c>
-      <c r="AD22">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 35242-2024 tillsynsbegäran mail.docx", "A 35242-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>S 3773-2023</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D23" s="1" t="n">
+      <c r="D24" s="1" t="n">
         <v>45223</v>
       </c>
-      <c r="E23" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F23" t="inlineStr">
+      <c r="E24" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I23" t="n">
+      <c r="I24" t="n">
         <v>0.3</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J24" t="n">
         <v>2</v>
       </c>
-      <c r="K23" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" t="n">
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
         <v>3</v>
       </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
         <v>2</v>
       </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
         <v>5</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R24" t="n">
         <v>2</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S24" t="n">
         <v>8</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T24" t="n">
         <v>9</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U24" t="n">
         <v>9</v>
       </c>
-      <c r="V23" s="2" t="inlineStr">
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>Ask
 Lundalm
@@ -3364,107 +3482,107 @@
 Gullviva</t>
         </is>
       </c>
-      <c r="W23">
+      <c r="W24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/S 3773-2023 artfynd.xlsx", "S 3773-2023")</f>
         <v/>
       </c>
-      <c r="X23">
+      <c r="X24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/S 3773-2023 karta.png", "S 3773-2023")</f>
         <v/>
       </c>
-      <c r="Y23">
+      <c r="Y24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/S 3773-2023 georefererad karta.tif", "S 3773-2023")</f>
         <v/>
       </c>
-      <c r="AA23">
+      <c r="AA24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/S 3773-2023 FSC-klagomål.docx", "S 3773-2023")</f>
         <v/>
       </c>
-      <c r="AB23">
+      <c r="AB24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/S 3773-2023 FSC-klagomål mail.docx", "S 3773-2023")</f>
         <v/>
       </c>
-      <c r="AC23">
+      <c r="AC24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/S 3773-2023 tillsynsbegäran.docx", "S 3773-2023")</f>
         <v/>
       </c>
-      <c r="AD23">
+      <c r="AD24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/S 3773-2023 tillsynsbegäran mail.docx", "S 3773-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>S 1833-2023</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D24" s="1" t="n">
+      <c r="D25" s="1" t="n">
         <v>45075</v>
       </c>
-      <c r="E24" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F24" t="inlineStr">
+      <c r="E25" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I24" t="n">
+      <c r="I25" t="n">
         <v>0.4</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J25" t="n">
         <v>3</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K25" t="n">
         <v>2</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L25" t="n">
         <v>3</v>
       </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
         <v>3</v>
       </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
         <v>8</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T25" t="n">
         <v>11</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U25" t="n">
         <v>10</v>
       </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Sårläka
 Vippärt
@@ -3476,107 +3594,107 @@
 Gullviva</t>
         </is>
       </c>
-      <c r="W24">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/S 1833-2023 artfynd.xlsx", "S 1833-2023")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/S 1833-2023 karta.png", "S 1833-2023")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/S 1833-2023 georefererad karta.tif", "S 1833-2023")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/S 1833-2023 FSC-klagomål.docx", "S 1833-2023")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/S 1833-2023 FSC-klagomål mail.docx", "S 1833-2023")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/S 1833-2023 tillsynsbegäran.docx", "S 1833-2023")</f>
         <v/>
       </c>
-      <c r="AD24">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/S 1833-2023 tillsynsbegäran mail.docx", "S 1833-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>A 40361-2023</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D25" s="1" t="n">
+      <c r="D26" s="1" t="n">
         <v>45169</v>
       </c>
-      <c r="E25" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F25" t="inlineStr">
+      <c r="E26" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I25" t="n">
+      <c r="I26" t="n">
         <v>1.1</v>
       </c>
-      <c r="J25" t="n">
-        <v>1</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
         <v>4</v>
       </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
         <v>2</v>
       </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
         <v>6</v>
       </c>
-      <c r="R25" t="n">
+      <c r="R26" t="n">
         <v>2</v>
       </c>
-      <c r="S25" t="n">
+      <c r="S26" t="n">
         <v>7</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T26" t="n">
         <v>11</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U26" t="n">
         <v>10</v>
       </c>
-      <c r="V25" s="2" t="inlineStr">
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Ask
 Lundalm
@@ -3587,111 +3705,221 @@
 Näktergal</t>
         </is>
       </c>
-      <c r="W25">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 40361-2023 artfynd.xlsx", "A 40361-2023")</f>
         <v/>
       </c>
-      <c r="X25">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 40361-2023 karta.png", "A 40361-2023")</f>
         <v/>
       </c>
-      <c r="Y25">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 40361-2023 georefererad karta.tif", "A 40361-2023")</f>
         <v/>
       </c>
-      <c r="AA25">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 40361-2023 FSC-klagomål.docx", "A 40361-2023")</f>
         <v/>
       </c>
-      <c r="AB25">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 40361-2023 FSC-klagomål mail.docx", "A 40361-2023")</f>
         <v/>
       </c>
-      <c r="AC25">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 40361-2023 tillsynsbegäran.docx", "A 40361-2023")</f>
         <v/>
       </c>
-      <c r="AD25">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 40361-2023 tillsynsbegäran mail.docx", "A 40361-2023")</f>
         <v/>
       </c>
-      <c r="AE25">
+      <c r="AE26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 40361-2023 prioriterade fågelarter.docx", "A 40361-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 43704-2025</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>45912</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J27" t="n">
+        <v>5</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>6</v>
+      </c>
+      <c r="T27" t="n">
+        <v>6</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp
+Långbensgroda
+Större vattensalamander
+Åkergroda
+Mindre vattensalamander
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43704-2025 artfynd.xlsx", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="X27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43704-2025 karta.png", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="Y27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43704-2025 georefererad karta.tif", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="AA27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43704-2025 FSC-klagomål.docx", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="AB27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43704-2025 FSC-klagomål mail.docx", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="AC27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43704-2025 tillsynsbegäran.docx", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="AD27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43704-2025 tillsynsbegäran mail.docx", "A 43704-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>A 43714-2025</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D26" s="1" t="n">
+      <c r="D28" s="1" t="n">
         <v>45912</v>
       </c>
-      <c r="E26" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F26" t="inlineStr">
+      <c r="E28" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I26" t="n">
+      <c r="I28" t="n">
         <v>7.9</v>
       </c>
-      <c r="J26" t="n">
-        <v>1</v>
-      </c>
-      <c r="K26" t="n">
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
         <v>3</v>
       </c>
-      <c r="L26" t="n">
-        <v>1</v>
-      </c>
-      <c r="M26" t="n">
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" t="n">
         <v>2</v>
       </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
         <v>3</v>
       </c>
-      <c r="R26" t="n">
+      <c r="R28" t="n">
         <v>2</v>
       </c>
-      <c r="S26" t="n">
+      <c r="S28" t="n">
         <v>6</v>
       </c>
-      <c r="T26" t="n">
+      <c r="T28" t="n">
         <v>8</v>
       </c>
-      <c r="U26" t="n">
+      <c r="U28" t="n">
         <v>2</v>
       </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>Mindre bastardsvärmare
 Sexfläckig bastardsvärmare
@@ -3701,221 +3929,111 @@
 Trädporella</t>
         </is>
       </c>
-      <c r="W26">
+      <c r="W28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43714-2025 artfynd.xlsx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="X26">
+      <c r="X28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43714-2025 karta.png", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="Y26">
+      <c r="Y28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43714-2025 georefererad karta.tif", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AA26">
+      <c r="AA28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43714-2025 FSC-klagomål.docx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AB26">
+      <c r="AB28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43714-2025 FSC-klagomål mail.docx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AC26">
+      <c r="AC28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43714-2025 tillsynsbegäran.docx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AD26">
+      <c r="AD28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43714-2025 tillsynsbegäran mail.docx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AE26">
+      <c r="AE28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 43714-2025 prioriterade fågelarter.docx", "A 43714-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 43704-2025</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>45912</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F27" t="inlineStr">
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>S 1814-2026</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I27" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J27" t="n">
-        <v>5</v>
-      </c>
-      <c r="K27" t="n">
-        <v>1</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
+      <c r="I29" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>2</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1</v>
+      </c>
+      <c r="S29" t="n">
         <v>6</v>
       </c>
-      <c r="T27" t="n">
-        <v>6</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Blomkålssvamp
-Långbensgroda
-Större vattensalamander
-Åkergroda
-Mindre vattensalamander
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43704-2025 artfynd.xlsx", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43704-2025 karta.png", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43704-2025 georefererad karta.tif", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43704-2025 FSC-klagomål.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43704-2025 FSC-klagomål mail.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43704-2025 tillsynsbegäran.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43704-2025 tillsynsbegäran mail.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>S 1814-2026</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>46190</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="J28" t="n">
-        <v>3</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>2</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>3</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1</v>
-      </c>
-      <c r="S28" t="n">
-        <v>6</v>
-      </c>
-      <c r="T28" t="n">
+      <c r="T29" t="n">
         <v>11</v>
       </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>Småvänderot
 Leopardsköldbagge
@@ -3925,107 +4043,107 @@
 Ängsnycklar</t>
         </is>
       </c>
-      <c r="W28">
+      <c r="W29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/S 1814-2026 artfynd.xlsx", "S 1814-2026")</f>
         <v/>
       </c>
-      <c r="X28">
+      <c r="X29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/S 1814-2026 karta.png", "S 1814-2026")</f>
         <v/>
       </c>
-      <c r="Y28">
+      <c r="Y29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/S 1814-2026 georefererad karta.tif", "S 1814-2026")</f>
         <v/>
       </c>
-      <c r="AA28">
+      <c r="AA29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/S 1814-2026 FSC-klagomål.docx", "S 1814-2026")</f>
         <v/>
       </c>
-      <c r="AB28">
+      <c r="AB29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/S 1814-2026 FSC-klagomål mail.docx", "S 1814-2026")</f>
         <v/>
       </c>
-      <c r="AC28">
+      <c r="AC29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/S 1814-2026 tillsynsbegäran.docx", "S 1814-2026")</f>
         <v/>
       </c>
-      <c r="AD28">
+      <c r="AD29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/S 1814-2026 tillsynsbegäran mail.docx", "S 1814-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>A 61963-2025</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D29" s="1" t="n">
+      <c r="D30" s="1" t="n">
         <v>46003</v>
       </c>
-      <c r="E29" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F29" t="inlineStr">
+      <c r="E30" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I29" t="n">
+      <c r="I30" t="n">
         <v>1.1</v>
       </c>
-      <c r="J29" t="n">
+      <c r="J30" t="n">
         <v>4</v>
       </c>
-      <c r="K29" t="n">
-        <v>1</v>
-      </c>
-      <c r="L29" t="n">
-        <v>1</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>1</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
+      <c r="K30" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
         <v>5</v>
       </c>
-      <c r="T29" t="n">
+      <c r="T30" t="n">
         <v>8</v>
       </c>
-      <c r="U29" t="n">
+      <c r="U30" t="n">
         <v>3</v>
       </c>
-      <c r="V29" s="2" t="inlineStr">
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>Gulsparv
 Mindre märgborre
@@ -4034,111 +4152,111 @@
 Röd glada</t>
         </is>
       </c>
-      <c r="W29">
+      <c r="W30">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 61963-2025 artfynd.xlsx", "A 61963-2025")</f>
         <v/>
       </c>
-      <c r="X29">
+      <c r="X30">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 61963-2025 karta.png", "A 61963-2025")</f>
         <v/>
       </c>
-      <c r="Y29">
+      <c r="Y30">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 61963-2025 georefererad karta.tif", "A 61963-2025")</f>
         <v/>
       </c>
-      <c r="AA29">
+      <c r="AA30">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 61963-2025 FSC-klagomål.docx", "A 61963-2025")</f>
         <v/>
       </c>
-      <c r="AB29">
+      <c r="AB30">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 61963-2025 FSC-klagomål mail.docx", "A 61963-2025")</f>
         <v/>
       </c>
-      <c r="AC29">
+      <c r="AC30">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 61963-2025 tillsynsbegäran.docx", "A 61963-2025")</f>
         <v/>
       </c>
-      <c r="AD29">
+      <c r="AD30">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 61963-2025 tillsynsbegäran mail.docx", "A 61963-2025")</f>
         <v/>
       </c>
-      <c r="AE29">
+      <c r="AE30">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 61963-2025 prioriterade fågelarter.docx", "A 61963-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>A 2864-2026</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D30" s="1" t="n">
+      <c r="D31" s="1" t="n">
         <v>46038</v>
       </c>
-      <c r="E30" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F30" t="inlineStr">
+      <c r="E31" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I30" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" t="n">
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="n">
         <v>4</v>
       </c>
-      <c r="K30" t="n">
-        <v>1</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
+      <c r="K31" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
         <v>5</v>
       </c>
-      <c r="T30" t="n">
+      <c r="T31" t="n">
         <v>8</v>
       </c>
-      <c r="U30" t="n">
+      <c r="U31" t="n">
         <v>3</v>
       </c>
-      <c r="V30" s="2" t="inlineStr">
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>Gulsparv
 Mindre märgborre
@@ -4147,111 +4265,111 @@
 Röd glada</t>
         </is>
       </c>
-      <c r="W30">
+      <c r="W31">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 2864-2026 artfynd.xlsx", "A 2864-2026")</f>
         <v/>
       </c>
-      <c r="X30">
+      <c r="X31">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 2864-2026 karta.png", "A 2864-2026")</f>
         <v/>
       </c>
-      <c r="Y30">
+      <c r="Y31">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 2864-2026 georefererad karta.tif", "A 2864-2026")</f>
         <v/>
       </c>
-      <c r="AA30">
+      <c r="AA31">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 2864-2026 FSC-klagomål.docx", "A 2864-2026")</f>
         <v/>
       </c>
-      <c r="AB30">
+      <c r="AB31">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 2864-2026 FSC-klagomål mail.docx", "A 2864-2026")</f>
         <v/>
       </c>
-      <c r="AC30">
+      <c r="AC31">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 2864-2026 tillsynsbegäran.docx", "A 2864-2026")</f>
         <v/>
       </c>
-      <c r="AD30">
+      <c r="AD31">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 2864-2026 tillsynsbegäran mail.docx", "A 2864-2026")</f>
         <v/>
       </c>
-      <c r="AE30">
+      <c r="AE31">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 2864-2026 prioriterade fågelarter.docx", "A 2864-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>A 54167-2024</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D31" s="1" t="n">
+      <c r="D32" s="1" t="n">
         <v>45616</v>
       </c>
-      <c r="E31" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F31" t="inlineStr">
+      <c r="E32" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I31" t="n">
+      <c r="I32" t="n">
         <v>1.5</v>
       </c>
-      <c r="J31" t="n">
+      <c r="J32" t="n">
         <v>2</v>
       </c>
-      <c r="K31" t="n">
+      <c r="K32" t="n">
         <v>2</v>
       </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>1</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>1</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1</v>
-      </c>
-      <c r="S31" t="n">
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1</v>
+      </c>
+      <c r="S32" t="n">
         <v>4</v>
       </c>
-      <c r="T31" t="n">
+      <c r="T32" t="n">
         <v>8</v>
       </c>
-      <c r="U31" t="n">
+      <c r="U32" t="n">
         <v>8</v>
       </c>
-      <c r="V31" s="2" t="inlineStr">
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>Ask
 Murgröna
@@ -4259,107 +4377,107 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W31">
+      <c r="W32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 54167-2024 artfynd.xlsx", "A 54167-2024")</f>
         <v/>
       </c>
-      <c r="X31">
+      <c r="X32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 54167-2024 karta.png", "A 54167-2024")</f>
         <v/>
       </c>
-      <c r="Y31">
+      <c r="Y32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 54167-2024 georefererad karta.tif", "A 54167-2024")</f>
         <v/>
       </c>
-      <c r="AA31">
+      <c r="AA32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 54167-2024 FSC-klagomål.docx", "A 54167-2024")</f>
         <v/>
       </c>
-      <c r="AB31">
+      <c r="AB32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 54167-2024 FSC-klagomål mail.docx", "A 54167-2024")</f>
         <v/>
       </c>
-      <c r="AC31">
+      <c r="AC32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 54167-2024 tillsynsbegäran.docx", "A 54167-2024")</f>
         <v/>
       </c>
-      <c r="AD31">
+      <c r="AD32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 54167-2024 tillsynsbegäran mail.docx", "A 54167-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>A 19459-2023</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D32" s="1" t="n">
+      <c r="D33" s="1" t="n">
         <v>45049</v>
       </c>
-      <c r="E32" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F32" t="inlineStr">
+      <c r="E33" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I32" t="n">
+      <c r="I33" t="n">
         <v>1.6</v>
       </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
         <v>4</v>
       </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
         <v>4</v>
       </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
         <v>4</v>
       </c>
-      <c r="T32" t="n">
+      <c r="T33" t="n">
         <v>4</v>
       </c>
-      <c r="U32" t="n">
+      <c r="U33" t="n">
         <v>4</v>
       </c>
-      <c r="V32" s="2" t="inlineStr">
+      <c r="V33" s="2" t="inlineStr">
         <is>
           <t>Kavelhirs
 Kösa
@@ -4367,107 +4485,107 @@
 Riddarsporre</t>
         </is>
       </c>
-      <c r="W32">
+      <c r="W33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 19459-2023 artfynd.xlsx", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="X32">
+      <c r="X33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 19459-2023 karta.png", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="Y32">
+      <c r="Y33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 19459-2023 georefererad karta.tif", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="AA32">
+      <c r="AA33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 19459-2023 FSC-klagomål.docx", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="AB32">
+      <c r="AB33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 19459-2023 FSC-klagomål mail.docx", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="AC32">
+      <c r="AC33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 19459-2023 tillsynsbegäran.docx", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="AD32">
+      <c r="AD33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 19459-2023 tillsynsbegäran mail.docx", "A 19459-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>A 26440-2026</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D33" s="1" t="n">
+      <c r="D34" s="1" t="n">
         <v>46183</v>
       </c>
-      <c r="E33" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F33" t="inlineStr">
+      <c r="E34" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I33" t="n">
+      <c r="I34" t="n">
         <v>1.1</v>
       </c>
-      <c r="J33" t="n">
-        <v>1</v>
-      </c>
-      <c r="K33" t="n">
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="n">
         <v>3</v>
       </c>
-      <c r="L33" t="n">
-        <v>1</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
+      <c r="L34" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
         <v>4</v>
       </c>
-      <c r="T33" t="n">
+      <c r="T34" t="n">
         <v>5</v>
       </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>Backstarr
 Murgröna
@@ -4475,107 +4593,107 @@
 Vätteros</t>
         </is>
       </c>
-      <c r="W33">
+      <c r="W34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 26440-2026 artfynd.xlsx", "A 26440-2026")</f>
         <v/>
       </c>
-      <c r="X33">
+      <c r="X34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 26440-2026 karta.png", "A 26440-2026")</f>
         <v/>
       </c>
-      <c r="Y33">
+      <c r="Y34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 26440-2026 georefererad karta.tif", "A 26440-2026")</f>
         <v/>
       </c>
-      <c r="AA33">
+      <c r="AA34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 26440-2026 FSC-klagomål.docx", "A 26440-2026")</f>
         <v/>
       </c>
-      <c r="AB33">
+      <c r="AB34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 26440-2026 FSC-klagomål mail.docx", "A 26440-2026")</f>
         <v/>
       </c>
-      <c r="AC33">
+      <c r="AC34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 26440-2026 tillsynsbegäran.docx", "A 26440-2026")</f>
         <v/>
       </c>
-      <c r="AD33">
+      <c r="AD34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 26440-2026 tillsynsbegäran mail.docx", "A 26440-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>A 34431-2026</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D34" s="1" t="n">
+      <c r="D35" s="1" t="n">
         <v>46254</v>
       </c>
-      <c r="E34" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F34" t="inlineStr">
+      <c r="E35" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I34" t="n">
+      <c r="I35" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="J34" t="n">
+      <c r="J35" t="n">
         <v>2</v>
       </c>
-      <c r="K34" t="n">
-        <v>1</v>
-      </c>
-      <c r="L34" t="n">
+      <c r="K35" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" t="n">
         <v>3</v>
       </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
         <v>3</v>
       </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
         <v>4</v>
       </c>
-      <c r="T34" t="n">
+      <c r="T35" t="n">
         <v>5</v>
       </c>
-      <c r="U34" t="n">
-        <v>1</v>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
+      <c r="U35" t="n">
+        <v>1</v>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
         <is>
           <t>Entita
 Mindre hackspett
@@ -4583,143 +4701,36 @@
 Murgröna</t>
         </is>
       </c>
-      <c r="W34">
+      <c r="W35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 34431-2026 artfynd.xlsx", "A 34431-2026")</f>
         <v/>
       </c>
-      <c r="X34">
+      <c r="X35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 34431-2026 karta.png", "A 34431-2026")</f>
         <v/>
       </c>
-      <c r="Y34">
+      <c r="Y35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 34431-2026 georefererad karta.tif", "A 34431-2026")</f>
         <v/>
       </c>
-      <c r="AA34">
+      <c r="AA35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 34431-2026 FSC-klagomål.docx", "A 34431-2026")</f>
         <v/>
       </c>
-      <c r="AB34">
+      <c r="AB35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 34431-2026 FSC-klagomål mail.docx", "A 34431-2026")</f>
         <v/>
       </c>
-      <c r="AC34">
+      <c r="AC35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 34431-2026 tillsynsbegäran.docx", "A 34431-2026")</f>
         <v/>
       </c>
-      <c r="AD34">
+      <c r="AD35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 34431-2026 tillsynsbegäran mail.docx", "A 34431-2026")</f>
         <v/>
       </c>
-      <c r="AE34">
+      <c r="AE35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 34431-2026 prioriterade fågelarter.docx", "A 34431-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>A 15600-2025</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="n">
-        <v>45747</v>
-      </c>
-      <c r="E35" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>3</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>3</v>
-      </c>
-      <c r="T35" t="n">
-        <v>3</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1</v>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>Kragjordstjärna
-Murgröna
-Scharlakansvårskål agg.</t>
-        </is>
-      </c>
-      <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 15600-2025 artfynd.xlsx", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 15600-2025 karta.png", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 15600-2025 georefererad karta.tif", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 15600-2025 FSC-klagomål.docx", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 15600-2025 FSC-klagomål mail.docx", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 15600-2025 tillsynsbegäran.docx", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 15600-2025 tillsynsbegäran mail.docx", "A 15600-2025")</f>
         <v/>
       </c>
     </row>
@@ -4743,7 +4754,7 @@
         <v>45912</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4850,7 +4861,7 @@
         <v>46203</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4940,7 +4951,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 72167-2021</t>
+          <t>A 62231-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4950,14 +4961,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44544</v>
+        <v>45267</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4970,7 +4981,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J38" t="n">
         <v>1</v>
@@ -5011,46 +5022,42 @@
       <c r="V38" s="2" t="inlineStr">
         <is>
           <t>Murgröna
-Röd glada</t>
+Blåsippa</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 72167-2021 artfynd.xlsx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62231-2023 artfynd.xlsx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 72167-2021 karta.png", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62231-2023 karta.png", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 72167-2021 georefererad karta.tif", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62231-2023 georefererad karta.tif", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 72167-2021 FSC-klagomål.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62231-2023 FSC-klagomål.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 72167-2021 FSC-klagomål mail.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62231-2023 FSC-klagomål mail.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 72167-2021 tillsynsbegäran.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62231-2023 tillsynsbegäran.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 72167-2021 tillsynsbegäran mail.docx", "A 72167-2021")</f>
-        <v/>
-      </c>
-      <c r="AE38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 72167-2021 prioriterade fågelarter.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62231-2023 tillsynsbegäran mail.docx", "A 62231-2023")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 62231-2023</t>
+          <t>A 72167-2021</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5060,14 +5067,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45267</v>
+        <v>44544</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5080,7 +5087,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J39" t="n">
         <v>1</v>
@@ -5121,35 +5128,39 @@
       <c r="V39" s="2" t="inlineStr">
         <is>
           <t>Murgröna
-Blåsippa</t>
+Röd glada</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62231-2023 artfynd.xlsx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 72167-2021 artfynd.xlsx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62231-2023 karta.png", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 72167-2021 karta.png", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62231-2023 georefererad karta.tif", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 72167-2021 georefererad karta.tif", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62231-2023 FSC-klagomål.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 72167-2021 FSC-klagomål.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62231-2023 FSC-klagomål mail.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 72167-2021 FSC-klagomål mail.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62231-2023 tillsynsbegäran.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 72167-2021 tillsynsbegäran.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62231-2023 tillsynsbegäran mail.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 72167-2021 tillsynsbegäran mail.docx", "A 72167-2021")</f>
+        <v/>
+      </c>
+      <c r="AE39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 72167-2021 prioriterade fågelarter.docx", "A 72167-2021")</f>
         <v/>
       </c>
     </row>
@@ -5173,7 +5184,7 @@
         <v>46246</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5262,7 +5273,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 13040-2024</t>
+          <t>A 62183-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5272,14 +5283,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45385</v>
+        <v>46006</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5292,7 +5303,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -5301,13 +5312,13 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5319,7 +5330,7 @@
         <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -5328,46 +5339,46 @@
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13040-2024 artfynd.xlsx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62183-2025 artfynd.xlsx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13040-2024 karta.png", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62183-2025 karta.png", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13040-2024 georefererad karta.tif", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62183-2025 georefererad karta.tif", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13040-2024 FSC-klagomål.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62183-2025 FSC-klagomål.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13040-2024 FSC-klagomål mail.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62183-2025 FSC-klagomål mail.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13040-2024 tillsynsbegäran.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62183-2025 tillsynsbegäran.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13040-2024 tillsynsbegäran mail.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62183-2025 tillsynsbegäran mail.docx", "A 62183-2025")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 24698-2023</t>
+          <t>A 13040-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5377,14 +5388,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45084</v>
+        <v>45385</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5397,7 +5408,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>5.5</v>
+        <v>1.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -5406,13 +5417,13 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5424,7 +5435,7 @@
         <v>1</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -5437,35 +5448,35 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24698-2023 artfynd.xlsx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13040-2024 artfynd.xlsx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24698-2023 karta.png", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13040-2024 karta.png", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24698-2023 georefererad karta.tif", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13040-2024 georefererad karta.tif", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24698-2023 FSC-klagomål.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13040-2024 FSC-klagomål.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24698-2023 FSC-klagomål mail.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13040-2024 FSC-klagomål mail.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24698-2023 tillsynsbegäran.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13040-2024 tillsynsbegäran.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24698-2023 tillsynsbegäran mail.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13040-2024 tillsynsbegäran mail.docx", "A 13040-2024")</f>
         <v/>
       </c>
     </row>
@@ -5489,7 +5500,7 @@
         <v>45005</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5577,7 +5588,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 62183-2025</t>
+          <t>A 30492-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5587,14 +5598,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46006</v>
+        <v>46210</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5607,7 +5618,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5647,42 +5658,42 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62183-2025 artfynd.xlsx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 30492-2026 artfynd.xlsx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62183-2025 karta.png", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 30492-2026 karta.png", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62183-2025 georefererad karta.tif", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 30492-2026 georefererad karta.tif", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62183-2025 FSC-klagomål.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 30492-2026 FSC-klagomål.docx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62183-2025 FSC-klagomål mail.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 30492-2026 FSC-klagomål mail.docx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62183-2025 tillsynsbegäran.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 30492-2026 tillsynsbegäran.docx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62183-2025 tillsynsbegäran mail.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 30492-2026 tillsynsbegäran mail.docx", "A 30492-2026")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 30492-2026</t>
+          <t>A 36928-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5692,14 +5703,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46210</v>
+        <v>46273</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5712,16 +5723,16 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -5736,7 +5747,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -5752,42 +5763,42 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 30492-2026 artfynd.xlsx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 36928-2026 artfynd.xlsx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 30492-2026 karta.png", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 36928-2026 karta.png", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 30492-2026 georefererad karta.tif", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 36928-2026 georefererad karta.tif", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 30492-2026 FSC-klagomål.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 36928-2026 FSC-klagomål.docx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 30492-2026 FSC-klagomål mail.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 36928-2026 FSC-klagomål mail.docx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 30492-2026 tillsynsbegäran.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 36928-2026 tillsynsbegäran.docx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 30492-2026 tillsynsbegäran mail.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 36928-2026 tillsynsbegäran mail.docx", "A 36928-2026")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 36928-2026</t>
+          <t>A 24698-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5801,10 +5812,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46273</v>
+        <v>45084</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5817,16 +5828,16 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.3</v>
+        <v>5.5</v>
       </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -5841,7 +5852,7 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -5853,39 +5864,39 @@
         <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 36928-2026 artfynd.xlsx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24698-2023 artfynd.xlsx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 36928-2026 karta.png", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24698-2023 karta.png", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 36928-2026 georefererad karta.tif", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24698-2023 georefererad karta.tif", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 36928-2026 FSC-klagomål.docx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24698-2023 FSC-klagomål.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 36928-2026 FSC-klagomål mail.docx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24698-2023 FSC-klagomål mail.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 36928-2026 tillsynsbegäran.docx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24698-2023 tillsynsbegäran.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 36928-2026 tillsynsbegäran mail.docx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24698-2023 tillsynsbegäran mail.docx", "A 24698-2023")</f>
         <v/>
       </c>
     </row>
@@ -5909,7 +5920,7 @@
         <v>44740</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5982,7 +5993,7 @@
         <v>45980</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6055,7 +6066,7 @@
         <v>46171</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>

--- a/Översikt MÖRBYLÅNGA.xlsx
+++ b/Översikt MÖRBYLÅNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44964</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>44655</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>45177</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45096</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45685</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>46289</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>45475</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>45062</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>46195</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>46189</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>45254</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>45062</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>44508</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>45999</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 24778-2022</t>
+          <t>A 38039-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2488,14 +2488,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44728</v>
+        <v>44811</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2508,45 +2508,275 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>7.4</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>4</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>6</v>
+      </c>
+      <c r="R16" t="n">
         <v>2</v>
-      </c>
-      <c r="L16" t="n">
-        <v>7</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>8</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>11</v>
       </c>
       <c r="T16" t="n">
+        <v>13</v>
+      </c>
+      <c r="U16" t="n">
+        <v>12</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Grov gulmossa
+Backtimjan
+Dvärgjordstjärna
+Solvända
+Ängsstarr
+Murgröna
+Alvarmalört
+Grönvit nattviol
+Krutbrännare
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 38039-2022 artfynd.xlsx", "A 38039-2022")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 38039-2022 karta.png", "A 38039-2022")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 38039-2022 georefererad karta.tif", "A 38039-2022")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 38039-2022 FSC-klagomål.docx", "A 38039-2022")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 38039-2022 FSC-klagomål mail.docx", "A 38039-2022")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 38039-2022 tillsynsbegäran.docx", "A 38039-2022")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 38039-2022 tillsynsbegäran mail.docx", "A 38039-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 27636-2023</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45097</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>4</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>6</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2</v>
+      </c>
+      <c r="S17" t="n">
+        <v>11</v>
+      </c>
+      <c r="T17" t="n">
+        <v>13</v>
+      </c>
+      <c r="U17" t="n">
+        <v>11</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Grov gulmossa
+Backtimjan
+Dvärgjordstjärna
+Solvända
+Ängsstarr
+Murgröna
+Alvarmalört
+Grönvit nattviol
+Krutbrännare
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 27636-2023 artfynd.xlsx", "A 27636-2023")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 27636-2023 karta.png", "A 27636-2023")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 27636-2023 georefererad karta.tif", "A 27636-2023")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 27636-2023 FSC-klagomål.docx", "A 27636-2023")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 27636-2023 FSC-klagomål mail.docx", "A 27636-2023")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 27636-2023 tillsynsbegäran.docx", "A 27636-2023")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 27636-2023 tillsynsbegäran mail.docx", "A 27636-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 24778-2022</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>44728</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" t="n">
+        <v>7</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>8</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>11</v>
+      </c>
+      <c r="T18" t="n">
         <v>20</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U18" t="n">
         <v>20</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Tofsäxing
 Backtimjan
@@ -2561,269 +2791,39 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24778-2022 artfynd.xlsx", "A 24778-2022")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24778-2022 karta.png", "A 24778-2022")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24778-2022 georefererad karta.tif", "A 24778-2022")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24778-2022 FSC-klagomål.docx", "A 24778-2022")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24778-2022 FSC-klagomål mail.docx", "A 24778-2022")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24778-2022 tillsynsbegäran.docx", "A 24778-2022")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24778-2022 tillsynsbegäran mail.docx", "A 24778-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 38039-2022</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>44811</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="J17" t="n">
-        <v>4</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>4</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>6</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2</v>
-      </c>
-      <c r="S17" t="n">
-        <v>11</v>
-      </c>
-      <c r="T17" t="n">
-        <v>13</v>
-      </c>
-      <c r="U17" t="n">
-        <v>12</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Grov gulmossa
-Backtimjan
-Dvärgjordstjärna
-Solvända
-Ängsstarr
-Murgröna
-Alvarmalört
-Grönvit nattviol
-Krutbrännare
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 38039-2022 artfynd.xlsx", "A 38039-2022")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 38039-2022 karta.png", "A 38039-2022")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 38039-2022 georefererad karta.tif", "A 38039-2022")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 38039-2022 FSC-klagomål.docx", "A 38039-2022")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 38039-2022 FSC-klagomål mail.docx", "A 38039-2022")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 38039-2022 tillsynsbegäran.docx", "A 38039-2022")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 38039-2022 tillsynsbegäran mail.docx", "A 38039-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 27636-2023</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45097</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="J18" t="n">
-        <v>4</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>4</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>6</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2</v>
-      </c>
-      <c r="S18" t="n">
-        <v>11</v>
-      </c>
-      <c r="T18" t="n">
-        <v>13</v>
-      </c>
-      <c r="U18" t="n">
-        <v>11</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Grov gulmossa
-Backtimjan
-Dvärgjordstjärna
-Solvända
-Ängsstarr
-Murgröna
-Alvarmalört
-Grönvit nattviol
-Krutbrännare
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 27636-2023 artfynd.xlsx", "A 27636-2023")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 27636-2023 karta.png", "A 27636-2023")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 27636-2023 georefererad karta.tif", "A 27636-2023")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 27636-2023 FSC-klagomål.docx", "A 27636-2023")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 27636-2023 FSC-klagomål mail.docx", "A 27636-2023")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 27636-2023 tillsynsbegäran.docx", "A 27636-2023")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 27636-2023 tillsynsbegäran mail.docx", "A 27636-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 39320-2024</t>
+          <t>A 15600-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2837,10 +2837,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45551</v>
+        <v>45747</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2853,45 +2853,163 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
       </c>
       <c r="T19" t="n">
+        <v>20</v>
+      </c>
+      <c r="U19" t="n">
+        <v>18</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Kragjordstjärna
+Murgröna
+Scharlakansvårskål agg.
+Tibast
+Blåsippa
+Skärmstarr
+Spillkråka
+Storrams
+Röd glada</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 15600-2025 artfynd.xlsx", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 15600-2025 karta.png", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 15600-2025 georefererad karta.tif", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 15600-2025 FSC-klagomål.docx", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 15600-2025 FSC-klagomål mail.docx", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 15600-2025 tillsynsbegäran.docx", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 15600-2025 tillsynsbegäran mail.docx", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 15600-2025 prioriterade fågelarter.docx", "A 15600-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 39320-2024</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45551</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>4</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>7</v>
+      </c>
+      <c r="R20" t="n">
+        <v>3</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="n">
         <v>11</v>
       </c>
-      <c r="U19" t="n">
+      <c r="U20" t="n">
         <v>10</v>
       </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Vresalm
 Lundalm
@@ -2905,150 +3023,32 @@
 Skogsduva</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 39320-2024 artfynd.xlsx", "A 39320-2024")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 39320-2024 karta.png", "A 39320-2024")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 39320-2024 georefererad karta.tif", "A 39320-2024")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 39320-2024 FSC-klagomål.docx", "A 39320-2024")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 39320-2024 FSC-klagomål mail.docx", "A 39320-2024")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 39320-2024 tillsynsbegäran.docx", "A 39320-2024")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 39320-2024 tillsynsbegäran mail.docx", "A 39320-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 15600-2025</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45747</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J20" t="n">
-        <v>3</v>
-      </c>
-      <c r="K20" t="n">
-        <v>4</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>1</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1</v>
-      </c>
-      <c r="S20" t="n">
-        <v>10</v>
-      </c>
-      <c r="T20" t="n">
-        <v>20</v>
-      </c>
-      <c r="U20" t="n">
-        <v>18</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Kragjordstjärna
-Murgröna
-Scharlakansvårskål agg.
-Tibast
-Blåsippa
-Skärmstarr
-Spillkråka
-Storrams
-Röd glada</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 15600-2025 artfynd.xlsx", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 15600-2025 karta.png", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 15600-2025 georefererad karta.tif", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 15600-2025 FSC-klagomål.docx", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 15600-2025 FSC-klagomål mail.docx", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 15600-2025 tillsynsbegäran.docx", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 15600-2025 tillsynsbegäran mail.docx", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 15600-2025 prioriterade fågelarter.docx", "A 15600-2025")</f>
         <v/>
       </c>
     </row>
@@ -3072,7 +3072,7 @@
         <v>44616</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>45000</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>45530</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>45223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         <v>45075</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45169</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 43704-2025</t>
+          <t>A 43714-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3758,7 +3758,7 @@
         <v>45912</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3771,19 +3771,19 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.7</v>
+        <v>7.9</v>
       </c>
       <c r="J27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3795,21 +3795,135 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S27" t="n">
         <v>6</v>
       </c>
       <c r="T27" t="n">
+        <v>8</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Mindre bastardsvärmare
+Sexfläckig bastardsvärmare
+Grönsångare
+Murgröna
+Tibast
+Trädporella</t>
+        </is>
+      </c>
+      <c r="W27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43714-2025 artfynd.xlsx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="X27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43714-2025 karta.png", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="Y27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43714-2025 georefererad karta.tif", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AA27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43714-2025 FSC-klagomål.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AB27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43714-2025 FSC-klagomål mail.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AC27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43714-2025 tillsynsbegäran.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AD27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43714-2025 tillsynsbegäran mail.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 43714-2025 prioriterade fågelarter.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A 43704-2025</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>45912</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J28" t="n">
+        <v>5</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
         <v>6</v>
       </c>
-      <c r="U27" t="n">
-        <v>1</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="T28" t="n">
+        <v>6</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>Blomkålssvamp
 Långbensgroda
@@ -3819,146 +3933,32 @@
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W27">
+      <c r="W28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43704-2025 artfynd.xlsx", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="X27">
+      <c r="X28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43704-2025 karta.png", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="Y27">
+      <c r="Y28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43704-2025 georefererad karta.tif", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="AA27">
+      <c r="AA28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43704-2025 FSC-klagomål.docx", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="AB27">
+      <c r="AB28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43704-2025 FSC-klagomål mail.docx", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="AC27">
+      <c r="AC28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43704-2025 tillsynsbegäran.docx", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="AD27">
+      <c r="AD28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43704-2025 tillsynsbegäran mail.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>A 43714-2025</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>45912</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="J28" t="n">
-        <v>1</v>
-      </c>
-      <c r="K28" t="n">
-        <v>3</v>
-      </c>
-      <c r="L28" t="n">
-        <v>1</v>
-      </c>
-      <c r="M28" t="n">
-        <v>2</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>3</v>
-      </c>
-      <c r="R28" t="n">
-        <v>2</v>
-      </c>
-      <c r="S28" t="n">
-        <v>6</v>
-      </c>
-      <c r="T28" t="n">
-        <v>8</v>
-      </c>
-      <c r="U28" t="n">
-        <v>2</v>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>Mindre bastardsvärmare
-Sexfläckig bastardsvärmare
-Grönsångare
-Murgröna
-Tibast
-Trädporella</t>
-        </is>
-      </c>
-      <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43714-2025 artfynd.xlsx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43714-2025 karta.png", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43714-2025 georefererad karta.tif", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43714-2025 FSC-klagomål.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43714-2025 FSC-klagomål mail.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43714-2025 tillsynsbegäran.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43714-2025 tillsynsbegäran mail.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 43714-2025 prioriterade fågelarter.docx", "A 43714-2025")</f>
         <v/>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
         <v>46190</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>46003</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>46038</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>45616</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>45049</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>46183</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>46254</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>45912</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>46203</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 62231-2023</t>
+          <t>A 72167-2021</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4961,14 +4961,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45267</v>
+        <v>44544</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J38" t="n">
         <v>1</v>
@@ -5022,42 +5022,46 @@
       <c r="V38" s="2" t="inlineStr">
         <is>
           <t>Murgröna
-Blåsippa</t>
+Röd glada</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62231-2023 artfynd.xlsx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 72167-2021 artfynd.xlsx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62231-2023 karta.png", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 72167-2021 karta.png", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62231-2023 georefererad karta.tif", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 72167-2021 georefererad karta.tif", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62231-2023 FSC-klagomål.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 72167-2021 FSC-klagomål.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62231-2023 FSC-klagomål mail.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 72167-2021 FSC-klagomål mail.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62231-2023 tillsynsbegäran.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 72167-2021 tillsynsbegäran.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62231-2023 tillsynsbegäran mail.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 72167-2021 tillsynsbegäran mail.docx", "A 72167-2021")</f>
+        <v/>
+      </c>
+      <c r="AE38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 72167-2021 prioriterade fågelarter.docx", "A 72167-2021")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 72167-2021</t>
+          <t>A 62231-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5067,14 +5071,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44544</v>
+        <v>45267</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5087,7 +5091,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J39" t="n">
         <v>1</v>
@@ -5128,39 +5132,35 @@
       <c r="V39" s="2" t="inlineStr">
         <is>
           <t>Murgröna
-Röd glada</t>
+Blåsippa</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 72167-2021 artfynd.xlsx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62231-2023 artfynd.xlsx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 72167-2021 karta.png", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62231-2023 karta.png", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 72167-2021 georefererad karta.tif", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62231-2023 georefererad karta.tif", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 72167-2021 FSC-klagomål.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62231-2023 FSC-klagomål.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 72167-2021 FSC-klagomål mail.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62231-2023 FSC-klagomål mail.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 72167-2021 tillsynsbegäran.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62231-2023 tillsynsbegäran.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 72167-2021 tillsynsbegäran mail.docx", "A 72167-2021")</f>
-        <v/>
-      </c>
-      <c r="AE39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 72167-2021 prioriterade fågelarter.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62231-2023 tillsynsbegäran mail.docx", "A 62231-2023")</f>
         <v/>
       </c>
     </row>
@@ -5184,7 +5184,7 @@
         <v>46246</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 62183-2025</t>
+          <t>A 13040-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5283,14 +5283,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46006</v>
+        <v>45385</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -5312,13 +5312,13 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5330,7 +5330,7 @@
         <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -5339,46 +5339,46 @@
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62183-2025 artfynd.xlsx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13040-2024 artfynd.xlsx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62183-2025 karta.png", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13040-2024 karta.png", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62183-2025 georefererad karta.tif", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13040-2024 georefererad karta.tif", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62183-2025 FSC-klagomål.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13040-2024 FSC-klagomål.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62183-2025 FSC-klagomål mail.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13040-2024 FSC-klagomål mail.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62183-2025 tillsynsbegäran.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13040-2024 tillsynsbegäran.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62183-2025 tillsynsbegäran mail.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13040-2024 tillsynsbegäran mail.docx", "A 13040-2024")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 13040-2024</t>
+          <t>A 13384-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5388,14 +5388,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45385</v>
+        <v>45005</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5408,10 +5408,10 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -5423,7 +5423,7 @@
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5432,10 +5432,10 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -5448,42 +5448,42 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13040-2024 artfynd.xlsx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13384-2023 artfynd.xlsx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13040-2024 karta.png", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13384-2023 karta.png", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13040-2024 georefererad karta.tif", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13384-2023 georefererad karta.tif", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13040-2024 FSC-klagomål.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13384-2023 FSC-klagomål.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13040-2024 FSC-klagomål mail.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13384-2023 FSC-klagomål mail.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13040-2024 tillsynsbegäran.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13384-2023 tillsynsbegäran.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13040-2024 tillsynsbegäran mail.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13384-2023 tillsynsbegäran mail.docx", "A 13384-2023")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 13384-2023</t>
+          <t>A 24698-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5497,10 +5497,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45005</v>
+        <v>45084</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5513,16 +5513,16 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.9</v>
+        <v>5.5</v>
       </c>
       <c r="J43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -5537,7 +5537,7 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -5553,42 +5553,42 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13384-2023 artfynd.xlsx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24698-2023 artfynd.xlsx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13384-2023 karta.png", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24698-2023 karta.png", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13384-2023 georefererad karta.tif", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24698-2023 georefererad karta.tif", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13384-2023 FSC-klagomål.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24698-2023 FSC-klagomål.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13384-2023 FSC-klagomål mail.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24698-2023 FSC-klagomål mail.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13384-2023 tillsynsbegäran.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24698-2023 tillsynsbegäran.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13384-2023 tillsynsbegäran mail.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24698-2023 tillsynsbegäran mail.docx", "A 24698-2023")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 30492-2026</t>
+          <t>A 62183-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5598,14 +5598,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46210</v>
+        <v>46006</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5658,42 +5658,42 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 30492-2026 artfynd.xlsx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62183-2025 artfynd.xlsx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 30492-2026 karta.png", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62183-2025 karta.png", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 30492-2026 georefererad karta.tif", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62183-2025 georefererad karta.tif", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 30492-2026 FSC-klagomål.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62183-2025 FSC-klagomål.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 30492-2026 FSC-klagomål mail.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62183-2025 FSC-klagomål mail.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 30492-2026 tillsynsbegäran.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62183-2025 tillsynsbegäran.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 30492-2026 tillsynsbegäran mail.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62183-2025 tillsynsbegäran mail.docx", "A 62183-2025")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 36928-2026</t>
+          <t>A 30492-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5703,14 +5703,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46273</v>
+        <v>46210</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5723,16 +5723,16 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -5747,7 +5747,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -5763,42 +5763,42 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 36928-2026 artfynd.xlsx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 30492-2026 artfynd.xlsx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 36928-2026 karta.png", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 30492-2026 karta.png", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 36928-2026 georefererad karta.tif", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 30492-2026 georefererad karta.tif", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 36928-2026 FSC-klagomål.docx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 30492-2026 FSC-klagomål.docx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 36928-2026 FSC-klagomål mail.docx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 30492-2026 FSC-klagomål mail.docx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 36928-2026 tillsynsbegäran.docx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 30492-2026 tillsynsbegäran.docx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 36928-2026 tillsynsbegäran mail.docx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 30492-2026 tillsynsbegäran mail.docx", "A 30492-2026")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 24698-2023</t>
+          <t>A 36928-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45084</v>
+        <v>46273</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5828,16 +5828,16 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>5.5</v>
+        <v>1.3</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -5852,7 +5852,7 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -5864,39 +5864,39 @@
         <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24698-2023 artfynd.xlsx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 36928-2026 artfynd.xlsx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24698-2023 karta.png", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 36928-2026 karta.png", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24698-2023 georefererad karta.tif", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 36928-2026 georefererad karta.tif", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24698-2023 FSC-klagomål.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 36928-2026 FSC-klagomål.docx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24698-2023 FSC-klagomål mail.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 36928-2026 FSC-klagomål mail.docx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24698-2023 tillsynsbegäran.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 36928-2026 tillsynsbegäran.docx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24698-2023 tillsynsbegäran mail.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 36928-2026 tillsynsbegäran mail.docx", "A 36928-2026")</f>
         <v/>
       </c>
     </row>
@@ -5920,7 +5920,7 @@
         <v>44740</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         <v>45980</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>46171</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>

--- a/Översikt MÖRBYLÅNGA.xlsx
+++ b/Översikt MÖRBYLÅNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44964</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>44655</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>45177</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45096</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45685</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>46289</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>45475</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>45062</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>46195</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>46189</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>45254</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>45062</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>44508</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>45999</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>44811</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>45097</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>44728</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>45747</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>45551</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>44616</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>45000</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>45530</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>45223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         <v>45075</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45169</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>45912</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>45912</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>46190</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>46003</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>46038</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>45616</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>45049</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>46183</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>46254</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>45912</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>46203</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>44544</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>45267</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         <v>46246</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>45385</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>45005</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
         <v>45084</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         <v>46006</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5710,7 +5710,7 @@
         <v>46210</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>46273</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>44740</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         <v>45980</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>46171</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>

--- a/Översikt MÖRBYLÅNGA.xlsx
+++ b/Översikt MÖRBYLÅNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44964</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>44655</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>45177</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45096</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45685</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>46289</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>45475</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>45062</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>46195</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>46189</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>45254</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>45062</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>44508</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>45999</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>44811</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>45097</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>44728</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>45747</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>45551</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>44616</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>45000</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>45530</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>45223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         <v>45075</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45169</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>45912</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>45912</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>46190</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>46003</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>46038</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>45616</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>45049</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>46183</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>46254</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>45912</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>46203</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>44544</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>45267</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         <v>46246</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>45385</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>45005</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
         <v>45084</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         <v>46006</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5710,7 +5710,7 @@
         <v>46210</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>46273</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>44740</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         <v>45980</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>46171</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>

--- a/Översikt MÖRBYLÅNGA.xlsx
+++ b/Översikt MÖRBYLÅNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44964</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>44655</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>45177</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45096</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45685</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>46289</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>45475</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>45062</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>46195</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>46189</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>45254</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>45062</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>44508</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>45999</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>44811</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>45097</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>44728</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>45747</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>45551</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>44616</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>45000</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>45530</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>45223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         <v>45075</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45169</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 43714-2025</t>
+          <t>A 43704-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3758,7 +3758,7 @@
         <v>45912</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3771,19 +3771,19 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>7.9</v>
+        <v>2.7</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3795,21 +3795,131 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>6</v>
       </c>
       <c r="T27" t="n">
+        <v>6</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp
+Långbensgroda
+Större vattensalamander
+Åkergroda
+Mindre vattensalamander
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43704-2025 artfynd.xlsx", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="X27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43704-2025 karta.png", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="Y27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43704-2025 georefererad karta.tif", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="AA27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43704-2025 FSC-klagomål.docx", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="AB27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43704-2025 FSC-klagomål mail.docx", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="AC27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43704-2025 tillsynsbegäran.docx", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="AD27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43704-2025 tillsynsbegäran mail.docx", "A 43704-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A 43714-2025</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>45912</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" t="n">
+        <v>2</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2</v>
+      </c>
+      <c r="S28" t="n">
+        <v>6</v>
+      </c>
+      <c r="T28" t="n">
         <v>8</v>
       </c>
-      <c r="U27" t="n">
+      <c r="U28" t="n">
         <v>2</v>
       </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>Mindre bastardsvärmare
 Sexfläckig bastardsvärmare
@@ -3819,146 +3929,36 @@
 Trädporella</t>
         </is>
       </c>
-      <c r="W27">
+      <c r="W28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43714-2025 artfynd.xlsx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="X27">
+      <c r="X28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43714-2025 karta.png", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="Y27">
+      <c r="Y28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43714-2025 georefererad karta.tif", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AA27">
+      <c r="AA28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43714-2025 FSC-klagomål.docx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AB27">
+      <c r="AB28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43714-2025 FSC-klagomål mail.docx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AC27">
+      <c r="AC28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43714-2025 tillsynsbegäran.docx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AD27">
+      <c r="AD28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43714-2025 tillsynsbegäran mail.docx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AE27">
+      <c r="AE28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 43714-2025 prioriterade fågelarter.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>A 43704-2025</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>45912</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J28" t="n">
-        <v>5</v>
-      </c>
-      <c r="K28" t="n">
-        <v>1</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>6</v>
-      </c>
-      <c r="T28" t="n">
-        <v>6</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1</v>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>Blomkålssvamp
-Långbensgroda
-Större vattensalamander
-Åkergroda
-Mindre vattensalamander
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43704-2025 artfynd.xlsx", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43704-2025 karta.png", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43704-2025 georefererad karta.tif", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43704-2025 FSC-klagomål.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43704-2025 FSC-klagomål mail.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43704-2025 tillsynsbegäran.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43704-2025 tillsynsbegäran mail.docx", "A 43704-2025")</f>
         <v/>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
         <v>46190</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 61963-2025</t>
+          <t>A 2864-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4085,14 +4085,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46003</v>
+        <v>46038</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>4</v>
@@ -4153,42 +4153,42 @@
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 61963-2025 artfynd.xlsx", "A 61963-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 2864-2026 artfynd.xlsx", "A 2864-2026")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 61963-2025 karta.png", "A 61963-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 2864-2026 karta.png", "A 2864-2026")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 61963-2025 georefererad karta.tif", "A 61963-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 2864-2026 georefererad karta.tif", "A 2864-2026")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 61963-2025 FSC-klagomål.docx", "A 61963-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 2864-2026 FSC-klagomål.docx", "A 2864-2026")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 61963-2025 FSC-klagomål mail.docx", "A 61963-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 2864-2026 FSC-klagomål mail.docx", "A 2864-2026")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 61963-2025 tillsynsbegäran.docx", "A 61963-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 2864-2026 tillsynsbegäran.docx", "A 2864-2026")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 61963-2025 tillsynsbegäran mail.docx", "A 61963-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 2864-2026 tillsynsbegäran mail.docx", "A 2864-2026")</f>
         <v/>
       </c>
       <c r="AE30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 61963-2025 prioriterade fågelarter.docx", "A 61963-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 2864-2026 prioriterade fågelarter.docx", "A 2864-2026")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 2864-2026</t>
+          <t>A 61963-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4198,14 +4198,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46038</v>
+        <v>46003</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J31" t="n">
         <v>4</v>
@@ -4266,42 +4266,42 @@
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 2864-2026 artfynd.xlsx", "A 2864-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 61963-2025 artfynd.xlsx", "A 61963-2025")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 2864-2026 karta.png", "A 2864-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 61963-2025 karta.png", "A 61963-2025")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 2864-2026 georefererad karta.tif", "A 2864-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 61963-2025 georefererad karta.tif", "A 61963-2025")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 2864-2026 FSC-klagomål.docx", "A 2864-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 61963-2025 FSC-klagomål.docx", "A 61963-2025")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 2864-2026 FSC-klagomål mail.docx", "A 2864-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 61963-2025 FSC-klagomål mail.docx", "A 61963-2025")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 2864-2026 tillsynsbegäran.docx", "A 2864-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 61963-2025 tillsynsbegäran.docx", "A 61963-2025")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 2864-2026 tillsynsbegäran mail.docx", "A 2864-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 61963-2025 tillsynsbegäran mail.docx", "A 61963-2025")</f>
         <v/>
       </c>
       <c r="AE31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 2864-2026 prioriterade fågelarter.docx", "A 2864-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 61963-2025 prioriterade fågelarter.docx", "A 61963-2025")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 54167-2024</t>
+          <t>A 26440-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4311,14 +4311,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45616</v>
+        <v>46183</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4331,22 +4331,22 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4358,18 +4358,238 @@
         <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>4</v>
       </c>
       <c r="T32" t="n">
+        <v>5</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>Backstarr
+Murgröna
+Nästrot
+Vätteros</t>
+        </is>
+      </c>
+      <c r="W32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 26440-2026 artfynd.xlsx", "A 26440-2026")</f>
+        <v/>
+      </c>
+      <c r="X32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 26440-2026 karta.png", "A 26440-2026")</f>
+        <v/>
+      </c>
+      <c r="Y32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 26440-2026 georefererad karta.tif", "A 26440-2026")</f>
+        <v/>
+      </c>
+      <c r="AA32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 26440-2026 FSC-klagomål.docx", "A 26440-2026")</f>
+        <v/>
+      </c>
+      <c r="AB32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 26440-2026 FSC-klagomål mail.docx", "A 26440-2026")</f>
+        <v/>
+      </c>
+      <c r="AC32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 26440-2026 tillsynsbegäran.docx", "A 26440-2026")</f>
+        <v/>
+      </c>
+      <c r="AD32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 26440-2026 tillsynsbegäran mail.docx", "A 26440-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>A 34431-2026</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" t="n">
+        <v>3</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>3</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>4</v>
+      </c>
+      <c r="T33" t="n">
+        <v>5</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Mindre hackspett
+Sandtimotej
+Murgröna</t>
+        </is>
+      </c>
+      <c r="W33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 34431-2026 artfynd.xlsx", "A 34431-2026")</f>
+        <v/>
+      </c>
+      <c r="X33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 34431-2026 karta.png", "A 34431-2026")</f>
+        <v/>
+      </c>
+      <c r="Y33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 34431-2026 georefererad karta.tif", "A 34431-2026")</f>
+        <v/>
+      </c>
+      <c r="AA33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 34431-2026 FSC-klagomål.docx", "A 34431-2026")</f>
+        <v/>
+      </c>
+      <c r="AB33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 34431-2026 FSC-klagomål mail.docx", "A 34431-2026")</f>
+        <v/>
+      </c>
+      <c r="AC33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 34431-2026 tillsynsbegäran.docx", "A 34431-2026")</f>
+        <v/>
+      </c>
+      <c r="AD33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 34431-2026 tillsynsbegäran mail.docx", "A 34431-2026")</f>
+        <v/>
+      </c>
+      <c r="AE33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 34431-2026 prioriterade fågelarter.docx", "A 34431-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>A 54167-2024</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="n">
+        <v>45616</v>
+      </c>
+      <c r="E34" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1</v>
+      </c>
+      <c r="S34" t="n">
+        <v>4</v>
+      </c>
+      <c r="T34" t="n">
         <v>8</v>
       </c>
-      <c r="U32" t="n">
+      <c r="U34" t="n">
         <v>8</v>
       </c>
-      <c r="V32" s="2" t="inlineStr">
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>Ask
 Murgröna
@@ -4377,107 +4597,107 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W32">
+      <c r="W34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 54167-2024 artfynd.xlsx", "A 54167-2024")</f>
         <v/>
       </c>
-      <c r="X32">
+      <c r="X34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 54167-2024 karta.png", "A 54167-2024")</f>
         <v/>
       </c>
-      <c r="Y32">
+      <c r="Y34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 54167-2024 georefererad karta.tif", "A 54167-2024")</f>
         <v/>
       </c>
-      <c r="AA32">
+      <c r="AA34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 54167-2024 FSC-klagomål.docx", "A 54167-2024")</f>
         <v/>
       </c>
-      <c r="AB32">
+      <c r="AB34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 54167-2024 FSC-klagomål mail.docx", "A 54167-2024")</f>
         <v/>
       </c>
-      <c r="AC32">
+      <c r="AC34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 54167-2024 tillsynsbegäran.docx", "A 54167-2024")</f>
         <v/>
       </c>
-      <c r="AD32">
+      <c r="AD34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 54167-2024 tillsynsbegäran mail.docx", "A 54167-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>A 19459-2023</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D33" s="1" t="n">
+      <c r="D35" s="1" t="n">
         <v>45049</v>
       </c>
-      <c r="E33" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F33" t="inlineStr">
+      <c r="E35" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I33" t="n">
+      <c r="I35" t="n">
         <v>1.6</v>
       </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
         <v>4</v>
       </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
         <v>4</v>
       </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
         <v>4</v>
       </c>
-      <c r="T33" t="n">
+      <c r="T35" t="n">
         <v>4</v>
       </c>
-      <c r="U33" t="n">
+      <c r="U35" t="n">
         <v>4</v>
       </c>
-      <c r="V33" s="2" t="inlineStr">
+      <c r="V35" s="2" t="inlineStr">
         <is>
           <t>Kavelhirs
 Kösa
@@ -4485,252 +4705,32 @@
 Riddarsporre</t>
         </is>
       </c>
-      <c r="W33">
+      <c r="W35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 19459-2023 artfynd.xlsx", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="X33">
+      <c r="X35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 19459-2023 karta.png", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="Y33">
+      <c r="Y35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 19459-2023 georefererad karta.tif", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="AA33">
+      <c r="AA35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 19459-2023 FSC-klagomål.docx", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="AB33">
+      <c r="AB35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 19459-2023 FSC-klagomål mail.docx", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="AC33">
+      <c r="AC35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 19459-2023 tillsynsbegäran.docx", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="AD33">
+      <c r="AD35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 19459-2023 tillsynsbegäran mail.docx", "A 19459-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>A 26440-2026</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="n">
-        <v>46183</v>
-      </c>
-      <c r="E34" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J34" t="n">
-        <v>1</v>
-      </c>
-      <c r="K34" t="n">
-        <v>3</v>
-      </c>
-      <c r="L34" t="n">
-        <v>1</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>1</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>4</v>
-      </c>
-      <c r="T34" t="n">
-        <v>5</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>Backstarr
-Murgröna
-Nästrot
-Vätteros</t>
-        </is>
-      </c>
-      <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 26440-2026 artfynd.xlsx", "A 26440-2026")</f>
-        <v/>
-      </c>
-      <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 26440-2026 karta.png", "A 26440-2026")</f>
-        <v/>
-      </c>
-      <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 26440-2026 georefererad karta.tif", "A 26440-2026")</f>
-        <v/>
-      </c>
-      <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 26440-2026 FSC-klagomål.docx", "A 26440-2026")</f>
-        <v/>
-      </c>
-      <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 26440-2026 FSC-klagomål mail.docx", "A 26440-2026")</f>
-        <v/>
-      </c>
-      <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 26440-2026 tillsynsbegäran.docx", "A 26440-2026")</f>
-        <v/>
-      </c>
-      <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 26440-2026 tillsynsbegäran mail.docx", "A 26440-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>A 34431-2026</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="n">
-        <v>46254</v>
-      </c>
-      <c r="E35" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="J35" t="n">
-        <v>2</v>
-      </c>
-      <c r="K35" t="n">
-        <v>1</v>
-      </c>
-      <c r="L35" t="n">
-        <v>3</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>3</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>4</v>
-      </c>
-      <c r="T35" t="n">
-        <v>5</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1</v>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Mindre hackspett
-Sandtimotej
-Murgröna</t>
-        </is>
-      </c>
-      <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 34431-2026 artfynd.xlsx", "A 34431-2026")</f>
-        <v/>
-      </c>
-      <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 34431-2026 karta.png", "A 34431-2026")</f>
-        <v/>
-      </c>
-      <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 34431-2026 georefererad karta.tif", "A 34431-2026")</f>
-        <v/>
-      </c>
-      <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 34431-2026 FSC-klagomål.docx", "A 34431-2026")</f>
-        <v/>
-      </c>
-      <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 34431-2026 FSC-klagomål mail.docx", "A 34431-2026")</f>
-        <v/>
-      </c>
-      <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 34431-2026 tillsynsbegäran.docx", "A 34431-2026")</f>
-        <v/>
-      </c>
-      <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 34431-2026 tillsynsbegäran mail.docx", "A 34431-2026")</f>
-        <v/>
-      </c>
-      <c r="AE35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 34431-2026 prioriterade fågelarter.docx", "A 34431-2026")</f>
         <v/>
       </c>
     </row>
@@ -4754,7 +4754,7 @@
         <v>45912</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>46203</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 72167-2021</t>
+          <t>A 62231-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4961,14 +4961,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44544</v>
+        <v>45267</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J38" t="n">
         <v>1</v>
@@ -5022,46 +5022,42 @@
       <c r="V38" s="2" t="inlineStr">
         <is>
           <t>Murgröna
-Röd glada</t>
+Blåsippa</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 72167-2021 artfynd.xlsx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62231-2023 artfynd.xlsx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 72167-2021 karta.png", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62231-2023 karta.png", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 72167-2021 georefererad karta.tif", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62231-2023 georefererad karta.tif", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 72167-2021 FSC-klagomål.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62231-2023 FSC-klagomål.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 72167-2021 FSC-klagomål mail.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62231-2023 FSC-klagomål mail.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 72167-2021 tillsynsbegäran.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62231-2023 tillsynsbegäran.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 72167-2021 tillsynsbegäran mail.docx", "A 72167-2021")</f>
-        <v/>
-      </c>
-      <c r="AE38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 72167-2021 prioriterade fågelarter.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62231-2023 tillsynsbegäran mail.docx", "A 62231-2023")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 62231-2023</t>
+          <t>A 72167-2021</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5071,14 +5067,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45267</v>
+        <v>44544</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5091,7 +5087,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J39" t="n">
         <v>1</v>
@@ -5132,35 +5128,39 @@
       <c r="V39" s="2" t="inlineStr">
         <is>
           <t>Murgröna
-Blåsippa</t>
+Röd glada</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62231-2023 artfynd.xlsx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 72167-2021 artfynd.xlsx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62231-2023 karta.png", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 72167-2021 karta.png", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62231-2023 georefererad karta.tif", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 72167-2021 georefererad karta.tif", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62231-2023 FSC-klagomål.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 72167-2021 FSC-klagomål.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62231-2023 FSC-klagomål mail.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 72167-2021 FSC-klagomål mail.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62231-2023 tillsynsbegäran.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 72167-2021 tillsynsbegäran.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62231-2023 tillsynsbegäran mail.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 72167-2021 tillsynsbegäran mail.docx", "A 72167-2021")</f>
+        <v/>
+      </c>
+      <c r="AE39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 72167-2021 prioriterade fågelarter.docx", "A 72167-2021")</f>
         <v/>
       </c>
     </row>
@@ -5184,7 +5184,7 @@
         <v>46246</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 13040-2024</t>
+          <t>A 30492-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5287,10 +5287,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45385</v>
+        <v>46210</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -5312,13 +5312,13 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5330,7 +5330,7 @@
         <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -5339,46 +5339,46 @@
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13040-2024 artfynd.xlsx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 30492-2026 artfynd.xlsx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13040-2024 karta.png", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 30492-2026 karta.png", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13040-2024 georefererad karta.tif", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 30492-2026 georefererad karta.tif", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13040-2024 FSC-klagomål.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 30492-2026 FSC-klagomål.docx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13040-2024 FSC-klagomål mail.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 30492-2026 FSC-klagomål mail.docx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13040-2024 tillsynsbegäran.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 30492-2026 tillsynsbegäran.docx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13040-2024 tillsynsbegäran mail.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 30492-2026 tillsynsbegäran mail.docx", "A 30492-2026")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 13384-2023</t>
+          <t>A 24698-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5392,10 +5392,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45005</v>
+        <v>45084</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5408,16 +5408,16 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.9</v>
+        <v>5.5</v>
       </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -5432,7 +5432,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -5448,42 +5448,42 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13384-2023 artfynd.xlsx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24698-2023 artfynd.xlsx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13384-2023 karta.png", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24698-2023 karta.png", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13384-2023 georefererad karta.tif", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24698-2023 georefererad karta.tif", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13384-2023 FSC-klagomål.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24698-2023 FSC-klagomål.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13384-2023 FSC-klagomål mail.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24698-2023 FSC-klagomål mail.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13384-2023 tillsynsbegäran.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24698-2023 tillsynsbegäran.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13384-2023 tillsynsbegäran mail.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24698-2023 tillsynsbegäran mail.docx", "A 24698-2023")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 24698-2023</t>
+          <t>A 36928-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5497,10 +5497,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45084</v>
+        <v>46273</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5513,16 +5513,16 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>5.5</v>
+        <v>1.3</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -5537,7 +5537,7 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -5549,39 +5549,39 @@
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24698-2023 artfynd.xlsx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 36928-2026 artfynd.xlsx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24698-2023 karta.png", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 36928-2026 karta.png", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24698-2023 georefererad karta.tif", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 36928-2026 georefererad karta.tif", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24698-2023 FSC-klagomål.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 36928-2026 FSC-klagomål.docx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24698-2023 FSC-klagomål mail.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 36928-2026 FSC-klagomål mail.docx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24698-2023 tillsynsbegäran.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 36928-2026 tillsynsbegäran.docx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24698-2023 tillsynsbegäran mail.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 36928-2026 tillsynsbegäran mail.docx", "A 36928-2026")</f>
         <v/>
       </c>
     </row>
@@ -5605,7 +5605,7 @@
         <v>46006</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 30492-2026</t>
+          <t>A 13040-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5707,10 +5707,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46210</v>
+        <v>45385</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5732,13 +5732,13 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5750,7 +5750,7 @@
         <v>1</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5759,46 +5759,46 @@
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 30492-2026 artfynd.xlsx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13040-2024 artfynd.xlsx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 30492-2026 karta.png", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13040-2024 karta.png", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 30492-2026 georefererad karta.tif", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13040-2024 georefererad karta.tif", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 30492-2026 FSC-klagomål.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13040-2024 FSC-klagomål.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 30492-2026 FSC-klagomål mail.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13040-2024 FSC-klagomål mail.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 30492-2026 tillsynsbegäran.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13040-2024 tillsynsbegäran.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 30492-2026 tillsynsbegäran mail.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13040-2024 tillsynsbegäran mail.docx", "A 13040-2024")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 36928-2026</t>
+          <t>A 13384-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46273</v>
+        <v>45005</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5828,13 +5828,13 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J46" t="n">
         <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -5864,39 +5864,39 @@
         <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 36928-2026 artfynd.xlsx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13384-2023 artfynd.xlsx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 36928-2026 karta.png", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13384-2023 karta.png", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 36928-2026 georefererad karta.tif", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13384-2023 georefererad karta.tif", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 36928-2026 FSC-klagomål.docx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13384-2023 FSC-klagomål.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 36928-2026 FSC-klagomål mail.docx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13384-2023 FSC-klagomål mail.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 36928-2026 tillsynsbegäran.docx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13384-2023 tillsynsbegäran.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 36928-2026 tillsynsbegäran mail.docx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13384-2023 tillsynsbegäran mail.docx", "A 13384-2023")</f>
         <v/>
       </c>
     </row>
@@ -5920,7 +5920,7 @@
         <v>44740</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         <v>45980</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>46171</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>

--- a/Översikt MÖRBYLÅNGA.xlsx
+++ b/Översikt MÖRBYLÅNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44964</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>44655</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>45177</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -964,10 +964,10 @@
         <v>45</v>
       </c>
       <c r="T4" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="U4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45096</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45685</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>46289</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>45475</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>45062</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>46195</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>46189</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>45254</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>45062</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>44508</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>45999</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>44811</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>45097</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>44728</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 15600-2025</t>
+          <t>A 39320-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2837,10 +2837,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45747</v>
+        <v>45551</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2853,45 +2853,159 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>4</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>7</v>
+      </c>
+      <c r="R19" t="n">
         <v>3</v>
-      </c>
-      <c r="K19" t="n">
-        <v>4</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>1</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
       </c>
       <c r="T19" t="n">
+        <v>11</v>
+      </c>
+      <c r="U19" t="n">
+        <v>10</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Vresalm
+Lundalm
+Toppjungfrulin
+Gulprickig vaxskivling
+Korskovall
+Sårläka
+Vårärt
+Strävlosta
+Underviol
+Skogsduva</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 39320-2024 artfynd.xlsx", "A 39320-2024")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 39320-2024 karta.png", "A 39320-2024")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 39320-2024 georefererad karta.tif", "A 39320-2024")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 39320-2024 FSC-klagomål.docx", "A 39320-2024")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 39320-2024 FSC-klagomål mail.docx", "A 39320-2024")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 39320-2024 tillsynsbegäran.docx", "A 39320-2024")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 39320-2024 tillsynsbegäran mail.docx", "A 39320-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 15600-2025</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45747</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="n">
         <v>20</v>
       </c>
-      <c r="U19" t="n">
+      <c r="U20" t="n">
         <v>18</v>
       </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Ask
 Kragjordstjärna
@@ -2905,150 +3019,36 @@
 Röd glada</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 15600-2025 artfynd.xlsx", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 15600-2025 karta.png", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 15600-2025 georefererad karta.tif", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 15600-2025 FSC-klagomål.docx", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 15600-2025 FSC-klagomål mail.docx", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 15600-2025 tillsynsbegäran.docx", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 15600-2025 tillsynsbegäran mail.docx", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="AE19">
+      <c r="AE20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 15600-2025 prioriterade fågelarter.docx", "A 15600-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 39320-2024</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45551</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>2</v>
-      </c>
-      <c r="L20" t="n">
-        <v>4</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N20" t="n">
-        <v>1</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>7</v>
-      </c>
-      <c r="R20" t="n">
-        <v>3</v>
-      </c>
-      <c r="S20" t="n">
-        <v>10</v>
-      </c>
-      <c r="T20" t="n">
-        <v>11</v>
-      </c>
-      <c r="U20" t="n">
-        <v>10</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Vresalm
-Lundalm
-Toppjungfrulin
-Gulprickig vaxskivling
-Korskovall
-Sårläka
-Vårärt
-Strävlosta
-Underviol
-Skogsduva</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 39320-2024 artfynd.xlsx", "A 39320-2024")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 39320-2024 karta.png", "A 39320-2024")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 39320-2024 georefererad karta.tif", "A 39320-2024")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 39320-2024 FSC-klagomål.docx", "A 39320-2024")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 39320-2024 FSC-klagomål mail.docx", "A 39320-2024")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 39320-2024 tillsynsbegäran.docx", "A 39320-2024")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 39320-2024 tillsynsbegäran mail.docx", "A 39320-2024")</f>
         <v/>
       </c>
     </row>
@@ -3072,7 +3072,7 @@
         <v>44616</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>45000</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>45530</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>45223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         <v>45075</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45169</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 43704-2025</t>
+          <t>A 43714-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3758,7 +3758,7 @@
         <v>45912</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3771,19 +3771,19 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.7</v>
+        <v>7.9</v>
       </c>
       <c r="J27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3795,21 +3795,135 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S27" t="n">
         <v>6</v>
       </c>
       <c r="T27" t="n">
+        <v>8</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Mindre bastardsvärmare
+Sexfläckig bastardsvärmare
+Grönsångare
+Murgröna
+Tibast
+Trädporella</t>
+        </is>
+      </c>
+      <c r="W27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43714-2025 artfynd.xlsx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="X27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43714-2025 karta.png", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="Y27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43714-2025 georefererad karta.tif", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AA27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43714-2025 FSC-klagomål.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AB27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43714-2025 FSC-klagomål mail.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AC27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43714-2025 tillsynsbegäran.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AD27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43714-2025 tillsynsbegäran mail.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 43714-2025 prioriterade fågelarter.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A 43704-2025</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>45912</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J28" t="n">
+        <v>5</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
         <v>6</v>
       </c>
-      <c r="U27" t="n">
-        <v>1</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="T28" t="n">
+        <v>6</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>Blomkålssvamp
 Långbensgroda
@@ -3819,146 +3933,32 @@
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W27">
+      <c r="W28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43704-2025 artfynd.xlsx", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="X27">
+      <c r="X28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43704-2025 karta.png", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="Y27">
+      <c r="Y28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43704-2025 georefererad karta.tif", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="AA27">
+      <c r="AA28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43704-2025 FSC-klagomål.docx", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="AB27">
+      <c r="AB28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43704-2025 FSC-klagomål mail.docx", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="AC27">
+      <c r="AC28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43704-2025 tillsynsbegäran.docx", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="AD27">
+      <c r="AD28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43704-2025 tillsynsbegäran mail.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>A 43714-2025</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>45912</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="J28" t="n">
-        <v>1</v>
-      </c>
-      <c r="K28" t="n">
-        <v>3</v>
-      </c>
-      <c r="L28" t="n">
-        <v>1</v>
-      </c>
-      <c r="M28" t="n">
-        <v>2</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>3</v>
-      </c>
-      <c r="R28" t="n">
-        <v>2</v>
-      </c>
-      <c r="S28" t="n">
-        <v>6</v>
-      </c>
-      <c r="T28" t="n">
-        <v>8</v>
-      </c>
-      <c r="U28" t="n">
-        <v>2</v>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>Mindre bastardsvärmare
-Sexfläckig bastardsvärmare
-Grönsångare
-Murgröna
-Tibast
-Trädporella</t>
-        </is>
-      </c>
-      <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43714-2025 artfynd.xlsx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43714-2025 karta.png", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43714-2025 georefererad karta.tif", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43714-2025 FSC-klagomål.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43714-2025 FSC-klagomål mail.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43714-2025 tillsynsbegäran.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43714-2025 tillsynsbegäran mail.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 43714-2025 prioriterade fågelarter.docx", "A 43714-2025")</f>
         <v/>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
         <v>46190</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 2864-2026</t>
+          <t>A 61963-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4085,14 +4085,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46038</v>
+        <v>46003</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J30" t="n">
         <v>4</v>
@@ -4153,42 +4153,42 @@
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 2864-2026 artfynd.xlsx", "A 2864-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 61963-2025 artfynd.xlsx", "A 61963-2025")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 2864-2026 karta.png", "A 2864-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 61963-2025 karta.png", "A 61963-2025")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 2864-2026 georefererad karta.tif", "A 2864-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 61963-2025 georefererad karta.tif", "A 61963-2025")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 2864-2026 FSC-klagomål.docx", "A 2864-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 61963-2025 FSC-klagomål.docx", "A 61963-2025")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 2864-2026 FSC-klagomål mail.docx", "A 2864-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 61963-2025 FSC-klagomål mail.docx", "A 61963-2025")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 2864-2026 tillsynsbegäran.docx", "A 2864-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 61963-2025 tillsynsbegäran.docx", "A 61963-2025")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 2864-2026 tillsynsbegäran mail.docx", "A 2864-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 61963-2025 tillsynsbegäran mail.docx", "A 61963-2025")</f>
         <v/>
       </c>
       <c r="AE30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 2864-2026 prioriterade fågelarter.docx", "A 2864-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 61963-2025 prioriterade fågelarter.docx", "A 61963-2025")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 61963-2025</t>
+          <t>A 2864-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4198,14 +4198,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46003</v>
+        <v>46038</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>4</v>
@@ -4266,42 +4266,42 @@
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 61963-2025 artfynd.xlsx", "A 61963-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 2864-2026 artfynd.xlsx", "A 2864-2026")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 61963-2025 karta.png", "A 61963-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 2864-2026 karta.png", "A 2864-2026")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 61963-2025 georefererad karta.tif", "A 61963-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 2864-2026 georefererad karta.tif", "A 2864-2026")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 61963-2025 FSC-klagomål.docx", "A 61963-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 2864-2026 FSC-klagomål.docx", "A 2864-2026")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 61963-2025 FSC-klagomål mail.docx", "A 61963-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 2864-2026 FSC-klagomål mail.docx", "A 2864-2026")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 61963-2025 tillsynsbegäran.docx", "A 61963-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 2864-2026 tillsynsbegäran.docx", "A 2864-2026")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 61963-2025 tillsynsbegäran mail.docx", "A 61963-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 2864-2026 tillsynsbegäran mail.docx", "A 2864-2026")</f>
         <v/>
       </c>
       <c r="AE31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 61963-2025 prioriterade fågelarter.docx", "A 61963-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 2864-2026 prioriterade fågelarter.docx", "A 2864-2026")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 26440-2026</t>
+          <t>A 54167-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4311,14 +4311,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46183</v>
+        <v>45616</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4331,22 +4331,22 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4358,18 +4358,234 @@
         <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" t="n">
         <v>4</v>
       </c>
       <c r="T32" t="n">
+        <v>8</v>
+      </c>
+      <c r="U32" t="n">
+        <v>8</v>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Murgröna
+Tvåblad
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 54167-2024 artfynd.xlsx", "A 54167-2024")</f>
+        <v/>
+      </c>
+      <c r="X32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 54167-2024 karta.png", "A 54167-2024")</f>
+        <v/>
+      </c>
+      <c r="Y32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 54167-2024 georefererad karta.tif", "A 54167-2024")</f>
+        <v/>
+      </c>
+      <c r="AA32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 54167-2024 FSC-klagomål.docx", "A 54167-2024")</f>
+        <v/>
+      </c>
+      <c r="AB32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 54167-2024 FSC-klagomål mail.docx", "A 54167-2024")</f>
+        <v/>
+      </c>
+      <c r="AC32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 54167-2024 tillsynsbegäran.docx", "A 54167-2024")</f>
+        <v/>
+      </c>
+      <c r="AD32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 54167-2024 tillsynsbegäran mail.docx", "A 54167-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>A 19459-2023</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="n">
+        <v>45049</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>4</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>4</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>4</v>
+      </c>
+      <c r="T33" t="n">
+        <v>4</v>
+      </c>
+      <c r="U33" t="n">
+        <v>4</v>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>Kavelhirs
+Kösa
+Luddvicker
+Riddarsporre</t>
+        </is>
+      </c>
+      <c r="W33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 19459-2023 artfynd.xlsx", "A 19459-2023")</f>
+        <v/>
+      </c>
+      <c r="X33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 19459-2023 karta.png", "A 19459-2023")</f>
+        <v/>
+      </c>
+      <c r="Y33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 19459-2023 georefererad karta.tif", "A 19459-2023")</f>
+        <v/>
+      </c>
+      <c r="AA33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 19459-2023 FSC-klagomål.docx", "A 19459-2023")</f>
+        <v/>
+      </c>
+      <c r="AB33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 19459-2023 FSC-klagomål mail.docx", "A 19459-2023")</f>
+        <v/>
+      </c>
+      <c r="AC33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 19459-2023 tillsynsbegäran.docx", "A 19459-2023")</f>
+        <v/>
+      </c>
+      <c r="AD33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 19459-2023 tillsynsbegäran mail.docx", "A 19459-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>A 26440-2026</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="E34" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>4</v>
+      </c>
+      <c r="T34" t="n">
         <v>5</v>
       </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>Backstarr
 Murgröna
@@ -4377,107 +4593,107 @@
 Vätteros</t>
         </is>
       </c>
-      <c r="W32">
+      <c r="W34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 26440-2026 artfynd.xlsx", "A 26440-2026")</f>
         <v/>
       </c>
-      <c r="X32">
+      <c r="X34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 26440-2026 karta.png", "A 26440-2026")</f>
         <v/>
       </c>
-      <c r="Y32">
+      <c r="Y34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 26440-2026 georefererad karta.tif", "A 26440-2026")</f>
         <v/>
       </c>
-      <c r="AA32">
+      <c r="AA34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 26440-2026 FSC-klagomål.docx", "A 26440-2026")</f>
         <v/>
       </c>
-      <c r="AB32">
+      <c r="AB34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 26440-2026 FSC-klagomål mail.docx", "A 26440-2026")</f>
         <v/>
       </c>
-      <c r="AC32">
+      <c r="AC34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 26440-2026 tillsynsbegäran.docx", "A 26440-2026")</f>
         <v/>
       </c>
-      <c r="AD32">
+      <c r="AD34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 26440-2026 tillsynsbegäran mail.docx", "A 26440-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>A 34431-2026</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D33" s="1" t="n">
+      <c r="D35" s="1" t="n">
         <v>46254</v>
       </c>
-      <c r="E33" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F33" t="inlineStr">
+      <c r="E35" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I33" t="n">
+      <c r="I35" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="J33" t="n">
+      <c r="J35" t="n">
         <v>2</v>
       </c>
-      <c r="K33" t="n">
-        <v>1</v>
-      </c>
-      <c r="L33" t="n">
+      <c r="K35" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" t="n">
         <v>3</v>
       </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
         <v>3</v>
       </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
         <v>4</v>
       </c>
-      <c r="T33" t="n">
+      <c r="T35" t="n">
         <v>5</v>
       </c>
-      <c r="U33" t="n">
-        <v>1</v>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
+      <c r="U35" t="n">
+        <v>1</v>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
         <is>
           <t>Entita
 Mindre hackspett
@@ -4485,252 +4701,36 @@
 Murgröna</t>
         </is>
       </c>
-      <c r="W33">
+      <c r="W35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 34431-2026 artfynd.xlsx", "A 34431-2026")</f>
         <v/>
       </c>
-      <c r="X33">
+      <c r="X35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 34431-2026 karta.png", "A 34431-2026")</f>
         <v/>
       </c>
-      <c r="Y33">
+      <c r="Y35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 34431-2026 georefererad karta.tif", "A 34431-2026")</f>
         <v/>
       </c>
-      <c r="AA33">
+      <c r="AA35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 34431-2026 FSC-klagomål.docx", "A 34431-2026")</f>
         <v/>
       </c>
-      <c r="AB33">
+      <c r="AB35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 34431-2026 FSC-klagomål mail.docx", "A 34431-2026")</f>
         <v/>
       </c>
-      <c r="AC33">
+      <c r="AC35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 34431-2026 tillsynsbegäran.docx", "A 34431-2026")</f>
         <v/>
       </c>
-      <c r="AD33">
+      <c r="AD35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 34431-2026 tillsynsbegäran mail.docx", "A 34431-2026")</f>
         <v/>
       </c>
-      <c r="AE33">
+      <c r="AE35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 34431-2026 prioriterade fågelarter.docx", "A 34431-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>A 54167-2024</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="n">
-        <v>45616</v>
-      </c>
-      <c r="E34" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J34" t="n">
-        <v>2</v>
-      </c>
-      <c r="K34" t="n">
-        <v>2</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>1</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>1</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1</v>
-      </c>
-      <c r="S34" t="n">
-        <v>4</v>
-      </c>
-      <c r="T34" t="n">
-        <v>8</v>
-      </c>
-      <c r="U34" t="n">
-        <v>8</v>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Murgröna
-Tvåblad
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 54167-2024 artfynd.xlsx", "A 54167-2024")</f>
-        <v/>
-      </c>
-      <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 54167-2024 karta.png", "A 54167-2024")</f>
-        <v/>
-      </c>
-      <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 54167-2024 georefererad karta.tif", "A 54167-2024")</f>
-        <v/>
-      </c>
-      <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 54167-2024 FSC-klagomål.docx", "A 54167-2024")</f>
-        <v/>
-      </c>
-      <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 54167-2024 FSC-klagomål mail.docx", "A 54167-2024")</f>
-        <v/>
-      </c>
-      <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 54167-2024 tillsynsbegäran.docx", "A 54167-2024")</f>
-        <v/>
-      </c>
-      <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 54167-2024 tillsynsbegäran mail.docx", "A 54167-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>A 19459-2023</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="n">
-        <v>45049</v>
-      </c>
-      <c r="E35" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>4</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>4</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>4</v>
-      </c>
-      <c r="T35" t="n">
-        <v>4</v>
-      </c>
-      <c r="U35" t="n">
-        <v>4</v>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>Kavelhirs
-Kösa
-Luddvicker
-Riddarsporre</t>
-        </is>
-      </c>
-      <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 19459-2023 artfynd.xlsx", "A 19459-2023")</f>
-        <v/>
-      </c>
-      <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 19459-2023 karta.png", "A 19459-2023")</f>
-        <v/>
-      </c>
-      <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 19459-2023 georefererad karta.tif", "A 19459-2023")</f>
-        <v/>
-      </c>
-      <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 19459-2023 FSC-klagomål.docx", "A 19459-2023")</f>
-        <v/>
-      </c>
-      <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 19459-2023 FSC-klagomål mail.docx", "A 19459-2023")</f>
-        <v/>
-      </c>
-      <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 19459-2023 tillsynsbegäran.docx", "A 19459-2023")</f>
-        <v/>
-      </c>
-      <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 19459-2023 tillsynsbegäran mail.docx", "A 19459-2023")</f>
         <v/>
       </c>
     </row>
@@ -4754,7 +4754,7 @@
         <v>45912</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>46203</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 62231-2023</t>
+          <t>A 72167-2021</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4961,14 +4961,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45267</v>
+        <v>44544</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J38" t="n">
         <v>1</v>
@@ -5022,42 +5022,46 @@
       <c r="V38" s="2" t="inlineStr">
         <is>
           <t>Murgröna
-Blåsippa</t>
+Röd glada</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62231-2023 artfynd.xlsx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 72167-2021 artfynd.xlsx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62231-2023 karta.png", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 72167-2021 karta.png", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62231-2023 georefererad karta.tif", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 72167-2021 georefererad karta.tif", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62231-2023 FSC-klagomål.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 72167-2021 FSC-klagomål.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62231-2023 FSC-klagomål mail.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 72167-2021 FSC-klagomål mail.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62231-2023 tillsynsbegäran.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 72167-2021 tillsynsbegäran.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62231-2023 tillsynsbegäran mail.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 72167-2021 tillsynsbegäran mail.docx", "A 72167-2021")</f>
+        <v/>
+      </c>
+      <c r="AE38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 72167-2021 prioriterade fågelarter.docx", "A 72167-2021")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 72167-2021</t>
+          <t>A 62231-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5067,14 +5071,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44544</v>
+        <v>45267</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5087,7 +5091,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J39" t="n">
         <v>1</v>
@@ -5128,39 +5132,35 @@
       <c r="V39" s="2" t="inlineStr">
         <is>
           <t>Murgröna
-Röd glada</t>
+Blåsippa</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 72167-2021 artfynd.xlsx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62231-2023 artfynd.xlsx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 72167-2021 karta.png", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62231-2023 karta.png", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 72167-2021 georefererad karta.tif", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62231-2023 georefererad karta.tif", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 72167-2021 FSC-klagomål.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62231-2023 FSC-klagomål.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 72167-2021 FSC-klagomål mail.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62231-2023 FSC-klagomål mail.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 72167-2021 tillsynsbegäran.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62231-2023 tillsynsbegäran.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 72167-2021 tillsynsbegäran mail.docx", "A 72167-2021")</f>
-        <v/>
-      </c>
-      <c r="AE39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 72167-2021 prioriterade fågelarter.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62231-2023 tillsynsbegäran mail.docx", "A 62231-2023")</f>
         <v/>
       </c>
     </row>
@@ -5184,7 +5184,7 @@
         <v>46246</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 30492-2026</t>
+          <t>A 13040-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5287,10 +5287,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46210</v>
+        <v>45385</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -5312,13 +5312,13 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5330,7 +5330,7 @@
         <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -5339,39 +5339,39 @@
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 30492-2026 artfynd.xlsx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13040-2024 artfynd.xlsx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 30492-2026 karta.png", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13040-2024 karta.png", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 30492-2026 georefererad karta.tif", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13040-2024 georefererad karta.tif", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 30492-2026 FSC-klagomål.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13040-2024 FSC-klagomål.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 30492-2026 FSC-klagomål mail.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13040-2024 FSC-klagomål mail.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 30492-2026 tillsynsbegäran.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13040-2024 tillsynsbegäran.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 30492-2026 tillsynsbegäran mail.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13040-2024 tillsynsbegäran mail.docx", "A 13040-2024")</f>
         <v/>
       </c>
     </row>
@@ -5395,7 +5395,7 @@
         <v>45084</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 36928-2026</t>
+          <t>A 13384-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5497,10 +5497,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46273</v>
+        <v>45005</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5513,13 +5513,13 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J43" t="n">
         <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -5549,39 +5549,39 @@
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 36928-2026 artfynd.xlsx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13384-2023 artfynd.xlsx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 36928-2026 karta.png", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13384-2023 karta.png", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 36928-2026 georefererad karta.tif", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13384-2023 georefererad karta.tif", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 36928-2026 FSC-klagomål.docx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13384-2023 FSC-klagomål.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 36928-2026 FSC-klagomål mail.docx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13384-2023 FSC-klagomål mail.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 36928-2026 tillsynsbegäran.docx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13384-2023 tillsynsbegäran.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 36928-2026 tillsynsbegäran mail.docx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13384-2023 tillsynsbegäran mail.docx", "A 13384-2023")</f>
         <v/>
       </c>
     </row>
@@ -5605,7 +5605,7 @@
         <v>46006</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 13040-2024</t>
+          <t>A 30492-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5707,10 +5707,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45385</v>
+        <v>46210</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5732,13 +5732,13 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5750,7 +5750,7 @@
         <v>1</v>
       </c>
       <c r="R45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5759,46 +5759,46 @@
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13040-2024 artfynd.xlsx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 30492-2026 artfynd.xlsx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13040-2024 karta.png", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 30492-2026 karta.png", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13040-2024 georefererad karta.tif", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 30492-2026 georefererad karta.tif", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13040-2024 FSC-klagomål.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 30492-2026 FSC-klagomål.docx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13040-2024 FSC-klagomål mail.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 30492-2026 FSC-klagomål mail.docx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13040-2024 tillsynsbegäran.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 30492-2026 tillsynsbegäran.docx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13040-2024 tillsynsbegäran mail.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 30492-2026 tillsynsbegäran mail.docx", "A 30492-2026")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 13384-2023</t>
+          <t>A 36928-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45005</v>
+        <v>46273</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5828,13 +5828,13 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J46" t="n">
         <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -5864,39 +5864,39 @@
         <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13384-2023 artfynd.xlsx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 36928-2026 artfynd.xlsx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13384-2023 karta.png", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 36928-2026 karta.png", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13384-2023 georefererad karta.tif", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 36928-2026 georefererad karta.tif", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13384-2023 FSC-klagomål.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 36928-2026 FSC-klagomål.docx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13384-2023 FSC-klagomål mail.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 36928-2026 FSC-klagomål mail.docx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13384-2023 tillsynsbegäran.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 36928-2026 tillsynsbegäran.docx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13384-2023 tillsynsbegäran mail.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 36928-2026 tillsynsbegäran mail.docx", "A 36928-2026")</f>
         <v/>
       </c>
     </row>
@@ -5920,7 +5920,7 @@
         <v>44740</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         <v>45980</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>46171</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>

--- a/Översikt MÖRBYLÅNGA.xlsx
+++ b/Översikt MÖRBYLÅNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44964</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>44655</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>45177</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45096</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45685</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>46289</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>45475</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>45062</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>46195</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>46189</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>45254</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>45062</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>44508</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 60875-2025</t>
+          <t>A 24778-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2373,10 +2373,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45999</v>
+        <v>44728</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2389,45 +2389,160 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>7</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
         <v>8</v>
       </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>5</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>7</v>
-      </c>
       <c r="R15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>11</v>
       </c>
       <c r="T15" t="n">
+        <v>20</v>
+      </c>
+      <c r="U15" t="n">
+        <v>20</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Tofsäxing
+Backtimjan
+Flentimotej
+Grådådra
+Poppeltofsskivling
+Slåtterfibbla
+Sminkrot
+Solvända
+Kalktallört
+Murgröna
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24778-2022 artfynd.xlsx", "A 24778-2022")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24778-2022 karta.png", "A 24778-2022")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24778-2022 georefererad karta.tif", "A 24778-2022")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24778-2022 FSC-klagomål.docx", "A 24778-2022")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24778-2022 FSC-klagomål mail.docx", "A 24778-2022")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24778-2022 tillsynsbegäran.docx", "A 24778-2022")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24778-2022 tillsynsbegäran mail.docx", "A 24778-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 60875-2025</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45999</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>8</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>5</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>7</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2</v>
+      </c>
+      <c r="S16" t="n">
+        <v>11</v>
+      </c>
+      <c r="T16" t="n">
         <v>12</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U16" t="n">
         <v>3</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Järnek
 Mosippa
@@ -2442,111 +2557,111 @@
 Skogsduva</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 60875-2025 artfynd.xlsx", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 60875-2025 karta.png", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 60875-2025 georefererad karta.tif", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 60875-2025 FSC-klagomål.docx", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 60875-2025 FSC-klagomål mail.docx", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 60875-2025 tillsynsbegäran.docx", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 60875-2025 tillsynsbegäran mail.docx", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 60875-2025 prioriterade fågelarter.docx", "A 60875-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>A 38039-2022</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D16" s="1" t="n">
+      <c r="D17" s="1" t="n">
         <v>44811</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>46309</v>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="E17" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I16" t="n">
+      <c r="I17" t="n">
         <v>7.4</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J17" t="n">
         <v>4</v>
       </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
         <v>4</v>
       </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>6</v>
       </c>
-      <c r="R16" t="n">
+      <c r="R17" t="n">
         <v>2</v>
       </c>
-      <c r="S16" t="n">
+      <c r="S17" t="n">
         <v>11</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T17" t="n">
         <v>13</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U17" t="n">
         <v>12</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Ask
 Grov gulmossa
@@ -2561,107 +2676,107 @@
 Gullviva</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 38039-2022 artfynd.xlsx", "A 38039-2022")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 38039-2022 karta.png", "A 38039-2022")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 38039-2022 georefererad karta.tif", "A 38039-2022")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 38039-2022 FSC-klagomål.docx", "A 38039-2022")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 38039-2022 FSC-klagomål mail.docx", "A 38039-2022")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 38039-2022 tillsynsbegäran.docx", "A 38039-2022")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 38039-2022 tillsynsbegäran mail.docx", "A 38039-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>A 27636-2023</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D17" s="1" t="n">
+      <c r="D18" s="1" t="n">
         <v>45097</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>46309</v>
-      </c>
-      <c r="F17" t="inlineStr">
+      <c r="E18" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I17" t="n">
+      <c r="I18" t="n">
         <v>7.4</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J18" t="n">
         <v>4</v>
       </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
         <v>4</v>
       </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
         <v>6</v>
       </c>
-      <c r="R17" t="n">
+      <c r="R18" t="n">
         <v>2</v>
       </c>
-      <c r="S17" t="n">
+      <c r="S18" t="n">
         <v>11</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T18" t="n">
         <v>13</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U18" t="n">
         <v>11</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Ask
 Grov gulmossa
@@ -2676,147 +2791,32 @@
 Gullviva</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 27636-2023 artfynd.xlsx", "A 27636-2023")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 27636-2023 karta.png", "A 27636-2023")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 27636-2023 georefererad karta.tif", "A 27636-2023")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 27636-2023 FSC-klagomål.docx", "A 27636-2023")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 27636-2023 FSC-klagomål mail.docx", "A 27636-2023")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 27636-2023 tillsynsbegäran.docx", "A 27636-2023")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 27636-2023 tillsynsbegäran mail.docx", "A 27636-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 24778-2022</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>44728</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46309</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2</v>
-      </c>
-      <c r="L18" t="n">
-        <v>7</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>8</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1</v>
-      </c>
-      <c r="S18" t="n">
-        <v>11</v>
-      </c>
-      <c r="T18" t="n">
-        <v>20</v>
-      </c>
-      <c r="U18" t="n">
-        <v>20</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Tofsäxing
-Backtimjan
-Flentimotej
-Grådådra
-Poppeltofsskivling
-Slåtterfibbla
-Sminkrot
-Solvända
-Kalktallört
-Murgröna
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24778-2022 artfynd.xlsx", "A 24778-2022")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24778-2022 karta.png", "A 24778-2022")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24778-2022 georefererad karta.tif", "A 24778-2022")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24778-2022 FSC-klagomål.docx", "A 24778-2022")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24778-2022 FSC-klagomål mail.docx", "A 24778-2022")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24778-2022 tillsynsbegäran.docx", "A 24778-2022")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24778-2022 tillsynsbegäran mail.docx", "A 24778-2022")</f>
         <v/>
       </c>
     </row>
@@ -2840,7 +2840,7 @@
         <v>45551</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>45747</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>44616</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>45000</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>45530</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>45223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         <v>45075</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45169</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 43714-2025</t>
+          <t>A 43704-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3758,7 +3758,7 @@
         <v>45912</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3771,19 +3771,19 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>7.9</v>
+        <v>2.7</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3795,21 +3795,131 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>6</v>
       </c>
       <c r="T27" t="n">
+        <v>6</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp
+Långbensgroda
+Större vattensalamander
+Åkergroda
+Mindre vattensalamander
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43704-2025 artfynd.xlsx", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="X27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43704-2025 karta.png", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="Y27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43704-2025 georefererad karta.tif", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="AA27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43704-2025 FSC-klagomål.docx", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="AB27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43704-2025 FSC-klagomål mail.docx", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="AC27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43704-2025 tillsynsbegäran.docx", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="AD27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43704-2025 tillsynsbegäran mail.docx", "A 43704-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A 43714-2025</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>45912</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" t="n">
+        <v>2</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2</v>
+      </c>
+      <c r="S28" t="n">
+        <v>6</v>
+      </c>
+      <c r="T28" t="n">
         <v>8</v>
       </c>
-      <c r="U27" t="n">
+      <c r="U28" t="n">
         <v>2</v>
       </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>Mindre bastardsvärmare
 Sexfläckig bastardsvärmare
@@ -3819,146 +3929,36 @@
 Trädporella</t>
         </is>
       </c>
-      <c r="W27">
+      <c r="W28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43714-2025 artfynd.xlsx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="X27">
+      <c r="X28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43714-2025 karta.png", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="Y27">
+      <c r="Y28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43714-2025 georefererad karta.tif", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AA27">
+      <c r="AA28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43714-2025 FSC-klagomål.docx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AB27">
+      <c r="AB28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43714-2025 FSC-klagomål mail.docx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AC27">
+      <c r="AC28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43714-2025 tillsynsbegäran.docx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AD27">
+      <c r="AD28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43714-2025 tillsynsbegäran mail.docx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AE27">
+      <c r="AE28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 43714-2025 prioriterade fågelarter.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>A 43704-2025</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>45912</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>46309</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J28" t="n">
-        <v>5</v>
-      </c>
-      <c r="K28" t="n">
-        <v>1</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>6</v>
-      </c>
-      <c r="T28" t="n">
-        <v>6</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1</v>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>Blomkålssvamp
-Långbensgroda
-Större vattensalamander
-Åkergroda
-Mindre vattensalamander
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43704-2025 artfynd.xlsx", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43704-2025 karta.png", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43704-2025 georefererad karta.tif", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43704-2025 FSC-klagomål.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43704-2025 FSC-klagomål mail.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43704-2025 tillsynsbegäran.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43704-2025 tillsynsbegäran mail.docx", "A 43704-2025")</f>
         <v/>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
         <v>46190</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>46003</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>46038</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>45616</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 19459-2023</t>
+          <t>A 26440-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4423,10 +4423,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45049</v>
+        <v>46183</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4439,16 +4439,16 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -4463,7 +4463,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -4472,12 +4472,120 @@
         <v>4</v>
       </c>
       <c r="T33" t="n">
+        <v>5</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>Backstarr
+Murgröna
+Nästrot
+Vätteros</t>
+        </is>
+      </c>
+      <c r="W33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 26440-2026 artfynd.xlsx", "A 26440-2026")</f>
+        <v/>
+      </c>
+      <c r="X33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 26440-2026 karta.png", "A 26440-2026")</f>
+        <v/>
+      </c>
+      <c r="Y33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 26440-2026 georefererad karta.tif", "A 26440-2026")</f>
+        <v/>
+      </c>
+      <c r="AA33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 26440-2026 FSC-klagomål.docx", "A 26440-2026")</f>
+        <v/>
+      </c>
+      <c r="AB33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 26440-2026 FSC-klagomål mail.docx", "A 26440-2026")</f>
+        <v/>
+      </c>
+      <c r="AC33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 26440-2026 tillsynsbegäran.docx", "A 26440-2026")</f>
+        <v/>
+      </c>
+      <c r="AD33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 26440-2026 tillsynsbegäran mail.docx", "A 26440-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>A 19459-2023</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="n">
+        <v>45049</v>
+      </c>
+      <c r="E34" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
         <v>4</v>
       </c>
-      <c r="U33" t="n">
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
         <v>4</v>
       </c>
-      <c r="V33" s="2" t="inlineStr">
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>4</v>
+      </c>
+      <c r="T34" t="n">
+        <v>4</v>
+      </c>
+      <c r="U34" t="n">
+        <v>4</v>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>Kavelhirs
 Kösa
@@ -4485,140 +4593,32 @@
 Riddarsporre</t>
         </is>
       </c>
-      <c r="W33">
+      <c r="W34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 19459-2023 artfynd.xlsx", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="X33">
+      <c r="X34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 19459-2023 karta.png", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="Y33">
+      <c r="Y34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 19459-2023 georefererad karta.tif", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="AA33">
+      <c r="AA34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 19459-2023 FSC-klagomål.docx", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="AB33">
+      <c r="AB34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 19459-2023 FSC-klagomål mail.docx", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="AC33">
+      <c r="AC34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 19459-2023 tillsynsbegäran.docx", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="AD33">
+      <c r="AD34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 19459-2023 tillsynsbegäran mail.docx", "A 19459-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>A 26440-2026</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="n">
-        <v>46183</v>
-      </c>
-      <c r="E34" s="1" t="n">
-        <v>46309</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J34" t="n">
-        <v>1</v>
-      </c>
-      <c r="K34" t="n">
-        <v>3</v>
-      </c>
-      <c r="L34" t="n">
-        <v>1</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>1</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>4</v>
-      </c>
-      <c r="T34" t="n">
-        <v>5</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>Backstarr
-Murgröna
-Nästrot
-Vätteros</t>
-        </is>
-      </c>
-      <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 26440-2026 artfynd.xlsx", "A 26440-2026")</f>
-        <v/>
-      </c>
-      <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 26440-2026 karta.png", "A 26440-2026")</f>
-        <v/>
-      </c>
-      <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 26440-2026 georefererad karta.tif", "A 26440-2026")</f>
-        <v/>
-      </c>
-      <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 26440-2026 FSC-klagomål.docx", "A 26440-2026")</f>
-        <v/>
-      </c>
-      <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 26440-2026 FSC-klagomål mail.docx", "A 26440-2026")</f>
-        <v/>
-      </c>
-      <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 26440-2026 tillsynsbegäran.docx", "A 26440-2026")</f>
-        <v/>
-      </c>
-      <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 26440-2026 tillsynsbegäran mail.docx", "A 26440-2026")</f>
         <v/>
       </c>
     </row>
@@ -4642,7 +4642,7 @@
         <v>46254</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>45912</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>46203</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 72167-2021</t>
+          <t>A 62231-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4961,14 +4961,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44544</v>
+        <v>45267</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J38" t="n">
         <v>1</v>
@@ -5022,46 +5022,42 @@
       <c r="V38" s="2" t="inlineStr">
         <is>
           <t>Murgröna
-Röd glada</t>
+Blåsippa</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 72167-2021 artfynd.xlsx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62231-2023 artfynd.xlsx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 72167-2021 karta.png", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62231-2023 karta.png", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 72167-2021 georefererad karta.tif", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62231-2023 georefererad karta.tif", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 72167-2021 FSC-klagomål.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62231-2023 FSC-klagomål.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 72167-2021 FSC-klagomål mail.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62231-2023 FSC-klagomål mail.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 72167-2021 tillsynsbegäran.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62231-2023 tillsynsbegäran.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 72167-2021 tillsynsbegäran mail.docx", "A 72167-2021")</f>
-        <v/>
-      </c>
-      <c r="AE38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 72167-2021 prioriterade fågelarter.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62231-2023 tillsynsbegäran mail.docx", "A 62231-2023")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 62231-2023</t>
+          <t>A 72167-2021</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5071,14 +5067,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45267</v>
+        <v>44544</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5091,7 +5087,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J39" t="n">
         <v>1</v>
@@ -5132,35 +5128,39 @@
       <c r="V39" s="2" t="inlineStr">
         <is>
           <t>Murgröna
-Blåsippa</t>
+Röd glada</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62231-2023 artfynd.xlsx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 72167-2021 artfynd.xlsx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62231-2023 karta.png", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 72167-2021 karta.png", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62231-2023 georefererad karta.tif", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 72167-2021 georefererad karta.tif", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62231-2023 FSC-klagomål.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 72167-2021 FSC-klagomål.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62231-2023 FSC-klagomål mail.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 72167-2021 FSC-klagomål mail.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62231-2023 tillsynsbegäran.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 72167-2021 tillsynsbegäran.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62231-2023 tillsynsbegäran mail.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 72167-2021 tillsynsbegäran mail.docx", "A 72167-2021")</f>
+        <v/>
+      </c>
+      <c r="AE39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 72167-2021 prioriterade fågelarter.docx", "A 72167-2021")</f>
         <v/>
       </c>
     </row>
@@ -5184,7 +5184,7 @@
         <v>46246</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 13040-2024</t>
+          <t>A 24698-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5283,14 +5283,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45385</v>
+        <v>45084</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.2</v>
+        <v>5.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -5312,13 +5312,13 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5330,7 +5330,7 @@
         <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -5343,42 +5343,42 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13040-2024 artfynd.xlsx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24698-2023 artfynd.xlsx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13040-2024 karta.png", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24698-2023 karta.png", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13040-2024 georefererad karta.tif", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24698-2023 georefererad karta.tif", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13040-2024 FSC-klagomål.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24698-2023 FSC-klagomål.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13040-2024 FSC-klagomål mail.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24698-2023 FSC-klagomål mail.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13040-2024 tillsynsbegäran.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24698-2023 tillsynsbegäran.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13040-2024 tillsynsbegäran mail.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24698-2023 tillsynsbegäran mail.docx", "A 24698-2023")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 24698-2023</t>
+          <t>A 62183-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5392,10 +5392,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45084</v>
+        <v>46006</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>5.5</v>
+        <v>0.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -5444,46 +5444,46 @@
         <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24698-2023 artfynd.xlsx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62183-2025 artfynd.xlsx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24698-2023 karta.png", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62183-2025 karta.png", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24698-2023 georefererad karta.tif", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62183-2025 georefererad karta.tif", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24698-2023 FSC-klagomål.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62183-2025 FSC-klagomål.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24698-2023 FSC-klagomål mail.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62183-2025 FSC-klagomål mail.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24698-2023 tillsynsbegäran.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62183-2025 tillsynsbegäran.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24698-2023 tillsynsbegäran mail.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62183-2025 tillsynsbegäran mail.docx", "A 62183-2025")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 13384-2023</t>
+          <t>A 13040-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5493,14 +5493,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45005</v>
+        <v>45385</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5513,10 +5513,10 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -5528,7 +5528,7 @@
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5537,10 +5537,10 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5553,42 +5553,42 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13384-2023 artfynd.xlsx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13040-2024 artfynd.xlsx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13384-2023 karta.png", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13040-2024 karta.png", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13384-2023 georefererad karta.tif", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13040-2024 georefererad karta.tif", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13384-2023 FSC-klagomål.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13040-2024 FSC-klagomål.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13384-2023 FSC-klagomål mail.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13040-2024 FSC-klagomål mail.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13384-2023 tillsynsbegäran.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13040-2024 tillsynsbegäran.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13384-2023 tillsynsbegäran mail.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13040-2024 tillsynsbegäran mail.docx", "A 13040-2024")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 62183-2025</t>
+          <t>A 13384-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5602,10 +5602,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46006</v>
+        <v>45005</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5618,16 +5618,16 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -5642,7 +5642,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -5654,39 +5654,39 @@
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62183-2025 artfynd.xlsx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13384-2023 artfynd.xlsx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62183-2025 karta.png", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13384-2023 karta.png", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62183-2025 georefererad karta.tif", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13384-2023 georefererad karta.tif", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62183-2025 FSC-klagomål.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13384-2023 FSC-klagomål.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62183-2025 FSC-klagomål mail.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13384-2023 FSC-klagomål mail.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62183-2025 tillsynsbegäran.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13384-2023 tillsynsbegäran.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62183-2025 tillsynsbegäran mail.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13384-2023 tillsynsbegäran mail.docx", "A 13384-2023")</f>
         <v/>
       </c>
     </row>
@@ -5710,7 +5710,7 @@
         <v>46210</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>46273</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>44740</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         <v>45980</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>46171</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>

--- a/Översikt MÖRBYLÅNGA.xlsx
+++ b/Översikt MÖRBYLÅNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44964</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>44655</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>45177</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45096</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45685</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1270,10 +1270,10 @@
         <v>36</v>
       </c>
       <c r="T6" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="U6" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>46289</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>45475</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>45062</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>46195</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>46189</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>45254</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>45062</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>44508</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 24778-2022</t>
+          <t>A 38039-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2369,14 +2369,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44728</v>
+        <v>44811</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2389,45 +2389,275 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>7.4</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>4</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>6</v>
+      </c>
+      <c r="R15" t="n">
         <v>2</v>
-      </c>
-      <c r="L15" t="n">
-        <v>7</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>8</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>11</v>
       </c>
       <c r="T15" t="n">
+        <v>13</v>
+      </c>
+      <c r="U15" t="n">
+        <v>12</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Grov gulmossa
+Backtimjan
+Dvärgjordstjärna
+Solvända
+Ängsstarr
+Murgröna
+Alvarmalört
+Grönvit nattviol
+Krutbrännare
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 38039-2022 artfynd.xlsx", "A 38039-2022")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 38039-2022 karta.png", "A 38039-2022")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 38039-2022 georefererad karta.tif", "A 38039-2022")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 38039-2022 FSC-klagomål.docx", "A 38039-2022")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 38039-2022 FSC-klagomål mail.docx", "A 38039-2022")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 38039-2022 tillsynsbegäran.docx", "A 38039-2022")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 38039-2022 tillsynsbegäran mail.docx", "A 38039-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 27636-2023</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45097</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>4</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>6</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2</v>
+      </c>
+      <c r="S16" t="n">
+        <v>11</v>
+      </c>
+      <c r="T16" t="n">
+        <v>13</v>
+      </c>
+      <c r="U16" t="n">
+        <v>11</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Grov gulmossa
+Backtimjan
+Dvärgjordstjärna
+Solvända
+Ängsstarr
+Murgröna
+Alvarmalört
+Grönvit nattviol
+Krutbrännare
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 27636-2023 artfynd.xlsx", "A 27636-2023")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 27636-2023 karta.png", "A 27636-2023")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 27636-2023 georefererad karta.tif", "A 27636-2023")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 27636-2023 FSC-klagomål.docx", "A 27636-2023")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 27636-2023 FSC-klagomål mail.docx", "A 27636-2023")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 27636-2023 tillsynsbegäran.docx", "A 27636-2023")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 27636-2023 tillsynsbegäran mail.docx", "A 27636-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 24778-2022</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>44728</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L17" t="n">
+        <v>7</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>8</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>11</v>
+      </c>
+      <c r="T17" t="n">
         <v>20</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U17" t="n">
         <v>20</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Tofsäxing
 Backtimjan
@@ -2442,107 +2672,107 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24778-2022 artfynd.xlsx", "A 24778-2022")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24778-2022 karta.png", "A 24778-2022")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24778-2022 georefererad karta.tif", "A 24778-2022")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24778-2022 FSC-klagomål.docx", "A 24778-2022")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24778-2022 FSC-klagomål mail.docx", "A 24778-2022")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24778-2022 tillsynsbegäran.docx", "A 24778-2022")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24778-2022 tillsynsbegäran mail.docx", "A 24778-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>A 60875-2025</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D16" s="1" t="n">
+      <c r="D18" s="1" t="n">
         <v>45999</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>46310</v>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="E18" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I16" t="n">
+      <c r="I18" t="n">
         <v>2.1</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J18" t="n">
         <v>8</v>
       </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
         <v>5</v>
       </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
         <v>7</v>
       </c>
-      <c r="R16" t="n">
+      <c r="R18" t="n">
         <v>2</v>
       </c>
-      <c r="S16" t="n">
+      <c r="S18" t="n">
         <v>11</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T18" t="n">
         <v>12</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U18" t="n">
         <v>3</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Järnek
 Mosippa
@@ -2557,273 +2787,43 @@
 Skogsduva</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 60875-2025 artfynd.xlsx", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 60875-2025 karta.png", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 60875-2025 georefererad karta.tif", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 60875-2025 FSC-klagomål.docx", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 60875-2025 FSC-klagomål mail.docx", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 60875-2025 tillsynsbegäran.docx", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 60875-2025 tillsynsbegäran mail.docx", "A 60875-2025")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 60875-2025 prioriterade fågelarter.docx", "A 60875-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 38039-2022</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>44811</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46310</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="J17" t="n">
-        <v>4</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>4</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>6</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2</v>
-      </c>
-      <c r="S17" t="n">
-        <v>11</v>
-      </c>
-      <c r="T17" t="n">
-        <v>13</v>
-      </c>
-      <c r="U17" t="n">
-        <v>12</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Grov gulmossa
-Backtimjan
-Dvärgjordstjärna
-Solvända
-Ängsstarr
-Murgröna
-Alvarmalört
-Grönvit nattviol
-Krutbrännare
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 38039-2022 artfynd.xlsx", "A 38039-2022")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 38039-2022 karta.png", "A 38039-2022")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 38039-2022 georefererad karta.tif", "A 38039-2022")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 38039-2022 FSC-klagomål.docx", "A 38039-2022")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 38039-2022 FSC-klagomål mail.docx", "A 38039-2022")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 38039-2022 tillsynsbegäran.docx", "A 38039-2022")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 38039-2022 tillsynsbegäran mail.docx", "A 38039-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 27636-2023</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45097</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46310</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="J18" t="n">
-        <v>4</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>4</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>6</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2</v>
-      </c>
-      <c r="S18" t="n">
-        <v>11</v>
-      </c>
-      <c r="T18" t="n">
-        <v>13</v>
-      </c>
-      <c r="U18" t="n">
-        <v>11</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Grov gulmossa
-Backtimjan
-Dvärgjordstjärna
-Solvända
-Ängsstarr
-Murgröna
-Alvarmalört
-Grönvit nattviol
-Krutbrännare
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 27636-2023 artfynd.xlsx", "A 27636-2023")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 27636-2023 karta.png", "A 27636-2023")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 27636-2023 georefererad karta.tif", "A 27636-2023")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 27636-2023 FSC-klagomål.docx", "A 27636-2023")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 27636-2023 FSC-klagomål mail.docx", "A 27636-2023")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 27636-2023 tillsynsbegäran.docx", "A 27636-2023")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 27636-2023 tillsynsbegäran mail.docx", "A 27636-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 39320-2024</t>
+          <t>A 15600-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2837,10 +2837,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45551</v>
+        <v>45747</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2853,45 +2853,163 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
       </c>
       <c r="T19" t="n">
+        <v>20</v>
+      </c>
+      <c r="U19" t="n">
+        <v>18</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Kragjordstjärna
+Murgröna
+Scharlakansvårskål agg.
+Tibast
+Blåsippa
+Skärmstarr
+Spillkråka
+Storrams
+Röd glada</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 15600-2025 artfynd.xlsx", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 15600-2025 karta.png", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 15600-2025 georefererad karta.tif", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 15600-2025 FSC-klagomål.docx", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 15600-2025 FSC-klagomål mail.docx", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 15600-2025 tillsynsbegäran.docx", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 15600-2025 tillsynsbegäran mail.docx", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 15600-2025 prioriterade fågelarter.docx", "A 15600-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 39320-2024</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45551</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>4</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>7</v>
+      </c>
+      <c r="R20" t="n">
+        <v>3</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="n">
         <v>11</v>
       </c>
-      <c r="U19" t="n">
+      <c r="U20" t="n">
         <v>10</v>
       </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Vresalm
 Lundalm
@@ -2905,150 +3023,32 @@
 Skogsduva</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 39320-2024 artfynd.xlsx", "A 39320-2024")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 39320-2024 karta.png", "A 39320-2024")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 39320-2024 georefererad karta.tif", "A 39320-2024")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 39320-2024 FSC-klagomål.docx", "A 39320-2024")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 39320-2024 FSC-klagomål mail.docx", "A 39320-2024")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 39320-2024 tillsynsbegäran.docx", "A 39320-2024")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 39320-2024 tillsynsbegäran mail.docx", "A 39320-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 15600-2025</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45747</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46310</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J20" t="n">
-        <v>3</v>
-      </c>
-      <c r="K20" t="n">
-        <v>4</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>1</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1</v>
-      </c>
-      <c r="S20" t="n">
-        <v>10</v>
-      </c>
-      <c r="T20" t="n">
-        <v>20</v>
-      </c>
-      <c r="U20" t="n">
-        <v>18</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Kragjordstjärna
-Murgröna
-Scharlakansvårskål agg.
-Tibast
-Blåsippa
-Skärmstarr
-Spillkråka
-Storrams
-Röd glada</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 15600-2025 artfynd.xlsx", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 15600-2025 karta.png", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 15600-2025 georefererad karta.tif", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 15600-2025 FSC-klagomål.docx", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 15600-2025 FSC-klagomål mail.docx", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 15600-2025 tillsynsbegäran.docx", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 15600-2025 tillsynsbegäran mail.docx", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 15600-2025 prioriterade fågelarter.docx", "A 15600-2025")</f>
         <v/>
       </c>
     </row>
@@ -3072,7 +3072,7 @@
         <v>44616</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>45000</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>45530</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>45223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         <v>45075</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45169</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 43704-2025</t>
+          <t>A 43714-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3758,7 +3758,7 @@
         <v>45912</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3771,19 +3771,19 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.7</v>
+        <v>7.9</v>
       </c>
       <c r="J27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3795,21 +3795,135 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S27" t="n">
         <v>6</v>
       </c>
       <c r="T27" t="n">
+        <v>8</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Mindre bastardsvärmare
+Sexfläckig bastardsvärmare
+Grönsångare
+Murgröna
+Tibast
+Trädporella</t>
+        </is>
+      </c>
+      <c r="W27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43714-2025 artfynd.xlsx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="X27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43714-2025 karta.png", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="Y27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43714-2025 georefererad karta.tif", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AA27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43714-2025 FSC-klagomål.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AB27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43714-2025 FSC-klagomål mail.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AC27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43714-2025 tillsynsbegäran.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AD27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43714-2025 tillsynsbegäran mail.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 43714-2025 prioriterade fågelarter.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A 43704-2025</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>45912</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J28" t="n">
+        <v>5</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
         <v>6</v>
       </c>
-      <c r="U27" t="n">
-        <v>1</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="T28" t="n">
+        <v>6</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>Blomkålssvamp
 Långbensgroda
@@ -3819,146 +3933,32 @@
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W27">
+      <c r="W28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43704-2025 artfynd.xlsx", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="X27">
+      <c r="X28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43704-2025 karta.png", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="Y27">
+      <c r="Y28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43704-2025 georefererad karta.tif", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="AA27">
+      <c r="AA28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43704-2025 FSC-klagomål.docx", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="AB27">
+      <c r="AB28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43704-2025 FSC-klagomål mail.docx", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="AC27">
+      <c r="AC28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43704-2025 tillsynsbegäran.docx", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="AD27">
+      <c r="AD28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43704-2025 tillsynsbegäran mail.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>A 43714-2025</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>45912</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>46310</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="J28" t="n">
-        <v>1</v>
-      </c>
-      <c r="K28" t="n">
-        <v>3</v>
-      </c>
-      <c r="L28" t="n">
-        <v>1</v>
-      </c>
-      <c r="M28" t="n">
-        <v>2</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>3</v>
-      </c>
-      <c r="R28" t="n">
-        <v>2</v>
-      </c>
-      <c r="S28" t="n">
-        <v>6</v>
-      </c>
-      <c r="T28" t="n">
-        <v>8</v>
-      </c>
-      <c r="U28" t="n">
-        <v>2</v>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>Mindre bastardsvärmare
-Sexfläckig bastardsvärmare
-Grönsångare
-Murgröna
-Tibast
-Trädporella</t>
-        </is>
-      </c>
-      <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43714-2025 artfynd.xlsx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43714-2025 karta.png", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43714-2025 georefererad karta.tif", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43714-2025 FSC-klagomål.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43714-2025 FSC-klagomål mail.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43714-2025 tillsynsbegäran.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43714-2025 tillsynsbegäran mail.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 43714-2025 prioriterade fågelarter.docx", "A 43714-2025")</f>
         <v/>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
         <v>46190</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>46003</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>46038</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>45616</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 26440-2026</t>
+          <t>A 19459-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4423,10 +4423,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46183</v>
+        <v>45049</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4439,16 +4439,16 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -4463,7 +4463,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -4472,12 +4472,120 @@
         <v>4</v>
       </c>
       <c r="T33" t="n">
+        <v>4</v>
+      </c>
+      <c r="U33" t="n">
+        <v>4</v>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>Kavelhirs
+Kösa
+Luddvicker
+Riddarsporre</t>
+        </is>
+      </c>
+      <c r="W33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 19459-2023 artfynd.xlsx", "A 19459-2023")</f>
+        <v/>
+      </c>
+      <c r="X33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 19459-2023 karta.png", "A 19459-2023")</f>
+        <v/>
+      </c>
+      <c r="Y33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 19459-2023 georefererad karta.tif", "A 19459-2023")</f>
+        <v/>
+      </c>
+      <c r="AA33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 19459-2023 FSC-klagomål.docx", "A 19459-2023")</f>
+        <v/>
+      </c>
+      <c r="AB33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 19459-2023 FSC-klagomål mail.docx", "A 19459-2023")</f>
+        <v/>
+      </c>
+      <c r="AC33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 19459-2023 tillsynsbegäran.docx", "A 19459-2023")</f>
+        <v/>
+      </c>
+      <c r="AD33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 19459-2023 tillsynsbegäran mail.docx", "A 19459-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>A 26440-2026</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="E34" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>4</v>
+      </c>
+      <c r="T34" t="n">
         <v>5</v>
       </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>Backstarr
 Murgröna
@@ -4485,140 +4593,32 @@
 Vätteros</t>
         </is>
       </c>
-      <c r="W33">
+      <c r="W34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 26440-2026 artfynd.xlsx", "A 26440-2026")</f>
         <v/>
       </c>
-      <c r="X33">
+      <c r="X34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 26440-2026 karta.png", "A 26440-2026")</f>
         <v/>
       </c>
-      <c r="Y33">
+      <c r="Y34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 26440-2026 georefererad karta.tif", "A 26440-2026")</f>
         <v/>
       </c>
-      <c r="AA33">
+      <c r="AA34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 26440-2026 FSC-klagomål.docx", "A 26440-2026")</f>
         <v/>
       </c>
-      <c r="AB33">
+      <c r="AB34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 26440-2026 FSC-klagomål mail.docx", "A 26440-2026")</f>
         <v/>
       </c>
-      <c r="AC33">
+      <c r="AC34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 26440-2026 tillsynsbegäran.docx", "A 26440-2026")</f>
         <v/>
       </c>
-      <c r="AD33">
+      <c r="AD34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 26440-2026 tillsynsbegäran mail.docx", "A 26440-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>A 19459-2023</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="n">
-        <v>45049</v>
-      </c>
-      <c r="E34" s="1" t="n">
-        <v>46310</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>4</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>4</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>4</v>
-      </c>
-      <c r="T34" t="n">
-        <v>4</v>
-      </c>
-      <c r="U34" t="n">
-        <v>4</v>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>Kavelhirs
-Kösa
-Luddvicker
-Riddarsporre</t>
-        </is>
-      </c>
-      <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 19459-2023 artfynd.xlsx", "A 19459-2023")</f>
-        <v/>
-      </c>
-      <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 19459-2023 karta.png", "A 19459-2023")</f>
-        <v/>
-      </c>
-      <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 19459-2023 georefererad karta.tif", "A 19459-2023")</f>
-        <v/>
-      </c>
-      <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 19459-2023 FSC-klagomål.docx", "A 19459-2023")</f>
-        <v/>
-      </c>
-      <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 19459-2023 FSC-klagomål mail.docx", "A 19459-2023")</f>
-        <v/>
-      </c>
-      <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 19459-2023 tillsynsbegäran.docx", "A 19459-2023")</f>
-        <v/>
-      </c>
-      <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 19459-2023 tillsynsbegäran mail.docx", "A 19459-2023")</f>
         <v/>
       </c>
     </row>
@@ -4642,7 +4642,7 @@
         <v>46254</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>45912</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>46203</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 62231-2023</t>
+          <t>A 72167-2021</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4961,14 +4961,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45267</v>
+        <v>44544</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J38" t="n">
         <v>1</v>
@@ -5022,42 +5022,46 @@
       <c r="V38" s="2" t="inlineStr">
         <is>
           <t>Murgröna
-Blåsippa</t>
+Röd glada</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62231-2023 artfynd.xlsx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 72167-2021 artfynd.xlsx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62231-2023 karta.png", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 72167-2021 karta.png", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62231-2023 georefererad karta.tif", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 72167-2021 georefererad karta.tif", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62231-2023 FSC-klagomål.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 72167-2021 FSC-klagomål.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62231-2023 FSC-klagomål mail.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 72167-2021 FSC-klagomål mail.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62231-2023 tillsynsbegäran.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 72167-2021 tillsynsbegäran.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62231-2023 tillsynsbegäran mail.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 72167-2021 tillsynsbegäran mail.docx", "A 72167-2021")</f>
+        <v/>
+      </c>
+      <c r="AE38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 72167-2021 prioriterade fågelarter.docx", "A 72167-2021")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 72167-2021</t>
+          <t>A 62231-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5067,14 +5071,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44544</v>
+        <v>45267</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5087,7 +5091,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J39" t="n">
         <v>1</v>
@@ -5128,39 +5132,35 @@
       <c r="V39" s="2" t="inlineStr">
         <is>
           <t>Murgröna
-Röd glada</t>
+Blåsippa</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 72167-2021 artfynd.xlsx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62231-2023 artfynd.xlsx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 72167-2021 karta.png", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62231-2023 karta.png", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 72167-2021 georefererad karta.tif", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62231-2023 georefererad karta.tif", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 72167-2021 FSC-klagomål.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62231-2023 FSC-klagomål.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 72167-2021 FSC-klagomål mail.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62231-2023 FSC-klagomål mail.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 72167-2021 tillsynsbegäran.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62231-2023 tillsynsbegäran.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 72167-2021 tillsynsbegäran mail.docx", "A 72167-2021")</f>
-        <v/>
-      </c>
-      <c r="AE39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 72167-2021 prioriterade fågelarter.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62231-2023 tillsynsbegäran mail.docx", "A 62231-2023")</f>
         <v/>
       </c>
     </row>
@@ -5184,7 +5184,7 @@
         <v>46246</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>45084</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 62183-2025</t>
+          <t>A 13040-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5388,14 +5388,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46006</v>
+        <v>45385</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -5417,13 +5417,13 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5435,7 +5435,7 @@
         <v>1</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -5444,46 +5444,46 @@
         <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62183-2025 artfynd.xlsx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13040-2024 artfynd.xlsx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62183-2025 karta.png", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13040-2024 karta.png", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62183-2025 georefererad karta.tif", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13040-2024 georefererad karta.tif", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62183-2025 FSC-klagomål.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13040-2024 FSC-klagomål.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62183-2025 FSC-klagomål mail.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13040-2024 FSC-klagomål mail.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62183-2025 tillsynsbegäran.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13040-2024 tillsynsbegäran.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62183-2025 tillsynsbegäran mail.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13040-2024 tillsynsbegäran mail.docx", "A 13040-2024")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 13040-2024</t>
+          <t>A 13384-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5493,14 +5493,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45385</v>
+        <v>45005</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5513,10 +5513,10 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -5528,7 +5528,7 @@
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5537,10 +5537,10 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5553,42 +5553,42 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13040-2024 artfynd.xlsx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13384-2023 artfynd.xlsx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13040-2024 karta.png", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13384-2023 karta.png", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13040-2024 georefererad karta.tif", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13384-2023 georefererad karta.tif", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13040-2024 FSC-klagomål.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13384-2023 FSC-klagomål.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13040-2024 FSC-klagomål mail.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13384-2023 FSC-klagomål mail.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13040-2024 tillsynsbegäran.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13384-2023 tillsynsbegäran.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13040-2024 tillsynsbegäran mail.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13384-2023 tillsynsbegäran mail.docx", "A 13384-2023")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 13384-2023</t>
+          <t>A 30492-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5598,14 +5598,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45005</v>
+        <v>46210</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5618,16 +5618,16 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -5642,7 +5642,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -5654,46 +5654,46 @@
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13384-2023 artfynd.xlsx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 30492-2026 artfynd.xlsx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13384-2023 karta.png", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 30492-2026 karta.png", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13384-2023 georefererad karta.tif", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 30492-2026 georefererad karta.tif", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13384-2023 FSC-klagomål.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 30492-2026 FSC-klagomål.docx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13384-2023 FSC-klagomål mail.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 30492-2026 FSC-klagomål mail.docx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13384-2023 tillsynsbegäran.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 30492-2026 tillsynsbegäran.docx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13384-2023 tillsynsbegäran mail.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 30492-2026 tillsynsbegäran mail.docx", "A 30492-2026")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 30492-2026</t>
+          <t>A 36928-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5703,14 +5703,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46210</v>
+        <v>46273</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5723,16 +5723,16 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -5747,7 +5747,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -5763,42 +5763,42 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 30492-2026 artfynd.xlsx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 36928-2026 artfynd.xlsx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 30492-2026 karta.png", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 36928-2026 karta.png", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 30492-2026 georefererad karta.tif", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 36928-2026 georefererad karta.tif", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 30492-2026 FSC-klagomål.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 36928-2026 FSC-klagomål.docx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 30492-2026 FSC-klagomål mail.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 36928-2026 FSC-klagomål mail.docx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 30492-2026 tillsynsbegäran.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 36928-2026 tillsynsbegäran.docx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 30492-2026 tillsynsbegäran mail.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 36928-2026 tillsynsbegäran mail.docx", "A 36928-2026")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 36928-2026</t>
+          <t>A 62183-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46273</v>
+        <v>46006</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5828,16 +5828,16 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -5852,7 +5852,7 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -5868,35 +5868,35 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 36928-2026 artfynd.xlsx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62183-2025 artfynd.xlsx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 36928-2026 karta.png", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62183-2025 karta.png", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 36928-2026 georefererad karta.tif", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62183-2025 georefererad karta.tif", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 36928-2026 FSC-klagomål.docx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62183-2025 FSC-klagomål.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 36928-2026 FSC-klagomål mail.docx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62183-2025 FSC-klagomål mail.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 36928-2026 tillsynsbegäran.docx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62183-2025 tillsynsbegäran.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 36928-2026 tillsynsbegäran mail.docx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62183-2025 tillsynsbegäran mail.docx", "A 62183-2025")</f>
         <v/>
       </c>
     </row>
@@ -5920,7 +5920,7 @@
         <v>44740</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         <v>45980</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>46171</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>

--- a/Översikt MÖRBYLÅNGA.xlsx
+++ b/Översikt MÖRBYLÅNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44964</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>44655</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>45177</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45096</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45685</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>46289</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>45475</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>45062</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>46195</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>46189</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>45254</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>45062</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>44508</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>44811</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>45097</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>44728</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>45999</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 15600-2025</t>
+          <t>A 39320-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2837,10 +2837,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45747</v>
+        <v>45551</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2853,45 +2853,159 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>4</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>7</v>
+      </c>
+      <c r="R19" t="n">
         <v>3</v>
-      </c>
-      <c r="K19" t="n">
-        <v>4</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>1</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
       </c>
       <c r="T19" t="n">
+        <v>11</v>
+      </c>
+      <c r="U19" t="n">
+        <v>10</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Vresalm
+Lundalm
+Toppjungfrulin
+Gulprickig vaxskivling
+Korskovall
+Sårläka
+Vårärt
+Strävlosta
+Underviol
+Skogsduva</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 39320-2024 artfynd.xlsx", "A 39320-2024")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 39320-2024 karta.png", "A 39320-2024")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 39320-2024 georefererad karta.tif", "A 39320-2024")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 39320-2024 FSC-klagomål.docx", "A 39320-2024")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 39320-2024 FSC-klagomål mail.docx", "A 39320-2024")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 39320-2024 tillsynsbegäran.docx", "A 39320-2024")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 39320-2024 tillsynsbegäran mail.docx", "A 39320-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 15600-2025</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45747</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46312</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="n">
         <v>20</v>
       </c>
-      <c r="U19" t="n">
+      <c r="U20" t="n">
         <v>18</v>
       </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Ask
 Kragjordstjärna
@@ -2905,150 +3019,36 @@
 Röd glada</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 15600-2025 artfynd.xlsx", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 15600-2025 karta.png", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 15600-2025 georefererad karta.tif", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 15600-2025 FSC-klagomål.docx", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 15600-2025 FSC-klagomål mail.docx", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 15600-2025 tillsynsbegäran.docx", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 15600-2025 tillsynsbegäran mail.docx", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="AE19">
+      <c r="AE20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 15600-2025 prioriterade fågelarter.docx", "A 15600-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 39320-2024</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45551</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46311</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>2</v>
-      </c>
-      <c r="L20" t="n">
-        <v>4</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N20" t="n">
-        <v>1</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>7</v>
-      </c>
-      <c r="R20" t="n">
-        <v>3</v>
-      </c>
-      <c r="S20" t="n">
-        <v>10</v>
-      </c>
-      <c r="T20" t="n">
-        <v>11</v>
-      </c>
-      <c r="U20" t="n">
-        <v>10</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Vresalm
-Lundalm
-Toppjungfrulin
-Gulprickig vaxskivling
-Korskovall
-Sårläka
-Vårärt
-Strävlosta
-Underviol
-Skogsduva</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 39320-2024 artfynd.xlsx", "A 39320-2024")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 39320-2024 karta.png", "A 39320-2024")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 39320-2024 georefererad karta.tif", "A 39320-2024")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 39320-2024 FSC-klagomål.docx", "A 39320-2024")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 39320-2024 FSC-klagomål mail.docx", "A 39320-2024")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 39320-2024 tillsynsbegäran.docx", "A 39320-2024")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 39320-2024 tillsynsbegäran mail.docx", "A 39320-2024")</f>
         <v/>
       </c>
     </row>
@@ -3072,7 +3072,7 @@
         <v>44616</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>45000</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>45530</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>45223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         <v>45075</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45169</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 43714-2025</t>
+          <t>A 43704-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3758,7 +3758,7 @@
         <v>45912</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3771,19 +3771,19 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>7.9</v>
+        <v>2.7</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3795,21 +3795,131 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>6</v>
       </c>
       <c r="T27" t="n">
+        <v>6</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp
+Långbensgroda
+Större vattensalamander
+Åkergroda
+Mindre vattensalamander
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43704-2025 artfynd.xlsx", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="X27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43704-2025 karta.png", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="Y27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43704-2025 georefererad karta.tif", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="AA27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43704-2025 FSC-klagomål.docx", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="AB27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43704-2025 FSC-klagomål mail.docx", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="AC27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43704-2025 tillsynsbegäran.docx", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="AD27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43704-2025 tillsynsbegäran mail.docx", "A 43704-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A 43714-2025</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>45912</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>46312</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" t="n">
+        <v>2</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2</v>
+      </c>
+      <c r="S28" t="n">
+        <v>6</v>
+      </c>
+      <c r="T28" t="n">
         <v>8</v>
       </c>
-      <c r="U27" t="n">
+      <c r="U28" t="n">
         <v>2</v>
       </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>Mindre bastardsvärmare
 Sexfläckig bastardsvärmare
@@ -3819,146 +3929,36 @@
 Trädporella</t>
         </is>
       </c>
-      <c r="W27">
+      <c r="W28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43714-2025 artfynd.xlsx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="X27">
+      <c r="X28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43714-2025 karta.png", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="Y27">
+      <c r="Y28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43714-2025 georefererad karta.tif", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AA27">
+      <c r="AA28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43714-2025 FSC-klagomål.docx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AB27">
+      <c r="AB28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43714-2025 FSC-klagomål mail.docx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AC27">
+      <c r="AC28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43714-2025 tillsynsbegäran.docx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AD27">
+      <c r="AD28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43714-2025 tillsynsbegäran mail.docx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AE27">
+      <c r="AE28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 43714-2025 prioriterade fågelarter.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>A 43704-2025</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>45912</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>46311</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J28" t="n">
-        <v>5</v>
-      </c>
-      <c r="K28" t="n">
-        <v>1</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>6</v>
-      </c>
-      <c r="T28" t="n">
-        <v>6</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1</v>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>Blomkålssvamp
-Långbensgroda
-Större vattensalamander
-Åkergroda
-Mindre vattensalamander
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43704-2025 artfynd.xlsx", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43704-2025 karta.png", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43704-2025 georefererad karta.tif", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43704-2025 FSC-klagomål.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43704-2025 FSC-klagomål mail.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43704-2025 tillsynsbegäran.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43704-2025 tillsynsbegäran mail.docx", "A 43704-2025")</f>
         <v/>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
         <v>46190</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>46003</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>46038</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>45616</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>45049</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>46183</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>46254</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>45912</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>46203</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 72167-2021</t>
+          <t>A 62231-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4961,14 +4961,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44544</v>
+        <v>45267</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J38" t="n">
         <v>1</v>
@@ -5022,46 +5022,42 @@
       <c r="V38" s="2" t="inlineStr">
         <is>
           <t>Murgröna
-Röd glada</t>
+Blåsippa</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 72167-2021 artfynd.xlsx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62231-2023 artfynd.xlsx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 72167-2021 karta.png", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62231-2023 karta.png", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 72167-2021 georefererad karta.tif", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62231-2023 georefererad karta.tif", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 72167-2021 FSC-klagomål.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62231-2023 FSC-klagomål.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 72167-2021 FSC-klagomål mail.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62231-2023 FSC-klagomål mail.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 72167-2021 tillsynsbegäran.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62231-2023 tillsynsbegäran.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 72167-2021 tillsynsbegäran mail.docx", "A 72167-2021")</f>
-        <v/>
-      </c>
-      <c r="AE38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 72167-2021 prioriterade fågelarter.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62231-2023 tillsynsbegäran mail.docx", "A 62231-2023")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 62231-2023</t>
+          <t>A 72167-2021</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5071,14 +5067,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45267</v>
+        <v>44544</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5091,7 +5087,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J39" t="n">
         <v>1</v>
@@ -5132,35 +5128,39 @@
       <c r="V39" s="2" t="inlineStr">
         <is>
           <t>Murgröna
-Blåsippa</t>
+Röd glada</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62231-2023 artfynd.xlsx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 72167-2021 artfynd.xlsx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62231-2023 karta.png", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 72167-2021 karta.png", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62231-2023 georefererad karta.tif", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 72167-2021 georefererad karta.tif", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62231-2023 FSC-klagomål.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 72167-2021 FSC-klagomål.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62231-2023 FSC-klagomål mail.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 72167-2021 FSC-klagomål mail.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62231-2023 tillsynsbegäran.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 72167-2021 tillsynsbegäran.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62231-2023 tillsynsbegäran mail.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 72167-2021 tillsynsbegäran mail.docx", "A 72167-2021")</f>
+        <v/>
+      </c>
+      <c r="AE39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 72167-2021 prioriterade fågelarter.docx", "A 72167-2021")</f>
         <v/>
       </c>
     </row>
@@ -5184,7 +5184,7 @@
         <v>46246</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 24698-2023</t>
+          <t>A 13040-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5283,14 +5283,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45084</v>
+        <v>45385</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>5.5</v>
+        <v>1.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -5312,13 +5312,13 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5330,7 +5330,7 @@
         <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -5343,42 +5343,42 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24698-2023 artfynd.xlsx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13040-2024 artfynd.xlsx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24698-2023 karta.png", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13040-2024 karta.png", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24698-2023 georefererad karta.tif", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13040-2024 georefererad karta.tif", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24698-2023 FSC-klagomål.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13040-2024 FSC-klagomål.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24698-2023 FSC-klagomål mail.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13040-2024 FSC-klagomål mail.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24698-2023 tillsynsbegäran.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13040-2024 tillsynsbegäran.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24698-2023 tillsynsbegäran mail.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13040-2024 tillsynsbegäran mail.docx", "A 13040-2024")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 13040-2024</t>
+          <t>A 62183-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5388,14 +5388,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45385</v>
+        <v>46006</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -5417,13 +5417,13 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5435,7 +5435,7 @@
         <v>1</v>
       </c>
       <c r="R42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -5444,39 +5444,39 @@
         <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13040-2024 artfynd.xlsx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62183-2025 artfynd.xlsx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13040-2024 karta.png", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62183-2025 karta.png", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13040-2024 georefererad karta.tif", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62183-2025 georefererad karta.tif", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13040-2024 FSC-klagomål.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62183-2025 FSC-klagomål.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13040-2024 FSC-klagomål mail.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62183-2025 FSC-klagomål mail.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13040-2024 tillsynsbegäran.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62183-2025 tillsynsbegäran.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13040-2024 tillsynsbegäran mail.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62183-2025 tillsynsbegäran mail.docx", "A 62183-2025")</f>
         <v/>
       </c>
     </row>
@@ -5500,7 +5500,7 @@
         <v>45005</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         <v>46210</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5710,7 +5710,7 @@
         <v>46273</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 62183-2025</t>
+          <t>A 24698-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46006</v>
+        <v>45084</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.8</v>
+        <v>5.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5864,39 +5864,39 @@
         <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62183-2025 artfynd.xlsx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24698-2023 artfynd.xlsx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62183-2025 karta.png", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24698-2023 karta.png", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62183-2025 georefererad karta.tif", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24698-2023 georefererad karta.tif", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62183-2025 FSC-klagomål.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24698-2023 FSC-klagomål.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62183-2025 FSC-klagomål mail.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24698-2023 FSC-klagomål mail.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62183-2025 tillsynsbegäran.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24698-2023 tillsynsbegäran.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62183-2025 tillsynsbegäran mail.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24698-2023 tillsynsbegäran mail.docx", "A 24698-2023")</f>
         <v/>
       </c>
     </row>
@@ -5920,7 +5920,7 @@
         <v>44740</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         <v>45980</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>46171</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>

--- a/Översikt MÖRBYLÅNGA.xlsx
+++ b/Översikt MÖRBYLÅNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44964</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>44655</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>45177</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45096</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45685</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>46289</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>45475</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>45062</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>46195</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>46189</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>45254</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>45062</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>44508</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>44811</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>45097</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>44728</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>45999</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>45551</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>45747</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>44616</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>45000</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>45530</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>45223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         <v>45075</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45169</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>45912</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>45912</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>46190</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>46003</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>46038</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>45616</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>45049</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>46183</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>46254</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>45912</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>46203</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>45267</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         <v>44544</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         <v>46246</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>45385</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>46006</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
         <v>45005</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         <v>46210</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5710,7 +5710,7 @@
         <v>46273</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>45084</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>44740</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         <v>45980</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>46171</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>

--- a/Översikt MÖRBYLÅNGA.xlsx
+++ b/Översikt MÖRBYLÅNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44964</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>44655</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>45177</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45096</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45685</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>46289</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>45475</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>45062</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>46195</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>46189</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>45254</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>45062</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>44508</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>44811</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>45097</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>44728</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>45999</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>45551</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>45747</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>44616</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>45000</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>45530</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>45223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         <v>45075</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45169</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>45912</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>45912</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>46190</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>46003</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>46038</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>45616</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>45049</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>46183</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>46254</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>45912</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>46203</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>45267</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         <v>44544</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         <v>46246</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>45385</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>46006</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
         <v>45005</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         <v>46210</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5710,7 +5710,7 @@
         <v>46273</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>45084</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>44740</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         <v>45980</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>46171</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>

--- a/Översikt MÖRBYLÅNGA.xlsx
+++ b/Översikt MÖRBYLÅNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44964</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>44655</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>45177</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45096</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45685</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>46289</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>45475</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>45062</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>46195</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>46189</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>45254</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>45062</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>44508</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 38039-2022</t>
+          <t>A 60875-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2369,14 +2369,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44811</v>
+        <v>45999</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2389,31 +2389,31 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>7.4</v>
+        <v>2.1</v>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R15" t="n">
         <v>2</v>
@@ -2422,12 +2422,131 @@
         <v>11</v>
       </c>
       <c r="T15" t="n">
+        <v>12</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Järnek
+Mosippa
+Grönsångare
+Gulsparv
+Göktyta
+Mindre hackspett
+Svinrot
+Murgröna
+Spillkråka
+Kråka
+Skogsduva</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 60875-2025 artfynd.xlsx", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 60875-2025 karta.png", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 60875-2025 georefererad karta.tif", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 60875-2025 FSC-klagomål.docx", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 60875-2025 FSC-klagomål mail.docx", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 60875-2025 tillsynsbegäran.docx", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 60875-2025 tillsynsbegäran mail.docx", "A 60875-2025")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 60875-2025 prioriterade fågelarter.docx", "A 60875-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 38039-2022</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>44811</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>4</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>6</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2</v>
+      </c>
+      <c r="S16" t="n">
+        <v>11</v>
+      </c>
+      <c r="T16" t="n">
         <v>13</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U16" t="n">
         <v>12</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Ask
 Grov gulmossa
@@ -2442,107 +2561,107 @@
 Gullviva</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 38039-2022 artfynd.xlsx", "A 38039-2022")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 38039-2022 karta.png", "A 38039-2022")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 38039-2022 georefererad karta.tif", "A 38039-2022")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 38039-2022 FSC-klagomål.docx", "A 38039-2022")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 38039-2022 FSC-klagomål mail.docx", "A 38039-2022")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 38039-2022 tillsynsbegäran.docx", "A 38039-2022")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 38039-2022 tillsynsbegäran mail.docx", "A 38039-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>A 27636-2023</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D16" s="1" t="n">
+      <c r="D17" s="1" t="n">
         <v>45097</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="E17" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I16" t="n">
+      <c r="I17" t="n">
         <v>7.4</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J17" t="n">
         <v>4</v>
       </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
         <v>4</v>
       </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>6</v>
       </c>
-      <c r="R16" t="n">
+      <c r="R17" t="n">
         <v>2</v>
       </c>
-      <c r="S16" t="n">
+      <c r="S17" t="n">
         <v>11</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T17" t="n">
         <v>13</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U17" t="n">
         <v>11</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Ask
 Grov gulmossa
@@ -2557,107 +2676,107 @@
 Gullviva</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 27636-2023 artfynd.xlsx", "A 27636-2023")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 27636-2023 karta.png", "A 27636-2023")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 27636-2023 georefererad karta.tif", "A 27636-2023")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 27636-2023 FSC-klagomål.docx", "A 27636-2023")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 27636-2023 FSC-klagomål mail.docx", "A 27636-2023")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 27636-2023 tillsynsbegäran.docx", "A 27636-2023")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 27636-2023 tillsynsbegäran mail.docx", "A 27636-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>A 24778-2022</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D17" s="1" t="n">
+      <c r="D18" s="1" t="n">
         <v>44728</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F17" t="inlineStr">
+      <c r="E18" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>KALMAR LÄN</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>MÖRBYLÅNGA</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
         <v>2</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L18" t="n">
         <v>7</v>
       </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
         <v>8</v>
       </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
         <v>11</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T18" t="n">
         <v>20</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U18" t="n">
         <v>20</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Tofsäxing
 Backtimjan
@@ -2672,158 +2791,39 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24778-2022 artfynd.xlsx", "A 24778-2022")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24778-2022 karta.png", "A 24778-2022")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24778-2022 georefererad karta.tif", "A 24778-2022")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24778-2022 FSC-klagomål.docx", "A 24778-2022")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24778-2022 FSC-klagomål mail.docx", "A 24778-2022")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24778-2022 tillsynsbegäran.docx", "A 24778-2022")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24778-2022 tillsynsbegäran mail.docx", "A 24778-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 60875-2025</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45999</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J18" t="n">
-        <v>8</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>5</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>7</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2</v>
-      </c>
-      <c r="S18" t="n">
-        <v>11</v>
-      </c>
-      <c r="T18" t="n">
-        <v>12</v>
-      </c>
-      <c r="U18" t="n">
-        <v>3</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Järnek
-Mosippa
-Grönsångare
-Gulsparv
-Göktyta
-Mindre hackspett
-Svinrot
-Murgröna
-Spillkråka
-Kråka
-Skogsduva</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 60875-2025 artfynd.xlsx", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 60875-2025 karta.png", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 60875-2025 georefererad karta.tif", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 60875-2025 FSC-klagomål.docx", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 60875-2025 FSC-klagomål mail.docx", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 60875-2025 tillsynsbegäran.docx", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 60875-2025 tillsynsbegäran mail.docx", "A 60875-2025")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 60875-2025 prioriterade fågelarter.docx", "A 60875-2025")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 39320-2024</t>
+          <t>A 15600-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2837,10 +2837,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45551</v>
+        <v>45747</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2853,45 +2853,163 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
       </c>
       <c r="T19" t="n">
+        <v>20</v>
+      </c>
+      <c r="U19" t="n">
+        <v>18</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Kragjordstjärna
+Murgröna
+Scharlakansvårskål agg.
+Tibast
+Blåsippa
+Skärmstarr
+Spillkråka
+Storrams
+Röd glada</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 15600-2025 artfynd.xlsx", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 15600-2025 karta.png", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 15600-2025 georefererad karta.tif", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 15600-2025 FSC-klagomål.docx", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 15600-2025 FSC-klagomål mail.docx", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 15600-2025 tillsynsbegäran.docx", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 15600-2025 tillsynsbegäran mail.docx", "A 15600-2025")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 15600-2025 prioriterade fågelarter.docx", "A 15600-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 39320-2024</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45551</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>4</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>7</v>
+      </c>
+      <c r="R20" t="n">
+        <v>3</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="n">
         <v>11</v>
       </c>
-      <c r="U19" t="n">
+      <c r="U20" t="n">
         <v>10</v>
       </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Vresalm
 Lundalm
@@ -2905,150 +3023,32 @@
 Skogsduva</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 39320-2024 artfynd.xlsx", "A 39320-2024")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 39320-2024 karta.png", "A 39320-2024")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 39320-2024 georefererad karta.tif", "A 39320-2024")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 39320-2024 FSC-klagomål.docx", "A 39320-2024")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 39320-2024 FSC-klagomål mail.docx", "A 39320-2024")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 39320-2024 tillsynsbegäran.docx", "A 39320-2024")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 39320-2024 tillsynsbegäran mail.docx", "A 39320-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 15600-2025</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45747</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J20" t="n">
-        <v>3</v>
-      </c>
-      <c r="K20" t="n">
-        <v>4</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>1</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1</v>
-      </c>
-      <c r="S20" t="n">
-        <v>10</v>
-      </c>
-      <c r="T20" t="n">
-        <v>20</v>
-      </c>
-      <c r="U20" t="n">
-        <v>18</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Kragjordstjärna
-Murgröna
-Scharlakansvårskål agg.
-Tibast
-Blåsippa
-Skärmstarr
-Spillkråka
-Storrams
-Röd glada</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 15600-2025 artfynd.xlsx", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 15600-2025 karta.png", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 15600-2025 georefererad karta.tif", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 15600-2025 FSC-klagomål.docx", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 15600-2025 FSC-klagomål mail.docx", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 15600-2025 tillsynsbegäran.docx", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 15600-2025 tillsynsbegäran mail.docx", "A 15600-2025")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 15600-2025 prioriterade fågelarter.docx", "A 15600-2025")</f>
         <v/>
       </c>
     </row>
@@ -3072,7 +3072,7 @@
         <v>44616</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>45000</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>45530</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>45223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         <v>45075</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45169</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 43704-2025</t>
+          <t>A 43714-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3758,7 +3758,7 @@
         <v>45912</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3771,19 +3771,19 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.7</v>
+        <v>7.9</v>
       </c>
       <c r="J27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3795,21 +3795,135 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S27" t="n">
         <v>6</v>
       </c>
       <c r="T27" t="n">
+        <v>8</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Mindre bastardsvärmare
+Sexfläckig bastardsvärmare
+Grönsångare
+Murgröna
+Tibast
+Trädporella</t>
+        </is>
+      </c>
+      <c r="W27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43714-2025 artfynd.xlsx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="X27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43714-2025 karta.png", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="Y27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43714-2025 georefererad karta.tif", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AA27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43714-2025 FSC-klagomål.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AB27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43714-2025 FSC-klagomål mail.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AC27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43714-2025 tillsynsbegäran.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AD27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43714-2025 tillsynsbegäran mail.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 43714-2025 prioriterade fågelarter.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A 43704-2025</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>45912</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J28" t="n">
+        <v>5</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
         <v>6</v>
       </c>
-      <c r="U27" t="n">
-        <v>1</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="T28" t="n">
+        <v>6</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>Blomkålssvamp
 Långbensgroda
@@ -3819,146 +3933,32 @@
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W27">
+      <c r="W28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43704-2025 artfynd.xlsx", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="X27">
+      <c r="X28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43704-2025 karta.png", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="Y27">
+      <c r="Y28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43704-2025 georefererad karta.tif", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="AA27">
+      <c r="AA28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43704-2025 FSC-klagomål.docx", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="AB27">
+      <c r="AB28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43704-2025 FSC-klagomål mail.docx", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="AC27">
+      <c r="AC28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43704-2025 tillsynsbegäran.docx", "A 43704-2025")</f>
         <v/>
       </c>
-      <c r="AD27">
+      <c r="AD28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43704-2025 tillsynsbegäran mail.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>A 43714-2025</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>45912</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="J28" t="n">
-        <v>1</v>
-      </c>
-      <c r="K28" t="n">
-        <v>3</v>
-      </c>
-      <c r="L28" t="n">
-        <v>1</v>
-      </c>
-      <c r="M28" t="n">
-        <v>2</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>3</v>
-      </c>
-      <c r="R28" t="n">
-        <v>2</v>
-      </c>
-      <c r="S28" t="n">
-        <v>6</v>
-      </c>
-      <c r="T28" t="n">
-        <v>8</v>
-      </c>
-      <c r="U28" t="n">
-        <v>2</v>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>Mindre bastardsvärmare
-Sexfläckig bastardsvärmare
-Grönsångare
-Murgröna
-Tibast
-Trädporella</t>
-        </is>
-      </c>
-      <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43714-2025 artfynd.xlsx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43714-2025 karta.png", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43714-2025 georefererad karta.tif", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43714-2025 FSC-klagomål.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43714-2025 FSC-klagomål mail.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43714-2025 tillsynsbegäran.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43714-2025 tillsynsbegäran mail.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 43714-2025 prioriterade fågelarter.docx", "A 43714-2025")</f>
         <v/>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
         <v>46190</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>46003</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>46038</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>45616</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>45049</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>46183</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>46254</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>45912</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>46203</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 62231-2023</t>
+          <t>A 72167-2021</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4961,14 +4961,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45267</v>
+        <v>44544</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J38" t="n">
         <v>1</v>
@@ -5022,42 +5022,46 @@
       <c r="V38" s="2" t="inlineStr">
         <is>
           <t>Murgröna
-Blåsippa</t>
+Röd glada</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62231-2023 artfynd.xlsx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 72167-2021 artfynd.xlsx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62231-2023 karta.png", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 72167-2021 karta.png", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62231-2023 georefererad karta.tif", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 72167-2021 georefererad karta.tif", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62231-2023 FSC-klagomål.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 72167-2021 FSC-klagomål.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62231-2023 FSC-klagomål mail.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 72167-2021 FSC-klagomål mail.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62231-2023 tillsynsbegäran.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 72167-2021 tillsynsbegäran.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62231-2023 tillsynsbegäran mail.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 72167-2021 tillsynsbegäran mail.docx", "A 72167-2021")</f>
+        <v/>
+      </c>
+      <c r="AE38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 72167-2021 prioriterade fågelarter.docx", "A 72167-2021")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 72167-2021</t>
+          <t>A 62231-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5067,14 +5071,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44544</v>
+        <v>45267</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5087,7 +5091,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J39" t="n">
         <v>1</v>
@@ -5128,39 +5132,35 @@
       <c r="V39" s="2" t="inlineStr">
         <is>
           <t>Murgröna
-Röd glada</t>
+Blåsippa</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 72167-2021 artfynd.xlsx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62231-2023 artfynd.xlsx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 72167-2021 karta.png", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62231-2023 karta.png", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 72167-2021 georefererad karta.tif", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62231-2023 georefererad karta.tif", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 72167-2021 FSC-klagomål.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62231-2023 FSC-klagomål.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 72167-2021 FSC-klagomål mail.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62231-2023 FSC-klagomål mail.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 72167-2021 tillsynsbegäran.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62231-2023 tillsynsbegäran.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 72167-2021 tillsynsbegäran mail.docx", "A 72167-2021")</f>
-        <v/>
-      </c>
-      <c r="AE39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 72167-2021 prioriterade fågelarter.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62231-2023 tillsynsbegäran mail.docx", "A 62231-2023")</f>
         <v/>
       </c>
     </row>
@@ -5184,7 +5184,7 @@
         <v>46246</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>45385</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 62183-2025</t>
+          <t>A 13384-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5392,10 +5392,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46006</v>
+        <v>45005</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5408,16 +5408,16 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -5432,7 +5432,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -5444,46 +5444,46 @@
         <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62183-2025 artfynd.xlsx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13384-2023 artfynd.xlsx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62183-2025 karta.png", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13384-2023 karta.png", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62183-2025 georefererad karta.tif", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13384-2023 georefererad karta.tif", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62183-2025 FSC-klagomål.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13384-2023 FSC-klagomål.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62183-2025 FSC-klagomål mail.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13384-2023 FSC-klagomål mail.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62183-2025 tillsynsbegäran.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13384-2023 tillsynsbegäran.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62183-2025 tillsynsbegäran mail.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13384-2023 tillsynsbegäran mail.docx", "A 13384-2023")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 13384-2023</t>
+          <t>A 62183-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5497,10 +5497,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45005</v>
+        <v>46006</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5513,16 +5513,16 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -5537,7 +5537,7 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -5549,39 +5549,39 @@
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13384-2023 artfynd.xlsx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62183-2025 artfynd.xlsx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13384-2023 karta.png", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62183-2025 karta.png", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13384-2023 georefererad karta.tif", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62183-2025 georefererad karta.tif", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13384-2023 FSC-klagomål.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62183-2025 FSC-klagomål.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13384-2023 FSC-klagomål mail.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62183-2025 FSC-klagomål mail.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13384-2023 tillsynsbegäran.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62183-2025 tillsynsbegäran.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13384-2023 tillsynsbegäran mail.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62183-2025 tillsynsbegäran mail.docx", "A 62183-2025")</f>
         <v/>
       </c>
     </row>
@@ -5605,7 +5605,7 @@
         <v>46210</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5710,7 +5710,7 @@
         <v>46273</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>45084</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>44740</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         <v>45980</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>46171</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>

--- a/Översikt MÖRBYLÅNGA.xlsx
+++ b/Översikt MÖRBYLÅNGA.xlsx
@@ -601,7 +601,7 @@
         <v>44964</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>44655</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>45177</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45096</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45685</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>46289</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>45475</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>45062</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>46195</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>46189</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>45254</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>45062</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>44508</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>45999</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>44811</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>45097</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>44728</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 15600-2025</t>
+          <t>A 39320-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2837,10 +2837,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45747</v>
+        <v>45551</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2853,45 +2853,159 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>4</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>7</v>
+      </c>
+      <c r="R19" t="n">
         <v>3</v>
-      </c>
-      <c r="K19" t="n">
-        <v>4</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>1</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
       </c>
       <c r="T19" t="n">
+        <v>11</v>
+      </c>
+      <c r="U19" t="n">
+        <v>10</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Vresalm
+Lundalm
+Toppjungfrulin
+Gulprickig vaxskivling
+Korskovall
+Sårläka
+Vårärt
+Strävlosta
+Underviol
+Skogsduva</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 39320-2024 artfynd.xlsx", "A 39320-2024")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 39320-2024 karta.png", "A 39320-2024")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 39320-2024 georefererad karta.tif", "A 39320-2024")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 39320-2024 FSC-klagomål.docx", "A 39320-2024")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 39320-2024 FSC-klagomål mail.docx", "A 39320-2024")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 39320-2024 tillsynsbegäran.docx", "A 39320-2024")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 39320-2024 tillsynsbegäran mail.docx", "A 39320-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 15600-2025</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45747</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="n">
         <v>20</v>
       </c>
-      <c r="U19" t="n">
+      <c r="U20" t="n">
         <v>18</v>
       </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Ask
 Kragjordstjärna
@@ -2905,150 +3019,36 @@
 Röd glada</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 15600-2025 artfynd.xlsx", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 15600-2025 karta.png", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 15600-2025 georefererad karta.tif", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 15600-2025 FSC-klagomål.docx", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 15600-2025 FSC-klagomål mail.docx", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 15600-2025 tillsynsbegäran.docx", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 15600-2025 tillsynsbegäran mail.docx", "A 15600-2025")</f>
         <v/>
       </c>
-      <c r="AE19">
+      <c r="AE20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 15600-2025 prioriterade fågelarter.docx", "A 15600-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 39320-2024</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45551</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46315</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>2</v>
-      </c>
-      <c r="L20" t="n">
-        <v>4</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N20" t="n">
-        <v>1</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>7</v>
-      </c>
-      <c r="R20" t="n">
-        <v>3</v>
-      </c>
-      <c r="S20" t="n">
-        <v>10</v>
-      </c>
-      <c r="T20" t="n">
-        <v>11</v>
-      </c>
-      <c r="U20" t="n">
-        <v>10</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Vresalm
-Lundalm
-Toppjungfrulin
-Gulprickig vaxskivling
-Korskovall
-Sårläka
-Vårärt
-Strävlosta
-Underviol
-Skogsduva</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 39320-2024 artfynd.xlsx", "A 39320-2024")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 39320-2024 karta.png", "A 39320-2024")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 39320-2024 georefererad karta.tif", "A 39320-2024")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 39320-2024 FSC-klagomål.docx", "A 39320-2024")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 39320-2024 FSC-klagomål mail.docx", "A 39320-2024")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 39320-2024 tillsynsbegäran.docx", "A 39320-2024")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 39320-2024 tillsynsbegäran mail.docx", "A 39320-2024")</f>
         <v/>
       </c>
     </row>
@@ -3072,7 +3072,7 @@
         <v>44616</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>45000</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>45530</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>45223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         <v>45075</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45169</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 43714-2025</t>
+          <t>A 43704-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3758,7 +3758,7 @@
         <v>45912</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3771,19 +3771,19 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>7.9</v>
+        <v>2.7</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3795,21 +3795,131 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>6</v>
       </c>
       <c r="T27" t="n">
+        <v>6</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp
+Långbensgroda
+Större vattensalamander
+Åkergroda
+Mindre vattensalamander
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43704-2025 artfynd.xlsx", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="X27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43704-2025 karta.png", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="Y27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43704-2025 georefererad karta.tif", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="AA27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43704-2025 FSC-klagomål.docx", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="AB27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43704-2025 FSC-klagomål mail.docx", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="AC27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43704-2025 tillsynsbegäran.docx", "A 43704-2025")</f>
+        <v/>
+      </c>
+      <c r="AD27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43704-2025 tillsynsbegäran mail.docx", "A 43704-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A 43714-2025</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>45912</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" t="n">
+        <v>2</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2</v>
+      </c>
+      <c r="S28" t="n">
+        <v>6</v>
+      </c>
+      <c r="T28" t="n">
         <v>8</v>
       </c>
-      <c r="U27" t="n">
+      <c r="U28" t="n">
         <v>2</v>
       </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>Mindre bastardsvärmare
 Sexfläckig bastardsvärmare
@@ -3819,146 +3929,36 @@
 Trädporella</t>
         </is>
       </c>
-      <c r="W27">
+      <c r="W28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43714-2025 artfynd.xlsx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="X27">
+      <c r="X28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43714-2025 karta.png", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="Y27">
+      <c r="Y28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43714-2025 georefererad karta.tif", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AA27">
+      <c r="AA28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43714-2025 FSC-klagomål.docx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AB27">
+      <c r="AB28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43714-2025 FSC-klagomål mail.docx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AC27">
+      <c r="AC28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43714-2025 tillsynsbegäran.docx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AD27">
+      <c r="AD28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43714-2025 tillsynsbegäran mail.docx", "A 43714-2025")</f>
         <v/>
       </c>
-      <c r="AE27">
+      <c r="AE28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 43714-2025 prioriterade fågelarter.docx", "A 43714-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>A 43704-2025</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>45912</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>46315</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J28" t="n">
-        <v>5</v>
-      </c>
-      <c r="K28" t="n">
-        <v>1</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>6</v>
-      </c>
-      <c r="T28" t="n">
-        <v>6</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1</v>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>Blomkålssvamp
-Långbensgroda
-Större vattensalamander
-Åkergroda
-Mindre vattensalamander
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43704-2025 artfynd.xlsx", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43704-2025 karta.png", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43704-2025 georefererad karta.tif", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43704-2025 FSC-klagomål.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43704-2025 FSC-klagomål mail.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43704-2025 tillsynsbegäran.docx", "A 43704-2025")</f>
-        <v/>
-      </c>
-      <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43704-2025 tillsynsbegäran mail.docx", "A 43704-2025")</f>
         <v/>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
         <v>46190</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>46003</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>46038</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>45616</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 19459-2023</t>
+          <t>A 26440-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4423,10 +4423,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45049</v>
+        <v>46183</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4439,16 +4439,16 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -4463,7 +4463,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -4472,12 +4472,232 @@
         <v>4</v>
       </c>
       <c r="T33" t="n">
+        <v>5</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>Backstarr
+Murgröna
+Nästrot
+Vätteros</t>
+        </is>
+      </c>
+      <c r="W33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 26440-2026 artfynd.xlsx", "A 26440-2026")</f>
+        <v/>
+      </c>
+      <c r="X33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 26440-2026 karta.png", "A 26440-2026")</f>
+        <v/>
+      </c>
+      <c r="Y33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 26440-2026 georefererad karta.tif", "A 26440-2026")</f>
+        <v/>
+      </c>
+      <c r="AA33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 26440-2026 FSC-klagomål.docx", "A 26440-2026")</f>
+        <v/>
+      </c>
+      <c r="AB33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 26440-2026 FSC-klagomål mail.docx", "A 26440-2026")</f>
+        <v/>
+      </c>
+      <c r="AC33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 26440-2026 tillsynsbegäran.docx", "A 26440-2026")</f>
+        <v/>
+      </c>
+      <c r="AD33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 26440-2026 tillsynsbegäran mail.docx", "A 26440-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>A 34431-2026</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="E34" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" t="n">
+        <v>3</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
         <v>4</v>
       </c>
-      <c r="U33" t="n">
+      <c r="T34" t="n">
+        <v>5</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Mindre hackspett
+Sandtimotej
+Murgröna</t>
+        </is>
+      </c>
+      <c r="W34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 34431-2026 artfynd.xlsx", "A 34431-2026")</f>
+        <v/>
+      </c>
+      <c r="X34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 34431-2026 karta.png", "A 34431-2026")</f>
+        <v/>
+      </c>
+      <c r="Y34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 34431-2026 georefererad karta.tif", "A 34431-2026")</f>
+        <v/>
+      </c>
+      <c r="AA34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 34431-2026 FSC-klagomål.docx", "A 34431-2026")</f>
+        <v/>
+      </c>
+      <c r="AB34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 34431-2026 FSC-klagomål mail.docx", "A 34431-2026")</f>
+        <v/>
+      </c>
+      <c r="AC34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 34431-2026 tillsynsbegäran.docx", "A 34431-2026")</f>
+        <v/>
+      </c>
+      <c r="AD34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 34431-2026 tillsynsbegäran mail.docx", "A 34431-2026")</f>
+        <v/>
+      </c>
+      <c r="AE34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 34431-2026 prioriterade fågelarter.docx", "A 34431-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>A 19459-2023</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D35" s="1" t="n">
+        <v>45049</v>
+      </c>
+      <c r="E35" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>MÖRBYLÅNGA</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
         <v>4</v>
       </c>
-      <c r="V33" s="2" t="inlineStr">
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>4</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>4</v>
+      </c>
+      <c r="T35" t="n">
+        <v>4</v>
+      </c>
+      <c r="U35" t="n">
+        <v>4</v>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
         <is>
           <t>Kavelhirs
 Kösa
@@ -4485,252 +4705,32 @@
 Riddarsporre</t>
         </is>
       </c>
-      <c r="W33">
+      <c r="W35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 19459-2023 artfynd.xlsx", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="X33">
+      <c r="X35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 19459-2023 karta.png", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="Y33">
+      <c r="Y35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 19459-2023 georefererad karta.tif", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="AA33">
+      <c r="AA35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 19459-2023 FSC-klagomål.docx", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="AB33">
+      <c r="AB35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 19459-2023 FSC-klagomål mail.docx", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="AC33">
+      <c r="AC35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 19459-2023 tillsynsbegäran.docx", "A 19459-2023")</f>
         <v/>
       </c>
-      <c r="AD33">
+      <c r="AD35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 19459-2023 tillsynsbegäran mail.docx", "A 19459-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>A 26440-2026</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="n">
-        <v>46183</v>
-      </c>
-      <c r="E34" s="1" t="n">
-        <v>46315</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J34" t="n">
-        <v>1</v>
-      </c>
-      <c r="K34" t="n">
-        <v>3</v>
-      </c>
-      <c r="L34" t="n">
-        <v>1</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>1</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>4</v>
-      </c>
-      <c r="T34" t="n">
-        <v>5</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>Backstarr
-Murgröna
-Nästrot
-Vätteros</t>
-        </is>
-      </c>
-      <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 26440-2026 artfynd.xlsx", "A 26440-2026")</f>
-        <v/>
-      </c>
-      <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 26440-2026 karta.png", "A 26440-2026")</f>
-        <v/>
-      </c>
-      <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 26440-2026 georefererad karta.tif", "A 26440-2026")</f>
-        <v/>
-      </c>
-      <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 26440-2026 FSC-klagomål.docx", "A 26440-2026")</f>
-        <v/>
-      </c>
-      <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 26440-2026 FSC-klagomål mail.docx", "A 26440-2026")</f>
-        <v/>
-      </c>
-      <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 26440-2026 tillsynsbegäran.docx", "A 26440-2026")</f>
-        <v/>
-      </c>
-      <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 26440-2026 tillsynsbegäran mail.docx", "A 26440-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>A 34431-2026</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="n">
-        <v>46254</v>
-      </c>
-      <c r="E35" s="1" t="n">
-        <v>46315</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>MÖRBYLÅNGA</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="J35" t="n">
-        <v>2</v>
-      </c>
-      <c r="K35" t="n">
-        <v>1</v>
-      </c>
-      <c r="L35" t="n">
-        <v>3</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>3</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>4</v>
-      </c>
-      <c r="T35" t="n">
-        <v>5</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1</v>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Mindre hackspett
-Sandtimotej
-Murgröna</t>
-        </is>
-      </c>
-      <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 34431-2026 artfynd.xlsx", "A 34431-2026")</f>
-        <v/>
-      </c>
-      <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 34431-2026 karta.png", "A 34431-2026")</f>
-        <v/>
-      </c>
-      <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 34431-2026 georefererad karta.tif", "A 34431-2026")</f>
-        <v/>
-      </c>
-      <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 34431-2026 FSC-klagomål.docx", "A 34431-2026")</f>
-        <v/>
-      </c>
-      <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 34431-2026 FSC-klagomål mail.docx", "A 34431-2026")</f>
-        <v/>
-      </c>
-      <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 34431-2026 tillsynsbegäran.docx", "A 34431-2026")</f>
-        <v/>
-      </c>
-      <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 34431-2026 tillsynsbegäran mail.docx", "A 34431-2026")</f>
-        <v/>
-      </c>
-      <c r="AE35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 34431-2026 prioriterade fågelarter.docx", "A 34431-2026")</f>
         <v/>
       </c>
     </row>
@@ -4754,7 +4754,7 @@
         <v>45912</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>46203</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 72167-2021</t>
+          <t>A 62231-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4961,14 +4961,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44544</v>
+        <v>45267</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J38" t="n">
         <v>1</v>
@@ -5022,46 +5022,42 @@
       <c r="V38" s="2" t="inlineStr">
         <is>
           <t>Murgröna
-Röd glada</t>
+Blåsippa</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 72167-2021 artfynd.xlsx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62231-2023 artfynd.xlsx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 72167-2021 karta.png", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62231-2023 karta.png", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 72167-2021 georefererad karta.tif", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62231-2023 georefererad karta.tif", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 72167-2021 FSC-klagomål.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62231-2023 FSC-klagomål.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 72167-2021 FSC-klagomål mail.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62231-2023 FSC-klagomål mail.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 72167-2021 tillsynsbegäran.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62231-2023 tillsynsbegäran.docx", "A 62231-2023")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 72167-2021 tillsynsbegäran mail.docx", "A 72167-2021")</f>
-        <v/>
-      </c>
-      <c r="AE38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 72167-2021 prioriterade fågelarter.docx", "A 72167-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62231-2023 tillsynsbegäran mail.docx", "A 62231-2023")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 62231-2023</t>
+          <t>A 72167-2021</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5071,14 +5067,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45267</v>
+        <v>44544</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5091,7 +5087,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J39" t="n">
         <v>1</v>
@@ -5132,35 +5128,39 @@
       <c r="V39" s="2" t="inlineStr">
         <is>
           <t>Murgröna
-Blåsippa</t>
+Röd glada</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62231-2023 artfynd.xlsx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 72167-2021 artfynd.xlsx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62231-2023 karta.png", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 72167-2021 karta.png", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62231-2023 georefererad karta.tif", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 72167-2021 georefererad karta.tif", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62231-2023 FSC-klagomål.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 72167-2021 FSC-klagomål.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62231-2023 FSC-klagomål mail.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 72167-2021 FSC-klagomål mail.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62231-2023 tillsynsbegäran.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 72167-2021 tillsynsbegäran.docx", "A 72167-2021")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62231-2023 tillsynsbegäran mail.docx", "A 62231-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 72167-2021 tillsynsbegäran mail.docx", "A 72167-2021")</f>
+        <v/>
+      </c>
+      <c r="AE39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 72167-2021 prioriterade fågelarter.docx", "A 72167-2021")</f>
         <v/>
       </c>
     </row>
@@ -5184,7 +5184,7 @@
         <v>46246</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 13040-2024</t>
+          <t>A 62183-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5283,14 +5283,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45385</v>
+        <v>46006</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -5312,13 +5312,13 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5330,7 +5330,7 @@
         <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -5339,46 +5339,46 @@
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13040-2024 artfynd.xlsx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62183-2025 artfynd.xlsx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13040-2024 karta.png", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62183-2025 karta.png", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13040-2024 georefererad karta.tif", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62183-2025 georefererad karta.tif", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13040-2024 FSC-klagomål.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62183-2025 FSC-klagomål.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13040-2024 FSC-klagomål mail.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62183-2025 FSC-klagomål mail.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13040-2024 tillsynsbegäran.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62183-2025 tillsynsbegäran.docx", "A 62183-2025")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13040-2024 tillsynsbegäran mail.docx", "A 13040-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62183-2025 tillsynsbegäran mail.docx", "A 62183-2025")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 13384-2023</t>
+          <t>A 24698-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5392,10 +5392,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45005</v>
+        <v>45084</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5408,16 +5408,16 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.9</v>
+        <v>5.5</v>
       </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -5432,7 +5432,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -5448,42 +5448,42 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13384-2023 artfynd.xlsx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24698-2023 artfynd.xlsx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13384-2023 karta.png", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24698-2023 karta.png", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13384-2023 georefererad karta.tif", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24698-2023 georefererad karta.tif", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13384-2023 FSC-klagomål.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24698-2023 FSC-klagomål.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13384-2023 FSC-klagomål mail.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24698-2023 FSC-klagomål mail.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13384-2023 tillsynsbegäran.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24698-2023 tillsynsbegäran.docx", "A 24698-2023")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13384-2023 tillsynsbegäran mail.docx", "A 13384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24698-2023 tillsynsbegäran mail.docx", "A 24698-2023")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 62183-2025</t>
+          <t>A 13040-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5493,14 +5493,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46006</v>
+        <v>45385</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5522,13 +5522,13 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5540,7 +5540,7 @@
         <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5549,46 +5549,46 @@
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 62183-2025 artfynd.xlsx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13040-2024 artfynd.xlsx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 62183-2025 karta.png", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13040-2024 karta.png", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 62183-2025 georefererad karta.tif", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13040-2024 georefererad karta.tif", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 62183-2025 FSC-klagomål.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13040-2024 FSC-klagomål.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 62183-2025 FSC-klagomål mail.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13040-2024 FSC-klagomål mail.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 62183-2025 tillsynsbegäran.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13040-2024 tillsynsbegäran.docx", "A 13040-2024")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 62183-2025 tillsynsbegäran mail.docx", "A 62183-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13040-2024 tillsynsbegäran mail.docx", "A 13040-2024")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 30492-2026</t>
+          <t>A 13384-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5598,14 +5598,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46210</v>
+        <v>45005</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5618,16 +5618,16 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -5642,7 +5642,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -5654,46 +5654,46 @@
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 30492-2026 artfynd.xlsx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 13384-2023 artfynd.xlsx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 30492-2026 karta.png", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 13384-2023 karta.png", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 30492-2026 georefererad karta.tif", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 13384-2023 georefererad karta.tif", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 30492-2026 FSC-klagomål.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 13384-2023 FSC-klagomål.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 30492-2026 FSC-klagomål mail.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 13384-2023 FSC-klagomål mail.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 30492-2026 tillsynsbegäran.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 13384-2023 tillsynsbegäran.docx", "A 13384-2023")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 30492-2026 tillsynsbegäran mail.docx", "A 30492-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 13384-2023 tillsynsbegäran mail.docx", "A 13384-2023")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 36928-2026</t>
+          <t>A 30492-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5703,14 +5703,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46273</v>
+        <v>46210</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5723,16 +5723,16 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -5747,7 +5747,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -5763,42 +5763,42 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 36928-2026 artfynd.xlsx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 30492-2026 artfynd.xlsx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 36928-2026 karta.png", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 30492-2026 karta.png", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 36928-2026 georefererad karta.tif", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 30492-2026 georefererad karta.tif", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 36928-2026 FSC-klagomål.docx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 30492-2026 FSC-klagomål.docx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 36928-2026 FSC-klagomål mail.docx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 30492-2026 FSC-klagomål mail.docx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 36928-2026 tillsynsbegäran.docx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 30492-2026 tillsynsbegäran.docx", "A 30492-2026")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 36928-2026 tillsynsbegäran mail.docx", "A 36928-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 30492-2026 tillsynsbegäran mail.docx", "A 30492-2026")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 24698-2023</t>
+          <t>A 36928-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45084</v>
+        <v>46273</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5828,16 +5828,16 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>5.5</v>
+        <v>1.3</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -5852,7 +5852,7 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -5864,39 +5864,39 @@
         <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 24698-2023 artfynd.xlsx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 36928-2026 artfynd.xlsx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 24698-2023 karta.png", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 36928-2026 karta.png", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 24698-2023 georefererad karta.tif", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 36928-2026 georefererad karta.tif", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 24698-2023 FSC-klagomål.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 36928-2026 FSC-klagomål.docx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 24698-2023 FSC-klagomål mail.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 36928-2026 FSC-klagomål mail.docx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 24698-2023 tillsynsbegäran.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 36928-2026 tillsynsbegäran.docx", "A 36928-2026")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 24698-2023 tillsynsbegäran mail.docx", "A 24698-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 36928-2026 tillsynsbegäran mail.docx", "A 36928-2026")</f>
         <v/>
       </c>
     </row>
@@ -5920,7 +5920,7 @@
         <v>44740</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         <v>45980</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>46171</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>

--- a/Översikt MÖRBYLÅNGA.xlsx
+++ b/Översikt MÖRBYLÅNGA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE49"/>
+  <dimension ref="A1:AE51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44964</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>44655</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>45177</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45096</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45685</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>46289</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>45475</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>45062</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>46195</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>46189</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>45254</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>45062</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>44508</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>45999</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>44811</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>45097</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>44728</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>45551</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>45747</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>44616</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>45000</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>45530</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>45223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         <v>45075</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45169</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 43704-2025</t>
+          <t>A 43714-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3758,7 +3758,7 @@
         <v>45912</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3771,19 +3771,19 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.7</v>
+        <v>7.9</v>
       </c>
       <c r="J27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3795,21 +3795,135 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S27" t="n">
         <v>6</v>
       </c>
       <c r="T27" t="n">
+        <v>8</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Mindre bastardsvärmare
+Sexfläckig bastardsvärmare
+Grönsångare
+Murgröna
+Tibast
+Trädporella</t>
+        </is>
+      </c>
+      <c r="W27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/artfynd/A 43714-2025 artfynd.xlsx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="X27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor/A 43714-2025 karta.png", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="Y27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/kartor_geotiff/A 43714-2025 georefererad karta.tif", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AA27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomål/A 43714-2025 FSC-klagomål.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AB27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/klagomålsmail/A 43714-2025 FSC-klagomål mail.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AC27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsyn/A 43714-2025 tillsynsbegäran.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AD27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/tillsynsmail/A 43714-2025 tillsynsbegäran mail.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0840/fåglar/A 43714-2025 prioriterade fågelarter.docx", "A 43714-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A 43704-2025</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>45912</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
